--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -1509,676 +1509,676 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.02657031293155685</v>
+        <v>0.02409424997156595</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.03542522124086899</v>
+        <v>0.03184071665926662</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.037620125278406</v>
+        <v>0.03376989515533502</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.03932255536846778</v>
+        <v>0.03533772760420039</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.03989541758474875</v>
+        <v>0.03584189538228544</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.03921848025289084</v>
+        <v>0.03524311972705521</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.03872495360209276</v>
+        <v>0.03482997268961281</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.03841303747250321</v>
+        <v>0.03448983584796323</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.03865972812393355</v>
+        <v>0.03476780014248716</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.03798368750661778</v>
+        <v>0.03416729434972343</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.0369487676240197</v>
+        <v>0.0333003398422682</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.03550462141770685</v>
+        <v>0.03244605028525065</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.03542355040890998</v>
+        <v>0.03239005064522088</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.03591280483302071</v>
+        <v>0.03301930037581247</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.05231442329569958</v>
+        <v>0.04829908546915937</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.06442027601569487</v>
+        <v>0.0585481943631677</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.06782088130314917</v>
+        <v>0.06100428438864031</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.06889214852886881</v>
+        <v>0.06221599747120271</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.07029065129376266</v>
+        <v>0.06340613097787057</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.06758270425708926</v>
+        <v>0.06131854406302968</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.06872123009172679</v>
+        <v>0.06231076517636623</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.0681076544793718</v>
+        <v>0.06200230148956505</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.06802414436859555</v>
+        <v>0.06153937307049831</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.0674972743273428</v>
+        <v>0.06117197607765418</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.06428626854486275</v>
+        <v>0.05841479801330376</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.06133304952291114</v>
+        <v>0.0563086127527754</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0.06130387127031267</v>
+        <v>0.05616216712374789</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0.06244623811016815</v>
+        <v>0.05758526592455462</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.08489852814116222</v>
+        <v>0.07866126438127166</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>0.0982556120689566</v>
+        <v>0.08955711517722895</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>0.09906205881914984</v>
+        <v>0.08930294968288695</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.1011308469078661</v>
+        <v>0.09173264247697605</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.1014953816057237</v>
+        <v>0.09213932245336849</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>0.1007878720869844</v>
+        <v>0.09166837362729238</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>0.09750199813070734</v>
+        <v>0.08883345452616066</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>0.09631870494490566</v>
+        <v>0.08807672978658548</v>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>0.09718565758191448</v>
+        <v>0.08839801155189728</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>0.09374701676377753</v>
+        <v>0.08548144181637674</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.08867109990978667</v>
+        <v>0.0817376608652487</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>0.08646391673613842</v>
+        <v>0.0799579307030017</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>0.08885887388062254</v>
+        <v>0.08208551421832175</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.08944467118895114</v>
+        <v>0.08289053547016954</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.1150897032337863</v>
+        <v>0.1067903671435371</v>
       </c>
       <c r="AS2" s="2" t="n">
-        <v>0.1251198811424334</v>
+        <v>0.112873719601973</v>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>0.1263353818368734</v>
+        <v>0.1139261563351639</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>0.1274632635437326</v>
+        <v>0.1161054764672611</v>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>0.1255394973841269</v>
+        <v>0.1138538322785264</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>0.120818032247536</v>
+        <v>0.1103450922688999</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>0.1213464313713983</v>
+        <v>0.1108812226715851</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>0.1200617780922633</v>
+        <v>0.1102469424043481</v>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>0.1191320032994297</v>
+        <v>0.1089714732216183</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>0.1147797321748339</v>
+        <v>0.1054786539841245</v>
       </c>
       <c r="BB2" s="2" t="n">
-        <v>0.1093655737122357</v>
+        <v>0.1012465360863909</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>0.1073454437055285</v>
+        <v>0.09972139506494188</v>
       </c>
       <c r="BD2" s="2" t="n">
-        <v>0.1058672011744747</v>
+        <v>0.09847014168297244</v>
       </c>
       <c r="BE2" s="2" t="n">
-        <v>0.1090130001311667</v>
+        <v>0.1015862272373955</v>
       </c>
       <c r="BF2" s="2" t="n">
-        <v>0.1458527912687325</v>
+        <v>0.1340107856630529</v>
       </c>
       <c r="BG2" s="2" t="n">
-        <v>0.1499948916324634</v>
+        <v>0.1356997900248912</v>
       </c>
       <c r="BH2" s="2" t="n">
-        <v>0.1495330123633145</v>
+        <v>0.1357045621413595</v>
       </c>
       <c r="BI2" s="2" t="n">
-        <v>0.146629747505056</v>
+        <v>0.1327212813603772</v>
       </c>
       <c r="BJ2" s="2" t="n">
-        <v>0.1462364179848133</v>
+        <v>0.1327552050946344</v>
       </c>
       <c r="BK2" s="2" t="n">
-        <v>0.1391765652206851</v>
+        <v>0.127138132077186</v>
       </c>
       <c r="BL2" s="2" t="n">
-        <v>0.1384789384033644</v>
+        <v>0.1269655644867322</v>
       </c>
       <c r="BM2" s="2" t="n">
-        <v>0.1354965341230171</v>
+        <v>0.124550552394277</v>
       </c>
       <c r="BN2" s="2" t="n">
-        <v>0.1340117592703761</v>
+        <v>0.122882775627613</v>
       </c>
       <c r="BO2" s="2" t="n">
-        <v>0.1351193083334079</v>
+        <v>0.1242997448178457</v>
       </c>
       <c r="BP2" s="2" t="n">
-        <v>0.1255972449743945</v>
+        <v>0.1166519934663059</v>
       </c>
       <c r="BQ2" s="2" t="n">
-        <v>0.1242923901890447</v>
+        <v>0.1160660035056708</v>
       </c>
       <c r="BR2" s="2" t="n">
-        <v>0.1235738301766733</v>
+        <v>0.1155145728244937</v>
       </c>
       <c r="BS2" s="2" t="n">
-        <v>0.1231096081357194</v>
+        <v>0.1155296914884321</v>
       </c>
       <c r="BT2" s="2" t="n">
-        <v>0.18493580802658</v>
+        <v>0.1664384387943894</v>
       </c>
       <c r="BU2" s="2" t="n">
-        <v>0.1841496469327287</v>
+        <v>0.1644967928681111</v>
       </c>
       <c r="BV2" s="2" t="n">
-        <v>0.1804938303418428</v>
+        <v>0.1613739494239298</v>
       </c>
       <c r="BW2" s="2" t="n">
-        <v>0.1808558029805121</v>
+        <v>0.1621982849953908</v>
       </c>
       <c r="BX2" s="2" t="n">
-        <v>0.1765502982765416</v>
+        <v>0.1606740861522626</v>
       </c>
       <c r="BY2" s="2" t="n">
-        <v>0.1718551051543227</v>
+        <v>0.1569092983086119</v>
       </c>
       <c r="BZ2" s="2" t="n">
-        <v>0.168029002148029</v>
+        <v>0.1537557580742758</v>
       </c>
       <c r="CA2" s="2" t="n">
-        <v>0.164514853866396</v>
+        <v>0.1509462941207121</v>
       </c>
       <c r="CB2" s="2" t="n">
-        <v>0.1619625900722763</v>
+        <v>0.1491328389206564</v>
       </c>
       <c r="CC2" s="2" t="n">
-        <v>0.1571953900518921</v>
+        <v>0.145362991218755</v>
       </c>
       <c r="CD2" s="2" t="n">
-        <v>0.152435920144823</v>
+        <v>0.1420341622276048</v>
       </c>
       <c r="CE2" s="2" t="n">
-        <v>0.1444638851244507</v>
+        <v>0.1356991675179119</v>
       </c>
       <c r="CF2" s="2" t="n">
-        <v>0.1445086692787022</v>
+        <v>0.1359314471090391</v>
       </c>
       <c r="CG2" s="2" t="n">
-        <v>0.1475583493598913</v>
+        <v>0.139087395797861</v>
       </c>
       <c r="CH2" s="2" t="n">
-        <v>0.2133457685097322</v>
+        <v>0.1922288379651869</v>
       </c>
       <c r="CI2" s="2" t="n">
-        <v>0.2137110895498502</v>
+        <v>0.1901681381270987</v>
       </c>
       <c r="CJ2" s="2" t="n">
-        <v>0.2092216637097572</v>
+        <v>0.1882917617841775</v>
       </c>
       <c r="CK2" s="2" t="n">
-        <v>0.2041449174304516</v>
+        <v>0.1851199161017104</v>
       </c>
       <c r="CL2" s="2" t="n">
-        <v>0.1998924587865716</v>
+        <v>0.1818376569052396</v>
       </c>
       <c r="CM2" s="2" t="n">
-        <v>0.1919545729324141</v>
+        <v>0.1755537951931204</v>
       </c>
       <c r="CN2" s="2" t="n">
-        <v>0.1918607793763317</v>
+        <v>0.1764439207518544</v>
       </c>
       <c r="CO2" s="2" t="n">
-        <v>0.1850332221369335</v>
+        <v>0.1704910158552031</v>
       </c>
       <c r="CP2" s="2" t="n">
-        <v>0.1833633610321991</v>
+        <v>0.1693086632328649</v>
       </c>
       <c r="CQ2" s="2" t="n">
-        <v>0.1834978773126313</v>
+        <v>0.1703174792925641</v>
       </c>
       <c r="CR2" s="2" t="n">
-        <v>0.168196210033705</v>
+        <v>0.157793160253454</v>
       </c>
       <c r="CS2" s="2" t="n">
-        <v>0.1646981322721191</v>
+        <v>0.1555902209268198</v>
       </c>
       <c r="CT2" s="2" t="n">
-        <v>0.1641849124937205</v>
+        <v>0.1557121076846294</v>
       </c>
       <c r="CU2" s="2" t="n">
-        <v>0.1706184931049206</v>
+        <v>0.1618317269763922</v>
       </c>
       <c r="CV2" s="2" t="n">
-        <v>0.2513273144729375</v>
+        <v>0.2283585294494069</v>
       </c>
       <c r="CW2" s="2" t="n">
-        <v>0.2396354762158834</v>
+        <v>0.2160444143199447</v>
       </c>
       <c r="CX2" s="2" t="n">
-        <v>0.2373404648965267</v>
+        <v>0.2162876823069333</v>
       </c>
       <c r="CY2" s="2" t="n">
-        <v>0.2346407533926639</v>
+        <v>0.2148776573571072</v>
       </c>
       <c r="CZ2" s="2" t="n">
-        <v>0.2249022694239294</v>
+        <v>0.2064481141976213</v>
       </c>
       <c r="DA2" s="2" t="n">
-        <v>0.2207293225179954</v>
+        <v>0.2033774240465049</v>
       </c>
       <c r="DB2" s="2" t="n">
-        <v>0.2203619860232323</v>
+        <v>0.2041680019801556</v>
       </c>
       <c r="DC2" s="2" t="n">
-        <v>0.2147182661003725</v>
+        <v>0.2001028074951225</v>
       </c>
       <c r="DD2" s="2" t="n">
-        <v>0.2126886509406944</v>
+        <v>0.1996034417993302</v>
       </c>
       <c r="DE2" s="2" t="n">
-        <v>0.206495521348174</v>
+        <v>0.1941359916390965</v>
       </c>
       <c r="DF2" s="2" t="n">
-        <v>0.1989837494775255</v>
+        <v>0.1886444834677441</v>
       </c>
       <c r="DG2" s="2" t="n">
-        <v>0.1957331356406446</v>
+        <v>0.186076192639629</v>
       </c>
       <c r="DH2" s="2" t="n">
-        <v>0.1937002694769184</v>
+        <v>0.1849897089744027</v>
       </c>
       <c r="DI2" s="2" t="n">
-        <v>0.1957521394466931</v>
+        <v>0.187648631514239</v>
       </c>
       <c r="DJ2" s="2" t="n">
-        <v>0.2684331897874201</v>
+        <v>0.2441081070444961</v>
       </c>
       <c r="DK2" s="2" t="n">
-        <v>0.2632800376488951</v>
+        <v>0.2415845263376467</v>
       </c>
       <c r="DL2" s="2" t="n">
-        <v>0.2549410705067199</v>
+        <v>0.2345428028008692</v>
       </c>
       <c r="DM2" s="2" t="n">
-        <v>0.2525057379525026</v>
+        <v>0.233051520664044</v>
       </c>
       <c r="DN2" s="2" t="n">
-        <v>0.2444232451112794</v>
+        <v>0.2265031071816037</v>
       </c>
       <c r="DO2" s="2" t="n">
-        <v>0.2445737352222858</v>
+        <v>0.2280909389837283</v>
       </c>
       <c r="DP2" s="2" t="n">
-        <v>0.2366553464476686</v>
+        <v>0.2225012392537851</v>
       </c>
       <c r="DQ2" s="2" t="n">
-        <v>0.2300779663055207</v>
+        <v>0.2167342377830909</v>
       </c>
       <c r="DR2" s="2" t="n">
-        <v>0.2271833144389607</v>
+        <v>0.2153036794250142</v>
       </c>
       <c r="DS2" s="2" t="n">
-        <v>0.2232260284246558</v>
+        <v>0.2125917475412855</v>
       </c>
       <c r="DT2" s="2" t="n">
-        <v>0.2179266471667639</v>
+        <v>0.2083365968411205</v>
       </c>
       <c r="DU2" s="2" t="n">
-        <v>0.2152727543392878</v>
+        <v>0.207191432172665</v>
       </c>
       <c r="DV2" s="2" t="n">
-        <v>0.217416382765025</v>
+        <v>0.2095289943887456</v>
       </c>
       <c r="DW2" s="2" t="n">
-        <v>0.2192393976424865</v>
+        <v>0.2118873893944378</v>
       </c>
       <c r="DX2" s="2" t="n">
-        <v>0.2834796568700734</v>
+        <v>0.2619793933695286</v>
       </c>
       <c r="DY2" s="2" t="n">
-        <v>0.2724952979160742</v>
+        <v>0.2524509223771627</v>
       </c>
       <c r="DZ2" s="2" t="n">
-        <v>0.2706627811090473</v>
+        <v>0.2510850648561191</v>
       </c>
       <c r="EA2" s="2" t="n">
-        <v>0.2619095229312363</v>
+        <v>0.2446576447777912</v>
       </c>
       <c r="EB2" s="2" t="n">
-        <v>0.2592722113848981</v>
+        <v>0.2442267455198696</v>
       </c>
       <c r="EC2" s="2" t="n">
-        <v>0.2526223867856587</v>
+        <v>0.2384654739163494</v>
       </c>
       <c r="ED2" s="2" t="n">
-        <v>0.2486850346278535</v>
+        <v>0.2360557880797425</v>
       </c>
       <c r="EE2" s="2" t="n">
-        <v>0.2460484900714464</v>
+        <v>0.2347051761942967</v>
       </c>
       <c r="EF2" s="2" t="n">
-        <v>0.2436263977536754</v>
+        <v>0.2325114174347612</v>
       </c>
       <c r="EG2" s="2" t="n">
-        <v>0.2410693937605698</v>
+        <v>0.2307131515072429</v>
       </c>
       <c r="EH2" s="2" t="n">
-        <v>0.227722354257607</v>
+        <v>0.2193056598966162</v>
       </c>
       <c r="EI2" s="2" t="n">
-        <v>0.2304051708433491</v>
+        <v>0.2232641787847676</v>
       </c>
       <c r="EJ2" s="2" t="n">
-        <v>0.2302836965848053</v>
+        <v>0.2245548621132168</v>
       </c>
       <c r="EK2" s="2" t="n">
-        <v>0.2322570647229814</v>
+        <v>0.2259233005258149</v>
       </c>
       <c r="EL2" s="2" t="n">
-        <v>0.2909569805559521</v>
+        <v>0.2733118519759635</v>
       </c>
       <c r="EM2" s="2" t="n">
-        <v>0.2852039428762912</v>
+        <v>0.2704023524812862</v>
       </c>
       <c r="EN2" s="2" t="n">
-        <v>0.2795770769135024</v>
+        <v>0.2663431089329122</v>
       </c>
       <c r="EO2" s="2" t="n">
-        <v>0.2716146234026657</v>
+        <v>0.2598750563203824</v>
       </c>
       <c r="EP2" s="2" t="n">
-        <v>0.274488632730595</v>
+        <v>0.2632742755130998</v>
       </c>
       <c r="EQ2" s="2" t="n">
-        <v>0.2626167411001084</v>
+        <v>0.2527116095925524</v>
       </c>
       <c r="ER2" s="2" t="n">
-        <v>0.2626113476625713</v>
+        <v>0.2524708092283977</v>
       </c>
       <c r="ES2" s="2" t="n">
-        <v>0.2550453358710655</v>
+        <v>0.2468564463154936</v>
       </c>
       <c r="ET2" s="2" t="n">
-        <v>0.2577671275717482</v>
+        <v>0.2496946750157399</v>
       </c>
       <c r="EU2" s="2" t="n">
-        <v>0.2564523002261577</v>
+        <v>0.2491787779471676</v>
       </c>
       <c r="EV2" s="2" t="n">
-        <v>0.2523439077270072</v>
+        <v>0.2456773437891051</v>
       </c>
       <c r="EW2" s="2" t="n">
-        <v>0.2511563346088469</v>
+        <v>0.2457456295993894</v>
       </c>
       <c r="EX2" s="2" t="n">
-        <v>0.2503845920111182</v>
+        <v>0.2458505984411185</v>
       </c>
       <c r="EY2" s="2" t="n">
-        <v>0.2623619113260687</v>
+        <v>0.2575555305023064</v>
       </c>
       <c r="EZ2" s="2" t="n">
-        <v>0.2897716738271473</v>
+        <v>0.2814380360728507</v>
       </c>
       <c r="FA2" s="2" t="n">
-        <v>0.2898308990404281</v>
+        <v>0.2820195079739359</v>
       </c>
       <c r="FB2" s="2" t="n">
-        <v>0.2785540317511062</v>
+        <v>0.2715177879890243</v>
       </c>
       <c r="FC2" s="2" t="n">
-        <v>0.2804056349166445</v>
+        <v>0.2738563971471997</v>
       </c>
       <c r="FD2" s="2" t="n">
-        <v>0.2705365121677181</v>
+        <v>0.2645286955514536</v>
       </c>
       <c r="FE2" s="2" t="n">
-        <v>0.27188860415001</v>
+        <v>0.2660187350314983</v>
       </c>
       <c r="FF2" s="2" t="n">
-        <v>0.2713829300654875</v>
+        <v>0.2656705692526807</v>
       </c>
       <c r="FG2" s="2" t="n">
-        <v>0.2679999753974443</v>
+        <v>0.2624861373607057</v>
       </c>
       <c r="FH2" s="2" t="n">
-        <v>0.263646964330801</v>
+        <v>0.2580648765094527</v>
       </c>
       <c r="FI2" s="2" t="n">
-        <v>0.2622426169664249</v>
+        <v>0.2568475287920846</v>
       </c>
       <c r="FJ2" s="2" t="n">
-        <v>0.2641982172151647</v>
+        <v>0.2592022534246</v>
       </c>
       <c r="FK2" s="2" t="n">
-        <v>0.2652582484368337</v>
+        <v>0.2614999523284197</v>
       </c>
       <c r="FL2" s="2" t="n">
-        <v>0.274532278574507</v>
+        <v>0.2712101247909575</v>
       </c>
       <c r="FM2" s="2" t="n">
-        <v>0.2847421896133162</v>
+        <v>0.2814078884382181</v>
       </c>
       <c r="FN2" s="2" t="n">
-        <v>0.2919603817190826</v>
+        <v>0.2856237444898547</v>
       </c>
       <c r="FO2" s="2" t="n">
-        <v>0.2919297928075961</v>
+        <v>0.2860680692630544</v>
       </c>
       <c r="FP2" s="2" t="n">
-        <v>0.2837477328107064</v>
+        <v>0.2782268727597935</v>
       </c>
       <c r="FQ2" s="2" t="n">
-        <v>0.2816334945262661</v>
+        <v>0.2762074788668352</v>
       </c>
       <c r="FR2" s="2" t="n">
-        <v>0.287526054573767</v>
+        <v>0.2815739099284627</v>
       </c>
       <c r="FS2" s="2" t="n">
-        <v>0.2850271809870526</v>
+        <v>0.2792352091984726</v>
       </c>
       <c r="FT2" s="2" t="n">
-        <v>0.2854789067793192</v>
+        <v>0.2794662222660528</v>
       </c>
       <c r="FU2" s="2" t="n">
-        <v>0.2836002545113289</v>
+        <v>0.277551544243633</v>
       </c>
       <c r="FV2" s="2" t="n">
-        <v>0.2853296881797978</v>
+        <v>0.2793543862730662</v>
       </c>
       <c r="FW2" s="2" t="n">
-        <v>0.2857757286791567</v>
+        <v>0.2797410491431369</v>
       </c>
       <c r="FX2" s="2" t="n">
-        <v>0.2841393510730419</v>
+        <v>0.279152772266053</v>
       </c>
       <c r="FY2" s="2" t="n">
-        <v>0.2941645185797092</v>
+        <v>0.2900142095338944</v>
       </c>
       <c r="FZ2" s="2" t="n">
-        <v>0.2986177797467662</v>
+        <v>0.2942550930494472</v>
       </c>
       <c r="GA2" s="2" t="n">
-        <v>0.3135486750975445</v>
+        <v>0.3090719838534712</v>
       </c>
       <c r="GB2" s="2" t="n">
-        <v>0.3100935200852651</v>
+        <v>0.3010790030750103</v>
       </c>
       <c r="GC2" s="2" t="n">
-        <v>0.3110492472521678</v>
+        <v>0.3016693324199951</v>
       </c>
       <c r="GD2" s="2" t="n">
-        <v>0.3124730334116251</v>
+        <v>0.3028361706789963</v>
       </c>
       <c r="GE2" s="2" t="n">
-        <v>0.3126741641251132</v>
+        <v>0.3027351299016601</v>
       </c>
       <c r="GF2" s="2" t="n">
-        <v>0.3105390324123782</v>
+        <v>0.3009048511501132</v>
       </c>
       <c r="GG2" s="2" t="n">
-        <v>0.308746913120243</v>
+        <v>0.299300683181334</v>
       </c>
       <c r="GH2" s="2" t="n">
-        <v>0.3050704250011832</v>
+        <v>0.2957799465468</v>
       </c>
       <c r="GI2" s="2" t="n">
-        <v>0.3048092817993507</v>
+        <v>0.2967155706321322</v>
       </c>
       <c r="GJ2" s="2" t="n">
-        <v>0.3054181847990876</v>
+        <v>0.2968871559990836</v>
       </c>
       <c r="GK2" s="2" t="n">
-        <v>0.3094072294783636</v>
+        <v>0.3007664321886963</v>
       </c>
       <c r="GL2" s="2" t="n">
-        <v>0.3146618508337339</v>
+        <v>0.3076523146366371</v>
       </c>
       <c r="GM2" s="2" t="n">
-        <v>0.3201166127258458</v>
+        <v>0.314468821617769</v>
       </c>
       <c r="GN2" s="2" t="n">
-        <v>0.3352549738170351</v>
+        <v>0.3293561710776611</v>
       </c>
       <c r="GO2" s="2" t="n">
-        <v>0.3439628161558426</v>
+        <v>0.3369912289992812</v>
       </c>
       <c r="GP2" s="2" t="n">
-        <v>0.3381281499101865</v>
+        <v>0.3294274452500432</v>
       </c>
       <c r="GQ2" s="2" t="n">
-        <v>0.3340912746958703</v>
+        <v>0.3268083314671927</v>
       </c>
       <c r="GR2" s="2" t="n">
-        <v>0.3336377205594225</v>
+        <v>0.3254784333206653</v>
       </c>
       <c r="GS2" s="2" t="n">
-        <v>0.3317686149494234</v>
+        <v>0.3239015349615907</v>
       </c>
       <c r="GT2" s="2" t="n">
-        <v>0.3334732076141485</v>
+        <v>0.3253258317732811</v>
       </c>
       <c r="GU2" s="2" t="n">
-        <v>0.3275681527296446</v>
+        <v>0.3197143127800004</v>
       </c>
       <c r="GV2" s="2" t="n">
-        <v>0.3327968432769749</v>
+        <v>0.3246935305248157</v>
       </c>
       <c r="GW2" s="2" t="n">
-        <v>0.3274491401949029</v>
+        <v>0.3199365693119702</v>
       </c>
       <c r="GX2" s="2" t="n">
-        <v>0.328790702213216</v>
+        <v>0.3209464717526108</v>
       </c>
       <c r="GY2" s="2" t="n">
-        <v>0.3290772133251552</v>
+        <v>0.3212170596625154</v>
       </c>
       <c r="GZ2" s="2" t="n">
-        <v>0.3414160951081344</v>
+        <v>0.3345531297308584</v>
       </c>
       <c r="HA2" s="2" t="n">
-        <v>0.354307598403612</v>
+        <v>0.3476909594242535</v>
       </c>
       <c r="HB2" s="2" t="n">
-        <v>0.3668264540435988</v>
+        <v>0.3596822525813633</v>
       </c>
       <c r="HC2" s="2" t="n">
-        <v>0.3600952783423381</v>
+        <v>0.3547180330837418</v>
       </c>
       <c r="HD2" s="2" t="n">
-        <v>0.3495138465030793</v>
+        <v>0.3417270033839377</v>
       </c>
       <c r="HE2" s="2" t="n">
-        <v>0.3438440213559505</v>
+        <v>0.337192057538734</v>
       </c>
       <c r="HF2" s="2" t="n">
-        <v>0.3460718091157101</v>
+        <v>0.33882592866601</v>
       </c>
       <c r="HG2" s="2" t="n">
-        <v>0.3528321222893373</v>
+        <v>0.3450685285042132</v>
       </c>
       <c r="HH2" s="2" t="n">
-        <v>0.3521769152925507</v>
+        <v>0.3436273896009651</v>
       </c>
       <c r="HI2" s="2" t="n">
-        <v>0.3505909485118297</v>
+        <v>0.3418325734043769</v>
       </c>
       <c r="HJ2" s="2" t="n">
-        <v>0.3535447471714867</v>
+        <v>0.3440420269761792</v>
       </c>
       <c r="HK2" s="2" t="n">
-        <v>0.3476565777823276</v>
+        <v>0.3378431143474985</v>
       </c>
       <c r="HL2" s="2" t="n">
-        <v>0.3499802421644977</v>
+        <v>0.3393313817367856</v>
       </c>
       <c r="HM2" s="2" t="n">
-        <v>0.347560222730494</v>
+        <v>0.3362441424738741</v>
       </c>
       <c r="HN2" s="2" t="n">
-        <v>0.369803260100003</v>
+        <v>0.3587241576336538</v>
       </c>
       <c r="HO2" s="2" t="n">
-        <v>0.3834241186770965</v>
+        <v>0.3728057036465496</v>
       </c>
       <c r="HP2" s="2" t="n">
-        <v>0.3609863909359899</v>
+        <v>0.3545593299576899</v>
       </c>
       <c r="HQ2" s="2" t="n">
-        <v>0.348058991886891</v>
+        <v>0.3443343662302008</v>
       </c>
       <c r="HR2" s="3" t="n">
         <v>55511</v>
@@ -2191,676 +2191,676 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.02688180172662134</v>
+        <v>0.02390804244479825</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.03591340941770962</v>
+        <v>0.03180695271692159</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.03811684351344668</v>
+        <v>0.03374192138504595</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.03978676531280557</v>
+        <v>0.03528424781090891</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.04032599582435477</v>
+        <v>0.03577029888540445</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.03960079881449648</v>
+        <v>0.03515086788694163</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.03904942257739854</v>
+        <v>0.03470102586384078</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.03872064834636806</v>
+        <v>0.03434585118805836</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.03894335920044583</v>
+        <v>0.03460991045424733</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.0382360750677602</v>
+        <v>0.03400095231622337</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.0371438012362772</v>
+        <v>0.03311482472556477</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.03566616143638296</v>
+        <v>0.03228187688367196</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.03557256593404132</v>
+        <v>0.03222159963305821</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.03604738921871457</v>
+        <v>0.03284832454523241</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.05293957024386732</v>
+        <v>0.04818124422256087</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.06522996093636156</v>
+        <v>0.05854319747870024</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.06862801373821587</v>
+        <v>0.06094859267356147</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.06958833695555632</v>
+        <v>0.06210201757504381</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.07095021879102471</v>
+        <v>0.06325316546767194</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.06815116162109144</v>
+        <v>0.06115339227218283</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.06922472403627962</v>
+        <v>0.06208644678266129</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.06854506979820314</v>
+        <v>0.06176050085699201</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.06842049858724572</v>
+        <v>0.06125203671328622</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.06785956402783226</v>
+        <v>0.06087877464601316</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.06455212135379793</v>
+        <v>0.05809832587815333</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.0615606630409434</v>
+        <v>0.05603147999808805</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.0615155674316618</v>
+        <v>0.05586653346532258</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.06265295549236261</v>
+        <v>0.05730549335685899</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.08588403151478319</v>
+        <v>0.07871631956915316</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>0.09935231664673984</v>
+        <v>0.08957164423477808</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>0.1001072353389475</v>
+        <v>0.08919847863479861</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0.1019941350383881</v>
+        <v>0.0915327583221572</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>0.1022676387230893</v>
+        <v>0.09187261770588429</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>0.1014749663637319</v>
+        <v>0.09136493394633621</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>0.09807968712938234</v>
+        <v>0.08848815468362448</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>0.09681691895272382</v>
+        <v>0.08771931343697999</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>0.09764399611394663</v>
+        <v>0.08798315916861651</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>0.09416325506003563</v>
+        <v>0.08508110093743773</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.08899242992977767</v>
+        <v>0.08137285734889721</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>0.08671828571650653</v>
+        <v>0.07958805029718516</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>0.08910925469157688</v>
+        <v>0.08168675624711511</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.08966047514419183</v>
+        <v>0.08249045257851718</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.1163480730477186</v>
+        <v>0.1069426563521473</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>0.1263853208919821</v>
+        <v>0.1127363011063082</v>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>0.1274201896997045</v>
+        <v>0.1136575452285896</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>0.1283299375346104</v>
+        <v>0.1157657930216328</v>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>0.1264115440456953</v>
+        <v>0.1134644010832849</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>0.1214984029519231</v>
+        <v>0.1099191610583165</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>0.1219641894003891</v>
+        <v>0.1104277831486671</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>0.1206055435347255</v>
+        <v>0.1097874543026118</v>
       </c>
       <c r="AZ3" s="2" t="n">
-        <v>0.1196198450311821</v>
+        <v>0.108456036399173</v>
       </c>
       <c r="BA3" s="2" t="n">
-        <v>0.1152221619958362</v>
+        <v>0.1050089651869749</v>
       </c>
       <c r="BB3" s="2" t="n">
-        <v>0.1096912934280335</v>
+        <v>0.1007975494298911</v>
       </c>
       <c r="BC3" s="2" t="n">
-        <v>0.1076214473868831</v>
+        <v>0.09927540783880563</v>
       </c>
       <c r="BD3" s="2" t="n">
-        <v>0.1061402281393447</v>
+        <v>0.09803455238225819</v>
       </c>
       <c r="BE3" s="2" t="n">
-        <v>0.1092476375129428</v>
+        <v>0.1011266176577391</v>
       </c>
       <c r="BF3" s="2" t="n">
-        <v>0.1472774835744812</v>
+        <v>0.1340640364223458</v>
       </c>
       <c r="BG3" s="2" t="n">
-        <v>0.151290685450334</v>
+        <v>0.135436233430072</v>
       </c>
       <c r="BH3" s="2" t="n">
-        <v>0.1505929156530808</v>
+        <v>0.1352973474726499</v>
       </c>
       <c r="BI3" s="2" t="n">
-        <v>0.1474759948570524</v>
+        <v>0.1321511122394537</v>
       </c>
       <c r="BJ3" s="2" t="n">
-        <v>0.1470652335073387</v>
+        <v>0.1322152009965466</v>
       </c>
       <c r="BK3" s="2" t="n">
-        <v>0.1398672094289344</v>
+        <v>0.1265960500998461</v>
       </c>
       <c r="BL3" s="2" t="n">
-        <v>0.1390471362219358</v>
+        <v>0.1263998497311198</v>
       </c>
       <c r="BM3" s="2" t="n">
-        <v>0.1360265111791789</v>
+        <v>0.124006016510005</v>
       </c>
       <c r="BN3" s="2" t="n">
-        <v>0.1344777752465151</v>
+        <v>0.1222804703916433</v>
       </c>
       <c r="BO3" s="2" t="n">
-        <v>0.1355278636293948</v>
+        <v>0.1236972886001279</v>
       </c>
       <c r="BP3" s="2" t="n">
-        <v>0.125908443432596</v>
+        <v>0.1161274461932152</v>
       </c>
       <c r="BQ3" s="2" t="n">
-        <v>0.1245774542339485</v>
+        <v>0.1155839875795802</v>
       </c>
       <c r="BR3" s="2" t="n">
-        <v>0.1238537510658418</v>
+        <v>0.1150347583394546</v>
       </c>
       <c r="BS3" s="2" t="n">
-        <v>0.1233652027026619</v>
+        <v>0.1150639871946373</v>
       </c>
       <c r="BT3" s="2" t="n">
-        <v>0.1866644681886904</v>
+        <v>0.1661446244366845</v>
       </c>
       <c r="BU3" s="2" t="n">
-        <v>0.1855808435594325</v>
+        <v>0.1639040263636218</v>
       </c>
       <c r="BV3" s="2" t="n">
-        <v>0.1816743946042744</v>
+        <v>0.16060982251376</v>
       </c>
       <c r="BW3" s="2" t="n">
-        <v>0.1817326744684571</v>
+        <v>0.1612719493161759</v>
       </c>
       <c r="BX3" s="2" t="n">
-        <v>0.1773759178414139</v>
+        <v>0.1599277440056057</v>
       </c>
       <c r="BY3" s="2" t="n">
-        <v>0.1726238847744606</v>
+        <v>0.1561925642967981</v>
       </c>
       <c r="BZ3" s="2" t="n">
-        <v>0.1686168798751214</v>
+        <v>0.1529657122118738</v>
       </c>
       <c r="CA3" s="2" t="n">
-        <v>0.1650623227353864</v>
+        <v>0.1502048866814636</v>
       </c>
       <c r="CB3" s="2" t="n">
-        <v>0.162463902703897</v>
+        <v>0.1484256394321269</v>
       </c>
       <c r="CC3" s="2" t="n">
-        <v>0.1576280542408419</v>
+        <v>0.1446864904449307</v>
       </c>
       <c r="CD3" s="2" t="n">
-        <v>0.1527718988174859</v>
+        <v>0.1414127755224943</v>
       </c>
       <c r="CE3" s="2" t="n">
-        <v>0.1447653072765246</v>
+        <v>0.1351686812539901</v>
       </c>
       <c r="CF3" s="2" t="n">
-        <v>0.1447933995915444</v>
+        <v>0.1354048708875185</v>
       </c>
       <c r="CG3" s="2" t="n">
-        <v>0.1478456952486783</v>
+        <v>0.1385690064682753</v>
       </c>
       <c r="CH3" s="2" t="n">
-        <v>0.214751555648951</v>
+        <v>0.191481095860534</v>
       </c>
       <c r="CI3" s="2" t="n">
-        <v>0.2149375832280012</v>
+        <v>0.1890948705799663</v>
       </c>
       <c r="CJ3" s="2" t="n">
-        <v>0.2102683349446236</v>
+        <v>0.1872705260910283</v>
       </c>
       <c r="CK3" s="2" t="n">
-        <v>0.2049744031682998</v>
+        <v>0.1841093155738022</v>
       </c>
       <c r="CL3" s="2" t="n">
-        <v>0.2006502632023585</v>
+        <v>0.180852549120973</v>
       </c>
       <c r="CM3" s="2" t="n">
-        <v>0.1926441789290845</v>
+        <v>0.1746676767251324</v>
       </c>
       <c r="CN3" s="2" t="n">
-        <v>0.1924670145094726</v>
+        <v>0.1755852577714538</v>
       </c>
       <c r="CO3" s="2" t="n">
-        <v>0.1855517664412968</v>
+        <v>0.1696547612630097</v>
       </c>
       <c r="CP3" s="2" t="n">
-        <v>0.1838016975644873</v>
+        <v>0.1684585499962472</v>
       </c>
       <c r="CQ3" s="2" t="n">
-        <v>0.1838687149629983</v>
+        <v>0.169480801634928</v>
       </c>
       <c r="CR3" s="2" t="n">
-        <v>0.168557632700106</v>
+        <v>0.1571882090045507</v>
       </c>
       <c r="CS3" s="2" t="n">
-        <v>0.1650128245500183</v>
+        <v>0.1550396917479392</v>
       </c>
       <c r="CT3" s="2" t="n">
-        <v>0.1644967016189882</v>
+        <v>0.1552042683771785</v>
       </c>
       <c r="CU3" s="2" t="n">
-        <v>0.1709266292758327</v>
+        <v>0.1612757557458227</v>
       </c>
       <c r="CV3" s="2" t="n">
-        <v>0.2523091180461001</v>
+        <v>0.2271002686563832</v>
       </c>
       <c r="CW3" s="2" t="n">
-        <v>0.2405631123454452</v>
+        <v>0.2146923905058434</v>
       </c>
       <c r="CX3" s="2" t="n">
-        <v>0.2381998266755307</v>
+        <v>0.2151357212325888</v>
       </c>
       <c r="CY3" s="2" t="n">
-        <v>0.2354682091353333</v>
+        <v>0.2138094403366204</v>
       </c>
       <c r="CZ3" s="2" t="n">
-        <v>0.2255499911883699</v>
+        <v>0.2053588447635679</v>
       </c>
       <c r="DA3" s="2" t="n">
-        <v>0.2212980007028303</v>
+        <v>0.2023209250293687</v>
       </c>
       <c r="DB3" s="2" t="n">
-        <v>0.220873073999913</v>
+        <v>0.2031670123587945</v>
       </c>
       <c r="DC3" s="2" t="n">
-        <v>0.2151331858004612</v>
+        <v>0.1991648153041077</v>
       </c>
       <c r="DD3" s="2" t="n">
-        <v>0.2131695024535731</v>
+        <v>0.1988340725270651</v>
       </c>
       <c r="DE3" s="2" t="n">
-        <v>0.2069427915494185</v>
+        <v>0.1934187592192884</v>
       </c>
       <c r="DF3" s="2" t="n">
-        <v>0.1993647225400674</v>
+        <v>0.1880413754620406</v>
       </c>
       <c r="DG3" s="2" t="n">
-        <v>0.1960251790507149</v>
+        <v>0.1854538277587326</v>
       </c>
       <c r="DH3" s="2" t="n">
-        <v>0.1939993174258684</v>
+        <v>0.1844474372262617</v>
       </c>
       <c r="DI3" s="2" t="n">
-        <v>0.1960549424178996</v>
+        <v>0.1871329802904998</v>
       </c>
       <c r="DJ3" s="2" t="n">
-        <v>0.2694636838245219</v>
+        <v>0.2427711933233607</v>
       </c>
       <c r="DK3" s="2" t="n">
-        <v>0.2642090210135141</v>
+        <v>0.2404075607347478</v>
       </c>
       <c r="DL3" s="2" t="n">
-        <v>0.2556412422837129</v>
+        <v>0.2333094700447487</v>
       </c>
       <c r="DM3" s="2" t="n">
-        <v>0.2531758700353737</v>
+        <v>0.2318841878304576</v>
       </c>
       <c r="DN3" s="2" t="n">
-        <v>0.2450106846506865</v>
+        <v>0.2254153335141187</v>
       </c>
       <c r="DO3" s="2" t="n">
-        <v>0.2450232583334997</v>
+        <v>0.227035470821946</v>
       </c>
       <c r="DP3" s="2" t="n">
-        <v>0.2371362341082228</v>
+        <v>0.2216318207179068</v>
       </c>
       <c r="DQ3" s="2" t="n">
-        <v>0.2305221527903114</v>
+        <v>0.2159313852834845</v>
       </c>
       <c r="DR3" s="2" t="n">
-        <v>0.2276560398165736</v>
+        <v>0.2146210071585833</v>
       </c>
       <c r="DS3" s="2" t="n">
-        <v>0.2236908555166972</v>
+        <v>0.2120004965533414</v>
       </c>
       <c r="DT3" s="2" t="n">
-        <v>0.2182948730827945</v>
+        <v>0.2077681292243714</v>
       </c>
       <c r="DU3" s="2" t="n">
-        <v>0.2155664368690756</v>
+        <v>0.2066948078135577</v>
       </c>
       <c r="DV3" s="2" t="n">
-        <v>0.2177403112373295</v>
+        <v>0.2090427758191867</v>
       </c>
       <c r="DW3" s="2" t="n">
-        <v>0.2195211701146783</v>
+        <v>0.2114058162776873</v>
       </c>
       <c r="DX3" s="2" t="n">
-        <v>0.2842936650290327</v>
+        <v>0.2607129336388703</v>
       </c>
       <c r="DY3" s="2" t="n">
-        <v>0.273221421283244</v>
+        <v>0.2512433397118228</v>
       </c>
       <c r="DZ3" s="2" t="n">
-        <v>0.2713684019065974</v>
+        <v>0.2499436303465567</v>
       </c>
       <c r="EA3" s="2" t="n">
-        <v>0.262422627215787</v>
+        <v>0.2435845122643128</v>
       </c>
       <c r="EB3" s="2" t="n">
-        <v>0.2598017227264154</v>
+        <v>0.2433264777890255</v>
       </c>
       <c r="EC3" s="2" t="n">
-        <v>0.2531324133613848</v>
+        <v>0.2376230382949404</v>
       </c>
       <c r="ED3" s="2" t="n">
-        <v>0.2491850720285876</v>
+        <v>0.2353212574967934</v>
       </c>
       <c r="EE3" s="2" t="n">
-        <v>0.2465501805038988</v>
+        <v>0.2340682456971974</v>
       </c>
       <c r="EF3" s="2" t="n">
-        <v>0.24407588225914</v>
+        <v>0.2318769710013913</v>
       </c>
       <c r="EG3" s="2" t="n">
-        <v>0.2414807617866387</v>
+        <v>0.230103293366428</v>
       </c>
       <c r="EH3" s="2" t="n">
-        <v>0.2280785546558374</v>
+        <v>0.2187852562114461</v>
       </c>
       <c r="EI3" s="2" t="n">
-        <v>0.2307374161728694</v>
+        <v>0.2228198587220937</v>
       </c>
       <c r="EJ3" s="2" t="n">
-        <v>0.2305893138045594</v>
+        <v>0.2241878055627862</v>
       </c>
       <c r="EK3" s="2" t="n">
-        <v>0.2325718195523833</v>
+        <v>0.2255191684662323</v>
       </c>
       <c r="EL3" s="2" t="n">
-        <v>0.2915088328840484</v>
+        <v>0.2722195808818859</v>
       </c>
       <c r="EM3" s="2" t="n">
-        <v>0.28576773618512</v>
+        <v>0.2695276789000672</v>
       </c>
       <c r="EN3" s="2" t="n">
-        <v>0.2801660796255683</v>
+        <v>0.2656012989355338</v>
       </c>
       <c r="EO3" s="2" t="n">
-        <v>0.2721455906522987</v>
+        <v>0.2592205079559852</v>
       </c>
       <c r="EP3" s="2" t="n">
-        <v>0.2749899096288539</v>
+        <v>0.2626356794167265</v>
       </c>
       <c r="EQ3" s="2" t="n">
-        <v>0.2630837707553345</v>
+        <v>0.2521514461782681</v>
       </c>
       <c r="ER3" s="2" t="n">
-        <v>0.2631110642391193</v>
+        <v>0.2519039234161848</v>
       </c>
       <c r="ES3" s="2" t="n">
-        <v>0.2555048135281091</v>
+        <v>0.2463891713541067</v>
       </c>
       <c r="ET3" s="2" t="n">
-        <v>0.258226564858064</v>
+        <v>0.2492541853536542</v>
       </c>
       <c r="EU3" s="2" t="n">
-        <v>0.2568475441976298</v>
+        <v>0.2487610322679652</v>
       </c>
       <c r="EV3" s="2" t="n">
-        <v>0.2527348588145711</v>
+        <v>0.2453029791751339</v>
       </c>
       <c r="EW3" s="2" t="n">
-        <v>0.2515351090216653</v>
+        <v>0.2454571367431017</v>
       </c>
       <c r="EX3" s="2" t="n">
-        <v>0.2507253930369147</v>
+        <v>0.2455903640462616</v>
       </c>
       <c r="EY3" s="2" t="n">
-        <v>0.2627294340209277</v>
+        <v>0.2572485205591213</v>
       </c>
       <c r="EZ3" s="2" t="n">
-        <v>0.2902024190413785</v>
+        <v>0.2809736147494518</v>
       </c>
       <c r="FA3" s="2" t="n">
-        <v>0.2902956351917036</v>
+        <v>0.2815971896546355</v>
       </c>
       <c r="FB3" s="2" t="n">
-        <v>0.2790226220331344</v>
+        <v>0.2711678343292964</v>
       </c>
       <c r="FC3" s="2" t="n">
-        <v>0.2809007590529302</v>
+        <v>0.2735501319738242</v>
       </c>
       <c r="FD3" s="2" t="n">
-        <v>0.271002087223276</v>
+        <v>0.264250270509155</v>
       </c>
       <c r="FE3" s="2" t="n">
-        <v>0.2723484871015427</v>
+        <v>0.265743324291853</v>
       </c>
       <c r="FF3" s="2" t="n">
-        <v>0.2718576777127331</v>
+        <v>0.2654168777343628</v>
       </c>
       <c r="FG3" s="2" t="n">
-        <v>0.2684596660510639</v>
+        <v>0.262227502460273</v>
       </c>
       <c r="FH3" s="2" t="n">
-        <v>0.2640855207965382</v>
+        <v>0.2578066167587605</v>
       </c>
       <c r="FI3" s="2" t="n">
-        <v>0.2626792405726449</v>
+        <v>0.2565849623042301</v>
       </c>
       <c r="FJ3" s="2" t="n">
-        <v>0.2646089347400492</v>
+        <v>0.2589384183927723</v>
       </c>
       <c r="FK3" s="2" t="n">
-        <v>0.2656189951789397</v>
+        <v>0.2612930972227017</v>
       </c>
       <c r="FL3" s="2" t="n">
-        <v>0.2749333203719027</v>
+        <v>0.2710485964119849</v>
       </c>
       <c r="FM3" s="2" t="n">
-        <v>0.2851520971822313</v>
+        <v>0.2812434531681126</v>
       </c>
       <c r="FN3" s="2" t="n">
-        <v>0.2925285460056656</v>
+        <v>0.2853486968652751</v>
       </c>
       <c r="FO3" s="2" t="n">
-        <v>0.292468159008293</v>
+        <v>0.285812976960942</v>
       </c>
       <c r="FP3" s="2" t="n">
-        <v>0.2842466058536408</v>
+        <v>0.2779715438275697</v>
       </c>
       <c r="FQ3" s="2" t="n">
-        <v>0.2821516120208891</v>
+        <v>0.275976774372922</v>
       </c>
       <c r="FR3" s="2" t="n">
-        <v>0.2880402989079506</v>
+        <v>0.2812959944854653</v>
       </c>
       <c r="FS3" s="2" t="n">
-        <v>0.2855250014597178</v>
+        <v>0.2789611226915656</v>
       </c>
       <c r="FT3" s="2" t="n">
-        <v>0.2859604287586506</v>
+        <v>0.2791543674939537</v>
       </c>
       <c r="FU3" s="2" t="n">
-        <v>0.2840706025942276</v>
+        <v>0.2772256365075397</v>
       </c>
       <c r="FV3" s="2" t="n">
-        <v>0.2857883041237865</v>
+        <v>0.2790191817778767</v>
       </c>
       <c r="FW3" s="2" t="n">
-        <v>0.2862304127439391</v>
+        <v>0.2793930399113408</v>
       </c>
       <c r="FX3" s="2" t="n">
-        <v>0.2845507941582913</v>
+        <v>0.2788455437440336</v>
       </c>
       <c r="FY3" s="2" t="n">
-        <v>0.2945433468856038</v>
+        <v>0.2897337771132058</v>
       </c>
       <c r="FZ3" s="2" t="n">
-        <v>0.2990528232339189</v>
+        <v>0.2939706733494584</v>
       </c>
       <c r="GA3" s="2" t="n">
-        <v>0.3139705993622374</v>
+        <v>0.3087682451699379</v>
       </c>
       <c r="GB3" s="2" t="n">
-        <v>0.3106664221442207</v>
+        <v>0.3005672983474763</v>
       </c>
       <c r="GC3" s="2" t="n">
-        <v>0.3116073684841309</v>
+        <v>0.3011412902585804</v>
       </c>
       <c r="GD3" s="2" t="n">
-        <v>0.3130336667215645</v>
+        <v>0.3022473839691732</v>
       </c>
       <c r="GE3" s="2" t="n">
-        <v>0.3132273030639942</v>
+        <v>0.3021377639285512</v>
       </c>
       <c r="GF3" s="2" t="n">
-        <v>0.3110772730825923</v>
+        <v>0.3003211007821149</v>
       </c>
       <c r="GG3" s="2" t="n">
-        <v>0.3092729687763041</v>
+        <v>0.2987437961086121</v>
       </c>
       <c r="GH3" s="2" t="n">
-        <v>0.3055306073073212</v>
+        <v>0.2951802973609974</v>
       </c>
       <c r="GI3" s="2" t="n">
-        <v>0.305204021867961</v>
+        <v>0.2961426915461123</v>
       </c>
       <c r="GJ3" s="2" t="n">
-        <v>0.3059134724358999</v>
+        <v>0.2963281665646729</v>
       </c>
       <c r="GK3" s="2" t="n">
-        <v>0.3098889805863277</v>
+        <v>0.3002041538503892</v>
       </c>
       <c r="GL3" s="2" t="n">
-        <v>0.3151310928620186</v>
+        <v>0.3071486503811694</v>
       </c>
       <c r="GM3" s="2" t="n">
-        <v>0.3205767841332713</v>
+        <v>0.3140250972010216</v>
       </c>
       <c r="GN3" s="2" t="n">
-        <v>0.3357882835041175</v>
+        <v>0.3289704347730815</v>
       </c>
       <c r="GO3" s="2" t="n">
-        <v>0.3445253882750557</v>
+        <v>0.3365318050101945</v>
       </c>
       <c r="GP3" s="2" t="n">
-        <v>0.3386960298211733</v>
+        <v>0.3289148502082095</v>
       </c>
       <c r="GQ3" s="2" t="n">
-        <v>0.334633529105703</v>
+        <v>0.3263696457877751</v>
       </c>
       <c r="GR3" s="2" t="n">
-        <v>0.3341670786352471</v>
+        <v>0.3249785531276876</v>
       </c>
       <c r="GS3" s="2" t="n">
-        <v>0.3323147000261173</v>
+        <v>0.3234309966241074</v>
       </c>
       <c r="GT3" s="2" t="n">
-        <v>0.3340091541481154</v>
+        <v>0.3248246044160387</v>
       </c>
       <c r="GU3" s="2" t="n">
-        <v>0.3281024620797927</v>
+        <v>0.3192156179638823</v>
       </c>
       <c r="GV3" s="2" t="n">
-        <v>0.3333647191771869</v>
+        <v>0.3241867318686409</v>
       </c>
       <c r="GW3" s="2" t="n">
-        <v>0.3280245503660804</v>
+        <v>0.3194522861522806</v>
       </c>
       <c r="GX3" s="2" t="n">
-        <v>0.3293848693081649</v>
+        <v>0.320453242586152</v>
       </c>
       <c r="GY3" s="2" t="n">
-        <v>0.3296761375241926</v>
+        <v>0.3207013987087024</v>
       </c>
       <c r="GZ3" s="2" t="n">
-        <v>0.3420682013547141</v>
+        <v>0.334151858261679</v>
       </c>
       <c r="HA3" s="2" t="n">
-        <v>0.3548751036915888</v>
+        <v>0.3472553589074186</v>
       </c>
       <c r="HB3" s="2" t="n">
-        <v>0.3675365412825221</v>
+        <v>0.359295540656767</v>
       </c>
       <c r="HC3" s="2" t="n">
-        <v>0.3606252091309965</v>
+        <v>0.3544072840006096</v>
       </c>
       <c r="HD3" s="2" t="n">
-        <v>0.3503698009606825</v>
+        <v>0.3413423246557197</v>
       </c>
       <c r="HE3" s="2" t="n">
-        <v>0.3447211374783697</v>
+        <v>0.3368893630049229</v>
       </c>
       <c r="HF3" s="2" t="n">
-        <v>0.3468887609267156</v>
+        <v>0.338452122955753</v>
       </c>
       <c r="HG3" s="2" t="n">
-        <v>0.3536722242226087</v>
+        <v>0.3446535878908904</v>
       </c>
       <c r="HH3" s="2" t="n">
-        <v>0.3530571977511323</v>
+        <v>0.3431906318746892</v>
       </c>
       <c r="HI3" s="2" t="n">
-        <v>0.3514921055161052</v>
+        <v>0.3413852666324564</v>
       </c>
       <c r="HJ3" s="2" t="n">
-        <v>0.3544924960831893</v>
+        <v>0.3435664431832263</v>
       </c>
       <c r="HK3" s="2" t="n">
-        <v>0.3485769799080305</v>
+        <v>0.3373370541687215</v>
       </c>
       <c r="HL3" s="2" t="n">
-        <v>0.3509208914311801</v>
+        <v>0.3387700640848791</v>
       </c>
       <c r="HM3" s="2" t="n">
-        <v>0.3484741690421874</v>
+        <v>0.335613329053305</v>
       </c>
       <c r="HN3" s="2" t="n">
-        <v>0.3708503350464358</v>
+        <v>0.3582932031709322</v>
       </c>
       <c r="HO3" s="2" t="n">
-        <v>0.3844876985634406</v>
+        <v>0.3724323859767131</v>
       </c>
       <c r="HP3" s="2" t="n">
-        <v>0.3618261990004777</v>
+        <v>0.3543456212064614</v>
       </c>
       <c r="HQ3" s="2" t="n">
-        <v>0.3486281451913719</v>
+        <v>0.344181726626602</v>
       </c>
       <c r="HR3" s="3" t="n">
         <v>55513</v>
@@ -2873,676 +2873,676 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.0270644620075987</v>
+        <v>0.02421883548362058</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.03611528353872134</v>
+        <v>0.03196442878308705</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03834155318580168</v>
+        <v>0.03386116637699772</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.04003284781408158</v>
+        <v>0.03538447166546103</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.04057991385591698</v>
+        <v>0.03583615802850014</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.03986628192838711</v>
+        <v>0.03521503853513604</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.03933523909976296</v>
+        <v>0.03476805479298632</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.03902840307549961</v>
+        <v>0.03441195533655463</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.03926390645400844</v>
+        <v>0.03468164046908989</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.03856071143721151</v>
+        <v>0.03407729732899303</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.0374702546679717</v>
+        <v>0.03318918907956794</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.03598887342634652</v>
+        <v>0.03238482859125221</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.03590158815852942</v>
+        <v>0.03233086368258872</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.03639197866408504</v>
+        <v>0.03297573297122168</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.05323400403960823</v>
+        <v>0.04859411973258355</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.06553609685694266</v>
+        <v>0.05871855985032069</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06899653980249407</v>
+        <v>0.06106769688338341</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.0699746089249127</v>
+        <v>0.06218149026239986</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.07139008960956703</v>
+        <v>0.06332022400573964</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.06861360241723605</v>
+        <v>0.06123602982436027</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.06970388256342314</v>
+        <v>0.06215341724413175</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.06905637073908211</v>
+        <v>0.06185113623998573</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.0689484283228019</v>
+        <v>0.06132884808468082</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.06839480028126771</v>
+        <v>0.06094873334310379</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.06507879626470157</v>
+        <v>0.05817969795599794</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.06209685646739277</v>
+        <v>0.05617537628810333</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>0.06207524255485746</v>
+        <v>0.05601642345484031</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>0.06322198942131096</v>
+        <v>0.05747568580648512</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.08617385826752751</v>
+        <v>0.0790060722846796</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>0.09970587674648881</v>
+        <v>0.08963351401698358</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.1005847249545029</v>
+        <v>0.08919776796284909</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>0.1025072236109416</v>
+        <v>0.09149614857748417</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1028578292655764</v>
+        <v>0.09186716760978642</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>0.1020964489007544</v>
+        <v>0.09137799821951947</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>0.09871899300857351</v>
+        <v>0.08850866174915412</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>0.09748476901190309</v>
+        <v>0.08777772759207528</v>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>0.09832862623510943</v>
+        <v>0.08801957720183805</v>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>0.09485844543977451</v>
+        <v>0.08513251227224963</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.08964598368020646</v>
+        <v>0.08147483653544157</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>0.08740898888727112</v>
+        <v>0.07974289527489054</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>0.08985636815575151</v>
+        <v>0.08185647226785707</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.09040791085848869</v>
+        <v>0.08267747425117941</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.1166404564608964</v>
+        <v>0.1071119203416263</v>
       </c>
       <c r="AS4" s="2" t="n">
-        <v>0.1268358908827738</v>
+        <v>0.1126074210583293</v>
       </c>
       <c r="AT4" s="2" t="n">
-        <v>0.1279445344890154</v>
+        <v>0.1135091439500212</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>0.1288806988486878</v>
+        <v>0.1156122243311925</v>
       </c>
       <c r="AV4" s="2" t="n">
-        <v>0.1271986636867022</v>
+        <v>0.1134462789056818</v>
       </c>
       <c r="AW4" s="2" t="n">
-        <v>0.1222257751863665</v>
+        <v>0.1098916532205009</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>0.1227418086367711</v>
+        <v>0.1104308573030912</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>0.121422963722653</v>
+        <v>0.1098312381169096</v>
       </c>
       <c r="AZ4" s="2" t="n">
-        <v>0.120442596731107</v>
+        <v>0.1084783821807984</v>
       </c>
       <c r="BA4" s="2" t="n">
-        <v>0.1160272056988994</v>
+        <v>0.1050682884780169</v>
       </c>
       <c r="BB4" s="2" t="n">
-        <v>0.1104620840973708</v>
+        <v>0.1008807211390796</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>0.1084553616885334</v>
+        <v>0.09943353728004303</v>
       </c>
       <c r="BD4" s="2" t="n">
-        <v>0.1069934426692585</v>
+        <v>0.09823068779012888</v>
       </c>
       <c r="BE4" s="2" t="n">
-        <v>0.1101252292236886</v>
+        <v>0.1013400133823111</v>
       </c>
       <c r="BF4" s="2" t="n">
-        <v>0.1475557145059728</v>
+        <v>0.1339097297844124</v>
       </c>
       <c r="BG4" s="2" t="n">
-        <v>0.1519031088615975</v>
+        <v>0.135216972100384</v>
       </c>
       <c r="BH4" s="2" t="n">
-        <v>0.151284916300836</v>
+        <v>0.1351042508094707</v>
       </c>
       <c r="BI4" s="2" t="n">
-        <v>0.1482386333610667</v>
+        <v>0.1319208558515857</v>
       </c>
       <c r="BJ4" s="2" t="n">
-        <v>0.1479828232859848</v>
+        <v>0.132143342706265</v>
       </c>
       <c r="BK4" s="2" t="n">
-        <v>0.1407672607328626</v>
+        <v>0.1265600728363755</v>
       </c>
       <c r="BL4" s="2" t="n">
-        <v>0.139913367462607</v>
+        <v>0.1263672197864909</v>
       </c>
       <c r="BM4" s="2" t="n">
-        <v>0.1369508181569085</v>
+        <v>0.1240439245488244</v>
       </c>
       <c r="BN4" s="2" t="n">
-        <v>0.1354016457793127</v>
+        <v>0.1222974958795317</v>
       </c>
       <c r="BO4" s="2" t="n">
-        <v>0.1364414303338969</v>
+        <v>0.1237161646359312</v>
       </c>
       <c r="BP4" s="2" t="n">
-        <v>0.1267802959319332</v>
+        <v>0.1162232204089404</v>
       </c>
       <c r="BQ4" s="2" t="n">
-        <v>0.1255019491760846</v>
+        <v>0.1157639875851854</v>
       </c>
       <c r="BR4" s="2" t="n">
-        <v>0.1248046769364122</v>
+        <v>0.1152552600454683</v>
       </c>
       <c r="BS4" s="2" t="n">
-        <v>0.1243149283163215</v>
+        <v>0.1153199520239638</v>
       </c>
       <c r="BT4" s="2" t="n">
-        <v>0.1874965891970975</v>
+        <v>0.1658801376813857</v>
       </c>
       <c r="BU4" s="2" t="n">
-        <v>0.1866935678440201</v>
+        <v>0.163538084502967</v>
       </c>
       <c r="BV4" s="2" t="n">
-        <v>0.182871468559869</v>
+        <v>0.1603973254994599</v>
       </c>
       <c r="BW4" s="2" t="n">
-        <v>0.1828807956896699</v>
+        <v>0.1610100461747491</v>
       </c>
       <c r="BX4" s="2" t="n">
-        <v>0.1785465085844108</v>
+        <v>0.1598210231867845</v>
       </c>
       <c r="BY4" s="2" t="n">
-        <v>0.1738456721934122</v>
+        <v>0.1561802897795716</v>
       </c>
       <c r="BZ4" s="2" t="n">
-        <v>0.1697719289949571</v>
+        <v>0.1529491590963934</v>
       </c>
       <c r="CA4" s="2" t="n">
-        <v>0.1662326181385757</v>
+        <v>0.1502374114693769</v>
       </c>
       <c r="CB4" s="2" t="n">
-        <v>0.1635959646723642</v>
+        <v>0.1484700974156589</v>
       </c>
       <c r="CC4" s="2" t="n">
-        <v>0.1586916544009909</v>
+        <v>0.1447448243074513</v>
       </c>
       <c r="CD4" s="2" t="n">
-        <v>0.1538185514711906</v>
+        <v>0.1415343091998361</v>
       </c>
       <c r="CE4" s="2" t="n">
-        <v>0.1458102907385883</v>
+        <v>0.1354023754439062</v>
       </c>
       <c r="CF4" s="2" t="n">
-        <v>0.145835368209779</v>
+        <v>0.1356733424427886</v>
       </c>
       <c r="CG4" s="2" t="n">
-        <v>0.1489614138540885</v>
+        <v>0.1388758915792425</v>
       </c>
       <c r="CH4" s="2" t="n">
-        <v>0.2160290919840959</v>
+        <v>0.1911843636656165</v>
       </c>
       <c r="CI4" s="2" t="n">
-        <v>0.2164470726100073</v>
+        <v>0.1887548467039964</v>
       </c>
       <c r="CJ4" s="2" t="n">
-        <v>0.2117713016089159</v>
+        <v>0.1871097739325467</v>
       </c>
       <c r="CK4" s="2" t="n">
-        <v>0.2064079399199173</v>
+        <v>0.18397978417971</v>
       </c>
       <c r="CL4" s="2" t="n">
-        <v>0.2021101051892852</v>
+        <v>0.180815234286098</v>
       </c>
       <c r="CM4" s="2" t="n">
-        <v>0.1940712575660113</v>
+        <v>0.1747087963335352</v>
       </c>
       <c r="CN4" s="2" t="n">
-        <v>0.1938400425227122</v>
+        <v>0.1756368371388364</v>
       </c>
       <c r="CO4" s="2" t="n">
-        <v>0.186877487616865</v>
+        <v>0.1697345711394965</v>
       </c>
       <c r="CP4" s="2" t="n">
-        <v>0.1850707588918187</v>
+        <v>0.1685327879276162</v>
       </c>
       <c r="CQ4" s="2" t="n">
-        <v>0.1850878190388311</v>
+        <v>0.1695409447259139</v>
       </c>
       <c r="CR4" s="2" t="n">
-        <v>0.1696971570487238</v>
+        <v>0.1573693246742304</v>
       </c>
       <c r="CS4" s="2" t="n">
-        <v>0.1661793338593608</v>
+        <v>0.1553316473949261</v>
       </c>
       <c r="CT4" s="2" t="n">
-        <v>0.165641319573346</v>
+        <v>0.1555408097006606</v>
       </c>
       <c r="CU4" s="2" t="n">
-        <v>0.1721700513930871</v>
+        <v>0.1616481084296129</v>
       </c>
       <c r="CV4" s="2" t="n">
-        <v>0.2540411990695567</v>
+        <v>0.2269130654855585</v>
       </c>
       <c r="CW4" s="2" t="n">
-        <v>0.2424044873429091</v>
+        <v>0.2145930119470834</v>
       </c>
       <c r="CX4" s="2" t="n">
-        <v>0.2399275208106405</v>
+        <v>0.2150779390481856</v>
       </c>
       <c r="CY4" s="2" t="n">
-        <v>0.2372422106363985</v>
+        <v>0.2138854072824612</v>
       </c>
       <c r="CZ4" s="2" t="n">
-        <v>0.2272353841271387</v>
+        <v>0.2054402437751598</v>
       </c>
       <c r="DA4" s="2" t="n">
-        <v>0.2229290204297384</v>
+        <v>0.2024267531532871</v>
       </c>
       <c r="DB4" s="2" t="n">
-        <v>0.2224206612876418</v>
+        <v>0.2032976046554289</v>
       </c>
       <c r="DC4" s="2" t="n">
-        <v>0.2165532833397313</v>
+        <v>0.1992770910890151</v>
       </c>
       <c r="DD4" s="2" t="n">
-        <v>0.214558553080428</v>
+        <v>0.1990453138968534</v>
       </c>
       <c r="DE4" s="2" t="n">
-        <v>0.2082881094141659</v>
+        <v>0.193621488246976</v>
       </c>
       <c r="DF4" s="2" t="n">
-        <v>0.2006569507266218</v>
+        <v>0.1883060207502518</v>
       </c>
       <c r="DG4" s="2" t="n">
-        <v>0.1972934850326874</v>
+        <v>0.1857700857757836</v>
       </c>
       <c r="DH4" s="2" t="n">
-        <v>0.1952289302481523</v>
+        <v>0.1848061792601149</v>
       </c>
       <c r="DI4" s="2" t="n">
-        <v>0.1973505235680393</v>
+        <v>0.187592345424412</v>
       </c>
       <c r="DJ4" s="2" t="n">
-        <v>0.2716418436186331</v>
+        <v>0.2428449434236502</v>
       </c>
       <c r="DK4" s="2" t="n">
-        <v>0.266276584721457</v>
+        <v>0.2405809907460848</v>
       </c>
       <c r="DL4" s="2" t="n">
-        <v>0.2575154479001242</v>
+        <v>0.2334189444413799</v>
       </c>
       <c r="DM4" s="2" t="n">
-        <v>0.2550251073709922</v>
+        <v>0.2320106890437281</v>
       </c>
       <c r="DN4" s="2" t="n">
-        <v>0.2467935870423611</v>
+        <v>0.2256003227935036</v>
       </c>
       <c r="DO4" s="2" t="n">
-        <v>0.2466486001659547</v>
+        <v>0.2271847296056477</v>
       </c>
       <c r="DP4" s="2" t="n">
-        <v>0.2386712949848152</v>
+        <v>0.2218491754807354</v>
       </c>
       <c r="DQ4" s="2" t="n">
-        <v>0.231970879205628</v>
+        <v>0.2161709797193341</v>
       </c>
       <c r="DR4" s="2" t="n">
-        <v>0.229072442684432</v>
+        <v>0.2149117346084304</v>
       </c>
       <c r="DS4" s="2" t="n">
-        <v>0.2250409473951497</v>
+        <v>0.2123370727926613</v>
       </c>
       <c r="DT4" s="2" t="n">
-        <v>0.2195867429592072</v>
+        <v>0.208113249716532</v>
       </c>
       <c r="DU4" s="2" t="n">
-        <v>0.2167805562666251</v>
+        <v>0.2070289330344123</v>
       </c>
       <c r="DV4" s="2" t="n">
-        <v>0.2190268200250222</v>
+        <v>0.20947914601069</v>
       </c>
       <c r="DW4" s="2" t="n">
-        <v>0.220818215921679</v>
+        <v>0.2119266208008092</v>
       </c>
       <c r="DX4" s="2" t="n">
-        <v>0.2863849534197184</v>
+        <v>0.2609181921070758</v>
       </c>
       <c r="DY4" s="2" t="n">
-        <v>0.2752122274334863</v>
+        <v>0.2514248892714409</v>
       </c>
       <c r="DZ4" s="2" t="n">
-        <v>0.2733400706482825</v>
+        <v>0.2501804809502957</v>
       </c>
       <c r="EA4" s="2" t="n">
-        <v>0.2641260765233489</v>
+        <v>0.2437709663081606</v>
       </c>
       <c r="EB4" s="2" t="n">
-        <v>0.2614303435840997</v>
+        <v>0.2436020223028637</v>
       </c>
       <c r="EC4" s="2" t="n">
-        <v>0.2547253746415145</v>
+        <v>0.237895121860803</v>
       </c>
       <c r="ED4" s="2" t="n">
-        <v>0.2506834814240523</v>
+        <v>0.2356398850151195</v>
       </c>
       <c r="EE4" s="2" t="n">
-        <v>0.2480095760786955</v>
+        <v>0.2344340320049843</v>
       </c>
       <c r="EF4" s="2" t="n">
-        <v>0.2454645702000574</v>
+        <v>0.2321741480726037</v>
       </c>
       <c r="EG4" s="2" t="n">
-        <v>0.2428247544211334</v>
+        <v>0.2304276002127537</v>
       </c>
       <c r="EH4" s="2" t="n">
-        <v>0.2293936261078715</v>
+        <v>0.2192595547184655</v>
       </c>
       <c r="EI4" s="2" t="n">
-        <v>0.2319678637031456</v>
+        <v>0.2233159702226298</v>
       </c>
       <c r="EJ4" s="2" t="n">
-        <v>0.231806049139485</v>
+        <v>0.2247432827493071</v>
       </c>
       <c r="EK4" s="2" t="n">
-        <v>0.2338611524795318</v>
+        <v>0.2260777698623381</v>
       </c>
       <c r="EL4" s="2" t="n">
-        <v>0.2934015916824955</v>
+        <v>0.2725228363688569</v>
       </c>
       <c r="EM4" s="2" t="n">
-        <v>0.2875700198846189</v>
+        <v>0.2699331790800896</v>
       </c>
       <c r="EN4" s="2" t="n">
-        <v>0.2818749942128524</v>
+        <v>0.2660072160014023</v>
       </c>
       <c r="EO4" s="2" t="n">
-        <v>0.2737240467796273</v>
+        <v>0.2596210762457808</v>
       </c>
       <c r="EP4" s="2" t="n">
-        <v>0.2765112825304869</v>
+        <v>0.2630214082877496</v>
       </c>
       <c r="EQ4" s="2" t="n">
-        <v>0.2645076870869995</v>
+        <v>0.2525539507054037</v>
       </c>
       <c r="ER4" s="2" t="n">
-        <v>0.2645267270581886</v>
+        <v>0.2523718974840459</v>
       </c>
       <c r="ES4" s="2" t="n">
-        <v>0.2568680727895005</v>
+        <v>0.2469536066632696</v>
       </c>
       <c r="ET4" s="2" t="n">
-        <v>0.2595186306623452</v>
+        <v>0.2497322202774724</v>
       </c>
       <c r="EU4" s="2" t="n">
-        <v>0.2581142604345123</v>
+        <v>0.2492723559028377</v>
       </c>
       <c r="EV4" s="2" t="n">
-        <v>0.2540320760353519</v>
+        <v>0.2458440373682043</v>
       </c>
       <c r="EW4" s="2" t="n">
-        <v>0.2527499824239062</v>
+        <v>0.2460090730277721</v>
       </c>
       <c r="EX4" s="2" t="n">
-        <v>0.2519408692322626</v>
+        <v>0.2461999976620051</v>
       </c>
       <c r="EY4" s="2" t="n">
-        <v>0.2640399902797445</v>
+        <v>0.2580036143237596</v>
       </c>
       <c r="EZ4" s="2" t="n">
-        <v>0.2915364893732528</v>
+        <v>0.2814303873283477</v>
       </c>
       <c r="FA4" s="2" t="n">
-        <v>0.2916234214071887</v>
+        <v>0.2821052457164092</v>
       </c>
       <c r="FB4" s="2" t="n">
-        <v>0.2802596192601417</v>
+        <v>0.2716479833436487</v>
       </c>
       <c r="FC4" s="2" t="n">
-        <v>0.2821624033434053</v>
+        <v>0.2740659668732232</v>
       </c>
       <c r="FD4" s="2" t="n">
-        <v>0.2722086199206994</v>
+        <v>0.2647806629879851</v>
       </c>
       <c r="FE4" s="2" t="n">
-        <v>0.273592504481678</v>
+        <v>0.2663050446341734</v>
       </c>
       <c r="FF4" s="2" t="n">
-        <v>0.2730722318729932</v>
+        <v>0.2659687405851714</v>
       </c>
       <c r="FG4" s="2" t="n">
-        <v>0.2696895849148738</v>
+        <v>0.2627995823545955</v>
       </c>
       <c r="FH4" s="2" t="n">
-        <v>0.2652727666957695</v>
+        <v>0.2583665211572261</v>
       </c>
       <c r="FI4" s="2" t="n">
-        <v>0.2638707979069531</v>
+        <v>0.2571446892903111</v>
       </c>
       <c r="FJ4" s="2" t="n">
-        <v>0.265855064482766</v>
+        <v>0.2595614718450892</v>
       </c>
       <c r="FK4" s="2" t="n">
-        <v>0.2668203995245605</v>
+        <v>0.2619605699896267</v>
       </c>
       <c r="FL4" s="2" t="n">
-        <v>0.2761934433691287</v>
+        <v>0.2717974814538589</v>
       </c>
       <c r="FM4" s="2" t="n">
-        <v>0.2864725490722416</v>
+        <v>0.2820444021434736</v>
       </c>
       <c r="FN4" s="2" t="n">
-        <v>0.2939131028185327</v>
+        <v>0.2860341112154146</v>
       </c>
       <c r="FO4" s="2" t="n">
-        <v>0.2938188321021322</v>
+        <v>0.2864945247025913</v>
       </c>
       <c r="FP4" s="2" t="n">
-        <v>0.2855545692034281</v>
+        <v>0.2786385802594764</v>
       </c>
       <c r="FQ4" s="2" t="n">
-        <v>0.2835018648811316</v>
+        <v>0.2766511833911737</v>
       </c>
       <c r="FR4" s="2" t="n">
-        <v>0.2893905731991799</v>
+        <v>0.281972778427258</v>
       </c>
       <c r="FS4" s="2" t="n">
-        <v>0.2869229065975428</v>
+        <v>0.2796645873883514</v>
       </c>
       <c r="FT4" s="2" t="n">
-        <v>0.2873753681800474</v>
+        <v>0.2798649149563903</v>
       </c>
       <c r="FU4" s="2" t="n">
-        <v>0.2855067325943555</v>
+        <v>0.2779542494047293</v>
       </c>
       <c r="FV4" s="2" t="n">
-        <v>0.2872783954448079</v>
+        <v>0.2797838210557953</v>
       </c>
       <c r="FW4" s="2" t="n">
-        <v>0.2877397763306614</v>
+        <v>0.2801713775085937</v>
       </c>
       <c r="FX4" s="2" t="n">
-        <v>0.286074299143732</v>
+        <v>0.2796850249128229</v>
       </c>
       <c r="FY4" s="2" t="n">
-        <v>0.2960879688616104</v>
+        <v>0.2906540817153804</v>
       </c>
       <c r="FZ4" s="2" t="n">
-        <v>0.3006713476617001</v>
+        <v>0.294935400739074</v>
       </c>
       <c r="GA4" s="2" t="n">
-        <v>0.315576306532439</v>
+        <v>0.3097892998517737</v>
       </c>
       <c r="GB4" s="2" t="n">
-        <v>0.3125029012278995</v>
+        <v>0.3013862190931629</v>
       </c>
       <c r="GC4" s="2" t="n">
-        <v>0.3134785006991353</v>
+        <v>0.3019753588169836</v>
       </c>
       <c r="GD4" s="2" t="n">
-        <v>0.3149870418764458</v>
+        <v>0.3031276985761032</v>
       </c>
       <c r="GE4" s="2" t="n">
-        <v>0.3151847791605809</v>
+        <v>0.3030257307899826</v>
       </c>
       <c r="GF4" s="2" t="n">
-        <v>0.3130454666451744</v>
+        <v>0.3012083520425725</v>
       </c>
       <c r="GG4" s="2" t="n">
-        <v>0.3111989420329596</v>
+        <v>0.2996223602307226</v>
       </c>
       <c r="GH4" s="2" t="n">
-        <v>0.3074851107784717</v>
+        <v>0.2960702240640674</v>
       </c>
       <c r="GI4" s="2" t="n">
-        <v>0.3072277070605308</v>
+        <v>0.2971324822306355</v>
       </c>
       <c r="GJ4" s="2" t="n">
-        <v>0.3079141832391329</v>
+        <v>0.2972905645231341</v>
       </c>
       <c r="GK4" s="2" t="n">
-        <v>0.3119232666045855</v>
+        <v>0.3012214126549149</v>
       </c>
       <c r="GL4" s="2" t="n">
-        <v>0.3171849666447104</v>
+        <v>0.3082641502875313</v>
       </c>
       <c r="GM4" s="2" t="n">
-        <v>0.3226008653730599</v>
+        <v>0.3152524172264353</v>
       </c>
       <c r="GN4" s="2" t="n">
-        <v>0.3378387146254042</v>
+        <v>0.3302082878816537</v>
       </c>
       <c r="GO4" s="2" t="n">
-        <v>0.3466805526342366</v>
+        <v>0.3378042618405498</v>
       </c>
       <c r="GP4" s="2" t="n">
-        <v>0.3407451608666064</v>
+        <v>0.3299402575143537</v>
       </c>
       <c r="GQ4" s="2" t="n">
-        <v>0.3366154846917435</v>
+        <v>0.3274411167874508</v>
       </c>
       <c r="GR4" s="2" t="n">
-        <v>0.3361698360524528</v>
+        <v>0.3259331334462604</v>
       </c>
       <c r="GS4" s="2" t="n">
-        <v>0.3343284524064058</v>
+        <v>0.3244325744708925</v>
       </c>
       <c r="GT4" s="2" t="n">
-        <v>0.3360573093286701</v>
+        <v>0.3258851903562224</v>
       </c>
       <c r="GU4" s="2" t="n">
-        <v>0.3301822083376602</v>
+        <v>0.3203112899325802</v>
       </c>
       <c r="GV4" s="2" t="n">
-        <v>0.3355175558701162</v>
+        <v>0.3253140377687995</v>
       </c>
       <c r="GW4" s="2" t="n">
-        <v>0.3301879258196321</v>
+        <v>0.3206391639360312</v>
       </c>
       <c r="GX4" s="2" t="n">
-        <v>0.3315959310590004</v>
+        <v>0.3216799928737913</v>
       </c>
       <c r="GY4" s="2" t="n">
-        <v>0.3319662128922429</v>
+        <v>0.3219716134463018</v>
       </c>
       <c r="GZ4" s="2" t="n">
-        <v>0.344297300325433</v>
+        <v>0.3355021710566444</v>
       </c>
       <c r="HA4" s="2" t="n">
-        <v>0.3570282217669664</v>
+        <v>0.3485442185226089</v>
       </c>
       <c r="HB4" s="2" t="n">
-        <v>0.3698740972697476</v>
+        <v>0.3607001204585671</v>
       </c>
       <c r="HC4" s="2" t="n">
-        <v>0.3625202136193595</v>
+        <v>0.3555976966136533</v>
       </c>
       <c r="HD4" s="2" t="n">
-        <v>0.3530860023965005</v>
+        <v>0.3430663982911665</v>
       </c>
       <c r="HE4" s="2" t="n">
-        <v>0.3473040636644094</v>
+        <v>0.3385962593326385</v>
       </c>
       <c r="HF4" s="2" t="n">
-        <v>0.3494566748692</v>
+        <v>0.3401340318000398</v>
       </c>
       <c r="HG4" s="2" t="n">
-        <v>0.3563499482798702</v>
+        <v>0.3463280295337608</v>
       </c>
       <c r="HH4" s="2" t="n">
-        <v>0.3558119116703801</v>
+        <v>0.3448702166232785</v>
       </c>
       <c r="HI4" s="2" t="n">
-        <v>0.3542923622923743</v>
+        <v>0.3430718892975396</v>
       </c>
       <c r="HJ4" s="2" t="n">
-        <v>0.3573778968162194</v>
+        <v>0.3452255918305785</v>
       </c>
       <c r="HK4" s="2" t="n">
-        <v>0.351445518576098</v>
+        <v>0.3390081398646101</v>
       </c>
       <c r="HL4" s="2" t="n">
-        <v>0.3538603247028781</v>
+        <v>0.3404065830425996</v>
       </c>
       <c r="HM4" s="2" t="n">
-        <v>0.3514212047517249</v>
+        <v>0.3372146003448917</v>
       </c>
       <c r="HN4" s="2" t="n">
-        <v>0.3737844985588937</v>
+        <v>0.3598677349020928</v>
       </c>
       <c r="HO4" s="2" t="n">
-        <v>0.387514416209113</v>
+        <v>0.3740603257070509</v>
       </c>
       <c r="HP4" s="2" t="n">
-        <v>0.3640185841384715</v>
+        <v>0.355710644302732</v>
       </c>
       <c r="HQ4" s="2" t="n">
-        <v>0.3502978148934234</v>
+        <v>0.3453663200860274</v>
       </c>
       <c r="HR4" s="3" t="n">
         <v>55514</v>
@@ -3555,676 +3555,676 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.02739544831189469</v>
+        <v>0.02444780639208735</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.0364936841402351</v>
+        <v>0.03237487993792686</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.03867545444627978</v>
+        <v>0.03426154747906859</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.04028683130986639</v>
+        <v>0.03573490053411237</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.04076199035824418</v>
+        <v>0.03613222335849506</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.03998933431952262</v>
+        <v>0.03546196971537827</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.03938427347718074</v>
+        <v>0.03495113369090708</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.03904864698445245</v>
+        <v>0.03457146082815026</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03925808372778945</v>
+        <v>0.03481799726525824</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03852657551239384</v>
+        <v>0.03419026900599027</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.03738031307204296</v>
+        <v>0.03325146192625164</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.03593097461456116</v>
+        <v>0.03244673791080416</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.03583449870007907</v>
+        <v>0.03238523604987006</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.03632863485892388</v>
+        <v>0.03302510712928656</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.0539086695195905</v>
+        <v>0.04915147064367589</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.06612562068028419</v>
+        <v>0.05939759542953686</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.06944257475927805</v>
+        <v>0.06167916033413742</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.07025100172809291</v>
+        <v>0.06265266118706755</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.07158656827524577</v>
+        <v>0.063728334590165</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.0687548569969168</v>
+        <v>0.06157228725429827</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.06973109838718999</v>
+        <v>0.06240028250369117</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.0690381189573205</v>
+        <v>0.06204978005427305</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.06884271615407198</v>
+        <v>0.06146670238059046</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.06825738433520273</v>
+        <v>0.06105554469992842</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.06487043005804524</v>
+        <v>0.05821413884896452</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.06195546269896236</v>
+        <v>0.05623414968867654</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>0.06190788175746978</v>
+        <v>0.05605640805504707</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.06308708962421344</v>
+        <v>0.05752695619146232</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>0.08706602533074047</v>
+        <v>0.07993068785314278</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>0.1003546241284934</v>
+        <v>0.09049327097863377</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.1009990771123744</v>
+        <v>0.08989176268579871</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>0.1026908085864484</v>
+        <v>0.09197117740483347</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.1029345327379411</v>
+        <v>0.09224335246303007</v>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>0.1020874927749207</v>
+        <v>0.09167843967034012</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>0.09860849413964534</v>
+        <v>0.08870784013519456</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>0.09733660344190159</v>
+        <v>0.08792987859489126</v>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>0.09807716595295676</v>
+        <v>0.08810198775528305</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>0.0946074446248263</v>
+        <v>0.08519965482905298</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.0894257210354682</v>
+        <v>0.08152226490327619</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>0.08717368409347009</v>
+        <v>0.07976799450074241</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>0.08959953638073963</v>
+        <v>0.08186513838183601</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.09013972792043559</v>
+        <v>0.08267008421781863</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.1176411031689223</v>
+        <v>0.1082633479729895</v>
       </c>
       <c r="AS5" s="2" t="n">
-        <v>0.1272534935107417</v>
+        <v>0.1133907662757746</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>0.1280937933324615</v>
+        <v>0.1140578397733534</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>0.1288478786147749</v>
+        <v>0.1159434490820538</v>
       </c>
       <c r="AV5" s="2" t="n">
-        <v>0.1271772162552088</v>
+        <v>0.1138016992614481</v>
       </c>
       <c r="AW5" s="2" t="n">
-        <v>0.1220615647932971</v>
+        <v>0.1100836389222555</v>
       </c>
       <c r="AX5" s="2" t="n">
-        <v>0.1225151754898736</v>
+        <v>0.1105792630710763</v>
       </c>
       <c r="AY5" s="2" t="n">
-        <v>0.1211800755383033</v>
+        <v>0.1099376532474698</v>
       </c>
       <c r="AZ5" s="2" t="n">
-        <v>0.1200906898407806</v>
+        <v>0.1085064942504584</v>
       </c>
       <c r="BA5" s="2" t="n">
-        <v>0.1157202378062991</v>
+        <v>0.1051086496712751</v>
       </c>
       <c r="BB5" s="2" t="n">
-        <v>0.1101390429385765</v>
+        <v>0.1008659562605647</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>0.1081517877266564</v>
+        <v>0.09942167183421324</v>
       </c>
       <c r="BD5" s="2" t="n">
-        <v>0.1067224245217728</v>
+        <v>0.09823981029506809</v>
       </c>
       <c r="BE5" s="2" t="n">
-        <v>0.1098176363079176</v>
+        <v>0.1013153848351704</v>
       </c>
       <c r="BF5" s="2" t="n">
-        <v>0.1482658075231564</v>
+        <v>0.1349533374882825</v>
       </c>
       <c r="BG5" s="2" t="n">
-        <v>0.1521382324030641</v>
+        <v>0.1358781554333243</v>
       </c>
       <c r="BH5" s="2" t="n">
-        <v>0.1512569368648279</v>
+        <v>0.1355070704463995</v>
       </c>
       <c r="BI5" s="2" t="n">
-        <v>0.1479108550482704</v>
+        <v>0.1320350235788408</v>
       </c>
       <c r="BJ5" s="2" t="n">
-        <v>0.1477333580863833</v>
+        <v>0.132344071170825</v>
       </c>
       <c r="BK5" s="2" t="n">
-        <v>0.1404705299738469</v>
+        <v>0.1266743504493971</v>
       </c>
       <c r="BL5" s="2" t="n">
-        <v>0.1395194515656248</v>
+        <v>0.1263898085565433</v>
       </c>
       <c r="BM5" s="2" t="n">
-        <v>0.1365943349425968</v>
+        <v>0.1240841141482032</v>
       </c>
       <c r="BN5" s="2" t="n">
-        <v>0.1349379760430998</v>
+        <v>0.1222501253933406</v>
       </c>
       <c r="BO5" s="2" t="n">
-        <v>0.1359456033292379</v>
+        <v>0.1236302091774609</v>
       </c>
       <c r="BP5" s="2" t="n">
-        <v>0.1263690488773303</v>
+        <v>0.1161565198804803</v>
       </c>
       <c r="BQ5" s="2" t="n">
-        <v>0.1251712616819031</v>
+        <v>0.115743813465665</v>
       </c>
       <c r="BR5" s="2" t="n">
-        <v>0.124502008413189</v>
+        <v>0.1152486061353246</v>
       </c>
       <c r="BS5" s="2" t="n">
-        <v>0.1240365373247888</v>
+        <v>0.1153189504577685</v>
       </c>
       <c r="BT5" s="2" t="n">
-        <v>0.1878940037185029</v>
+        <v>0.1668098448596415</v>
       </c>
       <c r="BU5" s="2" t="n">
-        <v>0.1865728789444508</v>
+        <v>0.163965963961428</v>
       </c>
       <c r="BV5" s="2" t="n">
-        <v>0.1824972229264751</v>
+        <v>0.1606253154628253</v>
       </c>
       <c r="BW5" s="2" t="n">
-        <v>0.1821556752019035</v>
+        <v>0.1608963095113758</v>
       </c>
       <c r="BX5" s="2" t="n">
-        <v>0.1780607209145235</v>
+        <v>0.1598548411329171</v>
       </c>
       <c r="BY5" s="2" t="n">
-        <v>0.1733967186327408</v>
+        <v>0.1562420863888029</v>
       </c>
       <c r="BZ5" s="2" t="n">
-        <v>0.1691531908099365</v>
+        <v>0.1528424520174897</v>
       </c>
       <c r="CA5" s="2" t="n">
-        <v>0.1656596626237931</v>
+        <v>0.1501603755103619</v>
       </c>
       <c r="CB5" s="2" t="n">
-        <v>0.1630409949334784</v>
+        <v>0.1483871603013575</v>
       </c>
       <c r="CC5" s="2" t="n">
-        <v>0.1581527506863249</v>
+        <v>0.1446433440183938</v>
       </c>
       <c r="CD5" s="2" t="n">
-        <v>0.1533216350190316</v>
+        <v>0.1414351678288244</v>
       </c>
       <c r="CE5" s="2" t="n">
-        <v>0.1454680170141659</v>
+        <v>0.1353809163023824</v>
       </c>
       <c r="CF5" s="2" t="n">
-        <v>0.1455034648883045</v>
+        <v>0.1356631113114153</v>
       </c>
       <c r="CG5" s="2" t="n">
-        <v>0.148672680583107</v>
+        <v>0.1388770938686108</v>
       </c>
       <c r="CH5" s="2" t="n">
-        <v>0.2157725878574143</v>
+        <v>0.1915312399423797</v>
       </c>
       <c r="CI5" s="2" t="n">
-        <v>0.2157288311205374</v>
+        <v>0.1887209343505475</v>
       </c>
       <c r="CJ5" s="2" t="n">
-        <v>0.2110792230682544</v>
+        <v>0.1870878349708917</v>
       </c>
       <c r="CK5" s="2" t="n">
-        <v>0.2056307920572217</v>
+        <v>0.1838263738986339</v>
       </c>
       <c r="CL5" s="2" t="n">
-        <v>0.2013595006796571</v>
+        <v>0.1806826718648038</v>
       </c>
       <c r="CM5" s="2" t="n">
-        <v>0.1934187463484666</v>
+        <v>0.1746319816517908</v>
       </c>
       <c r="CN5" s="2" t="n">
-        <v>0.1931705886811138</v>
+        <v>0.1755318654333273</v>
       </c>
       <c r="CO5" s="2" t="n">
-        <v>0.1861963587458871</v>
+        <v>0.1696015504027794</v>
       </c>
       <c r="CP5" s="2" t="n">
-        <v>0.1843393968121984</v>
+        <v>0.1683363876174819</v>
       </c>
       <c r="CQ5" s="2" t="n">
-        <v>0.1843478246511461</v>
+        <v>0.169295920236486</v>
       </c>
       <c r="CR5" s="2" t="n">
-        <v>0.1692692739276426</v>
+        <v>0.1573181719981173</v>
       </c>
       <c r="CS5" s="2" t="n">
-        <v>0.1658585192459039</v>
+        <v>0.1553237663226818</v>
       </c>
       <c r="CT5" s="2" t="n">
-        <v>0.1653914235289331</v>
+        <v>0.1555745885236227</v>
       </c>
       <c r="CU5" s="2" t="n">
-        <v>0.1718940410877773</v>
+        <v>0.1616596573648861</v>
       </c>
       <c r="CV5" s="2" t="n">
-        <v>0.2530916456518861</v>
+        <v>0.2266504150034231</v>
       </c>
       <c r="CW5" s="2" t="n">
-        <v>0.2413350182103406</v>
+        <v>0.2142928932868706</v>
       </c>
       <c r="CX5" s="2" t="n">
-        <v>0.2390384611447229</v>
+        <v>0.2148834012593509</v>
       </c>
       <c r="CY5" s="2" t="n">
-        <v>0.2364641909153182</v>
+        <v>0.2137965697008065</v>
       </c>
       <c r="CZ5" s="2" t="n">
-        <v>0.2263555809546662</v>
+        <v>0.2052212175840997</v>
       </c>
       <c r="DA5" s="2" t="n">
-        <v>0.2220578525120203</v>
+        <v>0.2021921922719029</v>
       </c>
       <c r="DB5" s="2" t="n">
-        <v>0.2215919062420265</v>
+        <v>0.2030754373933106</v>
       </c>
       <c r="DC5" s="2" t="n">
-        <v>0.2157506741668235</v>
+        <v>0.1990182028061808</v>
       </c>
       <c r="DD5" s="2" t="n">
-        <v>0.2140272993575869</v>
+        <v>0.198979527922527</v>
       </c>
       <c r="DE5" s="2" t="n">
-        <v>0.2077945848029811</v>
+        <v>0.1935582718243319</v>
       </c>
       <c r="DF5" s="2" t="n">
-        <v>0.2003039749494546</v>
+        <v>0.188287860101983</v>
       </c>
       <c r="DG5" s="2" t="n">
-        <v>0.1969057442099771</v>
+        <v>0.1857048187585465</v>
       </c>
       <c r="DH5" s="2" t="n">
-        <v>0.1949538429915486</v>
+        <v>0.1848100141967423</v>
       </c>
       <c r="DI5" s="2" t="n">
-        <v>0.1971687842350506</v>
+        <v>0.1876495844482999</v>
       </c>
       <c r="DJ5" s="2" t="n">
-        <v>0.2707013469592472</v>
+        <v>0.2426992093480058</v>
       </c>
       <c r="DK5" s="2" t="n">
-        <v>0.2654860552589393</v>
+        <v>0.2405258172971843</v>
       </c>
       <c r="DL5" s="2" t="n">
-        <v>0.2565243525281712</v>
+        <v>0.2331521589984819</v>
       </c>
       <c r="DM5" s="2" t="n">
-        <v>0.2540997141795888</v>
+        <v>0.231775912893233</v>
       </c>
       <c r="DN5" s="2" t="n">
-        <v>0.2459297527297858</v>
+        <v>0.2253957877943723</v>
       </c>
       <c r="DO5" s="2" t="n">
-        <v>0.2457491545260041</v>
+        <v>0.2268882295526795</v>
       </c>
       <c r="DP5" s="2" t="n">
-        <v>0.2380473966019073</v>
+        <v>0.2217122155259478</v>
       </c>
       <c r="DQ5" s="2" t="n">
-        <v>0.2313902933903315</v>
+        <v>0.2160712777986281</v>
       </c>
       <c r="DR5" s="2" t="n">
-        <v>0.2286812031197671</v>
+        <v>0.2149202327576358</v>
       </c>
       <c r="DS5" s="2" t="n">
-        <v>0.224777934478919</v>
+        <v>0.2124117057749803</v>
       </c>
       <c r="DT5" s="2" t="n">
-        <v>0.219311863710018</v>
+        <v>0.2081369954254156</v>
       </c>
       <c r="DU5" s="2" t="n">
-        <v>0.2165559162092009</v>
+        <v>0.2070290826997196</v>
       </c>
       <c r="DV5" s="2" t="n">
-        <v>0.2188851012003933</v>
+        <v>0.2095496181935484</v>
       </c>
       <c r="DW5" s="2" t="n">
-        <v>0.220692717680215</v>
+        <v>0.2120100034864152</v>
       </c>
       <c r="DX5" s="2" t="n">
-        <v>0.2854692366713805</v>
+        <v>0.2607425041683241</v>
       </c>
       <c r="DY5" s="2" t="n">
-        <v>0.2743087539533856</v>
+        <v>0.2512177507924205</v>
       </c>
       <c r="DZ5" s="2" t="n">
-        <v>0.2725030897133037</v>
+        <v>0.250037980885567</v>
       </c>
       <c r="EA5" s="2" t="n">
-        <v>0.2632486463660895</v>
+        <v>0.2435269544204771</v>
       </c>
       <c r="EB5" s="2" t="n">
-        <v>0.2608115555016888</v>
+        <v>0.2435102338687638</v>
       </c>
       <c r="EC5" s="2" t="n">
-        <v>0.2541665348701087</v>
+        <v>0.2378170091378054</v>
       </c>
       <c r="ED5" s="2" t="n">
-        <v>0.2502650994296205</v>
+        <v>0.2356450565747274</v>
       </c>
       <c r="EE5" s="2" t="n">
-        <v>0.2477349456131799</v>
+        <v>0.2345119882619648</v>
       </c>
       <c r="EF5" s="2" t="n">
-        <v>0.2451277253763224</v>
+        <v>0.2321895662026749</v>
       </c>
       <c r="EG5" s="2" t="n">
-        <v>0.2425169163428973</v>
+        <v>0.23044125149641</v>
       </c>
       <c r="EH5" s="2" t="n">
-        <v>0.2292433107297185</v>
+        <v>0.2193531010428611</v>
       </c>
       <c r="EI5" s="2" t="n">
-        <v>0.2319092337743453</v>
+        <v>0.2234413583304506</v>
       </c>
       <c r="EJ5" s="2" t="n">
-        <v>0.2318546337167663</v>
+        <v>0.2249134092642984</v>
       </c>
       <c r="EK5" s="2" t="n">
-        <v>0.2338742155911956</v>
+        <v>0.226230955036825</v>
       </c>
       <c r="EL5" s="2" t="n">
-        <v>0.2925874516191936</v>
+        <v>0.2723343916456234</v>
       </c>
       <c r="EM5" s="2" t="n">
-        <v>0.2870731827051068</v>
+        <v>0.2699210938273897</v>
       </c>
       <c r="EN5" s="2" t="n">
-        <v>0.2815593967855013</v>
+        <v>0.2660836106989797</v>
       </c>
       <c r="EO5" s="2" t="n">
-        <v>0.2734711046043339</v>
+        <v>0.2597119977996157</v>
       </c>
       <c r="EP5" s="2" t="n">
-        <v>0.2762593046437332</v>
+        <v>0.2630928776995601</v>
       </c>
       <c r="EQ5" s="2" t="n">
-        <v>0.2643366562690392</v>
+        <v>0.2526568401930856</v>
       </c>
       <c r="ER5" s="2" t="n">
-        <v>0.2643898719718064</v>
+        <v>0.2525373815901484</v>
       </c>
       <c r="ES5" s="2" t="n">
-        <v>0.2568788170136811</v>
+        <v>0.2471849657337882</v>
       </c>
       <c r="ET5" s="2" t="n">
-        <v>0.2595221391684847</v>
+        <v>0.2499368167999882</v>
       </c>
       <c r="EU5" s="2" t="n">
-        <v>0.2581250318244726</v>
+        <v>0.2494577111508792</v>
       </c>
       <c r="EV5" s="2" t="n">
-        <v>0.2541128906385195</v>
+        <v>0.2460563739789914</v>
       </c>
       <c r="EW5" s="2" t="n">
-        <v>0.2529196928170652</v>
+        <v>0.2462683411468732</v>
       </c>
       <c r="EX5" s="2" t="n">
-        <v>0.2521601849825131</v>
+        <v>0.2464663579473089</v>
       </c>
       <c r="EY5" s="2" t="n">
-        <v>0.2642942184845484</v>
+        <v>0.258325298461267</v>
       </c>
       <c r="EZ5" s="2" t="n">
-        <v>0.2914812408254177</v>
+        <v>0.2815845460831079</v>
       </c>
       <c r="FA5" s="2" t="n">
-        <v>0.2916640517540773</v>
+        <v>0.2823287466541431</v>
       </c>
       <c r="FB5" s="2" t="n">
-        <v>0.2803648685635763</v>
+        <v>0.2719110797194232</v>
       </c>
       <c r="FC5" s="2" t="n">
-        <v>0.2823600649210441</v>
+        <v>0.274378682612782</v>
       </c>
       <c r="FD5" s="2" t="n">
-        <v>0.2724251188367681</v>
+        <v>0.2651010445282811</v>
       </c>
       <c r="FE5" s="2" t="n">
-        <v>0.2738289114589416</v>
+        <v>0.2666305588190741</v>
       </c>
       <c r="FF5" s="2" t="n">
-        <v>0.2733335593376363</v>
+        <v>0.2663164233750834</v>
       </c>
       <c r="FG5" s="2" t="n">
-        <v>0.2699519656827576</v>
+        <v>0.2631394522847676</v>
       </c>
       <c r="FH5" s="2" t="n">
-        <v>0.2655075838752552</v>
+        <v>0.2586945598658601</v>
       </c>
       <c r="FI5" s="2" t="n">
-        <v>0.2641129410556262</v>
+        <v>0.257462983559278</v>
       </c>
       <c r="FJ5" s="2" t="n">
-        <v>0.266122671910565</v>
+        <v>0.2598793490318824</v>
       </c>
       <c r="FK5" s="2" t="n">
-        <v>0.2671448538227782</v>
+        <v>0.2622928187262542</v>
       </c>
       <c r="FL5" s="2" t="n">
-        <v>0.2766262261092655</v>
+        <v>0.2722109472751125</v>
       </c>
       <c r="FM5" s="2" t="n">
-        <v>0.2869261013939687</v>
+        <v>0.2824825529807363</v>
       </c>
       <c r="FN5" s="2" t="n">
-        <v>0.294275916364831</v>
+        <v>0.2864834962400881</v>
       </c>
       <c r="FO5" s="2" t="n">
-        <v>0.2941860156476205</v>
+        <v>0.2869309391823952</v>
       </c>
       <c r="FP5" s="2" t="n">
-        <v>0.2858923741073708</v>
+        <v>0.279043418015501</v>
       </c>
       <c r="FQ5" s="2" t="n">
-        <v>0.2838823058562566</v>
+        <v>0.2770783065477312</v>
       </c>
       <c r="FR5" s="2" t="n">
-        <v>0.2897204732461156</v>
+        <v>0.2823765340968513</v>
       </c>
       <c r="FS5" s="2" t="n">
-        <v>0.2872568507205003</v>
+        <v>0.2800667221839669</v>
       </c>
       <c r="FT5" s="2" t="n">
-        <v>0.2876658549661023</v>
+        <v>0.2802382146137565</v>
       </c>
       <c r="FU5" s="2" t="n">
-        <v>0.2857868721184859</v>
+        <v>0.278317850683062</v>
       </c>
       <c r="FV5" s="2" t="n">
-        <v>0.2875603096633005</v>
+        <v>0.2801443567489359</v>
       </c>
       <c r="FW5" s="2" t="n">
-        <v>0.2880153203491831</v>
+        <v>0.2805260032810503</v>
       </c>
       <c r="FX5" s="2" t="n">
-        <v>0.286408755154985</v>
+        <v>0.2800476474224548</v>
       </c>
       <c r="FY5" s="2" t="n">
-        <v>0.2964740105642319</v>
+        <v>0.2910367372064669</v>
       </c>
       <c r="FZ5" s="2" t="n">
-        <v>0.3011191360983382</v>
+        <v>0.295364569811273</v>
       </c>
       <c r="GA5" s="2" t="n">
-        <v>0.3160008743540704</v>
+        <v>0.3102401582074164</v>
       </c>
       <c r="GB5" s="2" t="n">
-        <v>0.3126810899546291</v>
+        <v>0.301735441151345</v>
       </c>
       <c r="GC5" s="2" t="n">
-        <v>0.3136171155763156</v>
+        <v>0.3023202863850658</v>
       </c>
       <c r="GD5" s="2" t="n">
-        <v>0.3151085788724037</v>
+        <v>0.3034490459149729</v>
       </c>
       <c r="GE5" s="2" t="n">
-        <v>0.3152806467276619</v>
+        <v>0.3033480401993984</v>
       </c>
       <c r="GF5" s="2" t="n">
-        <v>0.3131586507566032</v>
+        <v>0.3015185494021778</v>
       </c>
       <c r="GG5" s="2" t="n">
-        <v>0.3113160570520139</v>
+        <v>0.2999433453149842</v>
       </c>
       <c r="GH5" s="2" t="n">
-        <v>0.3075355428724255</v>
+        <v>0.2963217338953946</v>
       </c>
       <c r="GI5" s="2" t="n">
-        <v>0.307328727218206</v>
+        <v>0.2973812012407822</v>
       </c>
       <c r="GJ5" s="2" t="n">
-        <v>0.3080859354830461</v>
+        <v>0.2976076896716847</v>
       </c>
       <c r="GK5" s="2" t="n">
-        <v>0.3121000972369862</v>
+        <v>0.301551498023396</v>
       </c>
       <c r="GL5" s="2" t="n">
-        <v>0.317496786985915</v>
+        <v>0.3086397379427297</v>
       </c>
       <c r="GM5" s="2" t="n">
-        <v>0.3230340969195616</v>
+        <v>0.3156938605655846</v>
       </c>
       <c r="GN5" s="2" t="n">
-        <v>0.3383502212872965</v>
+        <v>0.3307492671635385</v>
       </c>
       <c r="GO5" s="2" t="n">
-        <v>0.3471347548598563</v>
+        <v>0.3383421855996731</v>
       </c>
       <c r="GP5" s="2" t="n">
-        <v>0.3409936022911359</v>
+        <v>0.3303607141326175</v>
       </c>
       <c r="GQ5" s="2" t="n">
-        <v>0.3369676409934111</v>
+        <v>0.3279010288514003</v>
       </c>
       <c r="GR5" s="2" t="n">
-        <v>0.3363922483893025</v>
+        <v>0.3262949969576937</v>
       </c>
       <c r="GS5" s="2" t="n">
-        <v>0.3346213554100119</v>
+        <v>0.3248421319637478</v>
       </c>
       <c r="GT5" s="2" t="n">
-        <v>0.3363306869164795</v>
+        <v>0.3263015609491481</v>
       </c>
       <c r="GU5" s="2" t="n">
-        <v>0.3304876279689672</v>
+        <v>0.320734322464771</v>
       </c>
       <c r="GV5" s="2" t="n">
-        <v>0.3358493146083379</v>
+        <v>0.3257656418194166</v>
       </c>
       <c r="GW5" s="2" t="n">
-        <v>0.3305916623819818</v>
+        <v>0.3211294377851161</v>
       </c>
       <c r="GX5" s="2" t="n">
-        <v>0.3320146951077928</v>
+        <v>0.3221949286553005</v>
       </c>
       <c r="GY5" s="2" t="n">
-        <v>0.3323947323751902</v>
+        <v>0.3224860447002722</v>
       </c>
       <c r="GZ5" s="2" t="n">
-        <v>0.3448968896205935</v>
+        <v>0.3361640387133953</v>
       </c>
       <c r="HA5" s="2" t="n">
-        <v>0.3574955090422169</v>
+        <v>0.3491113133900451</v>
       </c>
       <c r="HB5" s="2" t="n">
-        <v>0.3704954683737793</v>
+        <v>0.3614443830974438</v>
       </c>
       <c r="HC5" s="2" t="n">
-        <v>0.3630314309261022</v>
+        <v>0.3561929379009344</v>
       </c>
       <c r="HD5" s="2" t="n">
-        <v>0.3539330460930176</v>
+        <v>0.3440329898285597</v>
       </c>
       <c r="HE5" s="2" t="n">
-        <v>0.3482720956681207</v>
+        <v>0.3396220933517582</v>
       </c>
       <c r="HF5" s="2" t="n">
-        <v>0.3502787819617373</v>
+        <v>0.3410790138183946</v>
       </c>
       <c r="HG5" s="2" t="n">
-        <v>0.3571339133028119</v>
+        <v>0.3472546173711731</v>
       </c>
       <c r="HH5" s="2" t="n">
-        <v>0.3565948764091383</v>
+        <v>0.3458091531192573</v>
       </c>
       <c r="HI5" s="2" t="n">
-        <v>0.3550766420685513</v>
+        <v>0.344019614435112</v>
       </c>
       <c r="HJ5" s="2" t="n">
-        <v>0.3581430163589681</v>
+        <v>0.3461679039823821</v>
       </c>
       <c r="HK5" s="2" t="n">
-        <v>0.3521618064149857</v>
+        <v>0.3399269596238001</v>
       </c>
       <c r="HL5" s="2" t="n">
-        <v>0.3545123275634271</v>
+        <v>0.3412811147479243</v>
       </c>
       <c r="HM5" s="2" t="n">
-        <v>0.3519626807996512</v>
+        <v>0.3380203598898551</v>
       </c>
       <c r="HN5" s="2" t="n">
-        <v>0.3745100960528517</v>
+        <v>0.3608950665959378</v>
       </c>
       <c r="HO5" s="2" t="n">
-        <v>0.3882660887336954</v>
+        <v>0.3751654607702078</v>
       </c>
       <c r="HP5" s="2" t="n">
-        <v>0.3648384575295314</v>
+        <v>0.3566637465093638</v>
       </c>
       <c r="HQ5" s="2" t="n">
-        <v>0.3509823729699</v>
+        <v>0.3461107301549802</v>
       </c>
       <c r="HR5" s="3" t="n">
         <v>55516</v>
@@ -4237,676 +4237,676 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.02745155853916547</v>
+        <v>0.02465972874242865</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.03665304051423278</v>
+        <v>0.0326854229758971</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.03884344757691236</v>
+        <v>0.03457040422082429</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.04045164952076807</v>
+        <v>0.03602373866936341</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.04092899847932346</v>
+        <v>0.03639474562848264</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.04014418274569535</v>
+        <v>0.03570113854477941</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.03953442324440385</v>
+        <v>0.03516346952467082</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.03920337704637089</v>
+        <v>0.03477719677462161</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.0394118084747705</v>
+        <v>0.03501519301314893</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.03867195375243752</v>
+        <v>0.03437637422922991</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.03751887175639997</v>
+        <v>0.03341276432522432</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.03605059198176141</v>
+        <v>0.0325966485019889</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0359505626852764</v>
+        <v>0.03253300780150088</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.03644087978021596</v>
+        <v>0.0331714189779512</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.05407050967428915</v>
+        <v>0.04957734496461432</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.06640871731221049</v>
+        <v>0.05989867413816186</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.06973094364663472</v>
+        <v>0.0621663506774458</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.07052287396433399</v>
+        <v>0.06307090356298523</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.07186404288404781</v>
+        <v>0.06412762302873026</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.06900875414317328</v>
+        <v>0.06192957260611728</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.06998912847214198</v>
+        <v>0.06272290888481855</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.06928032964675021</v>
+        <v>0.06235125375021787</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.06909157678445935</v>
+        <v>0.06174923228300738</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.06850357092681292</v>
+        <v>0.0613223216371018</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.06509884019492639</v>
+        <v>0.05844064336641372</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.06215213031766634</v>
+        <v>0.05645998996599382</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.06211273603694266</v>
+        <v>0.05628070635712815</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.06328011072446933</v>
+        <v>0.05775242195335122</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.08740977403247643</v>
+        <v>0.08057273989949218</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.1007525288851379</v>
+        <v>0.09113322484627059</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.1014030054478294</v>
+        <v>0.09048245760346763</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>0.1030690906798709</v>
+        <v>0.09245537864772137</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.1033055329913756</v>
+        <v>0.0926948905469356</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>0.102441181993449</v>
+        <v>0.09209657622846913</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.09894640283617129</v>
+        <v>0.08907610047231863</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>0.09764990304257082</v>
+        <v>0.08827450746105613</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.0984006032717193</v>
+        <v>0.08842726152066446</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>0.09491752237659636</v>
+        <v>0.08551118026054169</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.08969517634810054</v>
+        <v>0.08179647798468567</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>0.08742568211375687</v>
+        <v>0.08003408628321973</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>0.08987135384263599</v>
+        <v>0.08213932005482641</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.09039380135159009</v>
+        <v>0.08293369428595491</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.1180968932985778</v>
+        <v>0.1090438205802041</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>0.1277544257606091</v>
+        <v>0.114061979560068</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>0.1285612239692589</v>
+        <v>0.1146301311310228</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>0.1292755570866715</v>
+        <v>0.1163977418143136</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>0.1276334906374443</v>
+        <v>0.1143188531704976</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>0.1224712894272212</v>
+        <v>0.1104936109139729</v>
       </c>
       <c r="AX6" s="2" t="n">
-        <v>0.122907136791157</v>
+        <v>0.1109800746505893</v>
       </c>
       <c r="AY6" s="2" t="n">
-        <v>0.1215627930797204</v>
+        <v>0.1103156060454308</v>
       </c>
       <c r="AZ6" s="2" t="n">
-        <v>0.1204767388503235</v>
+        <v>0.1088572862392493</v>
       </c>
       <c r="BA6" s="2" t="n">
-        <v>0.1160696301314401</v>
+        <v>0.1054457927022223</v>
       </c>
       <c r="BB6" s="2" t="n">
-        <v>0.110454429950174</v>
+        <v>0.1011532169297089</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>0.1084603378710226</v>
+        <v>0.09971633084874007</v>
       </c>
       <c r="BD6" s="2" t="n">
-        <v>0.1070201282954205</v>
+        <v>0.09854486516435654</v>
       </c>
       <c r="BE6" s="2" t="n">
-        <v>0.1101092957920458</v>
+        <v>0.1016104515384959</v>
       </c>
       <c r="BF6" s="2" t="n">
-        <v>0.1488012365437875</v>
+        <v>0.13571721842769</v>
       </c>
       <c r="BG6" s="2" t="n">
-        <v>0.1527040255172091</v>
+        <v>0.1365464090608838</v>
       </c>
       <c r="BH6" s="2" t="n">
-        <v>0.1517839493506012</v>
+        <v>0.1360619999967635</v>
       </c>
       <c r="BI6" s="2" t="n">
-        <v>0.1484202077385736</v>
+        <v>0.1324672460595522</v>
       </c>
       <c r="BJ6" s="2" t="n">
-        <v>0.1482287134178639</v>
+        <v>0.1328423381217808</v>
       </c>
       <c r="BK6" s="2" t="n">
-        <v>0.1409361908176119</v>
+        <v>0.1271065140454581</v>
       </c>
       <c r="BL6" s="2" t="n">
-        <v>0.1399439220327282</v>
+        <v>0.1267666579791397</v>
       </c>
       <c r="BM6" s="2" t="n">
-        <v>0.1370068953664321</v>
+        <v>0.1244705514549557</v>
       </c>
       <c r="BN6" s="2" t="n">
-        <v>0.1353569438070244</v>
+        <v>0.1226012535806228</v>
       </c>
       <c r="BO6" s="2" t="n">
-        <v>0.1363452085442763</v>
+        <v>0.1239555815864415</v>
       </c>
       <c r="BP6" s="2" t="n">
-        <v>0.1267182434659481</v>
+        <v>0.116454188357691</v>
       </c>
       <c r="BQ6" s="2" t="n">
-        <v>0.1254926278185509</v>
+        <v>0.1160625119954795</v>
       </c>
       <c r="BR6" s="2" t="n">
-        <v>0.1248212256437407</v>
+        <v>0.1155752489918165</v>
       </c>
       <c r="BS6" s="2" t="n">
-        <v>0.1243328327763701</v>
+        <v>0.1156399282387332</v>
       </c>
       <c r="BT6" s="2" t="n">
-        <v>0.1886314311136212</v>
+        <v>0.1677161669037358</v>
       </c>
       <c r="BU6" s="2" t="n">
-        <v>0.187326780714245</v>
+        <v>0.1646937126989586</v>
       </c>
       <c r="BV6" s="2" t="n">
-        <v>0.1831975004401232</v>
+        <v>0.1612820720576738</v>
       </c>
       <c r="BW6" s="2" t="n">
-        <v>0.1827953551859542</v>
+        <v>0.1613779585885068</v>
       </c>
       <c r="BX6" s="2" t="n">
-        <v>0.178650432139737</v>
+        <v>0.1603620848658989</v>
       </c>
       <c r="BY6" s="2" t="n">
-        <v>0.1739674538601605</v>
+        <v>0.1567599949497363</v>
       </c>
       <c r="BZ6" s="2" t="n">
-        <v>0.169689905998522</v>
+        <v>0.1532624871754736</v>
       </c>
       <c r="CA6" s="2" t="n">
-        <v>0.1661694919838674</v>
+        <v>0.1505855467978144</v>
       </c>
       <c r="CB6" s="2" t="n">
-        <v>0.1635205799184663</v>
+        <v>0.1487886850660204</v>
       </c>
       <c r="CC6" s="2" t="n">
-        <v>0.1585970961602854</v>
+        <v>0.1450091444828071</v>
       </c>
       <c r="CD6" s="2" t="n">
-        <v>0.1537219644804803</v>
+        <v>0.1417783594355618</v>
       </c>
       <c r="CE6" s="2" t="n">
-        <v>0.1458154741176016</v>
+        <v>0.13573147124988</v>
       </c>
       <c r="CF6" s="2" t="n">
-        <v>0.1458310266287036</v>
+        <v>0.1360172004174925</v>
       </c>
       <c r="CG6" s="2" t="n">
-        <v>0.1490045090757505</v>
+        <v>0.1392437998099304</v>
       </c>
       <c r="CH6" s="2" t="n">
-        <v>0.2165591954268939</v>
+        <v>0.1922853460753299</v>
       </c>
       <c r="CI6" s="2" t="n">
-        <v>0.2165461487949553</v>
+        <v>0.1893760912468848</v>
       </c>
       <c r="CJ6" s="2" t="n">
-        <v>0.211829225898752</v>
+        <v>0.1877186221302472</v>
       </c>
       <c r="CK6" s="2" t="n">
-        <v>0.2063136797933341</v>
+        <v>0.1843505539072969</v>
       </c>
       <c r="CL6" s="2" t="n">
-        <v>0.2020237450534184</v>
+        <v>0.1812116432351318</v>
       </c>
       <c r="CM6" s="2" t="n">
-        <v>0.1940341561302825</v>
+        <v>0.1751523373319825</v>
       </c>
       <c r="CN6" s="2" t="n">
-        <v>0.1937453969638861</v>
+        <v>0.1760166644898258</v>
       </c>
       <c r="CO6" s="2" t="n">
-        <v>0.1867341869431538</v>
+        <v>0.1700506586290495</v>
       </c>
       <c r="CP6" s="2" t="n">
-        <v>0.1848559029212489</v>
+        <v>0.1687391375576475</v>
       </c>
       <c r="CQ6" s="2" t="n">
-        <v>0.1848477106329089</v>
+        <v>0.1696526759699043</v>
       </c>
       <c r="CR6" s="2" t="n">
-        <v>0.1696735450430247</v>
+        <v>0.1576992294385911</v>
       </c>
       <c r="CS6" s="2" t="n">
-        <v>0.1662171271562701</v>
+        <v>0.1557067461166601</v>
       </c>
       <c r="CT6" s="2" t="n">
-        <v>0.1657110699699742</v>
+        <v>0.1559608103497466</v>
       </c>
       <c r="CU6" s="2" t="n">
-        <v>0.1722459226396926</v>
+        <v>0.1620608080824047</v>
       </c>
       <c r="CV6" s="2" t="n">
-        <v>0.2538958912269272</v>
+        <v>0.2272429248653666</v>
       </c>
       <c r="CW6" s="2" t="n">
-        <v>0.2421600064261747</v>
+        <v>0.2149089370846601</v>
       </c>
       <c r="CX6" s="2" t="n">
-        <v>0.2397960266676514</v>
+        <v>0.2154799807467663</v>
       </c>
       <c r="CY6" s="2" t="n">
-        <v>0.2371865408474553</v>
+        <v>0.2144355917370857</v>
       </c>
       <c r="CZ6" s="2" t="n">
-        <v>0.2270431259683499</v>
+        <v>0.2057643289842483</v>
       </c>
       <c r="DA6" s="2" t="n">
-        <v>0.2227174254150921</v>
+        <v>0.2027031287929223</v>
       </c>
       <c r="DB6" s="2" t="n">
-        <v>0.2222036505767729</v>
+        <v>0.2035594166022024</v>
       </c>
       <c r="DC6" s="2" t="n">
-        <v>0.2163076730681272</v>
+        <v>0.1994340729207653</v>
       </c>
       <c r="DD6" s="2" t="n">
-        <v>0.2145318486583311</v>
+        <v>0.1994489352885627</v>
       </c>
       <c r="DE6" s="2" t="n">
-        <v>0.2082727094424506</v>
+        <v>0.1940043665223414</v>
       </c>
       <c r="DF6" s="2" t="n">
-        <v>0.2007166301113756</v>
+        <v>0.1887076525597961</v>
       </c>
       <c r="DG6" s="2" t="n">
-        <v>0.1972878831269435</v>
+        <v>0.1860900756320809</v>
       </c>
       <c r="DH6" s="2" t="n">
-        <v>0.1952836010340785</v>
+        <v>0.1852006795613532</v>
       </c>
       <c r="DI6" s="2" t="n">
-        <v>0.1974685426228242</v>
+        <v>0.1880654105916185</v>
       </c>
       <c r="DJ6" s="2" t="n">
-        <v>0.2715773135637776</v>
+        <v>0.2434629766359295</v>
       </c>
       <c r="DK6" s="2" t="n">
-        <v>0.2662890396045485</v>
+        <v>0.2412676286333882</v>
       </c>
       <c r="DL6" s="2" t="n">
-        <v>0.2572793160742705</v>
+        <v>0.2337438252687017</v>
       </c>
       <c r="DM6" s="2" t="n">
-        <v>0.2548405236493839</v>
+        <v>0.2323619949666982</v>
       </c>
       <c r="DN6" s="2" t="n">
-        <v>0.2466083034965497</v>
+        <v>0.2259615237868523</v>
       </c>
       <c r="DO6" s="2" t="n">
-        <v>0.2463607304067558</v>
+        <v>0.2273563631856322</v>
       </c>
       <c r="DP6" s="2" t="n">
-        <v>0.2386059641490411</v>
+        <v>0.2221935079430596</v>
       </c>
       <c r="DQ6" s="2" t="n">
-        <v>0.2318848272376301</v>
+        <v>0.2165407421668417</v>
       </c>
       <c r="DR6" s="2" t="n">
-        <v>0.2291412092082233</v>
+        <v>0.2154050239963012</v>
       </c>
       <c r="DS6" s="2" t="n">
-        <v>0.2251821468210133</v>
+        <v>0.212889272749764</v>
       </c>
       <c r="DT6" s="2" t="n">
-        <v>0.2196770432718753</v>
+        <v>0.2085611523353404</v>
       </c>
       <c r="DU6" s="2" t="n">
-        <v>0.2168704782558797</v>
+        <v>0.2073969536974061</v>
       </c>
       <c r="DV6" s="2" t="n">
-        <v>0.2191820454322046</v>
+        <v>0.2099623164103069</v>
       </c>
       <c r="DW6" s="2" t="n">
-        <v>0.2209411517283966</v>
+        <v>0.2124227288823131</v>
       </c>
       <c r="DX6" s="2" t="n">
-        <v>0.2862652641443542</v>
+        <v>0.2614365627165854</v>
       </c>
       <c r="DY6" s="2" t="n">
-        <v>0.2750860944787793</v>
+        <v>0.2518544106650048</v>
       </c>
       <c r="DZ6" s="2" t="n">
-        <v>0.2732333698442222</v>
+        <v>0.2506921813872607</v>
       </c>
       <c r="EA6" s="2" t="n">
-        <v>0.2638702121528728</v>
+        <v>0.2440489359928172</v>
       </c>
       <c r="EB6" s="2" t="n">
-        <v>0.2613706767260476</v>
+        <v>0.2440471125501197</v>
       </c>
       <c r="EC6" s="2" t="n">
-        <v>0.2547124203241237</v>
+        <v>0.2383341780612246</v>
       </c>
       <c r="ED6" s="2" t="n">
-        <v>0.2507490186399796</v>
+        <v>0.2361572863182253</v>
       </c>
       <c r="EE6" s="2" t="n">
-        <v>0.2481706994637112</v>
+        <v>0.2350237040428359</v>
       </c>
       <c r="EF6" s="2" t="n">
-        <v>0.2455575204506234</v>
+        <v>0.2326543330977315</v>
       </c>
       <c r="EG6" s="2" t="n">
-        <v>0.2429138294271432</v>
+        <v>0.2308830702360798</v>
       </c>
       <c r="EH6" s="2" t="n">
-        <v>0.2295446989272337</v>
+        <v>0.2197941175221972</v>
       </c>
       <c r="EI6" s="2" t="n">
-        <v>0.2321584310039082</v>
+        <v>0.2238542046785863</v>
       </c>
       <c r="EJ6" s="2" t="n">
-        <v>0.2320462961651176</v>
+        <v>0.2253173514213635</v>
       </c>
       <c r="EK6" s="2" t="n">
-        <v>0.2340951853567044</v>
+        <v>0.2266506798914492</v>
       </c>
       <c r="EL6" s="2" t="n">
-        <v>0.2932265573987968</v>
+        <v>0.2729217576465358</v>
       </c>
       <c r="EM6" s="2" t="n">
-        <v>0.2876304850896542</v>
+        <v>0.2705179505093288</v>
       </c>
       <c r="EN6" s="2" t="n">
-        <v>0.2820863409403198</v>
+        <v>0.2666704640474142</v>
       </c>
       <c r="EO6" s="2" t="n">
-        <v>0.2739283948532283</v>
+        <v>0.2602556554781396</v>
       </c>
       <c r="EP6" s="2" t="n">
-        <v>0.2767008339767382</v>
+        <v>0.2636069944008462</v>
       </c>
       <c r="EQ6" s="2" t="n">
-        <v>0.264725080953584</v>
+        <v>0.2531431851786541</v>
       </c>
       <c r="ER6" s="2" t="n">
-        <v>0.2647607259318448</v>
+        <v>0.2530619936788863</v>
       </c>
       <c r="ES6" s="2" t="n">
-        <v>0.2571679472415447</v>
+        <v>0.2476938672756072</v>
       </c>
       <c r="ET6" s="2" t="n">
-        <v>0.2598235513768676</v>
+        <v>0.2504125842095979</v>
       </c>
       <c r="EU6" s="2" t="n">
-        <v>0.2583759735011442</v>
+        <v>0.2499045628933363</v>
       </c>
       <c r="EV6" s="2" t="n">
-        <v>0.2543511253950534</v>
+        <v>0.2465071170568384</v>
       </c>
       <c r="EW6" s="2" t="n">
-        <v>0.2531066237464166</v>
+        <v>0.2467020324275555</v>
       </c>
       <c r="EX6" s="2" t="n">
-        <v>0.2523084533971559</v>
+        <v>0.2468851549435475</v>
       </c>
       <c r="EY6" s="2" t="n">
-        <v>0.2644234293450574</v>
+        <v>0.2587971324202818</v>
       </c>
       <c r="EZ6" s="2" t="n">
-        <v>0.2917835660399486</v>
+        <v>0.2820461603041231</v>
       </c>
       <c r="FA6" s="2" t="n">
-        <v>0.291947755645351</v>
+        <v>0.2828123288775305</v>
       </c>
       <c r="FB6" s="2" t="n">
-        <v>0.280628726859998</v>
+        <v>0.2723823617574765</v>
       </c>
       <c r="FC6" s="2" t="n">
-        <v>0.2826138765930554</v>
+        <v>0.2748651196937158</v>
       </c>
       <c r="FD6" s="2" t="n">
-        <v>0.2726445743138994</v>
+        <v>0.2655718986432857</v>
       </c>
       <c r="FE6" s="2" t="n">
-        <v>0.274040472858233</v>
+        <v>0.2671060153230271</v>
       </c>
       <c r="FF6" s="2" t="n">
-        <v>0.2735384244436608</v>
+        <v>0.2667953310166311</v>
       </c>
       <c r="FG6" s="2" t="n">
-        <v>0.2701541548767137</v>
+        <v>0.2636140860787877</v>
       </c>
       <c r="FH6" s="2" t="n">
-        <v>0.2656908613102458</v>
+        <v>0.2591576215683226</v>
       </c>
       <c r="FI6" s="2" t="n">
-        <v>0.2643082549767772</v>
+        <v>0.2579189864901172</v>
       </c>
       <c r="FJ6" s="2" t="n">
-        <v>0.2662951862930513</v>
+        <v>0.2603367404078227</v>
       </c>
       <c r="FK6" s="2" t="n">
-        <v>0.2672584523518037</v>
+        <v>0.2627242119583887</v>
       </c>
       <c r="FL6" s="2" t="n">
-        <v>0.276714162962894</v>
+        <v>0.2726792285878152</v>
       </c>
       <c r="FM6" s="2" t="n">
-        <v>0.2870027625413867</v>
+        <v>0.2829737909614681</v>
       </c>
       <c r="FN6" s="2" t="n">
-        <v>0.2944945235774706</v>
+        <v>0.2870521279932318</v>
       </c>
       <c r="FO6" s="2" t="n">
-        <v>0.2943889963665751</v>
+        <v>0.2874765219892372</v>
       </c>
       <c r="FP6" s="2" t="n">
-        <v>0.2860793779096982</v>
+        <v>0.2795623133077864</v>
       </c>
       <c r="FQ6" s="2" t="n">
-        <v>0.2840731220009712</v>
+        <v>0.2776086818771514</v>
       </c>
       <c r="FR6" s="2" t="n">
-        <v>0.2899237132199288</v>
+        <v>0.2829090414477615</v>
       </c>
       <c r="FS6" s="2" t="n">
-        <v>0.2874475232229649</v>
+        <v>0.2806033884570276</v>
       </c>
       <c r="FT6" s="2" t="n">
-        <v>0.2878652014715119</v>
+        <v>0.280771960091193</v>
       </c>
       <c r="FU6" s="2" t="n">
-        <v>0.2859844767549893</v>
+        <v>0.2788519734476922</v>
       </c>
       <c r="FV6" s="2" t="n">
-        <v>0.2877487102249942</v>
+        <v>0.2806858455017698</v>
       </c>
       <c r="FW6" s="2" t="n">
-        <v>0.2882051735300556</v>
+        <v>0.2810698586990852</v>
       </c>
       <c r="FX6" s="2" t="n">
-        <v>0.2865493365150136</v>
+        <v>0.2805744342503527</v>
       </c>
       <c r="FY6" s="2" t="n">
-        <v>0.296559421084323</v>
+        <v>0.2915597527354141</v>
       </c>
       <c r="FZ6" s="2" t="n">
-        <v>0.3012302435059511</v>
+        <v>0.2959246605949596</v>
       </c>
       <c r="GA6" s="2" t="n">
-        <v>0.3160873699376867</v>
+        <v>0.3108170140819043</v>
       </c>
       <c r="GB6" s="2" t="n">
-        <v>0.3130094795527119</v>
+        <v>0.3023914782725107</v>
       </c>
       <c r="GC6" s="2" t="n">
-        <v>0.3139314503305454</v>
+        <v>0.3029899036498551</v>
       </c>
       <c r="GD6" s="2" t="n">
-        <v>0.3154562731748859</v>
+        <v>0.3041304754594026</v>
       </c>
       <c r="GE6" s="2" t="n">
-        <v>0.3156114846422848</v>
+        <v>0.3040375513909491</v>
       </c>
       <c r="GF6" s="2" t="n">
-        <v>0.3134936112047689</v>
+        <v>0.3021941065205371</v>
       </c>
       <c r="GG6" s="2" t="n">
-        <v>0.3116224049992326</v>
+        <v>0.3006129739198332</v>
       </c>
       <c r="GH6" s="2" t="n">
-        <v>0.3078440640333564</v>
+        <v>0.2969641059169466</v>
       </c>
       <c r="GI6" s="2" t="n">
-        <v>0.3075806063569034</v>
+        <v>0.298010816458796</v>
       </c>
       <c r="GJ6" s="2" t="n">
-        <v>0.3083831724651918</v>
+        <v>0.2982737890005199</v>
       </c>
       <c r="GK6" s="2" t="n">
-        <v>0.3123614876732972</v>
+        <v>0.3022297727496592</v>
       </c>
       <c r="GL6" s="2" t="n">
-        <v>0.3177092596604665</v>
+        <v>0.3093100923168329</v>
       </c>
       <c r="GM6" s="2" t="n">
-        <v>0.3231675664693608</v>
+        <v>0.3163609669952537</v>
       </c>
       <c r="GN6" s="2" t="n">
-        <v>0.3384800862312382</v>
+        <v>0.331470501691812</v>
       </c>
       <c r="GO6" s="2" t="n">
-        <v>0.3473176668758976</v>
+        <v>0.3391042119316938</v>
       </c>
       <c r="GP6" s="2" t="n">
-        <v>0.3412590378522819</v>
+        <v>0.3310791987553278</v>
       </c>
       <c r="GQ6" s="2" t="n">
-        <v>0.3371765950639227</v>
+        <v>0.3285978606737484</v>
       </c>
       <c r="GR6" s="2" t="n">
-        <v>0.3366725424992589</v>
+        <v>0.3269668075994426</v>
       </c>
       <c r="GS6" s="2" t="n">
-        <v>0.3348810920554605</v>
+        <v>0.3255313892054343</v>
       </c>
       <c r="GT6" s="2" t="n">
-        <v>0.3365696939617934</v>
+        <v>0.327008563663761</v>
       </c>
       <c r="GU6" s="2" t="n">
-        <v>0.3307282579914845</v>
+        <v>0.321443026343523</v>
       </c>
       <c r="GV6" s="2" t="n">
-        <v>0.3360993129126125</v>
+        <v>0.3265067610253437</v>
       </c>
       <c r="GW6" s="2" t="n">
-        <v>0.3308208056300745</v>
+        <v>0.3218803696689006</v>
       </c>
       <c r="GX6" s="2" t="n">
-        <v>0.3322353176957741</v>
+        <v>0.3229712131881406</v>
       </c>
       <c r="GY6" s="2" t="n">
-        <v>0.3326289823251593</v>
+        <v>0.323277049475505</v>
       </c>
       <c r="GZ6" s="2" t="n">
-        <v>0.3450667030325641</v>
+        <v>0.3369915928524569</v>
       </c>
       <c r="HA6" s="2" t="n">
-        <v>0.3576760872488509</v>
+        <v>0.3498816320218394</v>
       </c>
       <c r="HB6" s="2" t="n">
-        <v>0.3707082865101068</v>
+        <v>0.3623362604469512</v>
       </c>
       <c r="HC6" s="2" t="n">
-        <v>0.3631589009740513</v>
+        <v>0.3569051025866446</v>
       </c>
       <c r="HD6" s="2" t="n">
-        <v>0.3541222528135967</v>
+        <v>0.3451051253403682</v>
       </c>
       <c r="HE6" s="2" t="n">
-        <v>0.3484477150407059</v>
+        <v>0.3406782030690882</v>
       </c>
       <c r="HF6" s="2" t="n">
-        <v>0.3504521010710586</v>
+        <v>0.3421117691405554</v>
       </c>
       <c r="HG6" s="2" t="n">
-        <v>0.3573654471585775</v>
+        <v>0.3483096904179104</v>
       </c>
       <c r="HH6" s="2" t="n">
-        <v>0.3568528968335061</v>
+        <v>0.346894009205895</v>
       </c>
       <c r="HI6" s="2" t="n">
-        <v>0.3553465019381557</v>
+        <v>0.3451217803249764</v>
       </c>
       <c r="HJ6" s="2" t="n">
-        <v>0.3584701646404556</v>
+        <v>0.3472927088632275</v>
       </c>
       <c r="HK6" s="2" t="n">
-        <v>0.3524576816386569</v>
+        <v>0.3410471299303582</v>
       </c>
       <c r="HL6" s="2" t="n">
-        <v>0.3548584986749987</v>
+        <v>0.3424057307271871</v>
       </c>
       <c r="HM6" s="2" t="n">
-        <v>0.3523229030354063</v>
+        <v>0.3391319858783918</v>
       </c>
       <c r="HN6" s="2" t="n">
-        <v>0.3748747553728263</v>
+        <v>0.3620916369570475</v>
       </c>
       <c r="HO6" s="2" t="n">
-        <v>0.3886573532266862</v>
+        <v>0.3764046065501475</v>
       </c>
       <c r="HP6" s="2" t="n">
-        <v>0.3650665704828405</v>
+        <v>0.3576167976123774</v>
       </c>
       <c r="HQ6" s="2" t="n">
-        <v>0.3510723934262271</v>
+        <v>0.3468276889196563</v>
       </c>
       <c r="HR6" s="3" t="n">
         <v>55517</v>
@@ -4919,676 +4919,676 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.02774868529858915</v>
+        <v>0.02449445308845433</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.03706858414221835</v>
+        <v>0.03270312941027158</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03923967744080891</v>
+        <v>0.03459710423952335</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.04080106667298792</v>
+        <v>0.03602779954779053</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.04124109773907146</v>
+        <v>0.03638992650837671</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.04040929788102485</v>
+        <v>0.03567704074575098</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.03975231651599546</v>
+        <v>0.03510891982387018</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.03940691209381411</v>
+        <v>0.03471402689450438</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.03959764859226163</v>
+        <v>0.03494141288631544</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.03883222146582463</v>
+        <v>0.03429553631705093</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.03764021019885626</v>
+        <v>0.03332057856688236</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03615333772713153</v>
+        <v>0.03250951153988471</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.03604349895844317</v>
+        <v>0.03244281934103302</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.03652492094785268</v>
+        <v>0.03307570988723244</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.05466520420047163</v>
+        <v>0.04950690504869382</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.06708880337218587</v>
+        <v>0.05998411153675752</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.07034705956331415</v>
+        <v>0.06221616716201543</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.07102858399050382</v>
+        <v>0.06307205551138713</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.07232679181334144</v>
+        <v>0.06410476501847034</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.0693969830664718</v>
+        <v>0.06188753701696136</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.07032717093884978</v>
+        <v>0.0626404008673801</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.06956455460090086</v>
+        <v>0.06225197844080396</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.06934365520708324</v>
+        <v>0.06162472945474673</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.06873105381604888</v>
+        <v>0.06119752359893048</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.06526440964399249</v>
+        <v>0.05829553425462915</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.0622941161609277</v>
+        <v>0.0563257415168071</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0.06224727060606242</v>
+        <v>0.05613718206116025</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0.0634090920245507</v>
+        <v>0.05761434283114246</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>0.08833032114629605</v>
+        <v>0.08073446683984757</v>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>0.1016314837810219</v>
+        <v>0.09130190749561301</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.1021663149258168</v>
+        <v>0.09056388441363356</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>0.1036738347241042</v>
+        <v>0.09246240895485303</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.1038319455151595</v>
+        <v>0.09264631924799829</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>0.1028942928156211</v>
+        <v>0.09201230481647152</v>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>0.09931936867267857</v>
+        <v>0.08895693455245382</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>0.09796036499777452</v>
+        <v>0.0881381160757462</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>0.09868066136113267</v>
+        <v>0.08826195656283112</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>0.09516766642027261</v>
+        <v>0.08535338116275272</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.08989459472025513</v>
+        <v>0.08163944413555752</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>0.08757990458523104</v>
+        <v>0.07986572691774194</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>0.09002822504987396</v>
+        <v>0.08195781954495443</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>0.09052212565281284</v>
+        <v>0.08274550747460682</v>
       </c>
       <c r="AR7" s="2" t="n">
-        <v>0.1192185996016098</v>
+        <v>0.1093433579020484</v>
       </c>
       <c r="AS7" s="2" t="n">
-        <v>0.1286901983752583</v>
+        <v>0.114180642529498</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>0.1293178072045435</v>
+        <v>0.114645309196395</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>0.1298683838839711</v>
+        <v>0.1163518099023275</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>0.1282129362855016</v>
+        <v>0.1142250680146014</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>0.1229168835138957</v>
+        <v>0.1103533594072593</v>
       </c>
       <c r="AX7" s="2" t="n">
-        <v>0.1232931446407013</v>
+        <v>0.1108201245391117</v>
       </c>
       <c r="AY7" s="2" t="n">
-        <v>0.1219034443565937</v>
+        <v>0.1101420855468483</v>
       </c>
       <c r="AZ7" s="2" t="n">
-        <v>0.1207772449335197</v>
+        <v>0.1086541925076303</v>
       </c>
       <c r="BA7" s="2" t="n">
-        <v>0.1163338615930314</v>
+        <v>0.1052583854569388</v>
       </c>
       <c r="BB7" s="2" t="n">
-        <v>0.1106532413444511</v>
+        <v>0.1009711125996453</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>0.1086326652583361</v>
+        <v>0.09952508505829075</v>
       </c>
       <c r="BD7" s="2" t="n">
-        <v>0.1071879979141862</v>
+        <v>0.09835083575265108</v>
       </c>
       <c r="BE7" s="2" t="n">
-        <v>0.1102484095308607</v>
+        <v>0.1013991308007161</v>
       </c>
       <c r="BF7" s="2" t="n">
-        <v>0.1499403918368058</v>
+        <v>0.1360156970330575</v>
       </c>
       <c r="BG7" s="2" t="n">
-        <v>0.1536246905659255</v>
+        <v>0.1366263241259262</v>
       </c>
       <c r="BH7" s="2" t="n">
-        <v>0.1525111904105228</v>
+        <v>0.1360195433774195</v>
       </c>
       <c r="BI7" s="2" t="n">
-        <v>0.1489723994280716</v>
+        <v>0.1323150548940056</v>
       </c>
       <c r="BJ7" s="2" t="n">
-        <v>0.1487535873139386</v>
+        <v>0.1326863063455777</v>
       </c>
       <c r="BK7" s="2" t="n">
-        <v>0.1413743642258422</v>
+        <v>0.1269210446781752</v>
       </c>
       <c r="BL7" s="2" t="n">
-        <v>0.1402895234554626</v>
+        <v>0.1265573414042149</v>
       </c>
       <c r="BM7" s="2" t="n">
-        <v>0.1373262551713782</v>
+        <v>0.1242626765447324</v>
       </c>
       <c r="BN7" s="2" t="n">
-        <v>0.1356371188282553</v>
+        <v>0.1223599094778469</v>
       </c>
       <c r="BO7" s="2" t="n">
-        <v>0.1365826057691923</v>
+        <v>0.123713648285656</v>
       </c>
       <c r="BP7" s="2" t="n">
-        <v>0.1269059000333718</v>
+        <v>0.1162345376931615</v>
       </c>
       <c r="BQ7" s="2" t="n">
-        <v>0.1256606186158598</v>
+        <v>0.1158605251525022</v>
       </c>
       <c r="BR7" s="2" t="n">
-        <v>0.1249884717402715</v>
+        <v>0.1153629619181437</v>
       </c>
       <c r="BS7" s="2" t="n">
-        <v>0.1244774832375033</v>
+        <v>0.1154200231449666</v>
       </c>
       <c r="BT7" s="2" t="n">
-        <v>0.1898637997963246</v>
+        <v>0.1678681431940698</v>
       </c>
       <c r="BU7" s="2" t="n">
-        <v>0.1882846202281239</v>
+        <v>0.164683514891486</v>
       </c>
       <c r="BV7" s="2" t="n">
-        <v>0.1839579192442772</v>
+        <v>0.1610877233325999</v>
       </c>
       <c r="BW7" s="2" t="n">
-        <v>0.1833286906362175</v>
+        <v>0.161062682376336</v>
       </c>
       <c r="BX7" s="2" t="n">
-        <v>0.1791608936041482</v>
+        <v>0.1601198276486625</v>
       </c>
       <c r="BY7" s="2" t="n">
-        <v>0.17443855303158</v>
+        <v>0.1565101988936578</v>
       </c>
       <c r="BZ7" s="2" t="n">
-        <v>0.1700448137671763</v>
+        <v>0.152943977678155</v>
       </c>
       <c r="CA7" s="2" t="n">
-        <v>0.1664938738544016</v>
+        <v>0.1502927071764088</v>
       </c>
       <c r="CB7" s="2" t="n">
-        <v>0.1638104810439567</v>
+        <v>0.14850712214869</v>
       </c>
       <c r="CC7" s="2" t="n">
-        <v>0.1588517887607426</v>
+        <v>0.1447348114820255</v>
       </c>
       <c r="CD7" s="2" t="n">
-        <v>0.1539193847667325</v>
+        <v>0.1415233678487686</v>
       </c>
       <c r="CE7" s="2" t="n">
-        <v>0.14599041672313</v>
+        <v>0.1354966488271821</v>
       </c>
       <c r="CF7" s="2" t="n">
-        <v>0.1459889579724332</v>
+        <v>0.1357712976441596</v>
       </c>
       <c r="CG7" s="2" t="n">
-        <v>0.1491624565426132</v>
+        <v>0.1390032222172208</v>
       </c>
       <c r="CH7" s="2" t="n">
-        <v>0.2174944766188232</v>
+        <v>0.1921766470744787</v>
       </c>
       <c r="CI7" s="2" t="n">
-        <v>0.2173003694487592</v>
+        <v>0.1890700159418056</v>
       </c>
       <c r="CJ7" s="2" t="n">
-        <v>0.2124671542770633</v>
+        <v>0.1873709081894233</v>
       </c>
       <c r="CK7" s="2" t="n">
-        <v>0.206804200636263</v>
+        <v>0.1839765828354895</v>
       </c>
       <c r="CL7" s="2" t="n">
-        <v>0.2024765855207157</v>
+        <v>0.1808289522312334</v>
       </c>
       <c r="CM7" s="2" t="n">
-        <v>0.1944416290139783</v>
+        <v>0.1748041204063898</v>
       </c>
       <c r="CN7" s="2" t="n">
-        <v>0.1940944300109661</v>
+        <v>0.1756765438527378</v>
       </c>
       <c r="CO7" s="2" t="n">
-        <v>0.1870256889718327</v>
+        <v>0.1697071918012722</v>
       </c>
       <c r="CP7" s="2" t="n">
-        <v>0.1851031832889218</v>
+        <v>0.1683790888229312</v>
       </c>
       <c r="CQ7" s="2" t="n">
-        <v>0.1850651514911606</v>
+        <v>0.169298444489897</v>
       </c>
       <c r="CR7" s="2" t="n">
-        <v>0.1698846427628381</v>
+        <v>0.1574554713286367</v>
       </c>
       <c r="CS7" s="2" t="n">
-        <v>0.1663918174670134</v>
+        <v>0.155460123035266</v>
       </c>
       <c r="CT7" s="2" t="n">
-        <v>0.1658704884981584</v>
+        <v>0.1557183435520893</v>
       </c>
       <c r="CU7" s="2" t="n">
-        <v>0.1724106586553318</v>
+        <v>0.1617878553903167</v>
       </c>
       <c r="CV7" s="2" t="n">
-        <v>0.2544712885907955</v>
+        <v>0.2267766508133615</v>
       </c>
       <c r="CW7" s="2" t="n">
-        <v>0.2426910266197804</v>
+        <v>0.2143586463056794</v>
       </c>
       <c r="CX7" s="2" t="n">
-        <v>0.2402912383143868</v>
+        <v>0.215041976232226</v>
       </c>
       <c r="CY7" s="2" t="n">
-        <v>0.2376534242692599</v>
+        <v>0.2140187556439629</v>
       </c>
       <c r="CZ7" s="2" t="n">
-        <v>0.2274107613359461</v>
+        <v>0.2053105269944409</v>
       </c>
       <c r="DA7" s="2" t="n">
-        <v>0.2230460986521017</v>
+        <v>0.2022549784252471</v>
       </c>
       <c r="DB7" s="2" t="n">
-        <v>0.2224953379351624</v>
+        <v>0.2031274398458867</v>
       </c>
       <c r="DC7" s="2" t="n">
-        <v>0.2165465567409935</v>
+        <v>0.1990306848251873</v>
       </c>
       <c r="DD7" s="2" t="n">
-        <v>0.2148107048863558</v>
+        <v>0.1991226972065236</v>
       </c>
       <c r="DE7" s="2" t="n">
-        <v>0.2085297186707203</v>
+        <v>0.1937110533990266</v>
       </c>
       <c r="DF7" s="2" t="n">
-        <v>0.2009326739898174</v>
+        <v>0.1884628685553483</v>
       </c>
       <c r="DG7" s="2" t="n">
-        <v>0.1974459007542008</v>
+        <v>0.1858020424519617</v>
       </c>
       <c r="DH7" s="2" t="n">
-        <v>0.1954274428181453</v>
+        <v>0.1849396296432057</v>
       </c>
       <c r="DI7" s="2" t="n">
-        <v>0.1975970363398431</v>
+        <v>0.187788273652981</v>
       </c>
       <c r="DJ7" s="2" t="n">
-        <v>0.2721556429966828</v>
+        <v>0.2429320839451695</v>
       </c>
       <c r="DK7" s="2" t="n">
-        <v>0.2668118736110693</v>
+        <v>0.2407913267031758</v>
       </c>
       <c r="DL7" s="2" t="n">
-        <v>0.2576724507217213</v>
+        <v>0.2332095104297376</v>
       </c>
       <c r="DM7" s="2" t="n">
-        <v>0.2552290131231584</v>
+        <v>0.2318703765063083</v>
       </c>
       <c r="DN7" s="2" t="n">
-        <v>0.2469393917572549</v>
+        <v>0.2254979146518237</v>
       </c>
       <c r="DO7" s="2" t="n">
-        <v>0.2466072557162966</v>
+        <v>0.2269000703473463</v>
       </c>
       <c r="DP7" s="2" t="n">
-        <v>0.2388881988414464</v>
+        <v>0.2218215870688779</v>
       </c>
       <c r="DQ7" s="2" t="n">
-        <v>0.2321224672533488</v>
+        <v>0.2161935485981045</v>
       </c>
       <c r="DR7" s="2" t="n">
-        <v>0.229402922681588</v>
+        <v>0.2151128977537654</v>
       </c>
       <c r="DS7" s="2" t="n">
-        <v>0.2254297740571872</v>
+        <v>0.212625499446637</v>
       </c>
       <c r="DT7" s="2" t="n">
-        <v>0.2198636789137853</v>
+        <v>0.2082977269134099</v>
       </c>
       <c r="DU7" s="2" t="n">
-        <v>0.2170064758750033</v>
+        <v>0.2071698101352667</v>
       </c>
       <c r="DV7" s="2" t="n">
-        <v>0.2193228344824915</v>
+        <v>0.2097109707386144</v>
       </c>
       <c r="DW7" s="2" t="n">
-        <v>0.2210264369901112</v>
+        <v>0.2121325634216716</v>
       </c>
       <c r="DX7" s="2" t="n">
-        <v>0.2867179124305919</v>
+        <v>0.2608872297636141</v>
       </c>
       <c r="DY7" s="2" t="n">
-        <v>0.2755071474327466</v>
+        <v>0.251338632451316</v>
       </c>
       <c r="DZ7" s="2" t="n">
-        <v>0.2736256675135278</v>
+        <v>0.250207126158002</v>
       </c>
       <c r="EA7" s="2" t="n">
-        <v>0.2641427710764508</v>
+        <v>0.24358374181137</v>
       </c>
       <c r="EB7" s="2" t="n">
-        <v>0.2616601635631975</v>
+        <v>0.2436520408054142</v>
       </c>
       <c r="EC7" s="2" t="n">
-        <v>0.2549971382908907</v>
+        <v>0.2379716761160973</v>
       </c>
       <c r="ED7" s="2" t="n">
-        <v>0.2510234229370035</v>
+        <v>0.2358317657293448</v>
       </c>
       <c r="EE7" s="2" t="n">
-        <v>0.2484384430921236</v>
+        <v>0.2347366136959658</v>
       </c>
       <c r="EF7" s="2" t="n">
-        <v>0.2457981846046542</v>
+        <v>0.232385383880004</v>
       </c>
       <c r="EG7" s="2" t="n">
-        <v>0.2431261076524855</v>
+        <v>0.2306055150017256</v>
       </c>
       <c r="EH7" s="2" t="n">
-        <v>0.2296967359806278</v>
+        <v>0.2195046213458646</v>
       </c>
       <c r="EI7" s="2" t="n">
-        <v>0.2322855929834284</v>
+        <v>0.2235798989787709</v>
       </c>
       <c r="EJ7" s="2" t="n">
-        <v>0.232135204900722</v>
+        <v>0.2250603884064054</v>
       </c>
       <c r="EK7" s="2" t="n">
-        <v>0.2341929391201173</v>
+        <v>0.2263846218800389</v>
       </c>
       <c r="EL7" s="2" t="n">
-        <v>0.293509897387189</v>
+        <v>0.2724311767721691</v>
       </c>
       <c r="EM7" s="2" t="n">
-        <v>0.2879245961544594</v>
+        <v>0.2701182838976527</v>
       </c>
       <c r="EN7" s="2" t="n">
-        <v>0.2824125335176171</v>
+        <v>0.2663427903115013</v>
       </c>
       <c r="EO7" s="2" t="n">
-        <v>0.2742090486048459</v>
+        <v>0.2599655838327309</v>
       </c>
       <c r="EP7" s="2" t="n">
-        <v>0.2769653817525183</v>
+        <v>0.2633183422438437</v>
       </c>
       <c r="EQ7" s="2" t="n">
-        <v>0.2649632619136599</v>
+        <v>0.2528788319197612</v>
       </c>
       <c r="ER7" s="2" t="n">
-        <v>0.2650130287965681</v>
+        <v>0.2527668174335819</v>
       </c>
       <c r="ES7" s="2" t="n">
-        <v>0.2573712211232553</v>
+        <v>0.2474034292960579</v>
       </c>
       <c r="ET7" s="2" t="n">
-        <v>0.2600430533895086</v>
+        <v>0.2501632086110252</v>
       </c>
       <c r="EU7" s="2" t="n">
-        <v>0.2585332799883369</v>
+        <v>0.2496472685694767</v>
       </c>
       <c r="EV7" s="2" t="n">
-        <v>0.2545031674524674</v>
+        <v>0.2462737691906518</v>
       </c>
       <c r="EW7" s="2" t="n">
-        <v>0.2532371371984974</v>
+        <v>0.2464999900429339</v>
       </c>
       <c r="EX7" s="2" t="n">
-        <v>0.2523995415679982</v>
+        <v>0.2466676212409521</v>
       </c>
       <c r="EY7" s="2" t="n">
-        <v>0.2645042250696923</v>
+        <v>0.2584930205077526</v>
       </c>
       <c r="EZ7" s="2" t="n">
-        <v>0.2919700162034036</v>
+        <v>0.2817965735601744</v>
       </c>
       <c r="FA7" s="2" t="n">
-        <v>0.2921515578198092</v>
+        <v>0.282563818933172</v>
       </c>
       <c r="FB7" s="2" t="n">
-        <v>0.2808441560701654</v>
+        <v>0.2721803016572262</v>
       </c>
       <c r="FC7" s="2" t="n">
-        <v>0.2828428260927162</v>
+        <v>0.2746802272603784</v>
       </c>
       <c r="FD7" s="2" t="n">
-        <v>0.272847542487212</v>
+        <v>0.2653878314779949</v>
       </c>
       <c r="FE7" s="2" t="n">
-        <v>0.2742308357645096</v>
+        <v>0.266914892361489</v>
       </c>
       <c r="FF7" s="2" t="n">
-        <v>0.2737395900569053</v>
+        <v>0.2666197931290547</v>
       </c>
       <c r="FG7" s="2" t="n">
-        <v>0.2703443011369833</v>
+        <v>0.2634255867723443</v>
       </c>
       <c r="FH7" s="2" t="n">
-        <v>0.2658603478654178</v>
+        <v>0.2589694240029073</v>
       </c>
       <c r="FI7" s="2" t="n">
-        <v>0.2644875395012305</v>
+        <v>0.2577258187486174</v>
       </c>
       <c r="FJ7" s="2" t="n">
-        <v>0.2664411141993849</v>
+        <v>0.2601202080585103</v>
       </c>
       <c r="FK7" s="2" t="n">
-        <v>0.2673497261108139</v>
+        <v>0.262507270396381</v>
       </c>
       <c r="FL7" s="2" t="n">
-        <v>0.2768045416715064</v>
+        <v>0.2724604747282856</v>
       </c>
       <c r="FM7" s="2" t="n">
-        <v>0.2870796074740671</v>
+        <v>0.2827384502551237</v>
       </c>
       <c r="FN7" s="2" t="n">
-        <v>0.2947378834192429</v>
+        <v>0.2868354126829968</v>
       </c>
       <c r="FO7" s="2" t="n">
-        <v>0.2946107387413393</v>
+        <v>0.2872633650263504</v>
       </c>
       <c r="FP7" s="2" t="n">
-        <v>0.2862744109015577</v>
+        <v>0.2793457577790693</v>
       </c>
       <c r="FQ7" s="2" t="n">
-        <v>0.2842752232445948</v>
+        <v>0.2774118726534993</v>
       </c>
       <c r="FR7" s="2" t="n">
-        <v>0.2901306985035352</v>
+        <v>0.2826819646681229</v>
       </c>
       <c r="FS7" s="2" t="n">
-        <v>0.2876283152765257</v>
+        <v>0.2803751995857852</v>
       </c>
       <c r="FT7" s="2" t="n">
-        <v>0.2880391350278346</v>
+        <v>0.2805190341924462</v>
       </c>
       <c r="FU7" s="2" t="n">
-        <v>0.2861478904180339</v>
+        <v>0.2785852425136571</v>
       </c>
       <c r="FV7" s="2" t="n">
-        <v>0.2878906667733764</v>
+        <v>0.2804063330257701</v>
       </c>
       <c r="FW7" s="2" t="n">
-        <v>0.2883433738161545</v>
+        <v>0.2807789405159729</v>
       </c>
       <c r="FX7" s="2" t="n">
-        <v>0.2866334081393078</v>
+        <v>0.2802745213747475</v>
       </c>
       <c r="FY7" s="2" t="n">
-        <v>0.296587159854162</v>
+        <v>0.2912343025745601</v>
       </c>
       <c r="FZ7" s="2" t="n">
-        <v>0.3013001736846584</v>
+        <v>0.2955883483505237</v>
       </c>
       <c r="GA7" s="2" t="n">
-        <v>0.3161327503043371</v>
+        <v>0.3104401640843926</v>
       </c>
       <c r="GB7" s="2" t="n">
-        <v>0.3132393046792123</v>
+        <v>0.3020466757686098</v>
       </c>
       <c r="GC7" s="2" t="n">
-        <v>0.3141322999065829</v>
+        <v>0.3026407151255419</v>
       </c>
       <c r="GD7" s="2" t="n">
-        <v>0.3156733523742463</v>
+        <v>0.3037325560271609</v>
       </c>
       <c r="GE7" s="2" t="n">
-        <v>0.3158078734743917</v>
+        <v>0.3036366593999791</v>
       </c>
       <c r="GF7" s="2" t="n">
-        <v>0.3136856728467187</v>
+        <v>0.3018004145613034</v>
       </c>
       <c r="GG7" s="2" t="n">
-        <v>0.3117931279330706</v>
+        <v>0.3002360624687279</v>
       </c>
       <c r="GH7" s="2" t="n">
-        <v>0.3079761207187036</v>
+        <v>0.2965571887437811</v>
       </c>
       <c r="GI7" s="2" t="n">
-        <v>0.3076326123160765</v>
+        <v>0.2975793546973523</v>
       </c>
       <c r="GJ7" s="2" t="n">
-        <v>0.3085336106331157</v>
+        <v>0.2978632794110285</v>
       </c>
       <c r="GK7" s="2" t="n">
-        <v>0.3124720726022433</v>
+        <v>0.3017989694889922</v>
       </c>
       <c r="GL7" s="2" t="n">
-        <v>0.3177911028430477</v>
+        <v>0.3088575732220197</v>
       </c>
       <c r="GM7" s="2" t="n">
-        <v>0.3232005612587341</v>
+        <v>0.315868574868627</v>
       </c>
       <c r="GN7" s="2" t="n">
-        <v>0.3385454857985924</v>
+        <v>0.3310252629732347</v>
       </c>
       <c r="GO7" s="2" t="n">
-        <v>0.3474111788366316</v>
+        <v>0.3386162205548789</v>
       </c>
       <c r="GP7" s="2" t="n">
-        <v>0.341399874750933</v>
+        <v>0.3306629238440445</v>
       </c>
       <c r="GQ7" s="2" t="n">
-        <v>0.337289740656898</v>
+        <v>0.3281888558667456</v>
       </c>
       <c r="GR7" s="2" t="n">
-        <v>0.3368109258700685</v>
+        <v>0.3265812075904343</v>
       </c>
       <c r="GS7" s="2" t="n">
-        <v>0.3350225217868175</v>
+        <v>0.3251468604663859</v>
       </c>
       <c r="GT7" s="2" t="n">
-        <v>0.3366842985539086</v>
+        <v>0.3265836571996057</v>
       </c>
       <c r="GU7" s="2" t="n">
-        <v>0.3308426326683409</v>
+        <v>0.321004473801459</v>
       </c>
       <c r="GV7" s="2" t="n">
-        <v>0.3362289293102146</v>
+        <v>0.3260658988333492</v>
       </c>
       <c r="GW7" s="2" t="n">
-        <v>0.3309493719987112</v>
+        <v>0.3214248491396841</v>
       </c>
       <c r="GX7" s="2" t="n">
-        <v>0.3323598741929016</v>
+        <v>0.3225035312024035</v>
       </c>
       <c r="GY7" s="2" t="n">
-        <v>0.3327546974610657</v>
+        <v>0.3227861950544454</v>
       </c>
       <c r="GZ7" s="2" t="n">
-        <v>0.3451957950009253</v>
+        <v>0.3365220492304066</v>
       </c>
       <c r="HA7" s="2" t="n">
-        <v>0.3577630812540202</v>
+        <v>0.349393911382207</v>
       </c>
       <c r="HB7" s="2" t="n">
-        <v>0.3708639426719886</v>
+        <v>0.3618634201701481</v>
       </c>
       <c r="HC7" s="2" t="n">
-        <v>0.3632349774510314</v>
+        <v>0.3565004197563961</v>
       </c>
       <c r="HD7" s="2" t="n">
-        <v>0.3542909115588757</v>
+        <v>0.3445598031896377</v>
       </c>
       <c r="HE7" s="2" t="n">
-        <v>0.3486652304624785</v>
+        <v>0.3401717832265075</v>
       </c>
       <c r="HF7" s="2" t="n">
-        <v>0.3506208217974111</v>
+        <v>0.341566663942192</v>
       </c>
       <c r="HG7" s="2" t="n">
-        <v>0.3575612985340302</v>
+        <v>0.3477608990546572</v>
       </c>
       <c r="HH7" s="2" t="n">
-        <v>0.3570725887087758</v>
+        <v>0.3463455404100483</v>
       </c>
       <c r="HI7" s="2" t="n">
-        <v>0.3555762976269333</v>
+        <v>0.3445721328866282</v>
       </c>
       <c r="HJ7" s="2" t="n">
-        <v>0.3587420793428144</v>
+        <v>0.3467499872671591</v>
       </c>
       <c r="HK7" s="2" t="n">
-        <v>0.3526936975637917</v>
+        <v>0.340481103351208</v>
       </c>
       <c r="HL7" s="2" t="n">
-        <v>0.3551148623988807</v>
+        <v>0.3418280059837555</v>
       </c>
       <c r="HM7" s="2" t="n">
-        <v>0.3525641782200977</v>
+        <v>0.3385264958821403</v>
       </c>
       <c r="HN7" s="2" t="n">
-        <v>0.3751802029510961</v>
+        <v>0.3616368322501912</v>
       </c>
       <c r="HO7" s="2" t="n">
-        <v>0.3889511232151037</v>
+        <v>0.3759644018101058</v>
       </c>
       <c r="HP7" s="2" t="n">
-        <v>0.3653425397260319</v>
+        <v>0.3572680851057051</v>
       </c>
       <c r="HQ7" s="2" t="n">
-        <v>0.3512041815881792</v>
+        <v>0.346496319750446</v>
       </c>
       <c r="HR7" s="3" t="n">
         <v>55519</v>
@@ -5673,7 +5673,7 @@
         <v>0.0707983495227468</v>
       </c>
       <c r="Z8" s="7" t="n">
-        <v>0.06639461174486945</v>
+        <v>0.06761062145233154</v>
       </c>
       <c r="AA8" s="6" t="n">
         <v>0.06325361731976981</v>
@@ -5712,7 +5712,7 @@
         <v>0.102714844045793</v>
       </c>
       <c r="AM8" s="7" t="n">
-        <v>0.09724611372956703</v>
+        <v>0.09908564388751984</v>
       </c>
       <c r="AN8" s="6" t="n">
         <v>0.09259502537764119</v>
@@ -5871,7 +5871,7 @@
         <v>0.204818851764059</v>
       </c>
       <c r="CN8" s="7" t="n">
-        <v>0.1999567772736174</v>
+        <v>0.2018578201532364</v>
       </c>
       <c r="CO8" s="6" t="n">
         <v>0.196500406731799</v>
@@ -6129,7 +6129,7 @@
         <v>0.277654055693251</v>
       </c>
       <c r="FV8" s="7" t="n">
-        <v>0.2759273283067166</v>
+        <v>0.2779556810855865</v>
       </c>
       <c r="FW8" s="6" t="n">
         <v>0.279414809816803</v>
@@ -6295,7 +6295,7 @@
         <v>0.0381157332974437</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.0420418318385242</v>
+        <v>0.04350094124674797</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>0.0395341519679435</v>
@@ -6418,7 +6418,7 @@
         <v>0.131315746744894</v>
       </c>
       <c r="AU9" s="7" t="n">
-        <v>0.1391979557446825</v>
+        <v>0.1396824717521667</v>
       </c>
       <c r="AV9" s="6" t="n">
         <v>0.132513088922263</v>
@@ -6499,7 +6499,7 @@
         <v>0.199955283513327</v>
       </c>
       <c r="BV9" s="7" t="n">
-        <v>0.2019242254569212</v>
+        <v>0.2008426785469055</v>
       </c>
       <c r="BW9" s="6" t="n">
         <v>0.200606296983058</v>
@@ -6640,7 +6640,7 @@
         <v>0.251323415697041</v>
       </c>
       <c r="DQ9" s="7" t="n">
-        <v>0.2423753988256024</v>
+        <v>0.2394468784332275</v>
       </c>
       <c r="DR9" s="6" t="n">
         <v>0.23764445461862</v>
@@ -6694,7 +6694,7 @@
         <v>0.232519744722409</v>
       </c>
       <c r="EI9" s="7" t="n">
-        <v>0.2325445517403975</v>
+        <v>0.2306835949420929</v>
       </c>
       <c r="EJ9" s="6" t="n">
         <v>0.231332738185024</v>
@@ -6853,7 +6853,7 @@
         <v>0.304890545827317</v>
       </c>
       <c r="GJ9" s="7" t="n">
-        <v>0.3038854031715224</v>
+        <v>0.3020880818367004</v>
       </c>
       <c r="GK9" s="6" t="n">
         <v>0.308508043694741</v>

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -1509,676 +1509,676 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.02409424997156595</v>
+        <v>0.03216920038773417</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.03184071665926662</v>
+        <v>0.0409153116664631</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.03376989515533502</v>
+        <v>0.04301669283345232</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.03533772760420039</v>
+        <v>0.04462490142948638</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.03584189538228544</v>
+        <v>0.04501089666287749</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.03524311972705521</v>
+        <v>0.04400417349006929</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.03482997268961281</v>
+        <v>0.04333330899013352</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.03448983584796323</v>
+        <v>0.04300973734640468</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.03476780014248716</v>
+        <v>0.04317240830443438</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.03416729434972343</v>
+        <v>0.04223550673950645</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.0333003398422682</v>
+        <v>0.04087603491637532</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.03244605028525065</v>
+        <v>0.03873163938851151</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.03239005064522088</v>
+        <v>0.03855571086448963</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.03301930037581247</v>
+        <v>0.03889049783486669</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.04829908546915937</v>
+        <v>0.06034109802816749</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.0585481943631677</v>
+        <v>0.07292793422758571</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.06100428438864031</v>
+        <v>0.07663270022099347</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.06221599747120271</v>
+        <v>0.07719279916444349</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.06340613097787057</v>
+        <v>0.07852514985991031</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.06131854406302968</v>
+        <v>0.07492663916695477</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.06231076517636623</v>
+        <v>0.07616207109325428</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.06200230148956505</v>
+        <v>0.07500728867312005</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.06153937307049831</v>
+        <v>0.07497831645622649</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.06117197607765418</v>
+        <v>0.07420561570360515</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.05841479801330376</v>
+        <v>0.07031584329844451</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.0563086127527754</v>
+        <v>0.06631821032346098</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0.05616216712374789</v>
+        <v>0.0663241482459262</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0.05758526592455462</v>
+        <v>0.06712297026252578</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.07866126438127166</v>
+        <v>0.09490583484621977</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>0.08955711517722895</v>
+        <v>0.109531244199085</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>0.08930294968288695</v>
+        <v>0.1108649365877221</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.09173264247697605</v>
+        <v>0.1120854862406819</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.09213932245336849</v>
+        <v>0.1121650572267043</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>0.09166837362729238</v>
+        <v>0.1109327214287621</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>0.08883345452616066</v>
+        <v>0.1070807773395168</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>0.08807672978658548</v>
+        <v>0.1050633065926807</v>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>0.08839801155189728</v>
+        <v>0.1061950313675433</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>0.08548144181637674</v>
+        <v>0.1021244627551165</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.0817376608652487</v>
+        <v>0.09562960966320441</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>0.0799579307030017</v>
+        <v>0.09263320089343603</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>0.08208551421832175</v>
+        <v>0.09527927683361884</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.08289053547016954</v>
+        <v>0.09546431406068057</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.1067903671435371</v>
+        <v>0.1267609811149915</v>
       </c>
       <c r="AS2" s="2" t="n">
-        <v>0.112873719601973</v>
+        <v>0.1399184271715138</v>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>0.1139261563351639</v>
+        <v>0.1405756777346419</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>0.1161054764672611</v>
+        <v>0.1402166782226673</v>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>0.1138538322785264</v>
+        <v>0.1384490496692751</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>0.1103450922688999</v>
+        <v>0.1323676346712258</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>0.1108812226715851</v>
+        <v>0.1324405767351658</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>0.1102469424043481</v>
+        <v>0.1303766889534352</v>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>0.1089714732216183</v>
+        <v>0.1296139946505002</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>0.1054786539841245</v>
+        <v>0.1241163749154323</v>
       </c>
       <c r="BB2" s="2" t="n">
-        <v>0.1012465360863909</v>
+        <v>0.1172579585052857</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>0.09972139506494188</v>
+        <v>0.1145226863510781</v>
       </c>
       <c r="BD2" s="2" t="n">
-        <v>0.09847014168297244</v>
+        <v>0.1128021141686504</v>
       </c>
       <c r="BE2" s="2" t="n">
-        <v>0.1015862272373955</v>
+        <v>0.1156927589718842</v>
       </c>
       <c r="BF2" s="2" t="n">
-        <v>0.1340107856630529</v>
+        <v>0.1604268938407789</v>
       </c>
       <c r="BG2" s="2" t="n">
-        <v>0.1356997900248912</v>
+        <v>0.1662521406462699</v>
       </c>
       <c r="BH2" s="2" t="n">
-        <v>0.1357045621413595</v>
+        <v>0.1650224427804187</v>
       </c>
       <c r="BI2" s="2" t="n">
-        <v>0.1327212813603772</v>
+        <v>0.1618567381603025</v>
       </c>
       <c r="BJ2" s="2" t="n">
-        <v>0.1327552050946344</v>
+        <v>0.1604585541129967</v>
       </c>
       <c r="BK2" s="2" t="n">
-        <v>0.127138132077186</v>
+        <v>0.1520701714203502</v>
       </c>
       <c r="BL2" s="2" t="n">
-        <v>0.1269655644867322</v>
+        <v>0.1504370561689784</v>
       </c>
       <c r="BM2" s="2" t="n">
-        <v>0.124550552394277</v>
+        <v>0.1465355289574555</v>
       </c>
       <c r="BN2" s="2" t="n">
-        <v>0.122882775627613</v>
+        <v>0.1451781815202654</v>
       </c>
       <c r="BO2" s="2" t="n">
-        <v>0.1242997448178457</v>
+        <v>0.1456110930238552</v>
       </c>
       <c r="BP2" s="2" t="n">
-        <v>0.1166519934663059</v>
+        <v>0.1341277544774832</v>
       </c>
       <c r="BQ2" s="2" t="n">
-        <v>0.1160660035056708</v>
+        <v>0.1317908923271035</v>
       </c>
       <c r="BR2" s="2" t="n">
-        <v>0.1155145728244937</v>
+        <v>0.1308538976963006</v>
       </c>
       <c r="BS2" s="2" t="n">
-        <v>0.1155296914884321</v>
+        <v>0.1299141062262523</v>
       </c>
       <c r="BT2" s="2" t="n">
-        <v>0.1664384387943894</v>
+        <v>0.2057726509442012</v>
       </c>
       <c r="BU2" s="2" t="n">
-        <v>0.1644967928681111</v>
+        <v>0.205193320681231</v>
       </c>
       <c r="BV2" s="2" t="n">
-        <v>0.1613739494239298</v>
+        <v>0.200959500006559</v>
       </c>
       <c r="BW2" s="2" t="n">
-        <v>0.1621982849953908</v>
+        <v>0.2002429700406956</v>
       </c>
       <c r="BX2" s="2" t="n">
-        <v>0.1606740861522626</v>
+        <v>0.1929939995648748</v>
       </c>
       <c r="BY2" s="2" t="n">
-        <v>0.1569092983086119</v>
+        <v>0.1871939238569776</v>
       </c>
       <c r="BZ2" s="2" t="n">
-        <v>0.1537557580742758</v>
+        <v>0.1825262058306777</v>
       </c>
       <c r="CA2" s="2" t="n">
-        <v>0.1509462941207121</v>
+        <v>0.1777537976566964</v>
       </c>
       <c r="CB2" s="2" t="n">
-        <v>0.1491328389206564</v>
+        <v>0.1743036816386337</v>
       </c>
       <c r="CC2" s="2" t="n">
-        <v>0.145362991218755</v>
+        <v>0.1686113204645365</v>
       </c>
       <c r="CD2" s="2" t="n">
-        <v>0.1420341622276048</v>
+        <v>0.1621917385797379</v>
       </c>
       <c r="CE2" s="2" t="n">
-        <v>0.1356991675179119</v>
+        <v>0.1525181161263341</v>
       </c>
       <c r="CF2" s="2" t="n">
-        <v>0.1359314471090391</v>
+        <v>0.1522464456972728</v>
       </c>
       <c r="CG2" s="2" t="n">
-        <v>0.139087395797861</v>
+        <v>0.1549242874535172</v>
       </c>
       <c r="CH2" s="2" t="n">
-        <v>0.1922288379651869</v>
+        <v>0.2357232708388739</v>
       </c>
       <c r="CI2" s="2" t="n">
-        <v>0.1901681381270987</v>
+        <v>0.237804090557403</v>
       </c>
       <c r="CJ2" s="2" t="n">
-        <v>0.1882917617841775</v>
+        <v>0.2310186131521753</v>
       </c>
       <c r="CK2" s="2" t="n">
-        <v>0.1851199161017104</v>
+        <v>0.2235222838549183</v>
       </c>
       <c r="CL2" s="2" t="n">
-        <v>0.1818376569052396</v>
+        <v>0.2181430758877482</v>
       </c>
       <c r="CM2" s="2" t="n">
-        <v>0.1755537951931204</v>
+        <v>0.2080703580095359</v>
       </c>
       <c r="CN2" s="2" t="n">
-        <v>0.1764439207518544</v>
+        <v>0.2070837830123397</v>
       </c>
       <c r="CO2" s="2" t="n">
-        <v>0.1704910158552031</v>
+        <v>0.1989537195193294</v>
       </c>
       <c r="CP2" s="2" t="n">
-        <v>0.1693086632328649</v>
+        <v>0.1966981527655764</v>
       </c>
       <c r="CQ2" s="2" t="n">
-        <v>0.1703174792925641</v>
+        <v>0.1962144349950429</v>
       </c>
       <c r="CR2" s="2" t="n">
-        <v>0.157793160253454</v>
+        <v>0.1776922631816504</v>
       </c>
       <c r="CS2" s="2" t="n">
-        <v>0.1555902209268198</v>
+        <v>0.1727122868704835</v>
       </c>
       <c r="CT2" s="2" t="n">
-        <v>0.1557121076846294</v>
+        <v>0.171554119030015</v>
       </c>
       <c r="CU2" s="2" t="n">
-        <v>0.1618317269763922</v>
+        <v>0.1784370124518123</v>
       </c>
       <c r="CV2" s="2" t="n">
-        <v>0.2283585294494069</v>
+        <v>0.275025969522027</v>
       </c>
       <c r="CW2" s="2" t="n">
-        <v>0.2160444143199447</v>
+        <v>0.263744609372382</v>
       </c>
       <c r="CX2" s="2" t="n">
-        <v>0.2162876823069333</v>
+        <v>0.2582500580762244</v>
       </c>
       <c r="CY2" s="2" t="n">
-        <v>0.2148776573571072</v>
+        <v>0.2540437885072073</v>
       </c>
       <c r="CZ2" s="2" t="n">
-        <v>0.2064481141976213</v>
+        <v>0.2427775926815227</v>
       </c>
       <c r="DA2" s="2" t="n">
-        <v>0.2033774240465049</v>
+        <v>0.237516623924064</v>
       </c>
       <c r="DB2" s="2" t="n">
-        <v>0.2041680019801556</v>
+        <v>0.2360664312490288</v>
       </c>
       <c r="DC2" s="2" t="n">
-        <v>0.2001028074951225</v>
+        <v>0.2288257477641728</v>
       </c>
       <c r="DD2" s="2" t="n">
-        <v>0.1996034417993302</v>
+        <v>0.2251997729606021</v>
       </c>
       <c r="DE2" s="2" t="n">
-        <v>0.1941359916390965</v>
+        <v>0.2179084845225304</v>
       </c>
       <c r="DF2" s="2" t="n">
-        <v>0.1886444834677441</v>
+        <v>0.2081898376707867</v>
       </c>
       <c r="DG2" s="2" t="n">
-        <v>0.186076192639629</v>
+        <v>0.2042692122691747</v>
       </c>
       <c r="DH2" s="2" t="n">
-        <v>0.1849897089744027</v>
+        <v>0.2011622967930232</v>
       </c>
       <c r="DI2" s="2" t="n">
-        <v>0.187648631514239</v>
+        <v>0.2026137933965943</v>
       </c>
       <c r="DJ2" s="2" t="n">
-        <v>0.2441081070444961</v>
+        <v>0.2927569934805837</v>
       </c>
       <c r="DK2" s="2" t="n">
-        <v>0.2415845263376467</v>
+        <v>0.2844346823257884</v>
       </c>
       <c r="DL2" s="2" t="n">
-        <v>0.2345428028008692</v>
+        <v>0.2748369051002391</v>
       </c>
       <c r="DM2" s="2" t="n">
-        <v>0.233051520664044</v>
+        <v>0.2713566326713045</v>
       </c>
       <c r="DN2" s="2" t="n">
-        <v>0.2265031071816037</v>
+        <v>0.2615117585762145</v>
       </c>
       <c r="DO2" s="2" t="n">
-        <v>0.2280909389837283</v>
+        <v>0.260036549993365</v>
       </c>
       <c r="DP2" s="2" t="n">
-        <v>0.2225012392537851</v>
+        <v>0.2501055331875405</v>
       </c>
       <c r="DQ2" s="2" t="n">
-        <v>0.2167342377830909</v>
+        <v>0.2423408344766935</v>
       </c>
       <c r="DR2" s="2" t="n">
-        <v>0.2153036794250142</v>
+        <v>0.2382155909158974</v>
       </c>
       <c r="DS2" s="2" t="n">
-        <v>0.2125917475412855</v>
+        <v>0.2329355595865181</v>
       </c>
       <c r="DT2" s="2" t="n">
-        <v>0.2083365968411205</v>
+        <v>0.22632212836159</v>
       </c>
       <c r="DU2" s="2" t="n">
-        <v>0.207191432172665</v>
+        <v>0.22208999182844</v>
       </c>
       <c r="DV2" s="2" t="n">
-        <v>0.2095289943887456</v>
+        <v>0.224227593169422</v>
       </c>
       <c r="DW2" s="2" t="n">
-        <v>0.2118873893944378</v>
+        <v>0.2252760911108288</v>
       </c>
       <c r="DX2" s="2" t="n">
-        <v>0.2619793933695286</v>
+        <v>0.3047358032261323</v>
       </c>
       <c r="DY2" s="2" t="n">
-        <v>0.2524509223771627</v>
+        <v>0.2922531579952111</v>
       </c>
       <c r="DZ2" s="2" t="n">
-        <v>0.2510850648561191</v>
+        <v>0.2890550828905483</v>
       </c>
       <c r="EA2" s="2" t="n">
-        <v>0.2446576447777912</v>
+        <v>0.2781661278715378</v>
       </c>
       <c r="EB2" s="2" t="n">
-        <v>0.2442267455198696</v>
+        <v>0.273383433711628</v>
       </c>
       <c r="EC2" s="2" t="n">
-        <v>0.2384654739163494</v>
+        <v>0.2658399844837072</v>
       </c>
       <c r="ED2" s="2" t="n">
-        <v>0.2360557880797425</v>
+        <v>0.2605120352251383</v>
       </c>
       <c r="EE2" s="2" t="n">
-        <v>0.2347051761942967</v>
+        <v>0.2564894842008137</v>
       </c>
       <c r="EF2" s="2" t="n">
-        <v>0.2325114174347612</v>
+        <v>0.2537802994003157</v>
       </c>
       <c r="EG2" s="2" t="n">
-        <v>0.2307131515072429</v>
+        <v>0.2504647561763703</v>
       </c>
       <c r="EH2" s="2" t="n">
-        <v>0.2193056598966162</v>
+        <v>0.2351846800366543</v>
       </c>
       <c r="EI2" s="2" t="n">
-        <v>0.2232641787847676</v>
+        <v>0.2366081738407089</v>
       </c>
       <c r="EJ2" s="2" t="n">
-        <v>0.2245548621132168</v>
+        <v>0.2352137266698631</v>
       </c>
       <c r="EK2" s="2" t="n">
-        <v>0.2259233005258149</v>
+        <v>0.2375941246225604</v>
       </c>
       <c r="EL2" s="2" t="n">
-        <v>0.2733118519759635</v>
+        <v>0.3072070975574471</v>
       </c>
       <c r="EM2" s="2" t="n">
-        <v>0.2704023524812862</v>
+        <v>0.2986861864485799</v>
       </c>
       <c r="EN2" s="2" t="n">
-        <v>0.2663431089329122</v>
+        <v>0.291703025806667</v>
       </c>
       <c r="EO2" s="2" t="n">
-        <v>0.2598750563203824</v>
+        <v>0.282299498961791</v>
       </c>
       <c r="EP2" s="2" t="n">
-        <v>0.2632742755130998</v>
+        <v>0.2848190920751261</v>
       </c>
       <c r="EQ2" s="2" t="n">
-        <v>0.2527116095925524</v>
+        <v>0.2716698013401095</v>
       </c>
       <c r="ER2" s="2" t="n">
-        <v>0.2524708092283977</v>
+        <v>0.2721033443082876</v>
       </c>
       <c r="ES2" s="2" t="n">
-        <v>0.2468564463154936</v>
+        <v>0.2626928445839934</v>
       </c>
       <c r="ET2" s="2" t="n">
-        <v>0.2496946750157399</v>
+        <v>0.2652233257183971</v>
       </c>
       <c r="EU2" s="2" t="n">
-        <v>0.2491787779471676</v>
+        <v>0.2628747391878166</v>
       </c>
       <c r="EV2" s="2" t="n">
-        <v>0.2456773437891051</v>
+        <v>0.2580136289002973</v>
       </c>
       <c r="EW2" s="2" t="n">
-        <v>0.2457456295993894</v>
+        <v>0.2557687138617775</v>
       </c>
       <c r="EX2" s="2" t="n">
-        <v>0.2458505984411185</v>
+        <v>0.2541066364553179</v>
       </c>
       <c r="EY2" s="2" t="n">
-        <v>0.2575555305023064</v>
+        <v>0.2665956018592982</v>
       </c>
       <c r="EZ2" s="2" t="n">
-        <v>0.2814380360728507</v>
+        <v>0.2971431112076661</v>
       </c>
       <c r="FA2" s="2" t="n">
-        <v>0.2820195079739359</v>
+        <v>0.2969323867998504</v>
       </c>
       <c r="FB2" s="2" t="n">
-        <v>0.2715177879890243</v>
+        <v>0.2850415011235163</v>
       </c>
       <c r="FC2" s="2" t="n">
-        <v>0.2738563971471997</v>
+        <v>0.2864483441732086</v>
       </c>
       <c r="FD2" s="2" t="n">
-        <v>0.2645286955514536</v>
+        <v>0.2759294344005659</v>
       </c>
       <c r="FE2" s="2" t="n">
-        <v>0.2660187350314983</v>
+        <v>0.2770301558450811</v>
       </c>
       <c r="FF2" s="2" t="n">
-        <v>0.2656705692526807</v>
+        <v>0.2765389195136215</v>
       </c>
       <c r="FG2" s="2" t="n">
-        <v>0.2624861373607057</v>
+        <v>0.2730183305623894</v>
       </c>
       <c r="FH2" s="2" t="n">
-        <v>0.2580648765094527</v>
+        <v>0.2684366389679673</v>
       </c>
       <c r="FI2" s="2" t="n">
-        <v>0.2568475287920846</v>
+        <v>0.2671605341805945</v>
       </c>
       <c r="FJ2" s="2" t="n">
-        <v>0.2592022534246</v>
+        <v>0.2686211682794578</v>
       </c>
       <c r="FK2" s="2" t="n">
-        <v>0.2614999523284197</v>
+        <v>0.2684300881652023</v>
       </c>
       <c r="FL2" s="2" t="n">
-        <v>0.2712101247909575</v>
+        <v>0.2772692499839491</v>
       </c>
       <c r="FM2" s="2" t="n">
-        <v>0.2814078884382181</v>
+        <v>0.2874453158298713</v>
       </c>
       <c r="FN2" s="2" t="n">
-        <v>0.2856237444898547</v>
+        <v>0.2978727884476102</v>
       </c>
       <c r="FO2" s="2" t="n">
-        <v>0.2860680692630544</v>
+        <v>0.2972795712362236</v>
       </c>
       <c r="FP2" s="2" t="n">
-        <v>0.2782268727597935</v>
+        <v>0.2888659158567724</v>
       </c>
       <c r="FQ2" s="2" t="n">
-        <v>0.2762074788668352</v>
+        <v>0.2864396821299446</v>
       </c>
       <c r="FR2" s="2" t="n">
-        <v>0.2815739099284627</v>
+        <v>0.2928611465494865</v>
       </c>
       <c r="FS2" s="2" t="n">
-        <v>0.2792352091984726</v>
+        <v>0.2900398521459578</v>
       </c>
       <c r="FT2" s="2" t="n">
-        <v>0.2794662222660528</v>
+        <v>0.2908662167903289</v>
       </c>
       <c r="FU2" s="2" t="n">
-        <v>0.277551544243633</v>
+        <v>0.2889934347268071</v>
       </c>
       <c r="FV2" s="2" t="n">
-        <v>0.2793543862730662</v>
+        <v>0.2905606759521535</v>
       </c>
       <c r="FW2" s="2" t="n">
-        <v>0.2797410491431369</v>
+        <v>0.2910992406194318</v>
       </c>
       <c r="FX2" s="2" t="n">
-        <v>0.279152772266053</v>
+        <v>0.2882394292646854</v>
       </c>
       <c r="FY2" s="2" t="n">
-        <v>0.2900142095338944</v>
+        <v>0.2974422730676339</v>
       </c>
       <c r="FZ2" s="2" t="n">
-        <v>0.2942550930494472</v>
+        <v>0.3023747659190324</v>
       </c>
       <c r="GA2" s="2" t="n">
-        <v>0.3090719838534712</v>
+        <v>0.3173784324246526</v>
       </c>
       <c r="GB2" s="2" t="n">
-        <v>0.3010790030750103</v>
+        <v>0.3181047975718702</v>
       </c>
       <c r="GC2" s="2" t="n">
-        <v>0.3016693324199951</v>
+        <v>0.318981211995039</v>
       </c>
       <c r="GD2" s="2" t="n">
-        <v>0.3028361706789963</v>
+        <v>0.3211605843894643</v>
       </c>
       <c r="GE2" s="2" t="n">
-        <v>0.3027351299016601</v>
+        <v>0.3212899284990766</v>
       </c>
       <c r="GF2" s="2" t="n">
-        <v>0.3009048511501132</v>
+        <v>0.3187201707665751</v>
       </c>
       <c r="GG2" s="2" t="n">
-        <v>0.299300683181334</v>
+        <v>0.3165402211319239</v>
       </c>
       <c r="GH2" s="2" t="n">
-        <v>0.2957799465468</v>
+        <v>0.3127322696090278</v>
       </c>
       <c r="GI2" s="2" t="n">
-        <v>0.2967155706321322</v>
+        <v>0.3111948601270105</v>
       </c>
       <c r="GJ2" s="2" t="n">
-        <v>0.2968871559990836</v>
+        <v>0.3128404820092067</v>
       </c>
       <c r="GK2" s="2" t="n">
-        <v>0.3007664321886963</v>
+        <v>0.3163471398708241</v>
       </c>
       <c r="GL2" s="2" t="n">
-        <v>0.3076523146366371</v>
+        <v>0.3206330798230582</v>
       </c>
       <c r="GM2" s="2" t="n">
-        <v>0.314468821617769</v>
+        <v>0.3250646448155633</v>
       </c>
       <c r="GN2" s="2" t="n">
-        <v>0.3293561710776611</v>
+        <v>0.3401511757193038</v>
       </c>
       <c r="GO2" s="2" t="n">
-        <v>0.3369912289992812</v>
+        <v>0.3498493919883061</v>
       </c>
       <c r="GP2" s="2" t="n">
-        <v>0.3294274452500432</v>
+        <v>0.3452145869598103</v>
       </c>
       <c r="GQ2" s="2" t="n">
-        <v>0.3268083314671927</v>
+        <v>0.3400861219559365</v>
       </c>
       <c r="GR2" s="2" t="n">
-        <v>0.3254784333206653</v>
+        <v>0.34052576194542</v>
       </c>
       <c r="GS2" s="2" t="n">
-        <v>0.3239015349615907</v>
+        <v>0.3382297792257175</v>
       </c>
       <c r="GT2" s="2" t="n">
-        <v>0.3253258317732811</v>
+        <v>0.3400692639925818</v>
       </c>
       <c r="GU2" s="2" t="n">
-        <v>0.3197143127800004</v>
+        <v>0.3340234817194522</v>
       </c>
       <c r="GV2" s="2" t="n">
-        <v>0.3246935305248157</v>
+        <v>0.3395923856169553</v>
       </c>
       <c r="GW2" s="2" t="n">
-        <v>0.3199365693119702</v>
+        <v>0.3340344124063854</v>
       </c>
       <c r="GX2" s="2" t="n">
-        <v>0.3209464717526108</v>
+        <v>0.3353844531871324</v>
       </c>
       <c r="GY2" s="2" t="n">
-        <v>0.3212170596625154</v>
+        <v>0.3358487711241809</v>
       </c>
       <c r="GZ2" s="2" t="n">
-        <v>0.3345531297308584</v>
+        <v>0.347222937032087</v>
       </c>
       <c r="HA2" s="2" t="n">
-        <v>0.3476909594242535</v>
+        <v>0.3600871322910104</v>
       </c>
       <c r="HB2" s="2" t="n">
-        <v>0.3596822525813633</v>
+        <v>0.3729382035406626</v>
       </c>
       <c r="HC2" s="2" t="n">
-        <v>0.3547180330837418</v>
+        <v>0.3644495032936297</v>
       </c>
       <c r="HD2" s="2" t="n">
-        <v>0.3417270033839377</v>
+        <v>0.3557528462679959</v>
       </c>
       <c r="HE2" s="2" t="n">
-        <v>0.337192057538734</v>
+        <v>0.3498544848045081</v>
       </c>
       <c r="HF2" s="2" t="n">
-        <v>0.33882592866601</v>
+        <v>0.3524010462285371</v>
       </c>
       <c r="HG2" s="2" t="n">
-        <v>0.3450685285042132</v>
+        <v>0.3598669524932567</v>
       </c>
       <c r="HH2" s="2" t="n">
-        <v>0.3436273896009651</v>
+        <v>0.3595855631829942</v>
       </c>
       <c r="HI2" s="2" t="n">
-        <v>0.3418325734043769</v>
+        <v>0.358410729944927</v>
       </c>
       <c r="HJ2" s="2" t="n">
-        <v>0.3440420269761792</v>
+        <v>0.3620858753446208</v>
       </c>
       <c r="HK2" s="2" t="n">
-        <v>0.3378431143474985</v>
+        <v>0.3561747092725996</v>
       </c>
       <c r="HL2" s="2" t="n">
-        <v>0.3393313817367856</v>
+        <v>0.3592826420803387</v>
       </c>
       <c r="HM2" s="2" t="n">
-        <v>0.3362441424738741</v>
+        <v>0.3577279245727429</v>
       </c>
       <c r="HN2" s="2" t="n">
-        <v>0.3587241576336538</v>
+        <v>0.3785735345460251</v>
       </c>
       <c r="HO2" s="2" t="n">
-        <v>0.3728057036465496</v>
+        <v>0.3913579268253616</v>
       </c>
       <c r="HP2" s="2" t="n">
-        <v>0.3545593299576899</v>
+        <v>0.3667966291404061</v>
       </c>
       <c r="HQ2" s="2" t="n">
-        <v>0.3443343662302008</v>
+        <v>0.3514605593063599</v>
       </c>
       <c r="HR2" s="3" t="n">
         <v>55511</v>
@@ -2191,676 +2191,676 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.02390804244479825</v>
+        <v>0.02853817024780871</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.03180695271692159</v>
+        <v>0.03828656785217448</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.03374192138504595</v>
+        <v>0.04057772445847985</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.03528424781090891</v>
+        <v>0.04223383134731713</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.03577029888540445</v>
+        <v>0.04272744660948591</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.03515086788694163</v>
+        <v>0.04181582833192703</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.03470102586384078</v>
+        <v>0.04114656779972625</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.03434585118805836</v>
+        <v>0.04083496838683952</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.03460991045424733</v>
+        <v>0.04101227253617083</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.03400095231622337</v>
+        <v>0.04015781302914546</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.03311482472556477</v>
+        <v>0.03891247837785101</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.03228187688367196</v>
+        <v>0.0370693154855213</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.03222159963305821</v>
+        <v>0.03692010593033079</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.03284832454523241</v>
+        <v>0.037309996714973</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.04818124422256087</v>
+        <v>0.05580879622581338</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.05854319747870024</v>
+        <v>0.06918258440092689</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.06094859267356147</v>
+        <v>0.07276967407186857</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.06210201757504381</v>
+        <v>0.07349928393118678</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.06325316546767194</v>
+        <v>0.07483974656839533</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.06115339227218283</v>
+        <v>0.07163155050271144</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.06208644678266129</v>
+        <v>0.07271470436303276</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.06176050085699201</v>
+        <v>0.07177697609948967</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.06125203671328622</v>
+        <v>0.07159933160045082</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.06087877464601316</v>
+        <v>0.07097869961495872</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.05809832587815333</v>
+        <v>0.0673019276188794</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.05603147999808805</v>
+        <v>0.06377201573475964</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.05586653346532258</v>
+        <v>0.06373481173540285</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.05730549335685899</v>
+        <v>0.06469524072972017</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.07871631956915316</v>
+        <v>0.09043708157452751</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>0.08957164423477808</v>
+        <v>0.1048906519261006</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>0.08919847863479861</v>
+        <v>0.1058986249638958</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0.0915327583221572</v>
+        <v>0.1073287053478529</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>0.09187261770588429</v>
+        <v>0.1073992324377686</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>0.09136493394633621</v>
+        <v>0.1063135534273637</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>0.08848815468362448</v>
+        <v>0.1026538590604829</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>0.08771931343697999</v>
+        <v>0.1009360817376158</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>0.08798315916861651</v>
+        <v>0.101807189384665</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>0.08508110093743773</v>
+        <v>0.09809225408364042</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.08137285734889721</v>
+        <v>0.0921902854624268</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>0.07958805029718516</v>
+        <v>0.08948348934226995</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>0.08168675624711511</v>
+        <v>0.09200026745042363</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.08249045257851718</v>
+        <v>0.09231339452194377</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.1069426563521473</v>
+        <v>0.1221185586667053</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>0.1127363011063082</v>
+        <v>0.1336750893383497</v>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>0.1136575452285896</v>
+        <v>0.1342787934914726</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>0.1157657930216328</v>
+        <v>0.1344347589050326</v>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>0.1134644010832849</v>
+        <v>0.1325974050929718</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>0.1099191610583165</v>
+        <v>0.1269905470860513</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>0.1104277831486671</v>
+        <v>0.1272055805474346</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>0.1097874543026118</v>
+        <v>0.1254931911190722</v>
       </c>
       <c r="AZ3" s="2" t="n">
-        <v>0.108456036399173</v>
+        <v>0.1245296659644152</v>
       </c>
       <c r="BA3" s="2" t="n">
-        <v>0.1050089651869749</v>
+        <v>0.1195834030617581</v>
       </c>
       <c r="BB3" s="2" t="n">
-        <v>0.1007975494298911</v>
+        <v>0.1133561042594846</v>
       </c>
       <c r="BC3" s="2" t="n">
-        <v>0.09927540783880563</v>
+        <v>0.1109288687660169</v>
       </c>
       <c r="BD3" s="2" t="n">
-        <v>0.09803455238225819</v>
+        <v>0.1093044716578584</v>
       </c>
       <c r="BE3" s="2" t="n">
-        <v>0.1011266176577391</v>
+        <v>0.1121950593328364</v>
       </c>
       <c r="BF3" s="2" t="n">
-        <v>0.1340640364223458</v>
+        <v>0.1546889331530378</v>
       </c>
       <c r="BG3" s="2" t="n">
-        <v>0.135436233430072</v>
+        <v>0.1593090985023069</v>
       </c>
       <c r="BH3" s="2" t="n">
-        <v>0.1352973474726499</v>
+        <v>0.1580854314124182</v>
       </c>
       <c r="BI3" s="2" t="n">
-        <v>0.1321511122394537</v>
+        <v>0.1547238398925644</v>
       </c>
       <c r="BJ3" s="2" t="n">
-        <v>0.1322152009965466</v>
+        <v>0.1538581132527625</v>
       </c>
       <c r="BK3" s="2" t="n">
-        <v>0.1265960500998461</v>
+        <v>0.1460378202008614</v>
       </c>
       <c r="BL3" s="2" t="n">
-        <v>0.1263998497311198</v>
+        <v>0.1446918199720207</v>
       </c>
       <c r="BM3" s="2" t="n">
-        <v>0.124006016510005</v>
+        <v>0.1412213376154161</v>
       </c>
       <c r="BN3" s="2" t="n">
-        <v>0.1222804703916433</v>
+        <v>0.139668597897176</v>
       </c>
       <c r="BO3" s="2" t="n">
-        <v>0.1236972886001279</v>
+        <v>0.1403602038471353</v>
       </c>
       <c r="BP3" s="2" t="n">
-        <v>0.1161274461932152</v>
+        <v>0.1298387096258413</v>
       </c>
       <c r="BQ3" s="2" t="n">
-        <v>0.1155839875795802</v>
+        <v>0.1280204800368866</v>
       </c>
       <c r="BR3" s="2" t="n">
-        <v>0.1150347583394546</v>
+        <v>0.1271289754101219</v>
       </c>
       <c r="BS3" s="2" t="n">
-        <v>0.1150639871946373</v>
+        <v>0.1263770977377418</v>
       </c>
       <c r="BT3" s="2" t="n">
-        <v>0.1661446244366845</v>
+        <v>0.1970393120818475</v>
       </c>
       <c r="BU3" s="2" t="n">
-        <v>0.1639040263636218</v>
+        <v>0.1961171941705516</v>
       </c>
       <c r="BV3" s="2" t="n">
-        <v>0.16060982251376</v>
+        <v>0.191475342498993</v>
       </c>
       <c r="BW3" s="2" t="n">
-        <v>0.1612719493161759</v>
+        <v>0.1906895284063393</v>
       </c>
       <c r="BX3" s="2" t="n">
-        <v>0.1599277440056057</v>
+        <v>0.185216134940504</v>
       </c>
       <c r="BY3" s="2" t="n">
-        <v>0.1561925642967981</v>
+        <v>0.1799684391582171</v>
       </c>
       <c r="BZ3" s="2" t="n">
-        <v>0.1529657122118738</v>
+        <v>0.175323111978327</v>
       </c>
       <c r="CA3" s="2" t="n">
-        <v>0.1502048866814636</v>
+        <v>0.1711749043851589</v>
       </c>
       <c r="CB3" s="2" t="n">
-        <v>0.1484256394321269</v>
+        <v>0.1681606535116062</v>
       </c>
       <c r="CC3" s="2" t="n">
-        <v>0.1446864904449307</v>
+        <v>0.1628722232646366</v>
       </c>
       <c r="CD3" s="2" t="n">
-        <v>0.1414127755224943</v>
+        <v>0.1572883873891229</v>
       </c>
       <c r="CE3" s="2" t="n">
-        <v>0.1351686812539901</v>
+        <v>0.1484433182008788</v>
       </c>
       <c r="CF3" s="2" t="n">
-        <v>0.1354048708875185</v>
+        <v>0.1482175007756399</v>
       </c>
       <c r="CG3" s="2" t="n">
-        <v>0.1385690064682753</v>
+        <v>0.1510996679144975</v>
       </c>
       <c r="CH3" s="2" t="n">
-        <v>0.191481095860534</v>
+        <v>0.22560727460687</v>
       </c>
       <c r="CI3" s="2" t="n">
-        <v>0.1890948705799663</v>
+        <v>0.2262385178696414</v>
       </c>
       <c r="CJ3" s="2" t="n">
-        <v>0.1872705260910283</v>
+        <v>0.2205190867117892</v>
       </c>
       <c r="CK3" s="2" t="n">
-        <v>0.1841093155738022</v>
+        <v>0.213976962469831</v>
       </c>
       <c r="CL3" s="2" t="n">
-        <v>0.180852549120973</v>
+        <v>0.209106126126884</v>
       </c>
       <c r="CM3" s="2" t="n">
-        <v>0.1746676767251324</v>
+        <v>0.200105148871934</v>
       </c>
       <c r="CN3" s="2" t="n">
-        <v>0.1755852577714538</v>
+        <v>0.1996208989800682</v>
       </c>
       <c r="CO3" s="2" t="n">
-        <v>0.1696547612630097</v>
+        <v>0.1919679691066956</v>
       </c>
       <c r="CP3" s="2" t="n">
-        <v>0.1684585499962472</v>
+        <v>0.1898224785161962</v>
       </c>
       <c r="CQ3" s="2" t="n">
-        <v>0.169480801634928</v>
+        <v>0.1896733226415812</v>
       </c>
       <c r="CR3" s="2" t="n">
-        <v>0.1571882090045507</v>
+        <v>0.1729649292781605</v>
       </c>
       <c r="CS3" s="2" t="n">
-        <v>0.1550396917479392</v>
+        <v>0.1686130643702878</v>
       </c>
       <c r="CT3" s="2" t="n">
-        <v>0.1552042683771785</v>
+        <v>0.1677397050735774</v>
       </c>
       <c r="CU3" s="2" t="n">
-        <v>0.1612757557458227</v>
+        <v>0.1743868426945445</v>
       </c>
       <c r="CV3" s="2" t="n">
-        <v>0.2271002686563832</v>
+        <v>0.2632595026191887</v>
       </c>
       <c r="CW3" s="2" t="n">
-        <v>0.2146923905058434</v>
+        <v>0.2515175021740967</v>
       </c>
       <c r="CX3" s="2" t="n">
-        <v>0.2151357212325888</v>
+        <v>0.2479011168499844</v>
       </c>
       <c r="CY3" s="2" t="n">
-        <v>0.2138094403366204</v>
+        <v>0.2445577281674445</v>
       </c>
       <c r="CZ3" s="2" t="n">
-        <v>0.2053588447635679</v>
+        <v>0.2337302464087369</v>
       </c>
       <c r="DA3" s="2" t="n">
-        <v>0.2023209250293687</v>
+        <v>0.2289739331178732</v>
       </c>
       <c r="DB3" s="2" t="n">
-        <v>0.2031670123587945</v>
+        <v>0.2280571962351954</v>
       </c>
       <c r="DC3" s="2" t="n">
-        <v>0.1991648153041077</v>
+        <v>0.2215664344892738</v>
       </c>
       <c r="DD3" s="2" t="n">
-        <v>0.1988340725270651</v>
+        <v>0.2189530240879514</v>
       </c>
       <c r="DE3" s="2" t="n">
-        <v>0.1934187592192884</v>
+        <v>0.2122224728981723</v>
       </c>
       <c r="DF3" s="2" t="n">
-        <v>0.1880413754620406</v>
+        <v>0.2036567525077737</v>
       </c>
       <c r="DG3" s="2" t="n">
-        <v>0.1854538277587326</v>
+        <v>0.1998349371905747</v>
       </c>
       <c r="DH3" s="2" t="n">
-        <v>0.1844474372262617</v>
+        <v>0.1972800210021542</v>
       </c>
       <c r="DI3" s="2" t="n">
-        <v>0.1871329802904998</v>
+        <v>0.1989737208857483</v>
       </c>
       <c r="DJ3" s="2" t="n">
-        <v>0.2427711933233607</v>
+        <v>0.2808049662168765</v>
       </c>
       <c r="DK3" s="2" t="n">
-        <v>0.2404075607347478</v>
+        <v>0.2740537112575148</v>
       </c>
       <c r="DL3" s="2" t="n">
-        <v>0.2333094700447487</v>
+        <v>0.2646275911431073</v>
       </c>
       <c r="DM3" s="2" t="n">
-        <v>0.2318841878304576</v>
+        <v>0.2618190722050074</v>
       </c>
       <c r="DN3" s="2" t="n">
-        <v>0.2254153335141187</v>
+        <v>0.2528520629159585</v>
       </c>
       <c r="DO3" s="2" t="n">
-        <v>0.227035470821946</v>
+        <v>0.2519878516846351</v>
       </c>
       <c r="DP3" s="2" t="n">
-        <v>0.2216318207179068</v>
+        <v>0.2433002814581083</v>
       </c>
       <c r="DQ3" s="2" t="n">
-        <v>0.2159313852834845</v>
+        <v>0.2360829345621581</v>
       </c>
       <c r="DR3" s="2" t="n">
-        <v>0.2146210071585833</v>
+        <v>0.2327708039939889</v>
       </c>
       <c r="DS3" s="2" t="n">
-        <v>0.2120004965533414</v>
+        <v>0.2281380573197261</v>
       </c>
       <c r="DT3" s="2" t="n">
-        <v>0.2077681292243714</v>
+        <v>0.2220461993925186</v>
       </c>
       <c r="DU3" s="2" t="n">
-        <v>0.2066948078135577</v>
+        <v>0.2186749993279026</v>
       </c>
       <c r="DV3" s="2" t="n">
-        <v>0.2090427758191867</v>
+        <v>0.2207781699459523</v>
       </c>
       <c r="DW3" s="2" t="n">
-        <v>0.2114058162776873</v>
+        <v>0.2219736966324445</v>
       </c>
       <c r="DX3" s="2" t="n">
-        <v>0.2607129336388703</v>
+        <v>0.2940659803059046</v>
       </c>
       <c r="DY3" s="2" t="n">
-        <v>0.2512433397118228</v>
+        <v>0.2823508702918324</v>
       </c>
       <c r="DZ3" s="2" t="n">
-        <v>0.2499436303465567</v>
+        <v>0.2797374333215623</v>
       </c>
       <c r="EA3" s="2" t="n">
-        <v>0.2435845122643128</v>
+        <v>0.2697759624924336</v>
       </c>
       <c r="EB3" s="2" t="n">
-        <v>0.2433264777890255</v>
+        <v>0.2661952953904021</v>
       </c>
       <c r="EC3" s="2" t="n">
-        <v>0.2376230382949404</v>
+        <v>0.2592157834626382</v>
       </c>
       <c r="ED3" s="2" t="n">
-        <v>0.2353212574967934</v>
+        <v>0.2546129018507018</v>
       </c>
       <c r="EE3" s="2" t="n">
-        <v>0.2340682456971974</v>
+        <v>0.2513296862624596</v>
       </c>
       <c r="EF3" s="2" t="n">
-        <v>0.2318769710013913</v>
+        <v>0.2488273680788054</v>
       </c>
       <c r="EG3" s="2" t="n">
-        <v>0.230103293366428</v>
+        <v>0.2457664958071749</v>
       </c>
       <c r="EH3" s="2" t="n">
-        <v>0.2187852562114461</v>
+        <v>0.2312653904470171</v>
       </c>
       <c r="EI3" s="2" t="n">
-        <v>0.2228198587220937</v>
+        <v>0.2332689338292697</v>
       </c>
       <c r="EJ3" s="2" t="n">
-        <v>0.2241878055627862</v>
+        <v>0.2326074566547791</v>
       </c>
       <c r="EK3" s="2" t="n">
-        <v>0.2255191684662323</v>
+        <v>0.2347881645635062</v>
       </c>
       <c r="EL3" s="2" t="n">
-        <v>0.2722195808818859</v>
+        <v>0.2987675398346502</v>
       </c>
       <c r="EM3" s="2" t="n">
-        <v>0.2695276789000672</v>
+        <v>0.2918345700938502</v>
       </c>
       <c r="EN3" s="2" t="n">
-        <v>0.2656012989355338</v>
+        <v>0.2857348411481281</v>
       </c>
       <c r="EO3" s="2" t="n">
-        <v>0.2592205079559852</v>
+        <v>0.2770923554000508</v>
       </c>
       <c r="EP3" s="2" t="n">
-        <v>0.2626356794167265</v>
+        <v>0.2797812301887994</v>
       </c>
       <c r="EQ3" s="2" t="n">
-        <v>0.2521514461782681</v>
+        <v>0.2672532892201018</v>
       </c>
       <c r="ER3" s="2" t="n">
-        <v>0.2519039234161848</v>
+        <v>0.2673048899300329</v>
       </c>
       <c r="ES3" s="2" t="n">
-        <v>0.2463891713541067</v>
+        <v>0.2587434856259779</v>
       </c>
       <c r="ET3" s="2" t="n">
-        <v>0.2492541853536542</v>
+        <v>0.2614863224291578</v>
       </c>
       <c r="EU3" s="2" t="n">
-        <v>0.2487610322679652</v>
+        <v>0.2595539958408719</v>
       </c>
       <c r="EV3" s="2" t="n">
-        <v>0.2453029791751339</v>
+        <v>0.2551608868232458</v>
       </c>
       <c r="EW3" s="2" t="n">
-        <v>0.2454571367431017</v>
+        <v>0.2535607045361989</v>
       </c>
       <c r="EX3" s="2" t="n">
-        <v>0.2455903640462616</v>
+        <v>0.2522652346801661</v>
       </c>
       <c r="EY3" s="2" t="n">
-        <v>0.2572485205591213</v>
+        <v>0.2641865001546804</v>
       </c>
       <c r="EZ3" s="2" t="n">
-        <v>0.2809736147494518</v>
+        <v>0.2934868081736152</v>
       </c>
       <c r="FA3" s="2" t="n">
-        <v>0.2815971896546355</v>
+        <v>0.2934039859957658</v>
       </c>
       <c r="FB3" s="2" t="n">
-        <v>0.2711678343292964</v>
+        <v>0.2819765663553935</v>
       </c>
       <c r="FC3" s="2" t="n">
-        <v>0.2735501319738242</v>
+        <v>0.2836766475600795</v>
       </c>
       <c r="FD3" s="2" t="n">
-        <v>0.264250270509155</v>
+        <v>0.2733922814525946</v>
       </c>
       <c r="FE3" s="2" t="n">
-        <v>0.265743324291853</v>
+        <v>0.2746040436627301</v>
       </c>
       <c r="FF3" s="2" t="n">
-        <v>0.2654168777343628</v>
+        <v>0.2741746525281686</v>
       </c>
       <c r="FG3" s="2" t="n">
-        <v>0.262227502460273</v>
+        <v>0.2706938826382624</v>
       </c>
       <c r="FH3" s="2" t="n">
-        <v>0.2578066167587605</v>
+        <v>0.2661231543169091</v>
       </c>
       <c r="FI3" s="2" t="n">
-        <v>0.2565849623042301</v>
+        <v>0.2648260864396658</v>
       </c>
       <c r="FJ3" s="2" t="n">
-        <v>0.2589384183927723</v>
+        <v>0.2664485097423533</v>
       </c>
       <c r="FK3" s="2" t="n">
-        <v>0.2612930972227017</v>
+        <v>0.2668614348245647</v>
       </c>
       <c r="FL3" s="2" t="n">
-        <v>0.2710485964119849</v>
+        <v>0.2759736340997579</v>
       </c>
       <c r="FM3" s="2" t="n">
-        <v>0.2812434531681126</v>
+        <v>0.2861605416278891</v>
       </c>
       <c r="FN3" s="2" t="n">
-        <v>0.2853486968652751</v>
+        <v>0.2950736967429003</v>
       </c>
       <c r="FO3" s="2" t="n">
-        <v>0.285812976960942</v>
+        <v>0.2947416736687632</v>
       </c>
       <c r="FP3" s="2" t="n">
-        <v>0.2779715438275697</v>
+        <v>0.2864318453509085</v>
       </c>
       <c r="FQ3" s="2" t="n">
-        <v>0.275976774372922</v>
+        <v>0.2842570197504765</v>
       </c>
       <c r="FR3" s="2" t="n">
-        <v>0.2812959944854653</v>
+        <v>0.2902340500605614</v>
       </c>
       <c r="FS3" s="2" t="n">
-        <v>0.2789611226915656</v>
+        <v>0.2876208733013042</v>
       </c>
       <c r="FT3" s="2" t="n">
-        <v>0.2791543674939537</v>
+        <v>0.288194841852008</v>
       </c>
       <c r="FU3" s="2" t="n">
-        <v>0.2772256365075397</v>
+        <v>0.2862717610509288</v>
       </c>
       <c r="FV3" s="2" t="n">
-        <v>0.2790191817778767</v>
+        <v>0.2879009111925653</v>
       </c>
       <c r="FW3" s="2" t="n">
-        <v>0.2793930399113408</v>
+        <v>0.2883664985799082</v>
       </c>
       <c r="FX3" s="2" t="n">
-        <v>0.2788455437440336</v>
+        <v>0.286057862690843</v>
       </c>
       <c r="FY3" s="2" t="n">
-        <v>0.2897337771132058</v>
+        <v>0.2956131211025116</v>
       </c>
       <c r="FZ3" s="2" t="n">
-        <v>0.2939706733494584</v>
+        <v>0.3003528878151058</v>
       </c>
       <c r="GA3" s="2" t="n">
-        <v>0.3087682451699379</v>
+        <v>0.3151099587910406</v>
       </c>
       <c r="GB3" s="2" t="n">
-        <v>0.3005672983474763</v>
+        <v>0.3140455125540481</v>
       </c>
       <c r="GC3" s="2" t="n">
-        <v>0.3011412902585804</v>
+        <v>0.3149090013223862</v>
       </c>
       <c r="GD3" s="2" t="n">
-        <v>0.3022473839691732</v>
+        <v>0.3166364274801473</v>
       </c>
       <c r="GE3" s="2" t="n">
-        <v>0.3021377639285512</v>
+        <v>0.3167186901111394</v>
       </c>
       <c r="GF3" s="2" t="n">
-        <v>0.3003211007821149</v>
+        <v>0.3143908606144167</v>
       </c>
       <c r="GG3" s="2" t="n">
-        <v>0.2987437961086121</v>
+        <v>0.3124258919557545</v>
       </c>
       <c r="GH3" s="2" t="n">
-        <v>0.2951802973609974</v>
+        <v>0.3085944582693541</v>
       </c>
       <c r="GI3" s="2" t="n">
-        <v>0.2961426915461123</v>
+        <v>0.3076754772345471</v>
       </c>
       <c r="GJ3" s="2" t="n">
-        <v>0.2963281665646729</v>
+        <v>0.3089156791134356</v>
       </c>
       <c r="GK3" s="2" t="n">
-        <v>0.3002041538503892</v>
+        <v>0.3124683914484807</v>
       </c>
       <c r="GL3" s="2" t="n">
-        <v>0.3071486503811694</v>
+        <v>0.3172735417940145</v>
       </c>
       <c r="GM3" s="2" t="n">
-        <v>0.3140250972010216</v>
+        <v>0.3220720681690891</v>
       </c>
       <c r="GN3" s="2" t="n">
-        <v>0.3289704347730815</v>
+        <v>0.3374061598660508</v>
       </c>
       <c r="GO3" s="2" t="n">
-        <v>0.3365318050101945</v>
+        <v>0.3464938216671525</v>
       </c>
       <c r="GP3" s="2" t="n">
-        <v>0.3289148502082095</v>
+        <v>0.3414550348297787</v>
       </c>
       <c r="GQ3" s="2" t="n">
-        <v>0.3263696457877751</v>
+        <v>0.3368967413106235</v>
       </c>
       <c r="GR3" s="2" t="n">
-        <v>0.3249785531276876</v>
+        <v>0.337074338187268</v>
       </c>
       <c r="GS3" s="2" t="n">
-        <v>0.3234309966241074</v>
+        <v>0.3349208789463821</v>
       </c>
       <c r="GT3" s="2" t="n">
-        <v>0.3248246044160387</v>
+        <v>0.3365057334243196</v>
       </c>
       <c r="GU3" s="2" t="n">
-        <v>0.3192156179638823</v>
+        <v>0.3305213724120703</v>
       </c>
       <c r="GV3" s="2" t="n">
-        <v>0.3241867318686409</v>
+        <v>0.3359883364256995</v>
       </c>
       <c r="GW3" s="2" t="n">
-        <v>0.3194522861522806</v>
+        <v>0.330531959695523</v>
       </c>
       <c r="GX3" s="2" t="n">
-        <v>0.320453242586152</v>
+        <v>0.3317668008406885</v>
       </c>
       <c r="GY3" s="2" t="n">
-        <v>0.3207013987087024</v>
+        <v>0.3321401352491411</v>
       </c>
       <c r="GZ3" s="2" t="n">
-        <v>0.334151858261679</v>
+        <v>0.3440535139260855</v>
       </c>
       <c r="HA3" s="2" t="n">
-        <v>0.3472553589074186</v>
+        <v>0.3569295299689329</v>
       </c>
       <c r="HB3" s="2" t="n">
-        <v>0.359295540656767</v>
+        <v>0.3698794311048874</v>
       </c>
       <c r="HC3" s="2" t="n">
-        <v>0.3544072840006096</v>
+        <v>0.3621257400716145</v>
       </c>
       <c r="HD3" s="2" t="n">
-        <v>0.3413423246557197</v>
+        <v>0.3525097249531036</v>
       </c>
       <c r="HE3" s="2" t="n">
-        <v>0.3368893630049229</v>
+        <v>0.3469144478527892</v>
       </c>
       <c r="HF3" s="2" t="n">
-        <v>0.338452122955753</v>
+        <v>0.34908720274972</v>
       </c>
       <c r="HG3" s="2" t="n">
-        <v>0.3446535878908904</v>
+        <v>0.356378222014583</v>
       </c>
       <c r="HH3" s="2" t="n">
-        <v>0.3431906318746892</v>
+        <v>0.355893611390473</v>
       </c>
       <c r="HI3" s="2" t="n">
-        <v>0.3413852666324564</v>
+        <v>0.3546274860384075</v>
       </c>
       <c r="HJ3" s="2" t="n">
-        <v>0.3435664431832263</v>
+        <v>0.3580915242505822</v>
       </c>
       <c r="HK3" s="2" t="n">
-        <v>0.3373370541687215</v>
+        <v>0.3519500620878762</v>
       </c>
       <c r="HL3" s="2" t="n">
-        <v>0.3387700640848791</v>
+        <v>0.3546983820448575</v>
       </c>
       <c r="HM3" s="2" t="n">
-        <v>0.335613329053305</v>
+        <v>0.3526809062578409</v>
       </c>
       <c r="HN3" s="2" t="n">
-        <v>0.3582932031709322</v>
+        <v>0.3748497949424375</v>
       </c>
       <c r="HO3" s="2" t="n">
-        <v>0.3724323859767131</v>
+        <v>0.3883638506624195</v>
       </c>
       <c r="HP3" s="2" t="n">
-        <v>0.3543456212064614</v>
+        <v>0.3644144254235601</v>
       </c>
       <c r="HQ3" s="2" t="n">
-        <v>0.344181726626602</v>
+        <v>0.3498297524454621</v>
       </c>
       <c r="HR3" s="3" t="n">
         <v>55513</v>
@@ -2873,676 +2873,676 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.02421883548362058</v>
+        <v>0.02940107338565478</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.03196442878308705</v>
+        <v>0.03796155669446113</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03386116637699772</v>
+        <v>0.04015807668313805</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.03538447166546103</v>
+        <v>0.04187610183999813</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.03583615802850014</v>
+        <v>0.04229988802672696</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.03521503853513604</v>
+        <v>0.04157169861364149</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.03476805479298632</v>
+        <v>0.04110282409357713</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.03441195533655463</v>
+        <v>0.04089419518239924</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.03468164046908989</v>
+        <v>0.04119390435650665</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.03407729732899303</v>
+        <v>0.0404755335651328</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.03318918907956794</v>
+        <v>0.0393582305866334</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.03238482859125221</v>
+        <v>0.0378509760927846</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.03233086368258872</v>
+        <v>0.03779914066373356</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.03297573297122168</v>
+        <v>0.0384022487356793</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.04859411973258355</v>
+        <v>0.05658370158293729</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.05871855985032069</v>
+        <v>0.06814565466203511</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06106769688338341</v>
+        <v>0.07167555370179672</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.06218149026239986</v>
+        <v>0.07255538640529</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.06332022400573964</v>
+        <v>0.07411901586441222</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.06123602982436027</v>
+        <v>0.07141990316171981</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.06215341724413175</v>
+        <v>0.07252758522425605</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.06185113623998573</v>
+        <v>0.07206201729563291</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.06132884808468082</v>
+        <v>0.0718697856711239</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.06094873334310379</v>
+        <v>0.07134763674778213</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.05817969795599794</v>
+        <v>0.06793677586304207</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.05617537628810333</v>
+        <v>0.06506797052199494</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>0.05601642345484031</v>
+        <v>0.06513998912439442</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>0.05747568580648512</v>
+        <v>0.06635359624648922</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.0790060722846796</v>
+        <v>0.08920147150416173</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>0.08963351401698358</v>
+        <v>0.1023764415864697</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.08919776796284909</v>
+        <v>0.1036317586464734</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>0.09149614857748417</v>
+        <v>0.1054776694263359</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.09186716760978642</v>
+        <v>0.1062064338431783</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>0.09137799821951947</v>
+        <v>0.1055709689411509</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>0.08850866174915412</v>
+        <v>0.1022914894092228</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>0.08777772759207528</v>
+        <v>0.1011694973020526</v>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>0.08801957720183805</v>
+        <v>0.1019452155520603</v>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>0.08513251227224963</v>
+        <v>0.09856111695866726</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.08147483653544157</v>
+        <v>0.09316458339421943</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>0.07974289527489054</v>
+        <v>0.09111143014061115</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>0.08185647226785707</v>
+        <v>0.09384521241924228</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.08267747425117941</v>
+        <v>0.09439985095872221</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.1071119203416263</v>
+        <v>0.1193403214796318</v>
       </c>
       <c r="AS4" s="2" t="n">
-        <v>0.1126074210583293</v>
+        <v>0.1296202515182467</v>
       </c>
       <c r="AT4" s="2" t="n">
-        <v>0.1135091439500212</v>
+        <v>0.1308549456879162</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>0.1156122243311925</v>
+        <v>0.1317431084537193</v>
       </c>
       <c r="AV4" s="2" t="n">
-        <v>0.1134462789056818</v>
+        <v>0.1314830906313189</v>
       </c>
       <c r="AW4" s="2" t="n">
-        <v>0.1098916532205009</v>
+        <v>0.1261300859437852</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>0.1104308573030912</v>
+        <v>0.126910101097587</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>0.1098312381169096</v>
+        <v>0.1258085085786262</v>
       </c>
       <c r="AZ4" s="2" t="n">
-        <v>0.1084783821807984</v>
+        <v>0.1247685127571976</v>
       </c>
       <c r="BA4" s="2" t="n">
-        <v>0.1050682884780169</v>
+        <v>0.1202721439289303</v>
       </c>
       <c r="BB4" s="2" t="n">
-        <v>0.1008807211390796</v>
+        <v>0.114474933655836</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>0.09943353728004303</v>
+        <v>0.1128600518085177</v>
       </c>
       <c r="BD4" s="2" t="n">
-        <v>0.09823068779012888</v>
+        <v>0.1115818335196533</v>
       </c>
       <c r="BE4" s="2" t="n">
-        <v>0.1013400133823111</v>
+        <v>0.114746511379007</v>
       </c>
       <c r="BF4" s="2" t="n">
-        <v>0.1339097297844124</v>
+        <v>0.1494457098939571</v>
       </c>
       <c r="BG4" s="2" t="n">
-        <v>0.135216972100384</v>
+        <v>0.1551143469477817</v>
       </c>
       <c r="BH4" s="2" t="n">
-        <v>0.1351042508094707</v>
+        <v>0.1548879511129115</v>
       </c>
       <c r="BI4" s="2" t="n">
-        <v>0.1319208558515857</v>
+        <v>0.1520314707128116</v>
       </c>
       <c r="BJ4" s="2" t="n">
-        <v>0.132143342706265</v>
+        <v>0.1528077925689674</v>
       </c>
       <c r="BK4" s="2" t="n">
-        <v>0.1265600728363755</v>
+        <v>0.1455267974458615</v>
       </c>
       <c r="BL4" s="2" t="n">
-        <v>0.1263672197864909</v>
+        <v>0.1444497782946004</v>
       </c>
       <c r="BM4" s="2" t="n">
-        <v>0.1240439245488244</v>
+        <v>0.1417833281751535</v>
       </c>
       <c r="BN4" s="2" t="n">
-        <v>0.1222974958795317</v>
+        <v>0.1401305490360323</v>
       </c>
       <c r="BO4" s="2" t="n">
-        <v>0.1237161646359312</v>
+        <v>0.1410094686279793</v>
       </c>
       <c r="BP4" s="2" t="n">
-        <v>0.1162232204089404</v>
+        <v>0.1312513122516838</v>
       </c>
       <c r="BQ4" s="2" t="n">
-        <v>0.1157639875851854</v>
+        <v>0.1303737017724299</v>
       </c>
       <c r="BR4" s="2" t="n">
-        <v>0.1152552600454683</v>
+        <v>0.1298213712696054</v>
       </c>
       <c r="BS4" s="2" t="n">
-        <v>0.1153199520239638</v>
+        <v>0.129410945561123</v>
       </c>
       <c r="BT4" s="2" t="n">
-        <v>0.1658801376813857</v>
+        <v>0.1918871272561816</v>
       </c>
       <c r="BU4" s="2" t="n">
-        <v>0.163538084502967</v>
+        <v>0.1921577002417673</v>
       </c>
       <c r="BV4" s="2" t="n">
-        <v>0.1603973254994599</v>
+        <v>0.1890166421335977</v>
       </c>
       <c r="BW4" s="2" t="n">
-        <v>0.1610100461747491</v>
+        <v>0.1884422261776385</v>
       </c>
       <c r="BX4" s="2" t="n">
-        <v>0.1598210231867845</v>
+        <v>0.1845083156466693</v>
       </c>
       <c r="BY4" s="2" t="n">
-        <v>0.1561802897795716</v>
+        <v>0.1802159030125927</v>
       </c>
       <c r="BZ4" s="2" t="n">
-        <v>0.1529491590963934</v>
+        <v>0.1756086689276278</v>
       </c>
       <c r="CA4" s="2" t="n">
-        <v>0.1502374114693769</v>
+        <v>0.1720860018273485</v>
       </c>
       <c r="CB4" s="2" t="n">
-        <v>0.1484700974156589</v>
+        <v>0.1692488046771277</v>
       </c>
       <c r="CC4" s="2" t="n">
-        <v>0.1447448243074513</v>
+        <v>0.1640617868978202</v>
       </c>
       <c r="CD4" s="2" t="n">
-        <v>0.1415343091998361</v>
+        <v>0.1592265123217423</v>
       </c>
       <c r="CE4" s="2" t="n">
-        <v>0.1354023754439062</v>
+        <v>0.1513955024575319</v>
       </c>
       <c r="CF4" s="2" t="n">
-        <v>0.1356733424427886</v>
+        <v>0.1514344187656693</v>
       </c>
       <c r="CG4" s="2" t="n">
-        <v>0.1388758915792425</v>
+        <v>0.1548916358030307</v>
       </c>
       <c r="CH4" s="2" t="n">
-        <v>0.1911843636656165</v>
+        <v>0.2223731066742649</v>
       </c>
       <c r="CI4" s="2" t="n">
-        <v>0.1887548467039964</v>
+        <v>0.2236589587425816</v>
       </c>
       <c r="CJ4" s="2" t="n">
-        <v>0.1871097739325467</v>
+        <v>0.2194610077506175</v>
       </c>
       <c r="CK4" s="2" t="n">
-        <v>0.18397978417971</v>
+        <v>0.213549364798435</v>
       </c>
       <c r="CL4" s="2" t="n">
-        <v>0.180815234286098</v>
+        <v>0.2095100481317977</v>
       </c>
       <c r="CM4" s="2" t="n">
-        <v>0.1747087963335352</v>
+        <v>0.2012638056978872</v>
       </c>
       <c r="CN4" s="2" t="n">
-        <v>0.1756368371388364</v>
+        <v>0.2009782727838456</v>
       </c>
       <c r="CO4" s="2" t="n">
-        <v>0.1697345711394965</v>
+        <v>0.193620119469018</v>
       </c>
       <c r="CP4" s="2" t="n">
-        <v>0.1685327879276162</v>
+        <v>0.1914113401656645</v>
       </c>
       <c r="CQ4" s="2" t="n">
-        <v>0.1695409447259139</v>
+        <v>0.1912371130357698</v>
       </c>
       <c r="CR4" s="2" t="n">
-        <v>0.1573693246742304</v>
+        <v>0.1756335241415827</v>
       </c>
       <c r="CS4" s="2" t="n">
-        <v>0.1553316473949261</v>
+        <v>0.1723524013969157</v>
       </c>
       <c r="CT4" s="2" t="n">
-        <v>0.1555408097006606</v>
+        <v>0.1718375811576204</v>
       </c>
       <c r="CU4" s="2" t="n">
-        <v>0.1616481084296129</v>
+        <v>0.1789225375232927</v>
       </c>
       <c r="CV4" s="2" t="n">
-        <v>0.2269130654855585</v>
+        <v>0.2627716841810157</v>
       </c>
       <c r="CW4" s="2" t="n">
-        <v>0.2145930119470834</v>
+        <v>0.251732165129776</v>
       </c>
       <c r="CX4" s="2" t="n">
-        <v>0.2150779390481856</v>
+        <v>0.2486097640344593</v>
       </c>
       <c r="CY4" s="2" t="n">
-        <v>0.2138854072824612</v>
+        <v>0.2464580581730547</v>
       </c>
       <c r="CZ4" s="2" t="n">
-        <v>0.2054402437751598</v>
+        <v>0.2357338501296284</v>
       </c>
       <c r="DA4" s="2" t="n">
-        <v>0.2024267531532871</v>
+        <v>0.2311929564502484</v>
       </c>
       <c r="DB4" s="2" t="n">
-        <v>0.2032976046554289</v>
+        <v>0.230405134553429</v>
       </c>
       <c r="DC4" s="2" t="n">
-        <v>0.1992770910890151</v>
+        <v>0.2238239826432569</v>
       </c>
       <c r="DD4" s="2" t="n">
-        <v>0.1990453138968534</v>
+        <v>0.221927875786649</v>
       </c>
       <c r="DE4" s="2" t="n">
-        <v>0.193621488246976</v>
+        <v>0.2152790525769245</v>
       </c>
       <c r="DF4" s="2" t="n">
-        <v>0.1883060207502518</v>
+        <v>0.2074571542808289</v>
       </c>
       <c r="DG4" s="2" t="n">
-        <v>0.1857700857757836</v>
+        <v>0.2040216519604745</v>
       </c>
       <c r="DH4" s="2" t="n">
-        <v>0.1848061792601149</v>
+        <v>0.2018607118636994</v>
       </c>
       <c r="DI4" s="2" t="n">
-        <v>0.187592345424412</v>
+        <v>0.2045327814035469</v>
       </c>
       <c r="DJ4" s="2" t="n">
-        <v>0.2428449434236502</v>
+        <v>0.2830895745789456</v>
       </c>
       <c r="DK4" s="2" t="n">
-        <v>0.2405809907460848</v>
+        <v>0.2770791278331312</v>
       </c>
       <c r="DL4" s="2" t="n">
-        <v>0.2334189444413799</v>
+        <v>0.2669923787529769</v>
       </c>
       <c r="DM4" s="2" t="n">
-        <v>0.2320106890437281</v>
+        <v>0.2644269791563473</v>
       </c>
       <c r="DN4" s="2" t="n">
-        <v>0.2256003227935036</v>
+        <v>0.2559989811970684</v>
       </c>
       <c r="DO4" s="2" t="n">
-        <v>0.2271847296056477</v>
+        <v>0.2548929647198498</v>
       </c>
       <c r="DP4" s="2" t="n">
-        <v>0.2218491754807354</v>
+        <v>0.2466364040619061</v>
       </c>
       <c r="DQ4" s="2" t="n">
-        <v>0.2161709797193341</v>
+        <v>0.2395611031865414</v>
       </c>
       <c r="DR4" s="2" t="n">
-        <v>0.2149117346084304</v>
+        <v>0.2366930774376839</v>
       </c>
       <c r="DS4" s="2" t="n">
-        <v>0.2123370727926613</v>
+        <v>0.2323908522030973</v>
       </c>
       <c r="DT4" s="2" t="n">
-        <v>0.208113249716532</v>
+        <v>0.2265083314815356</v>
       </c>
       <c r="DU4" s="2" t="n">
-        <v>0.2070289330344123</v>
+        <v>0.2233038706298819</v>
       </c>
       <c r="DV4" s="2" t="n">
-        <v>0.20947914601069</v>
+        <v>0.2262496713503021</v>
       </c>
       <c r="DW4" s="2" t="n">
-        <v>0.2119266208008092</v>
+        <v>0.2281719267758586</v>
       </c>
       <c r="DX4" s="2" t="n">
-        <v>0.2609181921070758</v>
+        <v>0.2974530853471884</v>
       </c>
       <c r="DY4" s="2" t="n">
-        <v>0.2514248892714409</v>
+        <v>0.2855566338092306</v>
       </c>
       <c r="DZ4" s="2" t="n">
-        <v>0.2501804809502957</v>
+        <v>0.2834702021348963</v>
       </c>
       <c r="EA4" s="2" t="n">
-        <v>0.2437709663081606</v>
+        <v>0.2729944446284414</v>
       </c>
       <c r="EB4" s="2" t="n">
-        <v>0.2436020223028637</v>
+        <v>0.2700533213238718</v>
       </c>
       <c r="EC4" s="2" t="n">
-        <v>0.237895121860803</v>
+        <v>0.2631357636476966</v>
       </c>
       <c r="ED4" s="2" t="n">
-        <v>0.2356398850151195</v>
+        <v>0.2587819864373592</v>
       </c>
       <c r="EE4" s="2" t="n">
-        <v>0.2344340320049843</v>
+        <v>0.2559622945283424</v>
       </c>
       <c r="EF4" s="2" t="n">
-        <v>0.2321741480726037</v>
+        <v>0.2529638623875231</v>
       </c>
       <c r="EG4" s="2" t="n">
-        <v>0.2304276002127537</v>
+        <v>0.2500809442836476</v>
       </c>
       <c r="EH4" s="2" t="n">
-        <v>0.2192595547184655</v>
+        <v>0.2368374451327144</v>
       </c>
       <c r="EI4" s="2" t="n">
-        <v>0.2233159702226298</v>
+        <v>0.2389674722103995</v>
       </c>
       <c r="EJ4" s="2" t="n">
-        <v>0.2247432827493071</v>
+        <v>0.2390220403463788</v>
       </c>
       <c r="EK4" s="2" t="n">
-        <v>0.2260777698623381</v>
+        <v>0.2413649509913743</v>
       </c>
       <c r="EL4" s="2" t="n">
-        <v>0.2725228363688569</v>
+        <v>0.3032865860249836</v>
       </c>
       <c r="EM4" s="2" t="n">
-        <v>0.2699331790800896</v>
+        <v>0.2971829725996277</v>
       </c>
       <c r="EN4" s="2" t="n">
-        <v>0.2660072160014023</v>
+        <v>0.2910130949586285</v>
       </c>
       <c r="EO4" s="2" t="n">
-        <v>0.2596210762457808</v>
+        <v>0.2823259211475632</v>
       </c>
       <c r="EP4" s="2" t="n">
-        <v>0.2630214082877496</v>
+        <v>0.2848335916414553</v>
       </c>
       <c r="EQ4" s="2" t="n">
-        <v>0.2525539507054037</v>
+        <v>0.272370724797201</v>
       </c>
       <c r="ER4" s="2" t="n">
-        <v>0.2523718974840459</v>
+        <v>0.2725858583946231</v>
       </c>
       <c r="ES4" s="2" t="n">
-        <v>0.2469536066632696</v>
+        <v>0.2648707711225387</v>
       </c>
       <c r="ET4" s="2" t="n">
-        <v>0.2497322202774724</v>
+        <v>0.2668991225111</v>
       </c>
       <c r="EU4" s="2" t="n">
-        <v>0.2492723559028377</v>
+        <v>0.2654204900868127</v>
       </c>
       <c r="EV4" s="2" t="n">
-        <v>0.2458440373682043</v>
+        <v>0.2615172774021953</v>
       </c>
       <c r="EW4" s="2" t="n">
-        <v>0.2460090730277721</v>
+        <v>0.259996172364123</v>
       </c>
       <c r="EX4" s="2" t="n">
-        <v>0.2461999976620051</v>
+        <v>0.2592943006692043</v>
       </c>
       <c r="EY4" s="2" t="n">
-        <v>0.2580036143237596</v>
+        <v>0.272201837997985</v>
       </c>
       <c r="EZ4" s="2" t="n">
-        <v>0.2814303873283477</v>
+        <v>0.2990633640309601</v>
       </c>
       <c r="FA4" s="2" t="n">
-        <v>0.2821052457164092</v>
+        <v>0.2992624940832617</v>
       </c>
       <c r="FB4" s="2" t="n">
-        <v>0.2716479833436487</v>
+        <v>0.2874849681250449</v>
       </c>
       <c r="FC4" s="2" t="n">
-        <v>0.2740659668732232</v>
+        <v>0.289572342256323</v>
       </c>
       <c r="FD4" s="2" t="n">
-        <v>0.2647806629879851</v>
+        <v>0.2793430181277108</v>
       </c>
       <c r="FE4" s="2" t="n">
-        <v>0.2663050446341734</v>
+        <v>0.2809534496367786</v>
       </c>
       <c r="FF4" s="2" t="n">
-        <v>0.2659687405851714</v>
+        <v>0.2803668060229901</v>
       </c>
       <c r="FG4" s="2" t="n">
-        <v>0.2627995823545955</v>
+        <v>0.277096629231305</v>
       </c>
       <c r="FH4" s="2" t="n">
-        <v>0.2583665211572261</v>
+        <v>0.2723679320365889</v>
       </c>
       <c r="FI4" s="2" t="n">
-        <v>0.2571446892903111</v>
+        <v>0.2710425974618008</v>
       </c>
       <c r="FJ4" s="2" t="n">
-        <v>0.2595614718450892</v>
+        <v>0.2734059583644494</v>
       </c>
       <c r="FK4" s="2" t="n">
-        <v>0.2619605699896267</v>
+        <v>0.2742971105394396</v>
       </c>
       <c r="FL4" s="2" t="n">
-        <v>0.2717974814538589</v>
+        <v>0.2841924964540348</v>
       </c>
       <c r="FM4" s="2" t="n">
-        <v>0.2820444021434736</v>
+        <v>0.2949420139737131</v>
       </c>
       <c r="FN4" s="2" t="n">
-        <v>0.2860341112154146</v>
+        <v>0.3023898125197296</v>
       </c>
       <c r="FO4" s="2" t="n">
-        <v>0.2864945247025913</v>
+        <v>0.3020518215091094</v>
       </c>
       <c r="FP4" s="2" t="n">
-        <v>0.2786385802594764</v>
+        <v>0.293622826446825</v>
       </c>
       <c r="FQ4" s="2" t="n">
-        <v>0.2766511833911737</v>
+        <v>0.2917229412994232</v>
       </c>
       <c r="FR4" s="2" t="n">
-        <v>0.281972778427258</v>
+        <v>0.2975323776850581</v>
       </c>
       <c r="FS4" s="2" t="n">
-        <v>0.2796645873883514</v>
+        <v>0.2954064657719226</v>
       </c>
       <c r="FT4" s="2" t="n">
-        <v>0.2798649149563903</v>
+        <v>0.2960053270967867</v>
       </c>
       <c r="FU4" s="2" t="n">
-        <v>0.2779542494047293</v>
+        <v>0.2942711566040751</v>
       </c>
       <c r="FV4" s="2" t="n">
-        <v>0.2797838210557953</v>
+        <v>0.2964009004014155</v>
       </c>
       <c r="FW4" s="2" t="n">
-        <v>0.2801713775085937</v>
+        <v>0.2970014313344114</v>
       </c>
       <c r="FX4" s="2" t="n">
-        <v>0.2796850249128229</v>
+        <v>0.2954789290485018</v>
       </c>
       <c r="FY4" s="2" t="n">
-        <v>0.2906540817153804</v>
+        <v>0.3058867464718714</v>
       </c>
       <c r="FZ4" s="2" t="n">
-        <v>0.294935400739074</v>
+        <v>0.3109451284186611</v>
       </c>
       <c r="GA4" s="2" t="n">
-        <v>0.3097892998517737</v>
+        <v>0.3259159345484623</v>
       </c>
       <c r="GB4" s="2" t="n">
-        <v>0.3013862190931629</v>
+        <v>0.3232906393224539</v>
       </c>
       <c r="GC4" s="2" t="n">
-        <v>0.3019753588169836</v>
+        <v>0.3244577242275014</v>
       </c>
       <c r="GD4" s="2" t="n">
-        <v>0.3031276985761032</v>
+        <v>0.3265265639190996</v>
       </c>
       <c r="GE4" s="2" t="n">
-        <v>0.3030257307899826</v>
+        <v>0.3267237522333781</v>
       </c>
       <c r="GF4" s="2" t="n">
-        <v>0.3012083520425725</v>
+        <v>0.3245194112242734</v>
       </c>
       <c r="GG4" s="2" t="n">
-        <v>0.2996223602307226</v>
+        <v>0.3225036525460563</v>
       </c>
       <c r="GH4" s="2" t="n">
-        <v>0.2960702240640674</v>
+        <v>0.3189389013711919</v>
       </c>
       <c r="GI4" s="2" t="n">
-        <v>0.2971324822306355</v>
+        <v>0.3193189155487088</v>
       </c>
       <c r="GJ4" s="2" t="n">
-        <v>0.2972905645231341</v>
+        <v>0.3198983858134861</v>
       </c>
       <c r="GK4" s="2" t="n">
-        <v>0.3012214126549149</v>
+        <v>0.324040913764142</v>
       </c>
       <c r="GL4" s="2" t="n">
-        <v>0.3082641502875313</v>
+        <v>0.3297948710674808</v>
       </c>
       <c r="GM4" s="2" t="n">
-        <v>0.3152524172264353</v>
+        <v>0.335412721038766</v>
       </c>
       <c r="GN4" s="2" t="n">
-        <v>0.3302082878816537</v>
+        <v>0.3508941681671052</v>
       </c>
       <c r="GO4" s="2" t="n">
-        <v>0.3378042618405498</v>
+        <v>0.3601672092257197</v>
       </c>
       <c r="GP4" s="2" t="n">
-        <v>0.3299402575143537</v>
+        <v>0.352994728544894</v>
       </c>
       <c r="GQ4" s="2" t="n">
-        <v>0.3274411167874508</v>
+        <v>0.3487749796825085</v>
       </c>
       <c r="GR4" s="2" t="n">
-        <v>0.3259331334462604</v>
+        <v>0.3481590359708516</v>
       </c>
       <c r="GS4" s="2" t="n">
-        <v>0.3244325744708925</v>
+        <v>0.3463946600541053</v>
       </c>
       <c r="GT4" s="2" t="n">
-        <v>0.3258851903562224</v>
+        <v>0.3484312106702905</v>
       </c>
       <c r="GU4" s="2" t="n">
-        <v>0.3203112899325802</v>
+        <v>0.3427690237565244</v>
       </c>
       <c r="GV4" s="2" t="n">
-        <v>0.3253140377687995</v>
+        <v>0.3486308026389003</v>
       </c>
       <c r="GW4" s="2" t="n">
-        <v>0.3206391639360312</v>
+        <v>0.3436196579952673</v>
       </c>
       <c r="GX4" s="2" t="n">
-        <v>0.3216799928737913</v>
+        <v>0.3452376159921292</v>
       </c>
       <c r="GY4" s="2" t="n">
-        <v>0.3219716134463018</v>
+        <v>0.3461044124051811</v>
       </c>
       <c r="GZ4" s="2" t="n">
-        <v>0.3355021710566444</v>
+        <v>0.3584210579063948</v>
       </c>
       <c r="HA4" s="2" t="n">
-        <v>0.3485442185226089</v>
+        <v>0.3706782167144266</v>
       </c>
       <c r="HB4" s="2" t="n">
-        <v>0.3607001204585671</v>
+        <v>0.3846852635094284</v>
       </c>
       <c r="HC4" s="2" t="n">
-        <v>0.3555976966136533</v>
+        <v>0.3746689546974368</v>
       </c>
       <c r="HD4" s="2" t="n">
-        <v>0.3430663982911665</v>
+        <v>0.3704231429350535</v>
       </c>
       <c r="HE4" s="2" t="n">
-        <v>0.3385962593326385</v>
+        <v>0.3642517630285451</v>
       </c>
       <c r="HF4" s="2" t="n">
-        <v>0.3401340318000398</v>
+        <v>0.3661939244141561</v>
       </c>
       <c r="HG4" s="2" t="n">
-        <v>0.3463280295337608</v>
+        <v>0.3736394133477739</v>
       </c>
       <c r="HH4" s="2" t="n">
-        <v>0.3448702166232785</v>
+        <v>0.3733263371453815</v>
       </c>
       <c r="HI4" s="2" t="n">
-        <v>0.3430718892975396</v>
+        <v>0.3722075440427537</v>
       </c>
       <c r="HJ4" s="2" t="n">
-        <v>0.3452255918305785</v>
+        <v>0.3755844707548776</v>
       </c>
       <c r="HK4" s="2" t="n">
-        <v>0.3390081398646101</v>
+        <v>0.3695375771288706</v>
       </c>
       <c r="HL4" s="2" t="n">
-        <v>0.3404065830425996</v>
+        <v>0.3721071744459541</v>
       </c>
       <c r="HM4" s="2" t="n">
-        <v>0.3372146003448917</v>
+        <v>0.3698326564441826</v>
       </c>
       <c r="HN4" s="2" t="n">
-        <v>0.3598677349020928</v>
+        <v>0.3918735313650622</v>
       </c>
       <c r="HO4" s="2" t="n">
-        <v>0.3740603257070509</v>
+        <v>0.4060177162498385</v>
       </c>
       <c r="HP4" s="2" t="n">
-        <v>0.355710644302732</v>
+        <v>0.3782264375145689</v>
       </c>
       <c r="HQ4" s="2" t="n">
-        <v>0.3453663200860274</v>
+        <v>0.3615241243597562</v>
       </c>
       <c r="HR4" s="3" t="n">
         <v>55514</v>
@@ -3555,676 +3555,676 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.02444780639208735</v>
+        <v>0.02918500620868477</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.03237487993792686</v>
+        <v>0.03806103436407338</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.03426154747906859</v>
+        <v>0.04014434790143438</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.03573490053411237</v>
+        <v>0.04164978029545744</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.03613222335849506</v>
+        <v>0.0419340212467792</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.03546196971537827</v>
+        <v>0.04103504644579856</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.03495113369090708</v>
+        <v>0.04034000561957822</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.03457146082815026</v>
+        <v>0.04000229234013929</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03481799726525824</v>
+        <v>0.04019793081113983</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03419026900599027</v>
+        <v>0.03939409422254612</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.03325146192625164</v>
+        <v>0.03814224962887557</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.03244673791080416</v>
+        <v>0.03667017903727578</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.03238523604987006</v>
+        <v>0.03656675475292655</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.03302510712928656</v>
+        <v>0.03710270765039616</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.04915147064367589</v>
+        <v>0.05668346282729922</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.05939759542953686</v>
+        <v>0.06843880048906589</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.06167916033413742</v>
+        <v>0.07153284964517669</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.06265266118706755</v>
+        <v>0.07202696670600774</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.063728334590165</v>
+        <v>0.07325577195439271</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.06157228725429827</v>
+        <v>0.07032834557519517</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.06240028250369117</v>
+        <v>0.07116098571345714</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.06204978005427305</v>
+        <v>0.07045088853857789</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.06146670238059046</v>
+        <v>0.0700372106140707</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.06105554469992842</v>
+        <v>0.06941728134465089</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.05821413884896452</v>
+        <v>0.06585892550022693</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.05623414968867654</v>
+        <v>0.06301114552970616</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>0.05605640805504707</v>
+        <v>0.06295059537428921</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.05752695619146232</v>
+        <v>0.06416676334285627</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>0.07993068785314278</v>
+        <v>0.09008956963591548</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>0.09049327097863377</v>
+        <v>0.1028337293200008</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.08989176268579871</v>
+        <v>0.1032453318723098</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>0.09197117740483347</v>
+        <v>0.1044906292549647</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.09224335246303007</v>
+        <v>0.1046991657803363</v>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>0.09167843967034012</v>
+        <v>0.1037512114548998</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>0.08870784013519456</v>
+        <v>0.1001748207038431</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>0.08792987859489126</v>
+        <v>0.09881707005972229</v>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>0.08810198775528305</v>
+        <v>0.09933842002491039</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>0.08519965482905298</v>
+        <v>0.09588967943799465</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.08152226490327619</v>
+        <v>0.09062828592385953</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>0.07976799450074241</v>
+        <v>0.08835464930768538</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>0.08186513838183601</v>
+        <v>0.09084998445392314</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.08267008421781863</v>
+        <v>0.09134552258754666</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.1082633479729895</v>
+        <v>0.1206822480680899</v>
       </c>
       <c r="AS5" s="2" t="n">
-        <v>0.1133907662757746</v>
+        <v>0.1295125648270128</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>0.1140578397733534</v>
+        <v>0.1299130770346392</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>0.1159434490820538</v>
+        <v>0.1302742492968801</v>
       </c>
       <c r="AV5" s="2" t="n">
-        <v>0.1138016992614481</v>
+        <v>0.1291668977064327</v>
       </c>
       <c r="AW5" s="2" t="n">
-        <v>0.1100836389222555</v>
+        <v>0.1236884023474931</v>
       </c>
       <c r="AX5" s="2" t="n">
-        <v>0.1105792630710763</v>
+        <v>0.1241158222311405</v>
       </c>
       <c r="AY5" s="2" t="n">
-        <v>0.1099376532474698</v>
+        <v>0.1228008533228656</v>
       </c>
       <c r="AZ5" s="2" t="n">
-        <v>0.1085064942504584</v>
+        <v>0.1215229747987212</v>
       </c>
       <c r="BA5" s="2" t="n">
-        <v>0.1051086496712751</v>
+        <v>0.1171213233289786</v>
       </c>
       <c r="BB5" s="2" t="n">
-        <v>0.1008659562605647</v>
+        <v>0.11134912243384</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>0.09942167183421324</v>
+        <v>0.109492978143952</v>
       </c>
       <c r="BD5" s="2" t="n">
-        <v>0.09823981029506809</v>
+        <v>0.1081785008018836</v>
       </c>
       <c r="BE5" s="2" t="n">
-        <v>0.1013153848351704</v>
+        <v>0.1111605791635679</v>
       </c>
       <c r="BF5" s="2" t="n">
-        <v>0.1349533374882825</v>
+        <v>0.150573591955467</v>
       </c>
       <c r="BG5" s="2" t="n">
-        <v>0.1358781554333243</v>
+        <v>0.1541596606473553</v>
       </c>
       <c r="BH5" s="2" t="n">
-        <v>0.1355070704463995</v>
+        <v>0.1530401733966047</v>
       </c>
       <c r="BI5" s="2" t="n">
-        <v>0.1320350235788408</v>
+        <v>0.1492911463863563</v>
       </c>
       <c r="BJ5" s="2" t="n">
-        <v>0.132344071170825</v>
+        <v>0.1495895098021539</v>
       </c>
       <c r="BK5" s="2" t="n">
-        <v>0.1266743504493971</v>
+        <v>0.1422388457959693</v>
       </c>
       <c r="BL5" s="2" t="n">
-        <v>0.1263898085565433</v>
+        <v>0.1410190725692073</v>
       </c>
       <c r="BM5" s="2" t="n">
-        <v>0.1240841141482032</v>
+        <v>0.1381757952051193</v>
       </c>
       <c r="BN5" s="2" t="n">
-        <v>0.1222501253933406</v>
+        <v>0.1363208268641962</v>
       </c>
       <c r="BO5" s="2" t="n">
-        <v>0.1236302091774609</v>
+        <v>0.1371390938714008</v>
       </c>
       <c r="BP5" s="2" t="n">
-        <v>0.1161565198804803</v>
+        <v>0.1276045307496645</v>
       </c>
       <c r="BQ5" s="2" t="n">
-        <v>0.115743813465665</v>
+        <v>0.126612001829341</v>
       </c>
       <c r="BR5" s="2" t="n">
-        <v>0.1152486061353246</v>
+        <v>0.1260027670171435</v>
       </c>
       <c r="BS5" s="2" t="n">
-        <v>0.1153189504577685</v>
+        <v>0.1256052385887771</v>
       </c>
       <c r="BT5" s="2" t="n">
-        <v>0.1668098448596415</v>
+        <v>0.1906735906324964</v>
       </c>
       <c r="BU5" s="2" t="n">
-        <v>0.163965963961428</v>
+        <v>0.1888679191883235</v>
       </c>
       <c r="BV5" s="2" t="n">
-        <v>0.1606253154628253</v>
+        <v>0.1848012089743658</v>
       </c>
       <c r="BW5" s="2" t="n">
-        <v>0.1608963095113758</v>
+        <v>0.1836053156799252</v>
       </c>
       <c r="BX5" s="2" t="n">
-        <v>0.1598548411329171</v>
+        <v>0.1799838817953704</v>
       </c>
       <c r="BY5" s="2" t="n">
-        <v>0.1562420863888029</v>
+        <v>0.1755424509717121</v>
       </c>
       <c r="BZ5" s="2" t="n">
-        <v>0.1528424520174897</v>
+        <v>0.1707873315716341</v>
       </c>
       <c r="CA5" s="2" t="n">
-        <v>0.1501603755103619</v>
+        <v>0.167249017141767</v>
       </c>
       <c r="CB5" s="2" t="n">
-        <v>0.1483871603013575</v>
+        <v>0.1645486595533305</v>
       </c>
       <c r="CC5" s="2" t="n">
-        <v>0.1446433440183938</v>
+        <v>0.1595806129244924</v>
       </c>
       <c r="CD5" s="2" t="n">
-        <v>0.1414351678288244</v>
+        <v>0.154793545155766</v>
       </c>
       <c r="CE5" s="2" t="n">
-        <v>0.1353809163023824</v>
+        <v>0.1471791169115109</v>
       </c>
       <c r="CF5" s="2" t="n">
-        <v>0.1356631113114153</v>
+        <v>0.1472126860868415</v>
       </c>
       <c r="CG5" s="2" t="n">
-        <v>0.1388770938686108</v>
+        <v>0.1504686107995493</v>
       </c>
       <c r="CH5" s="2" t="n">
-        <v>0.1915312399423797</v>
+        <v>0.218192631777874</v>
       </c>
       <c r="CI5" s="2" t="n">
-        <v>0.1887209343505475</v>
+        <v>0.2177191258371891</v>
       </c>
       <c r="CJ5" s="2" t="n">
-        <v>0.1870878349708917</v>
+        <v>0.2134849131830254</v>
       </c>
       <c r="CK5" s="2" t="n">
-        <v>0.1838263738986339</v>
+        <v>0.2075634612842481</v>
       </c>
       <c r="CL5" s="2" t="n">
-        <v>0.1806826718648038</v>
+        <v>0.2034394749618517</v>
       </c>
       <c r="CM5" s="2" t="n">
-        <v>0.1746319816517908</v>
+        <v>0.1954450088978214</v>
       </c>
       <c r="CN5" s="2" t="n">
-        <v>0.1755318654333273</v>
+        <v>0.1952499826287364</v>
       </c>
       <c r="CO5" s="2" t="n">
-        <v>0.1696015504027794</v>
+        <v>0.1879933731643182</v>
       </c>
       <c r="CP5" s="2" t="n">
-        <v>0.1683363876174819</v>
+        <v>0.1858565181100113</v>
       </c>
       <c r="CQ5" s="2" t="n">
-        <v>0.169295920236486</v>
+        <v>0.1858117892942001</v>
       </c>
       <c r="CR5" s="2" t="n">
-        <v>0.1573181719981173</v>
+        <v>0.1709716157734069</v>
       </c>
       <c r="CS5" s="2" t="n">
-        <v>0.1553237663226818</v>
+        <v>0.1677144433122025</v>
       </c>
       <c r="CT5" s="2" t="n">
-        <v>0.1555745885236227</v>
+        <v>0.167359994655565</v>
       </c>
       <c r="CU5" s="2" t="n">
-        <v>0.1616596573648861</v>
+        <v>0.1740561317951679</v>
       </c>
       <c r="CV5" s="2" t="n">
-        <v>0.2266504150034231</v>
+        <v>0.2554401271344611</v>
       </c>
       <c r="CW5" s="2" t="n">
-        <v>0.2142928932868706</v>
+        <v>0.2437814082374064</v>
       </c>
       <c r="CX5" s="2" t="n">
-        <v>0.2148834012593509</v>
+        <v>0.2413644315498585</v>
       </c>
       <c r="CY5" s="2" t="n">
-        <v>0.2137965697008065</v>
+        <v>0.2391983666077644</v>
       </c>
       <c r="CZ5" s="2" t="n">
-        <v>0.2052212175840997</v>
+        <v>0.2285517445925703</v>
       </c>
       <c r="DA5" s="2" t="n">
-        <v>0.2021921922719029</v>
+        <v>0.2241873020432346</v>
       </c>
       <c r="DB5" s="2" t="n">
-        <v>0.2030754373933106</v>
+        <v>0.2237129980709291</v>
       </c>
       <c r="DC5" s="2" t="n">
-        <v>0.1990182028061808</v>
+        <v>0.217578359004872</v>
       </c>
       <c r="DD5" s="2" t="n">
-        <v>0.198979527922527</v>
+        <v>0.2162544998832456</v>
       </c>
       <c r="DE5" s="2" t="n">
-        <v>0.1935582718243319</v>
+        <v>0.2098109906544013</v>
       </c>
       <c r="DF5" s="2" t="n">
-        <v>0.188287860101983</v>
+        <v>0.2023479482358224</v>
       </c>
       <c r="DG5" s="2" t="n">
-        <v>0.1857048187585465</v>
+        <v>0.1988789434894754</v>
       </c>
       <c r="DH5" s="2" t="n">
-        <v>0.1848100141967423</v>
+        <v>0.1970156251755939</v>
       </c>
       <c r="DI5" s="2" t="n">
-        <v>0.1876495844482999</v>
+        <v>0.1995631987871986</v>
       </c>
       <c r="DJ5" s="2" t="n">
-        <v>0.2426992093480058</v>
+        <v>0.2741586359163021</v>
       </c>
       <c r="DK5" s="2" t="n">
-        <v>0.2405258172971843</v>
+        <v>0.2687844636465541</v>
       </c>
       <c r="DL5" s="2" t="n">
-        <v>0.2331521589984819</v>
+        <v>0.2589691944420943</v>
       </c>
       <c r="DM5" s="2" t="n">
-        <v>0.231775912893233</v>
+        <v>0.2565899437517218</v>
       </c>
       <c r="DN5" s="2" t="n">
-        <v>0.2253957877943723</v>
+        <v>0.2484246052332354</v>
       </c>
       <c r="DO5" s="2" t="n">
-        <v>0.2268882295526795</v>
+        <v>0.2477359296728167</v>
       </c>
       <c r="DP5" s="2" t="n">
-        <v>0.2217122155259478</v>
+        <v>0.2402978650250836</v>
       </c>
       <c r="DQ5" s="2" t="n">
-        <v>0.2160712777986281</v>
+        <v>0.2335396930988516</v>
       </c>
       <c r="DR5" s="2" t="n">
-        <v>0.2149202327576358</v>
+        <v>0.2311153099176975</v>
       </c>
       <c r="DS5" s="2" t="n">
-        <v>0.2124117057749803</v>
+        <v>0.227234352015225</v>
       </c>
       <c r="DT5" s="2" t="n">
-        <v>0.2081369954254156</v>
+        <v>0.2214849746020199</v>
       </c>
       <c r="DU5" s="2" t="n">
-        <v>0.2070290826997196</v>
+        <v>0.2185980365130854</v>
       </c>
       <c r="DV5" s="2" t="n">
-        <v>0.2095496181935484</v>
+        <v>0.2213878110223504</v>
       </c>
       <c r="DW5" s="2" t="n">
-        <v>0.2120100034864152</v>
+        <v>0.2232353582061151</v>
       </c>
       <c r="DX5" s="2" t="n">
-        <v>0.2607425041683241</v>
+        <v>0.2887729693477155</v>
       </c>
       <c r="DY5" s="2" t="n">
-        <v>0.2512177507924205</v>
+        <v>0.2772721495203782</v>
       </c>
       <c r="DZ5" s="2" t="n">
-        <v>0.250037980885567</v>
+        <v>0.2753093327437638</v>
       </c>
       <c r="EA5" s="2" t="n">
-        <v>0.2435269544204771</v>
+        <v>0.2655833497151999</v>
       </c>
       <c r="EB5" s="2" t="n">
-        <v>0.2435102338687638</v>
+        <v>0.2633504955946153</v>
       </c>
       <c r="EC5" s="2" t="n">
-        <v>0.2378170091378054</v>
+        <v>0.2566793747048076</v>
       </c>
       <c r="ED5" s="2" t="n">
-        <v>0.2356450565747274</v>
+        <v>0.2528651574857377</v>
       </c>
       <c r="EE5" s="2" t="n">
-        <v>0.2345119882619648</v>
+        <v>0.2504136572936525</v>
       </c>
       <c r="EF5" s="2" t="n">
-        <v>0.2321895662026749</v>
+        <v>0.2475518223071844</v>
       </c>
       <c r="EG5" s="2" t="n">
-        <v>0.23044125149641</v>
+        <v>0.2448492194300042</v>
       </c>
       <c r="EH5" s="2" t="n">
-        <v>0.2193531010428611</v>
+        <v>0.2318649517854362</v>
       </c>
       <c r="EI5" s="2" t="n">
-        <v>0.2234413583304506</v>
+        <v>0.2344373932984389</v>
       </c>
       <c r="EJ5" s="2" t="n">
-        <v>0.2249134092642984</v>
+        <v>0.2346666502938471</v>
       </c>
       <c r="EK5" s="2" t="n">
-        <v>0.226230955036825</v>
+        <v>0.2367007914031151</v>
       </c>
       <c r="EL5" s="2" t="n">
-        <v>0.2723343916456234</v>
+        <v>0.2952869563434929</v>
       </c>
       <c r="EM5" s="2" t="n">
-        <v>0.2699210938273897</v>
+        <v>0.2900470781727004</v>
       </c>
       <c r="EN5" s="2" t="n">
-        <v>0.2660836106989797</v>
+        <v>0.2845597035940579</v>
       </c>
       <c r="EO5" s="2" t="n">
-        <v>0.2597119977996157</v>
+        <v>0.2763850919914386</v>
       </c>
       <c r="EP5" s="2" t="n">
-        <v>0.2630928776995601</v>
+        <v>0.2790949011613677</v>
       </c>
       <c r="EQ5" s="2" t="n">
-        <v>0.2526568401930856</v>
+        <v>0.2670915965295448</v>
       </c>
       <c r="ER5" s="2" t="n">
-        <v>0.2525373815901484</v>
+        <v>0.2673631572446798</v>
       </c>
       <c r="ES5" s="2" t="n">
-        <v>0.2471849657337882</v>
+        <v>0.2600275784331839</v>
       </c>
       <c r="ET5" s="2" t="n">
-        <v>0.2499368167999882</v>
+        <v>0.2623453998059324</v>
       </c>
       <c r="EU5" s="2" t="n">
-        <v>0.2494577111508792</v>
+        <v>0.2608984953982417</v>
       </c>
       <c r="EV5" s="2" t="n">
-        <v>0.2460563739789914</v>
+        <v>0.2569910774390616</v>
       </c>
       <c r="EW5" s="2" t="n">
-        <v>0.2462683411468732</v>
+        <v>0.2559003591043845</v>
       </c>
       <c r="EX5" s="2" t="n">
-        <v>0.2464663579473089</v>
+        <v>0.2552333031151012</v>
       </c>
       <c r="EY5" s="2" t="n">
-        <v>0.258325298461267</v>
+        <v>0.2678170503851423</v>
       </c>
       <c r="EZ5" s="2" t="n">
-        <v>0.2815845460831079</v>
+        <v>0.2942343967550791</v>
       </c>
       <c r="FA5" s="2" t="n">
-        <v>0.2823287466541431</v>
+        <v>0.2946275778391291</v>
       </c>
       <c r="FB5" s="2" t="n">
-        <v>0.2719110797194232</v>
+        <v>0.2832985391542618</v>
       </c>
       <c r="FC5" s="2" t="n">
-        <v>0.274378682612782</v>
+        <v>0.2854632941915548</v>
       </c>
       <c r="FD5" s="2" t="n">
-        <v>0.2651010445282811</v>
+        <v>0.2754301024156436</v>
       </c>
       <c r="FE5" s="2" t="n">
-        <v>0.2666305588190741</v>
+        <v>0.2769219091693698</v>
       </c>
       <c r="FF5" s="2" t="n">
-        <v>0.2663164233750834</v>
+        <v>0.2764851201234452</v>
       </c>
       <c r="FG5" s="2" t="n">
-        <v>0.2631394522847676</v>
+        <v>0.2731571211661999</v>
       </c>
       <c r="FH5" s="2" t="n">
-        <v>0.2586945598658601</v>
+        <v>0.2685046841429267</v>
       </c>
       <c r="FI5" s="2" t="n">
-        <v>0.257462983559278</v>
+        <v>0.267197687714997</v>
       </c>
       <c r="FJ5" s="2" t="n">
-        <v>0.2598793490318824</v>
+        <v>0.2693599824612673</v>
       </c>
       <c r="FK5" s="2" t="n">
-        <v>0.2622928187262542</v>
+        <v>0.2704524382095567</v>
       </c>
       <c r="FL5" s="2" t="n">
-        <v>0.2722109472751125</v>
+        <v>0.280316806141749</v>
       </c>
       <c r="FM5" s="2" t="n">
-        <v>0.2824825529807363</v>
+        <v>0.2908591653212089</v>
       </c>
       <c r="FN5" s="2" t="n">
-        <v>0.2864834962400881</v>
+        <v>0.298066688203449</v>
       </c>
       <c r="FO5" s="2" t="n">
-        <v>0.2869309391823952</v>
+        <v>0.2978555500320459</v>
       </c>
       <c r="FP5" s="2" t="n">
-        <v>0.279043418015501</v>
+        <v>0.2895051159623938</v>
       </c>
       <c r="FQ5" s="2" t="n">
-        <v>0.2770783065477312</v>
+        <v>0.2875421339838846</v>
       </c>
       <c r="FR5" s="2" t="n">
-        <v>0.2823765340968513</v>
+        <v>0.2932627889354639</v>
       </c>
       <c r="FS5" s="2" t="n">
-        <v>0.2800667221839669</v>
+        <v>0.2909366294395933</v>
       </c>
       <c r="FT5" s="2" t="n">
-        <v>0.2802382146137565</v>
+        <v>0.2913881481219944</v>
       </c>
       <c r="FU5" s="2" t="n">
-        <v>0.278317850683062</v>
+        <v>0.2895435265794428</v>
       </c>
       <c r="FV5" s="2" t="n">
-        <v>0.2801443567489359</v>
+        <v>0.2914510448254289</v>
       </c>
       <c r="FW5" s="2" t="n">
-        <v>0.2805260032810503</v>
+        <v>0.2919635990872778</v>
       </c>
       <c r="FX5" s="2" t="n">
-        <v>0.2800476474224548</v>
+        <v>0.2904371293682457</v>
       </c>
       <c r="FY5" s="2" t="n">
-        <v>0.2910367372064669</v>
+        <v>0.3007865573483584</v>
       </c>
       <c r="FZ5" s="2" t="n">
-        <v>0.295364569811273</v>
+        <v>0.3057243094552099</v>
       </c>
       <c r="GA5" s="2" t="n">
-        <v>0.3102401582074164</v>
+        <v>0.320666060801532</v>
       </c>
       <c r="GB5" s="2" t="n">
-        <v>0.301735441151345</v>
+        <v>0.3169960489516674</v>
       </c>
       <c r="GC5" s="2" t="n">
-        <v>0.3023202863850658</v>
+        <v>0.317920842615556</v>
       </c>
       <c r="GD5" s="2" t="n">
-        <v>0.3034490459149729</v>
+        <v>0.3196793968736452</v>
       </c>
       <c r="GE5" s="2" t="n">
-        <v>0.3033480401993984</v>
+        <v>0.3197789142352725</v>
       </c>
       <c r="GF5" s="2" t="n">
-        <v>0.3015185494021778</v>
+        <v>0.3175800619926452</v>
       </c>
       <c r="GG5" s="2" t="n">
-        <v>0.2999433453149842</v>
+        <v>0.3156846395098653</v>
       </c>
       <c r="GH5" s="2" t="n">
-        <v>0.2963217338953946</v>
+        <v>0.3118655500658385</v>
       </c>
       <c r="GI5" s="2" t="n">
-        <v>0.2973812012407822</v>
+        <v>0.3119909791324014</v>
       </c>
       <c r="GJ5" s="2" t="n">
-        <v>0.2976076896716847</v>
+        <v>0.3128764958980542</v>
       </c>
       <c r="GK5" s="2" t="n">
-        <v>0.301551498023396</v>
+        <v>0.3168458601657196</v>
       </c>
       <c r="GL5" s="2" t="n">
-        <v>0.3086397379427297</v>
+        <v>0.3227299934890357</v>
       </c>
       <c r="GM5" s="2" t="n">
-        <v>0.3156938605655846</v>
+        <v>0.3286132096444736</v>
       </c>
       <c r="GN5" s="2" t="n">
-        <v>0.3307492671635385</v>
+        <v>0.3441493489765652</v>
       </c>
       <c r="GO5" s="2" t="n">
-        <v>0.3383421855996731</v>
+        <v>0.352997307532294</v>
       </c>
       <c r="GP5" s="2" t="n">
-        <v>0.3303607141326175</v>
+        <v>0.3459539544558627</v>
       </c>
       <c r="GQ5" s="2" t="n">
-        <v>0.3279010288514003</v>
+        <v>0.3421110848252223</v>
       </c>
       <c r="GR5" s="2" t="n">
-        <v>0.3262949969576937</v>
+        <v>0.3412663239265173</v>
       </c>
       <c r="GS5" s="2" t="n">
-        <v>0.3248421319637478</v>
+        <v>0.3395627537206174</v>
       </c>
       <c r="GT5" s="2" t="n">
-        <v>0.3263015609491481</v>
+        <v>0.3413887245889669</v>
       </c>
       <c r="GU5" s="2" t="n">
-        <v>0.320734322464771</v>
+        <v>0.3356708292138598</v>
       </c>
       <c r="GV5" s="2" t="n">
-        <v>0.3257656418194166</v>
+        <v>0.3413139748956537</v>
       </c>
       <c r="GW5" s="2" t="n">
-        <v>0.3211294377851161</v>
+        <v>0.3363673052832671</v>
       </c>
       <c r="GX5" s="2" t="n">
-        <v>0.3221949286553005</v>
+        <v>0.3378168051124882</v>
       </c>
       <c r="GY5" s="2" t="n">
-        <v>0.3224860447002722</v>
+        <v>0.3384239147588348</v>
       </c>
       <c r="GZ5" s="2" t="n">
-        <v>0.3361640387133953</v>
+        <v>0.3512394959689901</v>
       </c>
       <c r="HA5" s="2" t="n">
-        <v>0.3491113133900451</v>
+        <v>0.3635707956091419</v>
       </c>
       <c r="HB5" s="2" t="n">
-        <v>0.3614443830974438</v>
+        <v>0.3772629126366663</v>
       </c>
       <c r="HC5" s="2" t="n">
-        <v>0.3561929379009344</v>
+        <v>0.3685748493541943</v>
       </c>
       <c r="HD5" s="2" t="n">
-        <v>0.3440329898285597</v>
+        <v>0.3619621219748773</v>
       </c>
       <c r="HE5" s="2" t="n">
-        <v>0.3396220933517582</v>
+        <v>0.3564995701052289</v>
       </c>
       <c r="HF5" s="2" t="n">
-        <v>0.3410790138183946</v>
+        <v>0.3582061029890317</v>
       </c>
       <c r="HG5" s="2" t="n">
-        <v>0.3472546173711731</v>
+        <v>0.365254020956993</v>
       </c>
       <c r="HH5" s="2" t="n">
-        <v>0.3458091531192573</v>
+        <v>0.3646857384971522</v>
       </c>
       <c r="HI5" s="2" t="n">
-        <v>0.344019614435112</v>
+        <v>0.3634033316827028</v>
       </c>
       <c r="HJ5" s="2" t="n">
-        <v>0.3461679039823821</v>
+        <v>0.3665206695506737</v>
       </c>
       <c r="HK5" s="2" t="n">
-        <v>0.3399269596238001</v>
+        <v>0.3603809700758736</v>
       </c>
       <c r="HL5" s="2" t="n">
-        <v>0.3412811147479243</v>
+        <v>0.362631892081603</v>
       </c>
       <c r="HM5" s="2" t="n">
-        <v>0.3380203598898551</v>
+        <v>0.3601150962409393</v>
       </c>
       <c r="HN5" s="2" t="n">
-        <v>0.3608950665959378</v>
+        <v>0.3826582076854654</v>
       </c>
       <c r="HO5" s="2" t="n">
-        <v>0.3751654607702078</v>
+        <v>0.3966491027173855</v>
       </c>
       <c r="HP5" s="2" t="n">
-        <v>0.3566637465093638</v>
+        <v>0.3718157352715245</v>
       </c>
       <c r="HQ5" s="2" t="n">
-        <v>0.3461107301549802</v>
+        <v>0.3566136440328385</v>
       </c>
       <c r="HR5" s="3" t="n">
         <v>55516</v>
@@ -4237,676 +4237,676 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.02465972874242865</v>
+        <v>0.02695118908203359</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.0326854229758971</v>
+        <v>0.03628996895416723</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.03457040422082429</v>
+        <v>0.0385784514682936</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.03602373866936341</v>
+        <v>0.0402982468170651</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.03639474562848264</v>
+        <v>0.04092653251419698</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.03570113854477941</v>
+        <v>0.04012307581483073</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.03516346952467082</v>
+        <v>0.03956206530890323</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.03477719677462161</v>
+        <v>0.03926860482996383</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03501519301314893</v>
+        <v>0.03947422571986278</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.03437637422922991</v>
+        <v>0.03867895489516517</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.03341276432522432</v>
+        <v>0.03756169295709</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.0325966485019889</v>
+        <v>0.03582534330748614</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.03253300780150088</v>
+        <v>0.03568416495553128</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.0331714189779512</v>
+        <v>0.03607481235313366</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.04957734496461432</v>
+        <v>0.05301386324278722</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.05989867413816186</v>
+        <v>0.06603032469268383</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.0621663506774458</v>
+        <v>0.06957607446999836</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.06307090356298523</v>
+        <v>0.07063597996631218</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.06412762302873026</v>
+        <v>0.07203134909215506</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.06192957260611728</v>
+        <v>0.06905932569729664</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.06272290888481855</v>
+        <v>0.07027369708757357</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.06235125375021787</v>
+        <v>0.06943463821943749</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.06174923228300738</v>
+        <v>0.06931204756066112</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.0613223216371018</v>
+        <v>0.06877807259005804</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.05844064336641372</v>
+        <v>0.06532829838297192</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.05645998996599382</v>
+        <v>0.06185456272033953</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.05628070635712815</v>
+        <v>0.06180187123867847</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.05775242195335122</v>
+        <v>0.06277713670007649</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.08057273989949218</v>
+        <v>0.08656181246206279</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.09113322484627059</v>
+        <v>0.1008905012012238</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.09048245760346763</v>
+        <v>0.101977668027993</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>0.09245537864772137</v>
+        <v>0.1039337296503223</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.0926948905469356</v>
+        <v>0.1040912141966688</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>0.09209657622846913</v>
+        <v>0.1031472472686155</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.08907610047231863</v>
+        <v>0.09973848330697527</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>0.08827450746105613</v>
+        <v>0.09813964855424519</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.08842726152066446</v>
+        <v>0.09905093044962959</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>0.08551118026054169</v>
+        <v>0.09544435614625633</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.08179647798468567</v>
+        <v>0.08983854941858758</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>0.08003408628321973</v>
+        <v>0.08716745189435512</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>0.08213932005482641</v>
+        <v>0.08957915908763546</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.08293369428595491</v>
+        <v>0.08995916004533558</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.1090438205802041</v>
+        <v>0.1175130459111022</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>0.114061979560068</v>
+        <v>0.1292356262845273</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>0.1146301311310228</v>
+        <v>0.1302471302493249</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>0.1163977418143136</v>
+        <v>0.1310495063157381</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>0.1143188531704976</v>
+        <v>0.1286798759148461</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>0.1104936109139729</v>
+        <v>0.1236990740124722</v>
       </c>
       <c r="AX6" s="2" t="n">
-        <v>0.1109800746505893</v>
+        <v>0.1239228598039566</v>
       </c>
       <c r="AY6" s="2" t="n">
-        <v>0.1103156060454308</v>
+        <v>0.1223324799526539</v>
       </c>
       <c r="AZ6" s="2" t="n">
-        <v>0.1088572862392493</v>
+        <v>0.1214645790865322</v>
       </c>
       <c r="BA6" s="2" t="n">
-        <v>0.1054457927022223</v>
+        <v>0.1166619227060987</v>
       </c>
       <c r="BB6" s="2" t="n">
-        <v>0.1011532169297089</v>
+        <v>0.1108044524636182</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>0.09971633084874007</v>
+        <v>0.1083083958957371</v>
       </c>
       <c r="BD6" s="2" t="n">
-        <v>0.09854486516435654</v>
+        <v>0.1066235830968349</v>
       </c>
       <c r="BE6" s="2" t="n">
-        <v>0.1016104515384959</v>
+        <v>0.109551447103049</v>
       </c>
       <c r="BF6" s="2" t="n">
-        <v>0.13571721842769</v>
+        <v>0.1500277903551909</v>
       </c>
       <c r="BG6" s="2" t="n">
-        <v>0.1365464090608838</v>
+        <v>0.1546946200891296</v>
       </c>
       <c r="BH6" s="2" t="n">
-        <v>0.1360619999967635</v>
+        <v>0.1539539387138943</v>
       </c>
       <c r="BI6" s="2" t="n">
-        <v>0.1324672460595522</v>
+        <v>0.1511371911130235</v>
       </c>
       <c r="BJ6" s="2" t="n">
-        <v>0.1328423381217808</v>
+        <v>0.1498326760355057</v>
       </c>
       <c r="BK6" s="2" t="n">
-        <v>0.1271065140454581</v>
+        <v>0.1424188577883871</v>
       </c>
       <c r="BL6" s="2" t="n">
-        <v>0.1267666579791397</v>
+        <v>0.1413942153911854</v>
       </c>
       <c r="BM6" s="2" t="n">
-        <v>0.1244705514549557</v>
+        <v>0.1378712734355413</v>
       </c>
       <c r="BN6" s="2" t="n">
-        <v>0.1226012535806228</v>
+        <v>0.1364725765877045</v>
       </c>
       <c r="BO6" s="2" t="n">
-        <v>0.1239555815864415</v>
+        <v>0.1373324285901047</v>
       </c>
       <c r="BP6" s="2" t="n">
-        <v>0.116454188357691</v>
+        <v>0.1270935143322258</v>
       </c>
       <c r="BQ6" s="2" t="n">
-        <v>0.1160625119954795</v>
+        <v>0.1251952930433375</v>
       </c>
       <c r="BR6" s="2" t="n">
-        <v>0.1155752489918165</v>
+        <v>0.1242411671189961</v>
       </c>
       <c r="BS6" s="2" t="n">
-        <v>0.1156399282387332</v>
+        <v>0.1235317330461726</v>
       </c>
       <c r="BT6" s="2" t="n">
-        <v>0.1677161669037358</v>
+        <v>0.1908946628877519</v>
       </c>
       <c r="BU6" s="2" t="n">
-        <v>0.1646937126989586</v>
+        <v>0.1906422451001205</v>
       </c>
       <c r="BV6" s="2" t="n">
-        <v>0.1612820720576738</v>
+        <v>0.1861476415771155</v>
       </c>
       <c r="BW6" s="2" t="n">
-        <v>0.1613779585885068</v>
+        <v>0.1862619014161726</v>
       </c>
       <c r="BX6" s="2" t="n">
-        <v>0.1603620848658989</v>
+        <v>0.1808266605488821</v>
       </c>
       <c r="BY6" s="2" t="n">
-        <v>0.1567599949497363</v>
+        <v>0.1755365938135845</v>
       </c>
       <c r="BZ6" s="2" t="n">
-        <v>0.1532624871754736</v>
+        <v>0.1714042790500225</v>
       </c>
       <c r="CA6" s="2" t="n">
-        <v>0.1505855467978144</v>
+        <v>0.1672984109947734</v>
       </c>
       <c r="CB6" s="2" t="n">
-        <v>0.1487886850660204</v>
+        <v>0.1644797172214165</v>
       </c>
       <c r="CC6" s="2" t="n">
-        <v>0.1450091444828071</v>
+        <v>0.1594725717588192</v>
       </c>
       <c r="CD6" s="2" t="n">
-        <v>0.1417783594355618</v>
+        <v>0.1540981251507251</v>
       </c>
       <c r="CE6" s="2" t="n">
-        <v>0.13573147124988</v>
+        <v>0.1453188025429276</v>
       </c>
       <c r="CF6" s="2" t="n">
-        <v>0.1360172004174925</v>
+        <v>0.1450752379782088</v>
       </c>
       <c r="CG6" s="2" t="n">
-        <v>0.1392437998099304</v>
+        <v>0.1478727048246386</v>
       </c>
       <c r="CH6" s="2" t="n">
-        <v>0.1922853460753299</v>
+        <v>0.2197470215001663</v>
       </c>
       <c r="CI6" s="2" t="n">
-        <v>0.1893760912468848</v>
+        <v>0.2205175858858564</v>
       </c>
       <c r="CJ6" s="2" t="n">
-        <v>0.1877186221302472</v>
+        <v>0.2149510252058727</v>
       </c>
       <c r="CK6" s="2" t="n">
-        <v>0.1843505539072969</v>
+        <v>0.2090901013150059</v>
       </c>
       <c r="CL6" s="2" t="n">
-        <v>0.1812116432351318</v>
+        <v>0.2042207662188192</v>
       </c>
       <c r="CM6" s="2" t="n">
-        <v>0.1751523373319825</v>
+        <v>0.1953925357033022</v>
       </c>
       <c r="CN6" s="2" t="n">
-        <v>0.1760166644898258</v>
+        <v>0.195151690106776</v>
       </c>
       <c r="CO6" s="2" t="n">
-        <v>0.1700506586290495</v>
+        <v>0.1877702164833265</v>
       </c>
       <c r="CP6" s="2" t="n">
-        <v>0.1687391375576475</v>
+        <v>0.1859162477084082</v>
       </c>
       <c r="CQ6" s="2" t="n">
-        <v>0.1696526759699043</v>
+        <v>0.1860882048742253</v>
       </c>
       <c r="CR6" s="2" t="n">
-        <v>0.1576992294385911</v>
+        <v>0.1695520238010895</v>
       </c>
       <c r="CS6" s="2" t="n">
-        <v>0.1557067461166601</v>
+        <v>0.165237411964732</v>
       </c>
       <c r="CT6" s="2" t="n">
-        <v>0.1559608103497466</v>
+        <v>0.1643884966670979</v>
       </c>
       <c r="CU6" s="2" t="n">
-        <v>0.1620608080824047</v>
+        <v>0.1708579823432708</v>
       </c>
       <c r="CV6" s="2" t="n">
-        <v>0.2272429248653666</v>
+        <v>0.2576046482581382</v>
       </c>
       <c r="CW6" s="2" t="n">
-        <v>0.2149089370846601</v>
+        <v>0.2455300285097781</v>
       </c>
       <c r="CX6" s="2" t="n">
-        <v>0.2154799807467663</v>
+        <v>0.2423138464944803</v>
       </c>
       <c r="CY6" s="2" t="n">
-        <v>0.2144355917370857</v>
+        <v>0.2387616543963041</v>
       </c>
       <c r="CZ6" s="2" t="n">
-        <v>0.2057643289842483</v>
+        <v>0.2285405431492676</v>
       </c>
       <c r="DA6" s="2" t="n">
-        <v>0.2027031287929223</v>
+        <v>0.2240578895346566</v>
       </c>
       <c r="DB6" s="2" t="n">
-        <v>0.2035594166022024</v>
+        <v>0.223370297591223</v>
       </c>
       <c r="DC6" s="2" t="n">
-        <v>0.1994340729207653</v>
+        <v>0.2174455978705613</v>
       </c>
       <c r="DD6" s="2" t="n">
-        <v>0.1994489352885627</v>
+        <v>0.2146949668910043</v>
       </c>
       <c r="DE6" s="2" t="n">
-        <v>0.1940043665223414</v>
+        <v>0.2082128786712028</v>
       </c>
       <c r="DF6" s="2" t="n">
-        <v>0.1887076525597961</v>
+        <v>0.1999742747411664</v>
       </c>
       <c r="DG6" s="2" t="n">
-        <v>0.1860900756320809</v>
+        <v>0.1963313983143788</v>
       </c>
       <c r="DH6" s="2" t="n">
-        <v>0.1852006795613532</v>
+        <v>0.1938515998796169</v>
       </c>
       <c r="DI6" s="2" t="n">
-        <v>0.1880654105916185</v>
+        <v>0.1953822771622363</v>
       </c>
       <c r="DJ6" s="2" t="n">
-        <v>0.2434629766359295</v>
+        <v>0.2738006280516548</v>
       </c>
       <c r="DK6" s="2" t="n">
-        <v>0.2412676286333882</v>
+        <v>0.2674150199691839</v>
       </c>
       <c r="DL6" s="2" t="n">
-        <v>0.2337438252687017</v>
+        <v>0.2589208068184408</v>
       </c>
       <c r="DM6" s="2" t="n">
-        <v>0.2323619949666982</v>
+        <v>0.2562381661731442</v>
       </c>
       <c r="DN6" s="2" t="n">
-        <v>0.2259615237868523</v>
+        <v>0.2474928149339352</v>
       </c>
       <c r="DO6" s="2" t="n">
-        <v>0.2273563631856322</v>
+        <v>0.2473461783380837</v>
       </c>
       <c r="DP6" s="2" t="n">
-        <v>0.2221935079430596</v>
+        <v>0.2388395378592015</v>
       </c>
       <c r="DQ6" s="2" t="n">
-        <v>0.2165407421668417</v>
+        <v>0.2317827154816717</v>
       </c>
       <c r="DR6" s="2" t="n">
-        <v>0.2154050239963012</v>
+        <v>0.2285356833555515</v>
       </c>
       <c r="DS6" s="2" t="n">
-        <v>0.212889272749764</v>
+        <v>0.2240578091349134</v>
       </c>
       <c r="DT6" s="2" t="n">
-        <v>0.2085611523353404</v>
+        <v>0.2183523535214893</v>
       </c>
       <c r="DU6" s="2" t="n">
-        <v>0.2073969536974061</v>
+        <v>0.2154588881135709</v>
       </c>
       <c r="DV6" s="2" t="n">
-        <v>0.2099623164103069</v>
+        <v>0.2172448942440838</v>
       </c>
       <c r="DW6" s="2" t="n">
-        <v>0.2124227288823131</v>
+        <v>0.2184194322769092</v>
       </c>
       <c r="DX6" s="2" t="n">
-        <v>0.2614365627165854</v>
+        <v>0.2875802341206432</v>
       </c>
       <c r="DY6" s="2" t="n">
-        <v>0.2518544106650048</v>
+        <v>0.2763643655802601</v>
       </c>
       <c r="DZ6" s="2" t="n">
-        <v>0.2506921813872607</v>
+        <v>0.2737251678089384</v>
       </c>
       <c r="EA6" s="2" t="n">
-        <v>0.2440489359928172</v>
+        <v>0.2647301408418105</v>
       </c>
       <c r="EB6" s="2" t="n">
-        <v>0.2440471125501197</v>
+        <v>0.2612917853657649</v>
       </c>
       <c r="EC6" s="2" t="n">
-        <v>0.2383341780612246</v>
+        <v>0.2545322407867033</v>
       </c>
       <c r="ED6" s="2" t="n">
-        <v>0.2361572863182253</v>
+        <v>0.2501002811761573</v>
       </c>
       <c r="EE6" s="2" t="n">
-        <v>0.2350237040428359</v>
+        <v>0.2469684921138756</v>
       </c>
       <c r="EF6" s="2" t="n">
-        <v>0.2326543330977315</v>
+        <v>0.2447880600915488</v>
       </c>
       <c r="EG6" s="2" t="n">
-        <v>0.2308830702360798</v>
+        <v>0.2419031916259961</v>
       </c>
       <c r="EH6" s="2" t="n">
-        <v>0.2197941175221972</v>
+        <v>0.2274886241793544</v>
       </c>
       <c r="EI6" s="2" t="n">
-        <v>0.2238542046785863</v>
+        <v>0.2297706949897057</v>
       </c>
       <c r="EJ6" s="2" t="n">
-        <v>0.2253173514213635</v>
+        <v>0.2292482597954859</v>
       </c>
       <c r="EK6" s="2" t="n">
-        <v>0.2266506798914492</v>
+        <v>0.2312735810262986</v>
       </c>
       <c r="EL6" s="2" t="n">
-        <v>0.2729217576465358</v>
+        <v>0.2932313012461727</v>
       </c>
       <c r="EM6" s="2" t="n">
-        <v>0.2705179505093288</v>
+        <v>0.2865434415939191</v>
       </c>
       <c r="EN6" s="2" t="n">
-        <v>0.2666704640474142</v>
+        <v>0.2807156899641662</v>
       </c>
       <c r="EO6" s="2" t="n">
-        <v>0.2602556554781396</v>
+        <v>0.2724840405541951</v>
       </c>
       <c r="EP6" s="2" t="n">
-        <v>0.2636069944008462</v>
+        <v>0.2753875469943798</v>
       </c>
       <c r="EQ6" s="2" t="n">
-        <v>0.2531431851786541</v>
+        <v>0.263151928906613</v>
       </c>
       <c r="ER6" s="2" t="n">
-        <v>0.2530619936788863</v>
+        <v>0.2629148566215921</v>
       </c>
       <c r="ES6" s="2" t="n">
-        <v>0.2476938672756072</v>
+        <v>0.2545673547199008</v>
       </c>
       <c r="ET6" s="2" t="n">
-        <v>0.2504125842095979</v>
+        <v>0.2575928274992331</v>
       </c>
       <c r="EU6" s="2" t="n">
-        <v>0.2499045628933363</v>
+        <v>0.2558656095102923</v>
       </c>
       <c r="EV6" s="2" t="n">
-        <v>0.2465071170568384</v>
+        <v>0.2515012119376669</v>
       </c>
       <c r="EW6" s="2" t="n">
-        <v>0.2467020324275555</v>
+        <v>0.250128047154023</v>
       </c>
       <c r="EX6" s="2" t="n">
-        <v>0.2468851549435475</v>
+        <v>0.2489305011883121</v>
       </c>
       <c r="EY6" s="2" t="n">
-        <v>0.2587971324202818</v>
+        <v>0.2603837327744108</v>
       </c>
       <c r="EZ6" s="2" t="n">
-        <v>0.2820461603041231</v>
+        <v>0.2896501952937916</v>
       </c>
       <c r="FA6" s="2" t="n">
-        <v>0.2828123288775305</v>
+        <v>0.2894765786336366</v>
       </c>
       <c r="FB6" s="2" t="n">
-        <v>0.2723823617574765</v>
+        <v>0.2782395230838289</v>
       </c>
       <c r="FC6" s="2" t="n">
-        <v>0.2748651196937158</v>
+        <v>0.279895990435908</v>
       </c>
       <c r="FD6" s="2" t="n">
-        <v>0.2655718986432857</v>
+        <v>0.2697519624763357</v>
       </c>
       <c r="FE6" s="2" t="n">
-        <v>0.2671060153230271</v>
+        <v>0.2709197849609489</v>
       </c>
       <c r="FF6" s="2" t="n">
-        <v>0.2667953310166311</v>
+        <v>0.2705017996466764</v>
       </c>
       <c r="FG6" s="2" t="n">
-        <v>0.2636140860787877</v>
+        <v>0.2670366985881111</v>
       </c>
       <c r="FH6" s="2" t="n">
-        <v>0.2591576215683226</v>
+        <v>0.2625435892880189</v>
       </c>
       <c r="FI6" s="2" t="n">
-        <v>0.2579189864901172</v>
+        <v>0.2612861858890141</v>
       </c>
       <c r="FJ6" s="2" t="n">
-        <v>0.2603367404078227</v>
+        <v>0.2628715431475937</v>
       </c>
       <c r="FK6" s="2" t="n">
-        <v>0.2627242119583887</v>
+        <v>0.2634959545495645</v>
       </c>
       <c r="FL6" s="2" t="n">
-        <v>0.2726792285878152</v>
+        <v>0.2723973975345595</v>
       </c>
       <c r="FM6" s="2" t="n">
-        <v>0.2829737909614681</v>
+        <v>0.282404445156088</v>
       </c>
       <c r="FN6" s="2" t="n">
-        <v>0.2870521279932318</v>
+        <v>0.2907405144832032</v>
       </c>
       <c r="FO6" s="2" t="n">
-        <v>0.2874765219892372</v>
+        <v>0.2905810724567883</v>
       </c>
       <c r="FP6" s="2" t="n">
-        <v>0.2795623133077864</v>
+        <v>0.2824474799999854</v>
       </c>
       <c r="FQ6" s="2" t="n">
-        <v>0.2776086818771514</v>
+        <v>0.2802323968147087</v>
       </c>
       <c r="FR6" s="2" t="n">
-        <v>0.2829090414477615</v>
+        <v>0.2861400768904982</v>
       </c>
       <c r="FS6" s="2" t="n">
-        <v>0.2806033884570276</v>
+        <v>0.2834845055752457</v>
       </c>
       <c r="FT6" s="2" t="n">
-        <v>0.280771960091193</v>
+        <v>0.2840214475877945</v>
       </c>
       <c r="FU6" s="2" t="n">
-        <v>0.2788519734476922</v>
+        <v>0.2820631827345318</v>
       </c>
       <c r="FV6" s="2" t="n">
-        <v>0.2806858455017698</v>
+        <v>0.2836189346500048</v>
       </c>
       <c r="FW6" s="2" t="n">
-        <v>0.2810698586990852</v>
+        <v>0.2840470671725478</v>
       </c>
       <c r="FX6" s="2" t="n">
-        <v>0.2805744342503527</v>
+        <v>0.2818750968000489</v>
       </c>
       <c r="FY6" s="2" t="n">
-        <v>0.2915597527354141</v>
+        <v>0.2914428786862128</v>
       </c>
       <c r="FZ6" s="2" t="n">
-        <v>0.2959246605949596</v>
+        <v>0.2959102503615119</v>
       </c>
       <c r="GA6" s="2" t="n">
-        <v>0.3108170140819043</v>
+        <v>0.3105179436207666</v>
       </c>
       <c r="GB6" s="2" t="n">
-        <v>0.3023914782725107</v>
+        <v>0.3087534446700633</v>
       </c>
       <c r="GC6" s="2" t="n">
-        <v>0.3029899036498551</v>
+        <v>0.3095116536327118</v>
       </c>
       <c r="GD6" s="2" t="n">
-        <v>0.3041304754594026</v>
+        <v>0.3110626379363061</v>
       </c>
       <c r="GE6" s="2" t="n">
-        <v>0.3040375513909491</v>
+        <v>0.3110851042204607</v>
       </c>
       <c r="GF6" s="2" t="n">
-        <v>0.3021941065205371</v>
+        <v>0.3088602824018413</v>
       </c>
       <c r="GG6" s="2" t="n">
-        <v>0.3006129739198332</v>
+        <v>0.3069612035326412</v>
       </c>
       <c r="GH6" s="2" t="n">
-        <v>0.2969641059169466</v>
+        <v>0.3032403613878842</v>
       </c>
       <c r="GI6" s="2" t="n">
-        <v>0.298010816458796</v>
+        <v>0.3023801173861537</v>
       </c>
       <c r="GJ6" s="2" t="n">
-        <v>0.2982737890005199</v>
+        <v>0.3034414652472545</v>
       </c>
       <c r="GK6" s="2" t="n">
-        <v>0.3022297727496592</v>
+        <v>0.3068966476677898</v>
       </c>
       <c r="GL6" s="2" t="n">
-        <v>0.3093100923168329</v>
+        <v>0.3117817963115579</v>
       </c>
       <c r="GM6" s="2" t="n">
-        <v>0.3163609669952537</v>
+        <v>0.3166150337986535</v>
       </c>
       <c r="GN6" s="2" t="n">
-        <v>0.331470501691812</v>
+        <v>0.3316736873641332</v>
       </c>
       <c r="GO6" s="2" t="n">
-        <v>0.3391042119316938</v>
+        <v>0.3403903142958888</v>
       </c>
       <c r="GP6" s="2" t="n">
-        <v>0.3310791987553278</v>
+        <v>0.3356531263192433</v>
       </c>
       <c r="GQ6" s="2" t="n">
-        <v>0.3285978606737484</v>
+        <v>0.3313018235948335</v>
       </c>
       <c r="GR6" s="2" t="n">
-        <v>0.3269668075994426</v>
+        <v>0.3316136483802023</v>
       </c>
       <c r="GS6" s="2" t="n">
-        <v>0.3255313892054343</v>
+        <v>0.3293838788468937</v>
       </c>
       <c r="GT6" s="2" t="n">
-        <v>0.327008563663761</v>
+        <v>0.3307863054829951</v>
       </c>
       <c r="GU6" s="2" t="n">
-        <v>0.321443026343523</v>
+        <v>0.3247612183574105</v>
       </c>
       <c r="GV6" s="2" t="n">
-        <v>0.3265067610253437</v>
+        <v>0.3300113157613164</v>
       </c>
       <c r="GW6" s="2" t="n">
-        <v>0.3218803696689006</v>
+        <v>0.3244963583831211</v>
       </c>
       <c r="GX6" s="2" t="n">
-        <v>0.3229712131881406</v>
+        <v>0.3255421904885228</v>
       </c>
       <c r="GY6" s="2" t="n">
-        <v>0.323277049475505</v>
+        <v>0.32577921756568</v>
       </c>
       <c r="GZ6" s="2" t="n">
-        <v>0.3369915928524569</v>
+        <v>0.3375596325045536</v>
       </c>
       <c r="HA6" s="2" t="n">
-        <v>0.3498816320218394</v>
+        <v>0.3507710787351114</v>
       </c>
       <c r="HB6" s="2" t="n">
-        <v>0.3623362604469512</v>
+        <v>0.3629385438884106</v>
       </c>
       <c r="HC6" s="2" t="n">
-        <v>0.3569051025866446</v>
+        <v>0.3565391508454407</v>
       </c>
       <c r="HD6" s="2" t="n">
-        <v>0.3451051253403682</v>
+        <v>0.3442774092782729</v>
       </c>
       <c r="HE6" s="2" t="n">
-        <v>0.3406782030690882</v>
+        <v>0.3388940911017965</v>
       </c>
       <c r="HF6" s="2" t="n">
-        <v>0.3421117691405554</v>
+        <v>0.3411250189117638</v>
       </c>
       <c r="HG6" s="2" t="n">
-        <v>0.3483096904179104</v>
+        <v>0.3482215881334066</v>
       </c>
       <c r="HH6" s="2" t="n">
-        <v>0.346894009205895</v>
+        <v>0.3475192634825289</v>
       </c>
       <c r="HI6" s="2" t="n">
-        <v>0.3451217803249764</v>
+        <v>0.3461056314847495</v>
       </c>
       <c r="HJ6" s="2" t="n">
-        <v>0.3472927088632275</v>
+        <v>0.3493911940290598</v>
       </c>
       <c r="HK6" s="2" t="n">
-        <v>0.3410471299303582</v>
+        <v>0.3432693378019131</v>
       </c>
       <c r="HL6" s="2" t="n">
-        <v>0.3424057307271871</v>
+        <v>0.3458872558966084</v>
       </c>
       <c r="HM6" s="2" t="n">
-        <v>0.3391319858783918</v>
+        <v>0.3438912963648958</v>
       </c>
       <c r="HN6" s="2" t="n">
-        <v>0.3620916369570475</v>
+        <v>0.3657519000276082</v>
       </c>
       <c r="HO6" s="2" t="n">
-        <v>0.3764046065501475</v>
+        <v>0.3790279658223829</v>
       </c>
       <c r="HP6" s="2" t="n">
-        <v>0.3576167976123774</v>
+        <v>0.3573437024068727</v>
       </c>
       <c r="HQ6" s="2" t="n">
-        <v>0.3468276889196563</v>
+        <v>0.3444596542116353</v>
       </c>
       <c r="HR6" s="3" t="n">
         <v>55517</v>
@@ -4919,676 +4919,676 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.02449445308845433</v>
+        <v>0.0278243437428271</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.03270312941027158</v>
+        <v>0.03668829255389302</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03459710423952335</v>
+        <v>0.03895005056216976</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.03602779954779053</v>
+        <v>0.04072632970930028</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.03638992650837671</v>
+        <v>0.04131745516635058</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.03567704074575098</v>
+        <v>0.04062490050596125</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.03510891982387018</v>
+        <v>0.04020619107354359</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.03471402689450438</v>
+        <v>0.04000583128971801</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.03494141288631544</v>
+        <v>0.04030241703499671</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.03429553631705093</v>
+        <v>0.03959603512630577</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.03332057856688236</v>
+        <v>0.03856582103148626</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03250951153988471</v>
+        <v>0.03697249895084558</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.03244281934103302</v>
+        <v>0.03690204830660458</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.03307570988723244</v>
+        <v>0.0374262405126773</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.04950690504869382</v>
+        <v>0.05419416637318145</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.05998411153675752</v>
+        <v>0.06637226326503746</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.06221616716201543</v>
+        <v>0.06997149003244815</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.06307205551138713</v>
+        <v>0.07110756211129729</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.06410476501847034</v>
+        <v>0.07270325302736208</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.06188753701696136</v>
+        <v>0.07000216718273983</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.0626404008673801</v>
+        <v>0.07127747122463685</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.06225197844080396</v>
+        <v>0.07074433789031914</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.06162472945474673</v>
+        <v>0.07067779134159688</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.06119752359893048</v>
+        <v>0.07020945143547438</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.05829553425462915</v>
+        <v>0.06690451144403239</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.0563257415168071</v>
+        <v>0.06376872872108658</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0.05613718206116025</v>
+        <v>0.06383271091171513</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0.05761434283114246</v>
+        <v>0.06493488118260815</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>0.08073446683984757</v>
+        <v>0.08695876507098477</v>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>0.09130190749561301</v>
+        <v>0.1006770921644512</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.09056388441363356</v>
+        <v>0.1020372390662112</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>0.09246240895485303</v>
+        <v>0.1042282576709967</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.09264631924799829</v>
+        <v>0.104861451351282</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>0.09201230481647152</v>
+        <v>0.1042088398737114</v>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>0.08895693455245382</v>
+        <v>0.1010317637257395</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>0.0881381160757462</v>
+        <v>0.09979622415632354</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>0.08826195656283112</v>
+        <v>0.1007354267818308</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>0.08535338116275272</v>
+        <v>0.09730849565156756</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.08163944413555752</v>
+        <v>0.09186202696527056</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>0.07986572691774194</v>
+        <v>0.0896208661446839</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>0.08195781954495443</v>
+        <v>0.09226290513846409</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>0.08274550747460682</v>
+        <v>0.09277402976486118</v>
       </c>
       <c r="AR7" s="2" t="n">
-        <v>0.1093433579020484</v>
+        <v>0.1172416525407848</v>
       </c>
       <c r="AS7" s="2" t="n">
-        <v>0.114180642529498</v>
+        <v>0.1284248094314941</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>0.114645309196395</v>
+        <v>0.1298661683193056</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>0.1163518099023275</v>
+        <v>0.1310363503712361</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>0.1142250680146014</v>
+        <v>0.129921757049194</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>0.1103533594072593</v>
+        <v>0.1249330097916581</v>
       </c>
       <c r="AX7" s="2" t="n">
-        <v>0.1108201245391117</v>
+        <v>0.1255800598604645</v>
       </c>
       <c r="AY7" s="2" t="n">
-        <v>0.1101420855468483</v>
+        <v>0.1243573803602377</v>
       </c>
       <c r="AZ7" s="2" t="n">
-        <v>0.1086541925076303</v>
+        <v>0.1235086276117692</v>
       </c>
       <c r="BA7" s="2" t="n">
-        <v>0.1052583854569388</v>
+        <v>0.1188772827722499</v>
       </c>
       <c r="BB7" s="2" t="n">
-        <v>0.1009711125996453</v>
+        <v>0.1131756306425362</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>0.09952508505829075</v>
+        <v>0.1112253669192165</v>
       </c>
       <c r="BD7" s="2" t="n">
-        <v>0.09835083575265108</v>
+        <v>0.1097477489150057</v>
       </c>
       <c r="BE7" s="2" t="n">
-        <v>0.1013991308007161</v>
+        <v>0.1128828824067204</v>
       </c>
       <c r="BF7" s="2" t="n">
-        <v>0.1360156970330575</v>
+        <v>0.1484240073571139</v>
       </c>
       <c r="BG7" s="2" t="n">
-        <v>0.1366263241259262</v>
+        <v>0.1541086238158458</v>
       </c>
       <c r="BH7" s="2" t="n">
-        <v>0.1360195433774195</v>
+        <v>0.1540051074769258</v>
       </c>
       <c r="BI7" s="2" t="n">
-        <v>0.1323150548940056</v>
+        <v>0.1515594819126068</v>
       </c>
       <c r="BJ7" s="2" t="n">
-        <v>0.1326863063455777</v>
+        <v>0.1514243947648537</v>
       </c>
       <c r="BK7" s="2" t="n">
-        <v>0.1269210446781752</v>
+        <v>0.144209205629153</v>
       </c>
       <c r="BL7" s="2" t="n">
-        <v>0.1265573414042149</v>
+        <v>0.1432910430180446</v>
       </c>
       <c r="BM7" s="2" t="n">
-        <v>0.1242626765447324</v>
+        <v>0.1402836996955153</v>
       </c>
       <c r="BN7" s="2" t="n">
-        <v>0.1223599094778469</v>
+        <v>0.1388678086266918</v>
       </c>
       <c r="BO7" s="2" t="n">
-        <v>0.123713648285656</v>
+        <v>0.1398120352850925</v>
       </c>
       <c r="BP7" s="2" t="n">
-        <v>0.1162345376931615</v>
+        <v>0.1298522373016324</v>
       </c>
       <c r="BQ7" s="2" t="n">
-        <v>0.1158605251525022</v>
+        <v>0.1285359513110093</v>
       </c>
       <c r="BR7" s="2" t="n">
-        <v>0.1153629619181437</v>
+        <v>0.1277904251141659</v>
       </c>
       <c r="BS7" s="2" t="n">
-        <v>0.1154200231449666</v>
+        <v>0.1272306766807847</v>
       </c>
       <c r="BT7" s="2" t="n">
-        <v>0.1678681431940698</v>
+        <v>0.1903656777314363</v>
       </c>
       <c r="BU7" s="2" t="n">
-        <v>0.164683514891486</v>
+        <v>0.1911590523177121</v>
       </c>
       <c r="BV7" s="2" t="n">
-        <v>0.1610877233325999</v>
+        <v>0.1876762680520571</v>
       </c>
       <c r="BW7" s="2" t="n">
-        <v>0.161062682376336</v>
+        <v>0.1878306315607796</v>
       </c>
       <c r="BX7" s="2" t="n">
-        <v>0.1601198276486625</v>
+        <v>0.1831313504279618</v>
       </c>
       <c r="BY7" s="2" t="n">
-        <v>0.1565101988936578</v>
+        <v>0.1784311858412108</v>
       </c>
       <c r="BZ7" s="2" t="n">
-        <v>0.152943977678155</v>
+        <v>0.1742197837810712</v>
       </c>
       <c r="CA7" s="2" t="n">
-        <v>0.1502927071764088</v>
+        <v>0.1704784683232605</v>
       </c>
       <c r="CB7" s="2" t="n">
-        <v>0.14850712214869</v>
+        <v>0.1676532760345835</v>
       </c>
       <c r="CC7" s="2" t="n">
-        <v>0.1447348114820255</v>
+        <v>0.1625596275331933</v>
       </c>
       <c r="CD7" s="2" t="n">
-        <v>0.1415233678487686</v>
+        <v>0.1575366721523926</v>
       </c>
       <c r="CE7" s="2" t="n">
-        <v>0.1354966488271821</v>
+        <v>0.1492020632503844</v>
       </c>
       <c r="CF7" s="2" t="n">
-        <v>0.1357712976441596</v>
+        <v>0.1491016455396537</v>
       </c>
       <c r="CG7" s="2" t="n">
-        <v>0.1390032222172208</v>
+        <v>0.1522922638770766</v>
       </c>
       <c r="CH7" s="2" t="n">
-        <v>0.1921766470744787</v>
+        <v>0.22105386784896</v>
       </c>
       <c r="CI7" s="2" t="n">
-        <v>0.1890700159418056</v>
+        <v>0.2226280213147707</v>
       </c>
       <c r="CJ7" s="2" t="n">
-        <v>0.1873709081894233</v>
+        <v>0.2178464186984433</v>
       </c>
       <c r="CK7" s="2" t="n">
-        <v>0.1839765828354895</v>
+        <v>0.2121414031497208</v>
       </c>
       <c r="CL7" s="2" t="n">
-        <v>0.1808289522312334</v>
+        <v>0.207778705502475</v>
       </c>
       <c r="CM7" s="2" t="n">
-        <v>0.1748041204063898</v>
+        <v>0.1992444984661713</v>
       </c>
       <c r="CN7" s="2" t="n">
-        <v>0.1756765438527378</v>
+        <v>0.1990113764390017</v>
       </c>
       <c r="CO7" s="2" t="n">
-        <v>0.1697071918012722</v>
+        <v>0.1917003296165246</v>
       </c>
       <c r="CP7" s="2" t="n">
-        <v>0.1683790888229312</v>
+        <v>0.1897175300355103</v>
       </c>
       <c r="CQ7" s="2" t="n">
-        <v>0.169298444489897</v>
+        <v>0.1897506739288928</v>
       </c>
       <c r="CR7" s="2" t="n">
-        <v>0.1574554713286367</v>
+        <v>0.1735265320805869</v>
       </c>
       <c r="CS7" s="2" t="n">
-        <v>0.155460123035266</v>
+        <v>0.1697484238875848</v>
       </c>
       <c r="CT7" s="2" t="n">
-        <v>0.1557183435520893</v>
+        <v>0.1689976874159878</v>
       </c>
       <c r="CU7" s="2" t="n">
-        <v>0.1617878553903167</v>
+        <v>0.1758827197198232</v>
       </c>
       <c r="CV7" s="2" t="n">
-        <v>0.2267766508133615</v>
+        <v>0.2612329259389899</v>
       </c>
       <c r="CW7" s="2" t="n">
-        <v>0.2143586463056794</v>
+        <v>0.2498329741327023</v>
       </c>
       <c r="CX7" s="2" t="n">
-        <v>0.215041976232226</v>
+        <v>0.2465931579944362</v>
       </c>
       <c r="CY7" s="2" t="n">
-        <v>0.2140187556439629</v>
+        <v>0.2437603287497559</v>
       </c>
       <c r="CZ7" s="2" t="n">
-        <v>0.2053105269944409</v>
+        <v>0.2334282977364993</v>
       </c>
       <c r="DA7" s="2" t="n">
-        <v>0.2022549784252471</v>
+        <v>0.2289556169984616</v>
       </c>
       <c r="DB7" s="2" t="n">
-        <v>0.2031274398458867</v>
+        <v>0.2281630991459348</v>
       </c>
       <c r="DC7" s="2" t="n">
-        <v>0.1990306848251873</v>
+        <v>0.2219048177484147</v>
       </c>
       <c r="DD7" s="2" t="n">
-        <v>0.1991226972065236</v>
+        <v>0.2193683702871674</v>
       </c>
       <c r="DE7" s="2" t="n">
-        <v>0.1937110533990266</v>
+        <v>0.212813708038372</v>
       </c>
       <c r="DF7" s="2" t="n">
-        <v>0.1884628685553483</v>
+        <v>0.2047657077863929</v>
       </c>
       <c r="DG7" s="2" t="n">
-        <v>0.1858020424519617</v>
+        <v>0.2012744933035698</v>
       </c>
       <c r="DH7" s="2" t="n">
-        <v>0.1849396296432057</v>
+        <v>0.1988600630755125</v>
       </c>
       <c r="DI7" s="2" t="n">
-        <v>0.187788273652981</v>
+        <v>0.2009533607120196</v>
       </c>
       <c r="DJ7" s="2" t="n">
-        <v>0.2429320839451695</v>
+        <v>0.2798295939742969</v>
       </c>
       <c r="DK7" s="2" t="n">
-        <v>0.2407913267031758</v>
+        <v>0.2735774631488176</v>
       </c>
       <c r="DL7" s="2" t="n">
-        <v>0.2332095104297376</v>
+        <v>0.2644085825755179</v>
       </c>
       <c r="DM7" s="2" t="n">
-        <v>0.2318703765063083</v>
+        <v>0.2617877099481686</v>
       </c>
       <c r="DN7" s="2" t="n">
-        <v>0.2254979146518237</v>
+        <v>0.2531984727346947</v>
       </c>
       <c r="DO7" s="2" t="n">
-        <v>0.2269000703473463</v>
+        <v>0.2525985624138802</v>
       </c>
       <c r="DP7" s="2" t="n">
-        <v>0.2218215870688779</v>
+        <v>0.2439970845577961</v>
       </c>
       <c r="DQ7" s="2" t="n">
-        <v>0.2161935485981045</v>
+        <v>0.2368600178137404</v>
       </c>
       <c r="DR7" s="2" t="n">
-        <v>0.2151128977537654</v>
+        <v>0.2336716485833896</v>
       </c>
       <c r="DS7" s="2" t="n">
-        <v>0.212625499446637</v>
+        <v>0.2291542155354847</v>
       </c>
       <c r="DT7" s="2" t="n">
-        <v>0.2082977269134099</v>
+        <v>0.2234196964770535</v>
       </c>
       <c r="DU7" s="2" t="n">
-        <v>0.2071698101352667</v>
+        <v>0.2203765584865895</v>
       </c>
       <c r="DV7" s="2" t="n">
-        <v>0.2097109707386144</v>
+        <v>0.2227015648682726</v>
       </c>
       <c r="DW7" s="2" t="n">
-        <v>0.2121325634216716</v>
+        <v>0.2242563099989196</v>
       </c>
       <c r="DX7" s="2" t="n">
-        <v>0.2608872297636141</v>
+        <v>0.294003204922017</v>
       </c>
       <c r="DY7" s="2" t="n">
-        <v>0.251338632451316</v>
+        <v>0.282480209169544</v>
       </c>
       <c r="DZ7" s="2" t="n">
-        <v>0.250207126158002</v>
+        <v>0.2801071311933669</v>
       </c>
       <c r="EA7" s="2" t="n">
-        <v>0.24358374181137</v>
+        <v>0.2703207613152349</v>
       </c>
       <c r="EB7" s="2" t="n">
-        <v>0.2436520408054142</v>
+        <v>0.2669428617410278</v>
       </c>
       <c r="EC7" s="2" t="n">
-        <v>0.2379716761160973</v>
+        <v>0.2600826232747214</v>
       </c>
       <c r="ED7" s="2" t="n">
-        <v>0.2358317657293448</v>
+        <v>0.2555358607421773</v>
       </c>
       <c r="EE7" s="2" t="n">
-        <v>0.2347366136959658</v>
+        <v>0.2524753459332953</v>
       </c>
       <c r="EF7" s="2" t="n">
-        <v>0.232385383880004</v>
+        <v>0.2499157186037131</v>
       </c>
       <c r="EG7" s="2" t="n">
-        <v>0.2306055150017256</v>
+        <v>0.2469962357405696</v>
       </c>
       <c r="EH7" s="2" t="n">
-        <v>0.2195046213458646</v>
+        <v>0.2330785098882508</v>
       </c>
       <c r="EI7" s="2" t="n">
-        <v>0.2235798989787709</v>
+        <v>0.2351654057894629</v>
       </c>
       <c r="EJ7" s="2" t="n">
-        <v>0.2250603884064054</v>
+        <v>0.2348837110460573</v>
       </c>
       <c r="EK7" s="2" t="n">
-        <v>0.2263846218800389</v>
+        <v>0.2371555231324452</v>
       </c>
       <c r="EL7" s="2" t="n">
-        <v>0.2724311767721691</v>
+        <v>0.2998255888254788</v>
       </c>
       <c r="EM7" s="2" t="n">
-        <v>0.2701182838976527</v>
+        <v>0.2932166954823353</v>
       </c>
       <c r="EN7" s="2" t="n">
-        <v>0.2663427903115013</v>
+        <v>0.2870487204156098</v>
       </c>
       <c r="EO7" s="2" t="n">
-        <v>0.2599655838327309</v>
+        <v>0.2785040865582304</v>
       </c>
       <c r="EP7" s="2" t="n">
-        <v>0.2633183422438437</v>
+        <v>0.2811731104944595</v>
       </c>
       <c r="EQ7" s="2" t="n">
-        <v>0.2528788319197612</v>
+        <v>0.2687254433890692</v>
       </c>
       <c r="ER7" s="2" t="n">
-        <v>0.2527668174335819</v>
+        <v>0.2686006390403017</v>
       </c>
       <c r="ES7" s="2" t="n">
-        <v>0.2474034292960579</v>
+        <v>0.2604592680291357</v>
       </c>
       <c r="ET7" s="2" t="n">
-        <v>0.2501632086110252</v>
+        <v>0.2629568253385797</v>
       </c>
       <c r="EU7" s="2" t="n">
-        <v>0.2496472685694767</v>
+        <v>0.2613794338379179</v>
       </c>
       <c r="EV7" s="2" t="n">
-        <v>0.2462737691906518</v>
+        <v>0.2572678780700066</v>
       </c>
       <c r="EW7" s="2" t="n">
-        <v>0.2464999900429339</v>
+        <v>0.2557049353718698</v>
       </c>
       <c r="EX7" s="2" t="n">
-        <v>0.2466676212409521</v>
+        <v>0.2547349641710303</v>
       </c>
       <c r="EY7" s="2" t="n">
-        <v>0.2584930205077526</v>
+        <v>0.2668716498363675</v>
       </c>
       <c r="EZ7" s="2" t="n">
-        <v>0.2817965735601744</v>
+        <v>0.2951828386688398</v>
       </c>
       <c r="FA7" s="2" t="n">
-        <v>0.282563818933172</v>
+        <v>0.295091526488191</v>
       </c>
       <c r="FB7" s="2" t="n">
-        <v>0.2721803016572262</v>
+        <v>0.2834758479940269</v>
       </c>
       <c r="FC7" s="2" t="n">
-        <v>0.2746802272603784</v>
+        <v>0.2853076534189527</v>
       </c>
       <c r="FD7" s="2" t="n">
-        <v>0.2653878314779949</v>
+        <v>0.275079236923926</v>
       </c>
       <c r="FE7" s="2" t="n">
-        <v>0.266914892361489</v>
+        <v>0.27649197475724</v>
       </c>
       <c r="FF7" s="2" t="n">
-        <v>0.2666197931290547</v>
+        <v>0.275940086888933</v>
       </c>
       <c r="FG7" s="2" t="n">
-        <v>0.2634255867723443</v>
+        <v>0.2725922725970585</v>
       </c>
       <c r="FH7" s="2" t="n">
-        <v>0.2589694240029073</v>
+        <v>0.267971391961471</v>
       </c>
       <c r="FI7" s="2" t="n">
-        <v>0.2577258187486174</v>
+        <v>0.2666800535508869</v>
       </c>
       <c r="FJ7" s="2" t="n">
-        <v>0.2601202080585103</v>
+        <v>0.2687028256099233</v>
       </c>
       <c r="FK7" s="2" t="n">
-        <v>0.262507270396381</v>
+        <v>0.2694057470198048</v>
       </c>
       <c r="FL7" s="2" t="n">
-        <v>0.2724604747282856</v>
+        <v>0.2787412360654158</v>
       </c>
       <c r="FM7" s="2" t="n">
-        <v>0.2827384502551237</v>
+        <v>0.2891380939034187</v>
       </c>
       <c r="FN7" s="2" t="n">
-        <v>0.2868354126829968</v>
+        <v>0.2970476630376936</v>
       </c>
       <c r="FO7" s="2" t="n">
-        <v>0.2872633650263504</v>
+        <v>0.2967888076198197</v>
       </c>
       <c r="FP7" s="2" t="n">
-        <v>0.2793457577790693</v>
+        <v>0.2885153028840444</v>
       </c>
       <c r="FQ7" s="2" t="n">
-        <v>0.2774118726534993</v>
+        <v>0.2864796671339639</v>
       </c>
       <c r="FR7" s="2" t="n">
-        <v>0.2826819646681229</v>
+        <v>0.2923562394518562</v>
       </c>
       <c r="FS7" s="2" t="n">
-        <v>0.2803751995857852</v>
+        <v>0.2900235156785016</v>
       </c>
       <c r="FT7" s="2" t="n">
-        <v>0.2805190341924462</v>
+        <v>0.2906351597692624</v>
       </c>
       <c r="FU7" s="2" t="n">
-        <v>0.2785852425136571</v>
+        <v>0.2888155405424664</v>
       </c>
       <c r="FV7" s="2" t="n">
-        <v>0.2804063330257701</v>
+        <v>0.290717824144999</v>
       </c>
       <c r="FW7" s="2" t="n">
-        <v>0.2807789405159729</v>
+        <v>0.2912524066328208</v>
       </c>
       <c r="FX7" s="2" t="n">
-        <v>0.2802745213747475</v>
+        <v>0.2894137038108242</v>
       </c>
       <c r="FY7" s="2" t="n">
-        <v>0.2912343025745601</v>
+        <v>0.2993784627257579</v>
       </c>
       <c r="FZ7" s="2" t="n">
-        <v>0.2955883483505237</v>
+        <v>0.3041068910027815</v>
       </c>
       <c r="GA7" s="2" t="n">
-        <v>0.3104401640843926</v>
+        <v>0.3188624787643614</v>
       </c>
       <c r="GB7" s="2" t="n">
-        <v>0.3020466757686098</v>
+        <v>0.3170131708072084</v>
       </c>
       <c r="GC7" s="2" t="n">
-        <v>0.3026407151255419</v>
+        <v>0.3180596190777351</v>
       </c>
       <c r="GD7" s="2" t="n">
-        <v>0.3037325560271609</v>
+        <v>0.3199259878667924</v>
       </c>
       <c r="GE7" s="2" t="n">
-        <v>0.3036366593999791</v>
+        <v>0.3200644191271394</v>
       </c>
       <c r="GF7" s="2" t="n">
-        <v>0.3018004145613034</v>
+        <v>0.3178727121364034</v>
       </c>
       <c r="GG7" s="2" t="n">
-        <v>0.3002360624687279</v>
+        <v>0.3158823929333789</v>
       </c>
       <c r="GH7" s="2" t="n">
-        <v>0.2965571887437811</v>
+        <v>0.3123614712949808</v>
       </c>
       <c r="GI7" s="2" t="n">
-        <v>0.2975793546973523</v>
+        <v>0.3121945828328919</v>
       </c>
       <c r="GJ7" s="2" t="n">
-        <v>0.2978632794110285</v>
+        <v>0.3128738415445068</v>
       </c>
       <c r="GK7" s="2" t="n">
-        <v>0.3017989694889922</v>
+        <v>0.3167011959687113</v>
       </c>
       <c r="GL7" s="2" t="n">
-        <v>0.3088575732220197</v>
+        <v>0.3219290525194954</v>
       </c>
       <c r="GM7" s="2" t="n">
-        <v>0.315868574868627</v>
+        <v>0.3269789012637622</v>
       </c>
       <c r="GN7" s="2" t="n">
-        <v>0.3310252629732347</v>
+        <v>0.3421808399704576</v>
       </c>
       <c r="GO7" s="2" t="n">
-        <v>0.3386162205548789</v>
+        <v>0.3512611861289424</v>
       </c>
       <c r="GP7" s="2" t="n">
-        <v>0.3306629238440445</v>
+        <v>0.3454057407090666</v>
       </c>
       <c r="GQ7" s="2" t="n">
-        <v>0.3281888558667456</v>
+        <v>0.3409897755537593</v>
       </c>
       <c r="GR7" s="2" t="n">
-        <v>0.3265812075904343</v>
+        <v>0.3410097349752174</v>
       </c>
       <c r="GS7" s="2" t="n">
-        <v>0.3251468604663859</v>
+        <v>0.3389683239904815</v>
       </c>
       <c r="GT7" s="2" t="n">
-        <v>0.3265836571996057</v>
+        <v>0.340703779144487</v>
       </c>
       <c r="GU7" s="2" t="n">
-        <v>0.321004473801459</v>
+        <v>0.3348514891685087</v>
       </c>
       <c r="GV7" s="2" t="n">
-        <v>0.3260658988333492</v>
+        <v>0.3404442788105583</v>
       </c>
       <c r="GW7" s="2" t="n">
-        <v>0.3214248491396841</v>
+        <v>0.3351155935136903</v>
       </c>
       <c r="GX7" s="2" t="n">
-        <v>0.3225035312024035</v>
+        <v>0.3364614273735863</v>
       </c>
       <c r="GY7" s="2" t="n">
-        <v>0.3227861950544454</v>
+        <v>0.3370747497139321</v>
       </c>
       <c r="GZ7" s="2" t="n">
-        <v>0.3365220492304066</v>
+        <v>0.3488652984720115</v>
       </c>
       <c r="HA7" s="2" t="n">
-        <v>0.349393911382207</v>
+        <v>0.3616599003516046</v>
       </c>
       <c r="HB7" s="2" t="n">
-        <v>0.3618634201701481</v>
+        <v>0.3746808184668627</v>
       </c>
       <c r="HC7" s="2" t="n">
-        <v>0.3565004197563961</v>
+        <v>0.3663209038719709</v>
       </c>
       <c r="HD7" s="2" t="n">
-        <v>0.3445598031896377</v>
+        <v>0.3582449826815298</v>
       </c>
       <c r="HE7" s="2" t="n">
-        <v>0.3401717832265075</v>
+        <v>0.3522436585444852</v>
       </c>
       <c r="HF7" s="2" t="n">
-        <v>0.341566663942192</v>
+        <v>0.3544325613251032</v>
       </c>
       <c r="HG7" s="2" t="n">
-        <v>0.3477608990546572</v>
+        <v>0.3618296260103839</v>
       </c>
       <c r="HH7" s="2" t="n">
-        <v>0.3463455404100483</v>
+        <v>0.361374807126874</v>
       </c>
       <c r="HI7" s="2" t="n">
-        <v>0.3445721328866282</v>
+        <v>0.3601213716877551</v>
       </c>
       <c r="HJ7" s="2" t="n">
-        <v>0.3467499872671591</v>
+        <v>0.3635199127472747</v>
       </c>
       <c r="HK7" s="2" t="n">
-        <v>0.340481103351208</v>
+        <v>0.3574831254257582</v>
       </c>
       <c r="HL7" s="2" t="n">
-        <v>0.3418280059837555</v>
+        <v>0.3601492838787964</v>
       </c>
       <c r="HM7" s="2" t="n">
-        <v>0.3385264958821403</v>
+        <v>0.3581095426984946</v>
       </c>
       <c r="HN7" s="2" t="n">
-        <v>0.3616368322501912</v>
+        <v>0.3798674758511063</v>
       </c>
       <c r="HO7" s="2" t="n">
-        <v>0.3759644018101058</v>
+        <v>0.3936095289586018</v>
       </c>
       <c r="HP7" s="2" t="n">
-        <v>0.3572680851057051</v>
+        <v>0.3683234185410131</v>
       </c>
       <c r="HQ7" s="2" t="n">
-        <v>0.346496319750446</v>
+        <v>0.3533648210832124</v>
       </c>
       <c r="HR7" s="3" t="n">
         <v>55519</v>
@@ -5673,7 +5673,7 @@
         <v>0.0707983495227468</v>
       </c>
       <c r="Z8" s="7" t="n">
-        <v>0.06761062145233154</v>
+        <v>0.06776289641857147</v>
       </c>
       <c r="AA8" s="6" t="n">
         <v>0.06325361731976981</v>
@@ -5712,7 +5712,7 @@
         <v>0.102714844045793</v>
       </c>
       <c r="AM8" s="7" t="n">
-        <v>0.09908564388751984</v>
+        <v>0.09959778934717178</v>
       </c>
       <c r="AN8" s="6" t="n">
         <v>0.09259502537764119</v>
@@ -5871,7 +5871,7 @@
         <v>0.204818851764059</v>
       </c>
       <c r="CN8" s="7" t="n">
-        <v>0.2018578201532364</v>
+        <v>0.2053440064191818</v>
       </c>
       <c r="CO8" s="6" t="n">
         <v>0.196500406731799</v>
@@ -6129,7 +6129,7 @@
         <v>0.277654055693251</v>
       </c>
       <c r="FV8" s="7" t="n">
-        <v>0.2779556810855865</v>
+        <v>0.2791333496570587</v>
       </c>
       <c r="FW8" s="6" t="n">
         <v>0.279414809816803</v>
@@ -6295,7 +6295,7 @@
         <v>0.0381157332974437</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.04350094124674797</v>
+        <v>0.0413268469274044</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>0.0395341519679435</v>
@@ -6418,7 +6418,7 @@
         <v>0.131315746744894</v>
       </c>
       <c r="AU9" s="7" t="n">
-        <v>0.1396824717521667</v>
+        <v>0.1363729536533356</v>
       </c>
       <c r="AV9" s="6" t="n">
         <v>0.132513088922263</v>
@@ -6499,7 +6499,7 @@
         <v>0.199955283513327</v>
       </c>
       <c r="BV9" s="7" t="n">
-        <v>0.2008426785469055</v>
+        <v>0.1966657787561417</v>
       </c>
       <c r="BW9" s="6" t="n">
         <v>0.200606296983058</v>
@@ -6640,7 +6640,7 @@
         <v>0.251323415697041</v>
       </c>
       <c r="DQ9" s="7" t="n">
-        <v>0.2394468784332275</v>
+        <v>0.2402604669332504</v>
       </c>
       <c r="DR9" s="6" t="n">
         <v>0.23764445461862</v>
@@ -6694,7 +6694,7 @@
         <v>0.232519744722409</v>
       </c>
       <c r="EI9" s="7" t="n">
-        <v>0.2306835949420929</v>
+        <v>0.2326757311820984</v>
       </c>
       <c r="EJ9" s="6" t="n">
         <v>0.231332738185024</v>
@@ -6853,7 +6853,7 @@
         <v>0.304890545827317</v>
       </c>
       <c r="GJ9" s="7" t="n">
-        <v>0.3020880818367004</v>
+        <v>0.305094450712204</v>
       </c>
       <c r="GK9" s="6" t="n">
         <v>0.308508043694741</v>

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -1509,676 +1509,676 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.03216920038773417</v>
+        <v>0.03199679721235036</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.0409153116664631</v>
+        <v>0.04053134040746519</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.04301669283345232</v>
+        <v>0.04265038969501743</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.04462490142948638</v>
+        <v>0.04422283736683141</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.04501089666287749</v>
+        <v>0.04453795708964913</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.04400417349006929</v>
+        <v>0.04357367614921131</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.04333330899013352</v>
+        <v>0.04295486885590625</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.04300973734640468</v>
+        <v>0.04265720008694518</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.04317240830443438</v>
+        <v>0.04283502366326388</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.04223550673950645</v>
+        <v>0.04198828436810705</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.04087603491637532</v>
+        <v>0.04069910039100472</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.03873163938851151</v>
+        <v>0.03875228960395846</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.03855571086448963</v>
+        <v>0.03859512909246023</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.03889049783486669</v>
+        <v>0.03902558151770179</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.06034109802816749</v>
+        <v>0.0600859761786902</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.07292793422758571</v>
+        <v>0.07228123687028877</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.07663270022099347</v>
+        <v>0.07579686614995332</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.07719279916444349</v>
+        <v>0.07635531106451082</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.07852514985991031</v>
+        <v>0.07773379948032409</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.07492663916695477</v>
+        <v>0.07424316015589597</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.07616207109325428</v>
+        <v>0.07549595007234115</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.07500728867312005</v>
+        <v>0.07448804653544953</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.07497831645622649</v>
+        <v>0.07450037661209502</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.07420561570360515</v>
+        <v>0.0737495963989124</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.07031584329844451</v>
+        <v>0.07001900937349534</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.06631821032346098</v>
+        <v>0.06634786270291416</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0.0663241482459262</v>
+        <v>0.06638268000709563</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0.06712297026252578</v>
+        <v>0.06731349185293745</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.09490583484621977</v>
+        <v>0.0942665824815843</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>0.109531244199085</v>
+        <v>0.10835715935688</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>0.1108649365877221</v>
+        <v>0.1094308991258452</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.1120854862406819</v>
+        <v>0.1107695609703629</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.1121650572267043</v>
+        <v>0.1109083137807119</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>0.1109327214287621</v>
+        <v>0.1098612292187316</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>0.1070807773395168</v>
+        <v>0.1061737753226148</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>0.1050633065926807</v>
+        <v>0.1043714251893537</v>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>0.1061950313675433</v>
+        <v>0.1054490065950185</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>0.1021244627551165</v>
+        <v>0.1015638996974554</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.09562960966320441</v>
+        <v>0.09540986223907874</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>0.09263320089343603</v>
+        <v>0.09267983966532763</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>0.09527927683361884</v>
+        <v>0.09537130267986174</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.09546431406068057</v>
+        <v>0.09564884631561488</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.1267609811149915</v>
+        <v>0.1258376697771628</v>
       </c>
       <c r="AS2" s="2" t="n">
-        <v>0.1399184271715138</v>
+        <v>0.1378674332074378</v>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>0.1405756777346419</v>
+        <v>0.1385757258355903</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>0.1402166782226673</v>
+        <v>0.1383995784726253</v>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>0.1384490496692751</v>
+        <v>0.1369828107980583</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>0.1323676346712258</v>
+        <v>0.1311140987001803</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>0.1324405767351658</v>
+        <v>0.1314190984100373</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>0.1303766889534352</v>
+        <v>0.1295355817339776</v>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>0.1296139946505002</v>
+        <v>0.1287857434078625</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>0.1241163749154323</v>
+        <v>0.123493463536691</v>
       </c>
       <c r="BB2" s="2" t="n">
-        <v>0.1172579585052857</v>
+        <v>0.1169335248358378</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>0.1145226863510781</v>
+        <v>0.1145135947801047</v>
       </c>
       <c r="BD2" s="2" t="n">
-        <v>0.1128021141686504</v>
+        <v>0.1129332704641884</v>
       </c>
       <c r="BE2" s="2" t="n">
-        <v>0.1156927589718842</v>
+        <v>0.1159715429340147</v>
       </c>
       <c r="BF2" s="2" t="n">
-        <v>0.1604268938407789</v>
+        <v>0.1585804350778947</v>
       </c>
       <c r="BG2" s="2" t="n">
-        <v>0.1662521406462699</v>
+        <v>0.163795371299079</v>
       </c>
       <c r="BH2" s="2" t="n">
-        <v>0.1650224427804187</v>
+        <v>0.1627649764641955</v>
       </c>
       <c r="BI2" s="2" t="n">
-        <v>0.1618567381603025</v>
+        <v>0.1596361298662923</v>
       </c>
       <c r="BJ2" s="2" t="n">
-        <v>0.1604585541129967</v>
+        <v>0.1587384758234879</v>
       </c>
       <c r="BK2" s="2" t="n">
-        <v>0.1520701714203502</v>
+        <v>0.1507291563198711</v>
       </c>
       <c r="BL2" s="2" t="n">
-        <v>0.1504370561689784</v>
+        <v>0.149280852720206</v>
       </c>
       <c r="BM2" s="2" t="n">
-        <v>0.1465355289574555</v>
+        <v>0.1456825939413003</v>
       </c>
       <c r="BN2" s="2" t="n">
-        <v>0.1451781815202654</v>
+        <v>0.1443339860351504</v>
       </c>
       <c r="BO2" s="2" t="n">
-        <v>0.1456110930238552</v>
+        <v>0.1448879284952469</v>
       </c>
       <c r="BP2" s="2" t="n">
-        <v>0.1341277544774832</v>
+        <v>0.1338458990135015</v>
       </c>
       <c r="BQ2" s="2" t="n">
-        <v>0.1317908923271035</v>
+        <v>0.1319252393337821</v>
       </c>
       <c r="BR2" s="2" t="n">
-        <v>0.1308538976963006</v>
+        <v>0.1310918785537921</v>
       </c>
       <c r="BS2" s="2" t="n">
-        <v>0.1299141062262523</v>
+        <v>0.1303161674949395</v>
       </c>
       <c r="BT2" s="2" t="n">
-        <v>0.2057726509442012</v>
+        <v>0.2028970732857863</v>
       </c>
       <c r="BU2" s="2" t="n">
-        <v>0.205193320681231</v>
+        <v>0.2019616015449929</v>
       </c>
       <c r="BV2" s="2" t="n">
-        <v>0.200959500006559</v>
+        <v>0.198254332027557</v>
       </c>
       <c r="BW2" s="2" t="n">
-        <v>0.2002429700406956</v>
+        <v>0.1977345085653233</v>
       </c>
       <c r="BX2" s="2" t="n">
-        <v>0.1929939995648748</v>
+        <v>0.1911913464906102</v>
       </c>
       <c r="BY2" s="2" t="n">
-        <v>0.1871939238569776</v>
+        <v>0.1858509082756082</v>
       </c>
       <c r="BZ2" s="2" t="n">
-        <v>0.1825262058306777</v>
+        <v>0.1813966568339907</v>
       </c>
       <c r="CA2" s="2" t="n">
-        <v>0.1777537976566964</v>
+        <v>0.1767876138154679</v>
       </c>
       <c r="CB2" s="2" t="n">
-        <v>0.1743036816386337</v>
+        <v>0.173641384628212</v>
       </c>
       <c r="CC2" s="2" t="n">
-        <v>0.1686113204645365</v>
+        <v>0.1679787922488898</v>
       </c>
       <c r="CD2" s="2" t="n">
-        <v>0.1621917385797379</v>
+        <v>0.1619490247409222</v>
       </c>
       <c r="CE2" s="2" t="n">
-        <v>0.1525181161263341</v>
+        <v>0.152765762249505</v>
       </c>
       <c r="CF2" s="2" t="n">
-        <v>0.1522464456972728</v>
+        <v>0.1525899584409843</v>
       </c>
       <c r="CG2" s="2" t="n">
-        <v>0.1549242874535172</v>
+        <v>0.1554149044605344</v>
       </c>
       <c r="CH2" s="2" t="n">
-        <v>0.2357232708388739</v>
+        <v>0.2326558072024756</v>
       </c>
       <c r="CI2" s="2" t="n">
-        <v>0.237804090557403</v>
+        <v>0.2345709893384642</v>
       </c>
       <c r="CJ2" s="2" t="n">
-        <v>0.2310186131521753</v>
+        <v>0.2284798836931279</v>
       </c>
       <c r="CK2" s="2" t="n">
-        <v>0.2235222838549183</v>
+        <v>0.2215519480137394</v>
       </c>
       <c r="CL2" s="2" t="n">
-        <v>0.2181430758877482</v>
+        <v>0.2166462691469874</v>
       </c>
       <c r="CM2" s="2" t="n">
-        <v>0.2080703580095359</v>
+        <v>0.2071172909154483</v>
       </c>
       <c r="CN2" s="2" t="n">
-        <v>0.2070837830123397</v>
+        <v>0.2061585624632331</v>
       </c>
       <c r="CO2" s="2" t="n">
-        <v>0.1989537195193294</v>
+        <v>0.1982477472054485</v>
       </c>
       <c r="CP2" s="2" t="n">
-        <v>0.1966981527655764</v>
+        <v>0.1961096761077089</v>
       </c>
       <c r="CQ2" s="2" t="n">
-        <v>0.1962144349950429</v>
+        <v>0.1956262749868508</v>
       </c>
       <c r="CR2" s="2" t="n">
-        <v>0.1776922631816504</v>
+        <v>0.1777091797248957</v>
       </c>
       <c r="CS2" s="2" t="n">
-        <v>0.1727122868704835</v>
+        <v>0.1731421332168618</v>
       </c>
       <c r="CT2" s="2" t="n">
-        <v>0.171554119030015</v>
+        <v>0.1721148124728365</v>
       </c>
       <c r="CU2" s="2" t="n">
-        <v>0.1784370124518123</v>
+        <v>0.1790682442664351</v>
       </c>
       <c r="CV2" s="2" t="n">
-        <v>0.275025969522027</v>
+        <v>0.2726582718658723</v>
       </c>
       <c r="CW2" s="2" t="n">
-        <v>0.263744609372382</v>
+        <v>0.2617652918562935</v>
       </c>
       <c r="CX2" s="2" t="n">
-        <v>0.2582500580762244</v>
+        <v>0.2563819516514159</v>
       </c>
       <c r="CY2" s="2" t="n">
-        <v>0.2540437885072073</v>
+        <v>0.2528110526945433</v>
       </c>
       <c r="CZ2" s="2" t="n">
-        <v>0.2427775926815227</v>
+        <v>0.2417179599331573</v>
       </c>
       <c r="DA2" s="2" t="n">
-        <v>0.237516623924064</v>
+        <v>0.236762971619653</v>
       </c>
       <c r="DB2" s="2" t="n">
-        <v>0.2360664312490288</v>
+        <v>0.2354665999063317</v>
       </c>
       <c r="DC2" s="2" t="n">
-        <v>0.2288257477641728</v>
+        <v>0.2283757736743119</v>
       </c>
       <c r="DD2" s="2" t="n">
-        <v>0.2251997729606021</v>
+        <v>0.2249702652758945</v>
       </c>
       <c r="DE2" s="2" t="n">
-        <v>0.2179084845225304</v>
+        <v>0.2178792298178166</v>
       </c>
       <c r="DF2" s="2" t="n">
-        <v>0.2081898376707867</v>
+        <v>0.2085600905482605</v>
       </c>
       <c r="DG2" s="2" t="n">
-        <v>0.2042692122691747</v>
+        <v>0.2048139577442284</v>
       </c>
       <c r="DH2" s="2" t="n">
-        <v>0.2011622967930232</v>
+        <v>0.2018504212410842</v>
       </c>
       <c r="DI2" s="2" t="n">
-        <v>0.2026137933965943</v>
+        <v>0.2036743351157925</v>
       </c>
       <c r="DJ2" s="2" t="n">
-        <v>0.2927569934805837</v>
+        <v>0.2910593861421552</v>
       </c>
       <c r="DK2" s="2" t="n">
-        <v>0.2844346823257884</v>
+        <v>0.2834065916103801</v>
       </c>
       <c r="DL2" s="2" t="n">
-        <v>0.2748369051002391</v>
+        <v>0.2738382702552207</v>
       </c>
       <c r="DM2" s="2" t="n">
-        <v>0.2713566326713045</v>
+        <v>0.2705209010457476</v>
       </c>
       <c r="DN2" s="2" t="n">
-        <v>0.2615117585762145</v>
+        <v>0.2610748751564624</v>
       </c>
       <c r="DO2" s="2" t="n">
-        <v>0.260036549993365</v>
+        <v>0.2595181199689796</v>
       </c>
       <c r="DP2" s="2" t="n">
-        <v>0.2501055331875405</v>
+        <v>0.2500389771510682</v>
       </c>
       <c r="DQ2" s="2" t="n">
-        <v>0.2423408344766935</v>
+        <v>0.242362247445329</v>
       </c>
       <c r="DR2" s="2" t="n">
-        <v>0.2382155909158974</v>
+        <v>0.2384614898779182</v>
       </c>
       <c r="DS2" s="2" t="n">
-        <v>0.2329355595865181</v>
+        <v>0.2333005858817032</v>
       </c>
       <c r="DT2" s="2" t="n">
-        <v>0.22632212836159</v>
+        <v>0.2269154814244581</v>
       </c>
       <c r="DU2" s="2" t="n">
-        <v>0.22208999182844</v>
+        <v>0.2227316879835113</v>
       </c>
       <c r="DV2" s="2" t="n">
-        <v>0.224227593169422</v>
+        <v>0.22518553294322</v>
       </c>
       <c r="DW2" s="2" t="n">
-        <v>0.2252760911108288</v>
+        <v>0.2265275576831135</v>
       </c>
       <c r="DX2" s="2" t="n">
-        <v>0.3047358032261323</v>
+        <v>0.3037059318219613</v>
       </c>
       <c r="DY2" s="2" t="n">
-        <v>0.2922531579952111</v>
+        <v>0.2915273671369424</v>
       </c>
       <c r="DZ2" s="2" t="n">
-        <v>0.2890550828905483</v>
+        <v>0.2886402718158145</v>
       </c>
       <c r="EA2" s="2" t="n">
-        <v>0.2781661278715378</v>
+        <v>0.2776642418613678</v>
       </c>
       <c r="EB2" s="2" t="n">
-        <v>0.273383433711628</v>
+        <v>0.2733038503349819</v>
       </c>
       <c r="EC2" s="2" t="n">
-        <v>0.2658399844837072</v>
+        <v>0.2658669779372098</v>
       </c>
       <c r="ED2" s="2" t="n">
-        <v>0.2605120352251383</v>
+        <v>0.2607353477520796</v>
       </c>
       <c r="EE2" s="2" t="n">
-        <v>0.2564894842008137</v>
+        <v>0.2569183470705533</v>
       </c>
       <c r="EF2" s="2" t="n">
-        <v>0.2537802994003157</v>
+        <v>0.2540058396508554</v>
       </c>
       <c r="EG2" s="2" t="n">
-        <v>0.2504647561763703</v>
+        <v>0.2508513258253514</v>
       </c>
       <c r="EH2" s="2" t="n">
-        <v>0.2351846800366543</v>
+        <v>0.2361497202137611</v>
       </c>
       <c r="EI2" s="2" t="n">
-        <v>0.2366081738407089</v>
+        <v>0.2377404236728622</v>
       </c>
       <c r="EJ2" s="2" t="n">
-        <v>0.2352137266698631</v>
+        <v>0.2365834525826724</v>
       </c>
       <c r="EK2" s="2" t="n">
-        <v>0.2375941246225604</v>
+        <v>0.2389715656115778</v>
       </c>
       <c r="EL2" s="2" t="n">
-        <v>0.3072070975574471</v>
+        <v>0.307133403864763</v>
       </c>
       <c r="EM2" s="2" t="n">
-        <v>0.2986861864485799</v>
+        <v>0.2990689451255857</v>
       </c>
       <c r="EN2" s="2" t="n">
-        <v>0.291703025806667</v>
+        <v>0.2921707583553806</v>
       </c>
       <c r="EO2" s="2" t="n">
-        <v>0.282299498961791</v>
+        <v>0.2828447249992933</v>
       </c>
       <c r="EP2" s="2" t="n">
-        <v>0.2848190920751261</v>
+        <v>0.2852953704397844</v>
       </c>
       <c r="EQ2" s="2" t="n">
-        <v>0.2716698013401095</v>
+        <v>0.2724064551448885</v>
       </c>
       <c r="ER2" s="2" t="n">
-        <v>0.2721033443082876</v>
+        <v>0.2727721903790541</v>
       </c>
       <c r="ES2" s="2" t="n">
-        <v>0.2626928445839934</v>
+        <v>0.2638802994930796</v>
       </c>
       <c r="ET2" s="2" t="n">
-        <v>0.2652233257183971</v>
+        <v>0.2661409094223919</v>
       </c>
       <c r="EU2" s="2" t="n">
-        <v>0.2628747391878166</v>
+        <v>0.2639278601287403</v>
       </c>
       <c r="EV2" s="2" t="n">
-        <v>0.2580136289002973</v>
+        <v>0.2592851561608392</v>
       </c>
       <c r="EW2" s="2" t="n">
-        <v>0.2557687138617775</v>
+        <v>0.2570490216315529</v>
       </c>
       <c r="EX2" s="2" t="n">
-        <v>0.2541066364553179</v>
+        <v>0.2556176849808897</v>
       </c>
       <c r="EY2" s="2" t="n">
-        <v>0.2665956018592982</v>
+        <v>0.2684189302947192</v>
       </c>
       <c r="EZ2" s="2" t="n">
-        <v>0.2971431112076661</v>
+        <v>0.2980383282687089</v>
       </c>
       <c r="FA2" s="2" t="n">
-        <v>0.2969323867998504</v>
+        <v>0.297953541024723</v>
       </c>
       <c r="FB2" s="2" t="n">
-        <v>0.2850415011235163</v>
+        <v>0.2860148449726985</v>
       </c>
       <c r="FC2" s="2" t="n">
-        <v>0.2864483441732086</v>
+        <v>0.2875067214987435</v>
       </c>
       <c r="FD2" s="2" t="n">
-        <v>0.2759294344005659</v>
+        <v>0.2770657373485639</v>
       </c>
       <c r="FE2" s="2" t="n">
-        <v>0.2770301558450811</v>
+        <v>0.278248549290096</v>
       </c>
       <c r="FF2" s="2" t="n">
-        <v>0.2765389195136215</v>
+        <v>0.2778056597761299</v>
       </c>
       <c r="FG2" s="2" t="n">
-        <v>0.2730183305623894</v>
+        <v>0.2743484901669388</v>
       </c>
       <c r="FH2" s="2" t="n">
-        <v>0.2684366389679673</v>
+        <v>0.2697605549859765</v>
       </c>
       <c r="FI2" s="2" t="n">
-        <v>0.2671605341805945</v>
+        <v>0.2684342854394446</v>
       </c>
       <c r="FJ2" s="2" t="n">
-        <v>0.2686211682794578</v>
+        <v>0.2700656719444282</v>
       </c>
       <c r="FK2" s="2" t="n">
-        <v>0.2684300881652023</v>
+        <v>0.2701108124879981</v>
       </c>
       <c r="FL2" s="2" t="n">
-        <v>0.2772692499839491</v>
+        <v>0.279062820800466</v>
       </c>
       <c r="FM2" s="2" t="n">
-        <v>0.2874453158298713</v>
+        <v>0.289507651440261</v>
       </c>
       <c r="FN2" s="2" t="n">
-        <v>0.2978727884476102</v>
+        <v>0.2993684328977979</v>
       </c>
       <c r="FO2" s="2" t="n">
-        <v>0.2972795712362236</v>
+        <v>0.2987075644145912</v>
       </c>
       <c r="FP2" s="2" t="n">
-        <v>0.2888659158567724</v>
+        <v>0.2903371596555052</v>
       </c>
       <c r="FQ2" s="2" t="n">
-        <v>0.2864396821299446</v>
+        <v>0.2880232732334984</v>
       </c>
       <c r="FR2" s="2" t="n">
-        <v>0.2928611465494865</v>
+        <v>0.2943991400997871</v>
       </c>
       <c r="FS2" s="2" t="n">
-        <v>0.2900398521459578</v>
+        <v>0.2916134147680282</v>
       </c>
       <c r="FT2" s="2" t="n">
-        <v>0.2908662167903289</v>
+        <v>0.2924656776305541</v>
       </c>
       <c r="FU2" s="2" t="n">
-        <v>0.2889934347268071</v>
+        <v>0.2907120154496159</v>
       </c>
       <c r="FV2" s="2" t="n">
-        <v>0.2905606759521535</v>
+        <v>0.2923911867472699</v>
       </c>
       <c r="FW2" s="2" t="n">
-        <v>0.2910992406194318</v>
+        <v>0.2929473645870794</v>
       </c>
       <c r="FX2" s="2" t="n">
-        <v>0.2882394292646854</v>
+        <v>0.2904204898768871</v>
       </c>
       <c r="FY2" s="2" t="n">
-        <v>0.2974422730676339</v>
+        <v>0.2997431986204789</v>
       </c>
       <c r="FZ2" s="2" t="n">
-        <v>0.3023747659190324</v>
+        <v>0.3048064342601922</v>
       </c>
       <c r="GA2" s="2" t="n">
-        <v>0.3173784324246526</v>
+        <v>0.3198519581276059</v>
       </c>
       <c r="GB2" s="2" t="n">
-        <v>0.3181047975718702</v>
+        <v>0.3199206903278554</v>
       </c>
       <c r="GC2" s="2" t="n">
-        <v>0.318981211995039</v>
+        <v>0.3210411038149929</v>
       </c>
       <c r="GD2" s="2" t="n">
-        <v>0.3211605843894643</v>
+        <v>0.3232739862792653</v>
       </c>
       <c r="GE2" s="2" t="n">
-        <v>0.3212899284990766</v>
+        <v>0.3234617652924993</v>
       </c>
       <c r="GF2" s="2" t="n">
-        <v>0.3187201707665751</v>
+        <v>0.3208973570768664</v>
       </c>
       <c r="GG2" s="2" t="n">
-        <v>0.3165402211319239</v>
+        <v>0.3187453620206149</v>
       </c>
       <c r="GH2" s="2" t="n">
-        <v>0.3127322696090278</v>
+        <v>0.3149477221012649</v>
       </c>
       <c r="GI2" s="2" t="n">
-        <v>0.3111948601270105</v>
+        <v>0.3138966120148088</v>
       </c>
       <c r="GJ2" s="2" t="n">
-        <v>0.3128404820092067</v>
+        <v>0.3153083452709063</v>
       </c>
       <c r="GK2" s="2" t="n">
-        <v>0.3163471398708241</v>
+        <v>0.3189419535753148</v>
       </c>
       <c r="GL2" s="2" t="n">
-        <v>0.3206330798230582</v>
+        <v>0.3235170207581931</v>
       </c>
       <c r="GM2" s="2" t="n">
-        <v>0.3250646448155633</v>
+        <v>0.3281024104377023</v>
       </c>
       <c r="GN2" s="2" t="n">
-        <v>0.3401511757193038</v>
+        <v>0.3432415275392958</v>
       </c>
       <c r="GO2" s="2" t="n">
-        <v>0.3498493919883061</v>
+        <v>0.3531394789729405</v>
       </c>
       <c r="GP2" s="2" t="n">
-        <v>0.3452145869598103</v>
+        <v>0.3478785271510793</v>
       </c>
       <c r="GQ2" s="2" t="n">
-        <v>0.3400861219559365</v>
+        <v>0.3427011341844254</v>
       </c>
       <c r="GR2" s="2" t="n">
-        <v>0.34052576194542</v>
+        <v>0.3428398899270828</v>
       </c>
       <c r="GS2" s="2" t="n">
-        <v>0.3382297792257175</v>
+        <v>0.3408567943395481</v>
       </c>
       <c r="GT2" s="2" t="n">
-        <v>0.3400692639925818</v>
+        <v>0.3426868541219573</v>
       </c>
       <c r="GU2" s="2" t="n">
-        <v>0.3340234817194522</v>
+        <v>0.336742839329201</v>
       </c>
       <c r="GV2" s="2" t="n">
-        <v>0.3395923856169553</v>
+        <v>0.3424141738087506</v>
       </c>
       <c r="GW2" s="2" t="n">
-        <v>0.3340344124063854</v>
+        <v>0.3368172787651424</v>
       </c>
       <c r="GX2" s="2" t="n">
-        <v>0.3353844531871324</v>
+        <v>0.3384387814499383</v>
       </c>
       <c r="GY2" s="2" t="n">
-        <v>0.3358487711241809</v>
+        <v>0.3391167522361842</v>
       </c>
       <c r="GZ2" s="2" t="n">
-        <v>0.347222937032087</v>
+        <v>0.3505569451893402</v>
       </c>
       <c r="HA2" s="2" t="n">
-        <v>0.3600871322910104</v>
+        <v>0.3633005379001412</v>
       </c>
       <c r="HB2" s="2" t="n">
-        <v>0.3729382035406626</v>
+        <v>0.3761819032105005</v>
       </c>
       <c r="HC2" s="2" t="n">
-        <v>0.3644495032936297</v>
+        <v>0.3673004158049784</v>
       </c>
       <c r="HD2" s="2" t="n">
-        <v>0.3557528462679959</v>
+        <v>0.3598024156363583</v>
       </c>
       <c r="HE2" s="2" t="n">
-        <v>0.3498544848045081</v>
+        <v>0.3535362041076392</v>
       </c>
       <c r="HF2" s="2" t="n">
-        <v>0.3524010462285371</v>
+        <v>0.3562420365930886</v>
       </c>
       <c r="HG2" s="2" t="n">
-        <v>0.3598669524932567</v>
+        <v>0.3638368006492321</v>
       </c>
       <c r="HH2" s="2" t="n">
-        <v>0.3595855631829942</v>
+        <v>0.3633983680011476</v>
       </c>
       <c r="HI2" s="2" t="n">
-        <v>0.358410729944927</v>
+        <v>0.3623787527086561</v>
       </c>
       <c r="HJ2" s="2" t="n">
-        <v>0.3620858753446208</v>
+        <v>0.3656615505341159</v>
       </c>
       <c r="HK2" s="2" t="n">
-        <v>0.3561747092725996</v>
+        <v>0.3600596357109312</v>
       </c>
       <c r="HL2" s="2" t="n">
-        <v>0.3592826420803387</v>
+        <v>0.3630113521952946</v>
       </c>
       <c r="HM2" s="2" t="n">
-        <v>0.3577279245727429</v>
+        <v>0.3614902964108357</v>
       </c>
       <c r="HN2" s="2" t="n">
-        <v>0.3785735345460251</v>
+        <v>0.382178326604493</v>
       </c>
       <c r="HO2" s="2" t="n">
-        <v>0.3913579268253616</v>
+        <v>0.395227534869986</v>
       </c>
       <c r="HP2" s="2" t="n">
-        <v>0.3667966291404061</v>
+        <v>0.3697016403174691</v>
       </c>
       <c r="HQ2" s="2" t="n">
-        <v>0.3514605593063599</v>
+        <v>0.3541566264011627</v>
       </c>
       <c r="HR2" s="3" t="n">
         <v>55511</v>
@@ -2191,676 +2191,676 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.02853817024780871</v>
+        <v>0.02838799634529712</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.03828656785217448</v>
+        <v>0.03792388290194198</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.04057772445847985</v>
+        <v>0.04022006958147284</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.04223383134731713</v>
+        <v>0.04183899155387345</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.04272744660948591</v>
+        <v>0.04226155528550224</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.04181582833192703</v>
+        <v>0.04138671121112462</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.04114656779972625</v>
+        <v>0.0407692825054915</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.04083496838683952</v>
+        <v>0.04048257082576622</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.04101227253617083</v>
+        <v>0.04067552771360909</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.04015781302914546</v>
+        <v>0.03990652822867559</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.03891247837785101</v>
+        <v>0.03873312613907671</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.0370693154855213</v>
+        <v>0.03709049748615836</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.03692010593033079</v>
+        <v>0.03696047131335977</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.037309996714973</v>
+        <v>0.03744560473241761</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.05580879622581338</v>
+        <v>0.05558588789286947</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.06918258440092689</v>
+        <v>0.06855545040563232</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.07276967407186857</v>
+        <v>0.07195026666839949</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.07349928393118678</v>
+        <v>0.07267617358916102</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.07483974656839533</v>
+        <v>0.07405093869943781</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.07163155050271144</v>
+        <v>0.07094957092099777</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.07271470436303276</v>
+        <v>0.07204718822090286</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.07177697609948967</v>
+        <v>0.07125415582048748</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.07159933160045082</v>
+        <v>0.07110952298142845</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.07097869961495872</v>
+        <v>0.07051563299234385</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.0673019276188794</v>
+        <v>0.06699755370636615</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.06377201573475964</v>
+        <v>0.06380254821404584</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.06373481173540285</v>
+        <v>0.06378398184205225</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.06469524072972017</v>
+        <v>0.06488348616775948</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.09043708157452751</v>
+        <v>0.08983945374104191</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>0.1048906519261006</v>
+        <v>0.1037370394167307</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>0.1058986249638958</v>
+        <v>0.1044766052885218</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0.1073287053478529</v>
+        <v>0.1060054356677105</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>0.1073992324377686</v>
+        <v>0.1061382850016743</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>0.1063135534273637</v>
+        <v>0.1052256047474397</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>0.1026538590604829</v>
+        <v>0.1017368117982911</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>0.1009360817376158</v>
+        <v>0.1002362524274371</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>0.101807189384665</v>
+        <v>0.101047969633903</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>0.09809225408364042</v>
+        <v>0.09751723876226648</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.0921902854624268</v>
+        <v>0.09195290065138306</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>0.08948348934226995</v>
+        <v>0.08951855549984937</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>0.09200026745042363</v>
+        <v>0.09208027923545399</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.09231339452194377</v>
+        <v>0.09249745925294563</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.1221185586667053</v>
+        <v>0.1212286035782091</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>0.1336750893383497</v>
+        <v>0.1316230187653774</v>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>0.1342787934914726</v>
+        <v>0.1322642421797413</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>0.1344347589050326</v>
+        <v>0.1325986005698237</v>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>0.1325974050929718</v>
+        <v>0.1311121821423941</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>0.1269905470860513</v>
+        <v>0.1257170007181676</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>0.1272055805474346</v>
+        <v>0.1261616741120641</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>0.1254931911190722</v>
+        <v>0.1246268301566813</v>
       </c>
       <c r="AZ3" s="2" t="n">
-        <v>0.1245296659644152</v>
+        <v>0.1236788115228916</v>
       </c>
       <c r="BA3" s="2" t="n">
-        <v>0.1195834030617581</v>
+        <v>0.1189433255453215</v>
       </c>
       <c r="BB3" s="2" t="n">
-        <v>0.1133561042594846</v>
+        <v>0.1130133775520261</v>
       </c>
       <c r="BC3" s="2" t="n">
-        <v>0.1109288687660169</v>
+        <v>0.1109115405781936</v>
       </c>
       <c r="BD3" s="2" t="n">
-        <v>0.1093044716578584</v>
+        <v>0.109434225381599</v>
       </c>
       <c r="BE3" s="2" t="n">
-        <v>0.1121950593328364</v>
+        <v>0.1124702390766032</v>
       </c>
       <c r="BF3" s="2" t="n">
-        <v>0.1546889331530378</v>
+        <v>0.1528462592850969</v>
       </c>
       <c r="BG3" s="2" t="n">
-        <v>0.1593090985023069</v>
+        <v>0.156842218717246</v>
       </c>
       <c r="BH3" s="2" t="n">
-        <v>0.1580854314124182</v>
+        <v>0.1557986060833528</v>
       </c>
       <c r="BI3" s="2" t="n">
-        <v>0.1547238398925644</v>
+        <v>0.1524698567227703</v>
       </c>
       <c r="BJ3" s="2" t="n">
-        <v>0.1538581132527625</v>
+        <v>0.1521261848148142</v>
       </c>
       <c r="BK3" s="2" t="n">
-        <v>0.1460378202008614</v>
+        <v>0.1446704486715206</v>
       </c>
       <c r="BL3" s="2" t="n">
-        <v>0.1446918199720207</v>
+        <v>0.1435122030737225</v>
       </c>
       <c r="BM3" s="2" t="n">
-        <v>0.1412213376154161</v>
+        <v>0.1403488634516454</v>
       </c>
       <c r="BN3" s="2" t="n">
-        <v>0.139668597897176</v>
+        <v>0.138785972317342</v>
       </c>
       <c r="BO3" s="2" t="n">
-        <v>0.1403602038471353</v>
+        <v>0.139616557672466</v>
       </c>
       <c r="BP3" s="2" t="n">
-        <v>0.1298387096258413</v>
+        <v>0.1295445420774233</v>
       </c>
       <c r="BQ3" s="2" t="n">
-        <v>0.1280204800368866</v>
+        <v>0.1281423380078396</v>
       </c>
       <c r="BR3" s="2" t="n">
-        <v>0.1271289754101219</v>
+        <v>0.1273514255323591</v>
       </c>
       <c r="BS3" s="2" t="n">
-        <v>0.1263770977377418</v>
+        <v>0.1267704809426787</v>
       </c>
       <c r="BT3" s="2" t="n">
-        <v>0.1970393120818475</v>
+        <v>0.1941433198325971</v>
       </c>
       <c r="BU3" s="2" t="n">
-        <v>0.1961171941705516</v>
+        <v>0.1928331347056201</v>
       </c>
       <c r="BV3" s="2" t="n">
-        <v>0.191475342498993</v>
+        <v>0.1887301611768952</v>
       </c>
       <c r="BW3" s="2" t="n">
-        <v>0.1906895284063393</v>
+        <v>0.1881214362091595</v>
       </c>
       <c r="BX3" s="2" t="n">
-        <v>0.185216134940504</v>
+        <v>0.1833790490080107</v>
       </c>
       <c r="BY3" s="2" t="n">
-        <v>0.1799684391582171</v>
+        <v>0.1785947756135622</v>
       </c>
       <c r="BZ3" s="2" t="n">
-        <v>0.175323111978327</v>
+        <v>0.1741592120797979</v>
       </c>
       <c r="CA3" s="2" t="n">
-        <v>0.1711749043851589</v>
+        <v>0.1701886710315441</v>
       </c>
       <c r="CB3" s="2" t="n">
-        <v>0.1681606535116062</v>
+        <v>0.1674690012136326</v>
       </c>
       <c r="CC3" s="2" t="n">
-        <v>0.1628722232646366</v>
+        <v>0.1622019764847179</v>
       </c>
       <c r="CD3" s="2" t="n">
-        <v>0.1572883873891229</v>
+        <v>0.1570309325765962</v>
       </c>
       <c r="CE3" s="2" t="n">
-        <v>0.1484433182008788</v>
+        <v>0.1486771248705909</v>
       </c>
       <c r="CF3" s="2" t="n">
-        <v>0.1482175007756399</v>
+        <v>0.148556990205829</v>
       </c>
       <c r="CG3" s="2" t="n">
-        <v>0.1510996679144975</v>
+        <v>0.1515856394845125</v>
       </c>
       <c r="CH3" s="2" t="n">
-        <v>0.22560727460687</v>
+        <v>0.2225091518313154</v>
       </c>
       <c r="CI3" s="2" t="n">
-        <v>0.2262385178696414</v>
+        <v>0.2229374152015944</v>
       </c>
       <c r="CJ3" s="2" t="n">
-        <v>0.2205190867117892</v>
+        <v>0.2179215237430582</v>
       </c>
       <c r="CK3" s="2" t="n">
-        <v>0.213976962469831</v>
+        <v>0.2119495402801185</v>
       </c>
       <c r="CL3" s="2" t="n">
-        <v>0.209106126126884</v>
+        <v>0.2075403903397307</v>
       </c>
       <c r="CM3" s="2" t="n">
-        <v>0.200105148871934</v>
+        <v>0.1991050313613769</v>
       </c>
       <c r="CN3" s="2" t="n">
-        <v>0.1996208989800682</v>
+        <v>0.1986464971484413</v>
       </c>
       <c r="CO3" s="2" t="n">
-        <v>0.1919679691066956</v>
+        <v>0.1912150544097638</v>
       </c>
       <c r="CP3" s="2" t="n">
-        <v>0.1898224785161962</v>
+        <v>0.1891963279975404</v>
       </c>
       <c r="CQ3" s="2" t="n">
-        <v>0.1896733226415812</v>
+        <v>0.1890564443704782</v>
       </c>
       <c r="CR3" s="2" t="n">
-        <v>0.1729649292781605</v>
+        <v>0.1729517119481816</v>
       </c>
       <c r="CS3" s="2" t="n">
-        <v>0.1686130643702878</v>
+        <v>0.169044233194722</v>
       </c>
       <c r="CT3" s="2" t="n">
-        <v>0.1677397050735774</v>
+        <v>0.1683011100468459</v>
       </c>
       <c r="CU3" s="2" t="n">
-        <v>0.1743868426945445</v>
+        <v>0.1750250817802188</v>
       </c>
       <c r="CV3" s="2" t="n">
-        <v>0.2632595026191887</v>
+        <v>0.2608284489509282</v>
       </c>
       <c r="CW3" s="2" t="n">
-        <v>0.2515175021740967</v>
+        <v>0.2494599535617406</v>
       </c>
       <c r="CX3" s="2" t="n">
-        <v>0.2479011168499844</v>
+        <v>0.2459698071499722</v>
       </c>
       <c r="CY3" s="2" t="n">
-        <v>0.2445577281674445</v>
+        <v>0.2432776923438609</v>
       </c>
       <c r="CZ3" s="2" t="n">
-        <v>0.2337302464087369</v>
+        <v>0.2326384457786442</v>
       </c>
       <c r="DA3" s="2" t="n">
-        <v>0.2289739331178732</v>
+        <v>0.2281810795836515</v>
       </c>
       <c r="DB3" s="2" t="n">
-        <v>0.2280571962351954</v>
+        <v>0.2274170647020495</v>
       </c>
       <c r="DC3" s="2" t="n">
-        <v>0.2215664344892738</v>
+        <v>0.2210712316498992</v>
       </c>
       <c r="DD3" s="2" t="n">
-        <v>0.2189530240879514</v>
+        <v>0.2187106417999723</v>
       </c>
       <c r="DE3" s="2" t="n">
-        <v>0.2122224728981723</v>
+        <v>0.2121884013931025</v>
       </c>
       <c r="DF3" s="2" t="n">
-        <v>0.2036567525077737</v>
+        <v>0.2040046499181665</v>
       </c>
       <c r="DG3" s="2" t="n">
-        <v>0.1998349371905747</v>
+        <v>0.2003654110784951</v>
       </c>
       <c r="DH3" s="2" t="n">
-        <v>0.1972800210021542</v>
+        <v>0.1979657873414563</v>
       </c>
       <c r="DI3" s="2" t="n">
-        <v>0.1989737208857483</v>
+        <v>0.2000398840680069</v>
       </c>
       <c r="DJ3" s="2" t="n">
-        <v>0.2808049662168765</v>
+        <v>0.2790540835018896</v>
       </c>
       <c r="DK3" s="2" t="n">
-        <v>0.2740537112575148</v>
+        <v>0.2729736750941847</v>
       </c>
       <c r="DL3" s="2" t="n">
-        <v>0.2646275911431073</v>
+        <v>0.2635861154596566</v>
       </c>
       <c r="DM3" s="2" t="n">
-        <v>0.2618190722050074</v>
+        <v>0.260942693937004</v>
       </c>
       <c r="DN3" s="2" t="n">
-        <v>0.2528520629159585</v>
+        <v>0.2523648955277578</v>
       </c>
       <c r="DO3" s="2" t="n">
-        <v>0.2519878516846351</v>
+        <v>0.2514353799575023</v>
       </c>
       <c r="DP3" s="2" t="n">
-        <v>0.2433002814581083</v>
+        <v>0.2431964166392969</v>
       </c>
       <c r="DQ3" s="2" t="n">
-        <v>0.2360829345621581</v>
+        <v>0.2360670573749061</v>
       </c>
       <c r="DR3" s="2" t="n">
-        <v>0.2327708039939889</v>
+        <v>0.2330062833190449</v>
       </c>
       <c r="DS3" s="2" t="n">
-        <v>0.2281380573197261</v>
+        <v>0.2284927757366554</v>
       </c>
       <c r="DT3" s="2" t="n">
-        <v>0.2220461993925186</v>
+        <v>0.2226352199427696</v>
       </c>
       <c r="DU3" s="2" t="n">
-        <v>0.2186749993279026</v>
+        <v>0.2193200407936619</v>
       </c>
       <c r="DV3" s="2" t="n">
-        <v>0.2207781699459523</v>
+        <v>0.221746290938136</v>
       </c>
       <c r="DW3" s="2" t="n">
-        <v>0.2219736966324445</v>
+        <v>0.2232423665953275</v>
       </c>
       <c r="DX3" s="2" t="n">
-        <v>0.2940659803059046</v>
+        <v>0.2930082139279788</v>
       </c>
       <c r="DY3" s="2" t="n">
-        <v>0.2823508702918324</v>
+        <v>0.2815832146211895</v>
       </c>
       <c r="DZ3" s="2" t="n">
-        <v>0.2797374333215623</v>
+        <v>0.2793017680717378</v>
       </c>
       <c r="EA3" s="2" t="n">
-        <v>0.2697759624924336</v>
+        <v>0.2692407649364147</v>
       </c>
       <c r="EB3" s="2" t="n">
-        <v>0.2661952953904021</v>
+        <v>0.2660904247432101</v>
       </c>
       <c r="EC3" s="2" t="n">
-        <v>0.2592157834626382</v>
+        <v>0.2592112311578935</v>
       </c>
       <c r="ED3" s="2" t="n">
-        <v>0.2546129018507018</v>
+        <v>0.2548273519120231</v>
       </c>
       <c r="EE3" s="2" t="n">
-        <v>0.2513296862624596</v>
+        <v>0.2517493141375493</v>
       </c>
       <c r="EF3" s="2" t="n">
-        <v>0.2488273680788054</v>
+        <v>0.2490517683905138</v>
       </c>
       <c r="EG3" s="2" t="n">
-        <v>0.2457664958071749</v>
+        <v>0.2461535832715074</v>
       </c>
       <c r="EH3" s="2" t="n">
-        <v>0.2312653904470171</v>
+        <v>0.2322366630347933</v>
       </c>
       <c r="EI3" s="2" t="n">
-        <v>0.2332689338292697</v>
+        <v>0.2344186217453101</v>
       </c>
       <c r="EJ3" s="2" t="n">
-        <v>0.2326074566547791</v>
+        <v>0.2339973773662964</v>
       </c>
       <c r="EK3" s="2" t="n">
-        <v>0.2347881645635062</v>
+        <v>0.236183557726472</v>
       </c>
       <c r="EL3" s="2" t="n">
-        <v>0.2987675398346502</v>
+        <v>0.2986423626300413</v>
       </c>
       <c r="EM3" s="2" t="n">
-        <v>0.2918345700938502</v>
+        <v>0.2922151532013216</v>
       </c>
       <c r="EN3" s="2" t="n">
-        <v>0.2857348411481281</v>
+        <v>0.2861992134849926</v>
       </c>
       <c r="EO3" s="2" t="n">
-        <v>0.2770923554000508</v>
+        <v>0.2776295571622502</v>
       </c>
       <c r="EP3" s="2" t="n">
-        <v>0.2797812301887994</v>
+        <v>0.2802546624316697</v>
       </c>
       <c r="EQ3" s="2" t="n">
-        <v>0.2672532892201018</v>
+        <v>0.2679879909727644</v>
       </c>
       <c r="ER3" s="2" t="n">
-        <v>0.2673048899300329</v>
+        <v>0.2679775954015485</v>
       </c>
       <c r="ES3" s="2" t="n">
-        <v>0.2587434856259779</v>
+        <v>0.2599540112578825</v>
       </c>
       <c r="ET3" s="2" t="n">
-        <v>0.2614863224291578</v>
+        <v>0.2624168664181009</v>
       </c>
       <c r="EU3" s="2" t="n">
-        <v>0.2595539958408719</v>
+        <v>0.2606256091228372</v>
       </c>
       <c r="EV3" s="2" t="n">
-        <v>0.2551608868232458</v>
+        <v>0.2564607039383143</v>
       </c>
       <c r="EW3" s="2" t="n">
-        <v>0.2535607045361989</v>
+        <v>0.2548708779582971</v>
       </c>
       <c r="EX3" s="2" t="n">
-        <v>0.2522652346801661</v>
+        <v>0.2538136478674315</v>
       </c>
       <c r="EY3" s="2" t="n">
-        <v>0.2641865001546804</v>
+        <v>0.2660423317479555</v>
       </c>
       <c r="EZ3" s="2" t="n">
-        <v>0.2934868081736152</v>
+        <v>0.2943967401313369</v>
       </c>
       <c r="FA3" s="2" t="n">
-        <v>0.2934039859957658</v>
+        <v>0.294446366924759</v>
       </c>
       <c r="FB3" s="2" t="n">
-        <v>0.2819765663553935</v>
+        <v>0.2829685143043261</v>
       </c>
       <c r="FC3" s="2" t="n">
-        <v>0.2836766475600795</v>
+        <v>0.284768247024496</v>
       </c>
       <c r="FD3" s="2" t="n">
-        <v>0.2733922814525946</v>
+        <v>0.2745511149563178</v>
       </c>
       <c r="FE3" s="2" t="n">
-        <v>0.2746040436627301</v>
+        <v>0.2758641603590878</v>
       </c>
       <c r="FF3" s="2" t="n">
-        <v>0.2741746525281686</v>
+        <v>0.2754645268434304</v>
       </c>
       <c r="FG3" s="2" t="n">
-        <v>0.2706938826382624</v>
+        <v>0.2720551335156428</v>
       </c>
       <c r="FH3" s="2" t="n">
-        <v>0.2661231543169091</v>
+        <v>0.2674777667269776</v>
       </c>
       <c r="FI3" s="2" t="n">
-        <v>0.2648260864396658</v>
+        <v>0.2661270844717588</v>
       </c>
       <c r="FJ3" s="2" t="n">
-        <v>0.2664485097423533</v>
+        <v>0.2679216534391383</v>
       </c>
       <c r="FK3" s="2" t="n">
-        <v>0.2668614348245647</v>
+        <v>0.2685752322746303</v>
       </c>
       <c r="FL3" s="2" t="n">
-        <v>0.2759736340997579</v>
+        <v>0.2778134953735235</v>
       </c>
       <c r="FM3" s="2" t="n">
-        <v>0.2861605416278891</v>
+        <v>0.2882794494967513</v>
       </c>
       <c r="FN3" s="2" t="n">
-        <v>0.2950736967429003</v>
+        <v>0.2966029805644831</v>
       </c>
       <c r="FO3" s="2" t="n">
-        <v>0.2947416736687632</v>
+        <v>0.2962160988654108</v>
       </c>
       <c r="FP3" s="2" t="n">
-        <v>0.2864318453509085</v>
+        <v>0.2879286595422499</v>
       </c>
       <c r="FQ3" s="2" t="n">
-        <v>0.2842570197504765</v>
+        <v>0.2858861190003162</v>
       </c>
       <c r="FR3" s="2" t="n">
-        <v>0.2902340500605614</v>
+        <v>0.291804483438781</v>
       </c>
       <c r="FS3" s="2" t="n">
-        <v>0.2876208733013042</v>
+        <v>0.2892331938436397</v>
       </c>
       <c r="FT3" s="2" t="n">
-        <v>0.288194841852008</v>
+        <v>0.2898438341520416</v>
       </c>
       <c r="FU3" s="2" t="n">
-        <v>0.2862717610509288</v>
+        <v>0.288030112972964</v>
       </c>
       <c r="FV3" s="2" t="n">
-        <v>0.2879009111925653</v>
+        <v>0.2897738604947618</v>
       </c>
       <c r="FW3" s="2" t="n">
-        <v>0.2883664985799082</v>
+        <v>0.2902652864956148</v>
       </c>
       <c r="FX3" s="2" t="n">
-        <v>0.286057862690843</v>
+        <v>0.2882955402650007</v>
       </c>
       <c r="FY3" s="2" t="n">
-        <v>0.2956131211025116</v>
+        <v>0.2979757970673439</v>
       </c>
       <c r="FZ3" s="2" t="n">
-        <v>0.3003528878151058</v>
+        <v>0.302841664856541</v>
       </c>
       <c r="GA3" s="2" t="n">
-        <v>0.3151099587910406</v>
+        <v>0.3176363612644903</v>
       </c>
       <c r="GB3" s="2" t="n">
-        <v>0.3140455125540481</v>
+        <v>0.3159097968310103</v>
       </c>
       <c r="GC3" s="2" t="n">
-        <v>0.3149090013223862</v>
+        <v>0.3170001408773636</v>
       </c>
       <c r="GD3" s="2" t="n">
-        <v>0.3166364274801473</v>
+        <v>0.3187781192244749</v>
       </c>
       <c r="GE3" s="2" t="n">
-        <v>0.3167186901111394</v>
+        <v>0.3189131915707379</v>
       </c>
       <c r="GF3" s="2" t="n">
-        <v>0.3143908606144167</v>
+        <v>0.3165974990698076</v>
       </c>
       <c r="GG3" s="2" t="n">
-        <v>0.3124258919557545</v>
+        <v>0.3146633162101719</v>
       </c>
       <c r="GH3" s="2" t="n">
-        <v>0.3085944582693541</v>
+        <v>0.3108529229633772</v>
       </c>
       <c r="GI3" s="2" t="n">
-        <v>0.3076754772345471</v>
+        <v>0.3104387858192372</v>
       </c>
       <c r="GJ3" s="2" t="n">
-        <v>0.3089156791134356</v>
+        <v>0.3114280819459437</v>
       </c>
       <c r="GK3" s="2" t="n">
-        <v>0.3124683914484807</v>
+        <v>0.3151287330093213</v>
       </c>
       <c r="GL3" s="2" t="n">
-        <v>0.3172735417940145</v>
+        <v>0.3202056730844503</v>
       </c>
       <c r="GM3" s="2" t="n">
-        <v>0.3220720681690891</v>
+        <v>0.325164752020808</v>
       </c>
       <c r="GN3" s="2" t="n">
-        <v>0.3374061598660508</v>
+        <v>0.3405657797338525</v>
       </c>
       <c r="GO3" s="2" t="n">
-        <v>0.3464938216671525</v>
+        <v>0.3498553820714532</v>
       </c>
       <c r="GP3" s="2" t="n">
-        <v>0.3414550348297787</v>
+        <v>0.344178266741438</v>
       </c>
       <c r="GQ3" s="2" t="n">
-        <v>0.3368967413106235</v>
+        <v>0.3395714773931774</v>
       </c>
       <c r="GR3" s="2" t="n">
-        <v>0.337074338187268</v>
+        <v>0.339434801329663</v>
       </c>
       <c r="GS3" s="2" t="n">
-        <v>0.3349208789463821</v>
+        <v>0.3376050400133911</v>
       </c>
       <c r="GT3" s="2" t="n">
-        <v>0.3365057334243196</v>
+        <v>0.3391622304855721</v>
       </c>
       <c r="GU3" s="2" t="n">
-        <v>0.3305213724120703</v>
+        <v>0.3332908649786558</v>
       </c>
       <c r="GV3" s="2" t="n">
-        <v>0.3359883364256995</v>
+        <v>0.3388688202914374</v>
       </c>
       <c r="GW3" s="2" t="n">
-        <v>0.330531959695523</v>
+        <v>0.3333794821927001</v>
       </c>
       <c r="GX3" s="2" t="n">
-        <v>0.3317668008406885</v>
+        <v>0.3349001276095637</v>
       </c>
       <c r="GY3" s="2" t="n">
-        <v>0.3321401352491411</v>
+        <v>0.3354882399048837</v>
       </c>
       <c r="GZ3" s="2" t="n">
-        <v>0.3440535139260855</v>
+        <v>0.347466371577796</v>
       </c>
       <c r="HA3" s="2" t="n">
-        <v>0.3569295299689329</v>
+        <v>0.3602134404222525</v>
       </c>
       <c r="HB3" s="2" t="n">
-        <v>0.3698794311048874</v>
+        <v>0.3732090583207497</v>
       </c>
       <c r="HC3" s="2" t="n">
-        <v>0.3621257400716145</v>
+        <v>0.3650377696955998</v>
       </c>
       <c r="HD3" s="2" t="n">
-        <v>0.3525097249531036</v>
+        <v>0.3566774009250885</v>
       </c>
       <c r="HE3" s="2" t="n">
-        <v>0.3469144478527892</v>
+        <v>0.3506927117792953</v>
       </c>
       <c r="HF3" s="2" t="n">
-        <v>0.34908720274972</v>
+        <v>0.3530344160418419</v>
       </c>
       <c r="HG3" s="2" t="n">
-        <v>0.356378222014583</v>
+        <v>0.3604425286313661</v>
       </c>
       <c r="HH3" s="2" t="n">
-        <v>0.355893611390473</v>
+        <v>0.3598116854618804</v>
       </c>
       <c r="HI3" s="2" t="n">
-        <v>0.3546274860384075</v>
+        <v>0.3586749319912998</v>
       </c>
       <c r="HJ3" s="2" t="n">
-        <v>0.3580915242505822</v>
+        <v>0.3617717906904969</v>
       </c>
       <c r="HK3" s="2" t="n">
-        <v>0.3519500620878762</v>
+        <v>0.3559455327905243</v>
       </c>
       <c r="HL3" s="2" t="n">
-        <v>0.3546983820448575</v>
+        <v>0.358524806524342</v>
       </c>
       <c r="HM3" s="2" t="n">
-        <v>0.3526809062578409</v>
+        <v>0.356502994499418</v>
       </c>
       <c r="HN3" s="2" t="n">
-        <v>0.3748497949424375</v>
+        <v>0.3785696239653219</v>
       </c>
       <c r="HO3" s="2" t="n">
-        <v>0.3883638506624195</v>
+        <v>0.3923139026257488</v>
       </c>
       <c r="HP3" s="2" t="n">
-        <v>0.3644144254235601</v>
+        <v>0.367423394551692</v>
       </c>
       <c r="HQ3" s="2" t="n">
-        <v>0.3498297524454621</v>
+        <v>0.3525903415682343</v>
       </c>
       <c r="HR3" s="3" t="n">
         <v>55513</v>
@@ -2873,676 +2873,676 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.02940107338565478</v>
+        <v>0.02926647725018748</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.03796155669446113</v>
+        <v>0.03761772450710657</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.04015807668313805</v>
+        <v>0.03980352497294967</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.04187610183999813</v>
+        <v>0.04148331654415405</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.04229988802672696</v>
+        <v>0.04183653083146882</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.04157169861364149</v>
+        <v>0.04113907878863596</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.04110282409357713</v>
+        <v>0.04072059720176147</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.04089419518239924</v>
+        <v>0.04053575147517154</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.04119390435650665</v>
+        <v>0.04085053410514909</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.0404755335651328</v>
+        <v>0.04021125867739219</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.0393582305866334</v>
+        <v>0.03916767267464133</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0378509760927846</v>
+        <v>0.03786184090194007</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.03779914066373356</v>
+        <v>0.03782899420886286</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.0384022487356793</v>
+        <v>0.03852517865891567</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.05658370158293729</v>
+        <v>0.0563817452139545</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.06814565466203511</v>
+        <v>0.06753347956993401</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07167555370179672</v>
+        <v>0.07086780831960697</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.07255538640529</v>
+        <v>0.07174287265151821</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.07411901586441222</v>
+        <v>0.07332634300677005</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.07141990316171981</v>
+        <v>0.07073087719340659</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.07252758522425605</v>
+        <v>0.07184853744600726</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.07206201729563291</v>
+        <v>0.0715233775713783</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.0718697856711239</v>
+        <v>0.07135375287104551</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.07134763674778213</v>
+        <v>0.07086519302767982</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.06793677586304207</v>
+        <v>0.06761043857025166</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.06506797052199494</v>
+        <v>0.06508274595464121</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>0.06513998912439442</v>
+        <v>0.06515904025898075</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>0.06635359624648922</v>
+        <v>0.06651857910925978</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.08920147150416173</v>
+        <v>0.08864126421172418</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>0.1023764415864697</v>
+        <v>0.1012439421598664</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.1036317586464734</v>
+        <v>0.1022213842285723</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>0.1054776694263359</v>
+        <v>0.1041434194530388</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1062064338431783</v>
+        <v>0.1049336735115476</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>0.1055709689411509</v>
+        <v>0.1044572561535227</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>0.1022914894092228</v>
+        <v>0.1013530533927824</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>0.1011694973020526</v>
+        <v>0.1004477930872413</v>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>0.1019452155520603</v>
+        <v>0.1011573688079998</v>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>0.09856111695866726</v>
+        <v>0.09795473841827057</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.09316458339421943</v>
+        <v>0.09288766766517356</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>0.09111143014061115</v>
+        <v>0.09111069439577721</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>0.09384521241924228</v>
+        <v>0.09388780738851489</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.09439985095872221</v>
+        <v>0.09455749220563707</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.1193403214796318</v>
+        <v>0.1184829589559568</v>
       </c>
       <c r="AS4" s="2" t="n">
-        <v>0.1296202515182467</v>
+        <v>0.1275733609614344</v>
       </c>
       <c r="AT4" s="2" t="n">
-        <v>0.1308549456879162</v>
+        <v>0.1288300939485096</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>0.1317431084537193</v>
+        <v>0.1298898100578472</v>
       </c>
       <c r="AV4" s="2" t="n">
-        <v>0.1314830906313189</v>
+        <v>0.1299696988981493</v>
       </c>
       <c r="AW4" s="2" t="n">
-        <v>0.1261300859437852</v>
+        <v>0.124828786163178</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>0.126910101097587</v>
+        <v>0.125827656534079</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>0.1258085085786262</v>
+        <v>0.1248988206274191</v>
       </c>
       <c r="AZ4" s="2" t="n">
-        <v>0.1247685127571976</v>
+        <v>0.1238779262319958</v>
       </c>
       <c r="BA4" s="2" t="n">
-        <v>0.1202721439289303</v>
+        <v>0.1195951692747326</v>
       </c>
       <c r="BB4" s="2" t="n">
-        <v>0.114474933655836</v>
+        <v>0.1140924376117962</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>0.1128600518085177</v>
+        <v>0.1128087582863981</v>
       </c>
       <c r="BD4" s="2" t="n">
-        <v>0.1115818335196533</v>
+        <v>0.1116824368468084</v>
       </c>
       <c r="BE4" s="2" t="n">
-        <v>0.114746511379007</v>
+        <v>0.1149870347471272</v>
       </c>
       <c r="BF4" s="2" t="n">
-        <v>0.1494457098939571</v>
+        <v>0.1476165439286384</v>
       </c>
       <c r="BG4" s="2" t="n">
-        <v>0.1551143469477817</v>
+        <v>0.1526472920740768</v>
       </c>
       <c r="BH4" s="2" t="n">
-        <v>0.1548879511129115</v>
+        <v>0.1525733053158972</v>
       </c>
       <c r="BI4" s="2" t="n">
-        <v>0.1520314707128116</v>
+        <v>0.1497426001993724</v>
       </c>
       <c r="BJ4" s="2" t="n">
-        <v>0.1528077925689674</v>
+        <v>0.1510530765302635</v>
       </c>
       <c r="BK4" s="2" t="n">
-        <v>0.1455267974458615</v>
+        <v>0.1441186749659459</v>
       </c>
       <c r="BL4" s="2" t="n">
-        <v>0.1444497782946004</v>
+        <v>0.1432324055791272</v>
       </c>
       <c r="BM4" s="2" t="n">
-        <v>0.1417833281751535</v>
+        <v>0.1408728336985967</v>
       </c>
       <c r="BN4" s="2" t="n">
-        <v>0.1401305490360323</v>
+        <v>0.1391877078638139</v>
       </c>
       <c r="BO4" s="2" t="n">
-        <v>0.1410094686279793</v>
+        <v>0.1402265988717575</v>
       </c>
       <c r="BP4" s="2" t="n">
-        <v>0.1312513122516838</v>
+        <v>0.1309221195238796</v>
       </c>
       <c r="BQ4" s="2" t="n">
-        <v>0.1303737017724299</v>
+        <v>0.1304517000380539</v>
       </c>
       <c r="BR4" s="2" t="n">
-        <v>0.1298213712696054</v>
+        <v>0.1299943718884208</v>
       </c>
       <c r="BS4" s="2" t="n">
-        <v>0.129410945561123</v>
+        <v>0.129758597102356</v>
       </c>
       <c r="BT4" s="2" t="n">
-        <v>0.1918871272561816</v>
+        <v>0.1889731046018866</v>
       </c>
       <c r="BU4" s="2" t="n">
-        <v>0.1921577002417673</v>
+        <v>0.1888197358262171</v>
       </c>
       <c r="BV4" s="2" t="n">
-        <v>0.1890166421335977</v>
+        <v>0.186222022483949</v>
       </c>
       <c r="BW4" s="2" t="n">
-        <v>0.1884422261776385</v>
+        <v>0.1858041395010409</v>
       </c>
       <c r="BX4" s="2" t="n">
-        <v>0.1845083156466693</v>
+        <v>0.182618680769226</v>
       </c>
       <c r="BY4" s="2" t="n">
-        <v>0.1802159030125927</v>
+        <v>0.1787872132049392</v>
       </c>
       <c r="BZ4" s="2" t="n">
-        <v>0.1756086689276278</v>
+        <v>0.1743874032837927</v>
       </c>
       <c r="CA4" s="2" t="n">
-        <v>0.1720860018273485</v>
+        <v>0.1710546291311873</v>
       </c>
       <c r="CB4" s="2" t="n">
-        <v>0.1692488046771277</v>
+        <v>0.1684960874205817</v>
       </c>
       <c r="CC4" s="2" t="n">
-        <v>0.1640617868978202</v>
+        <v>0.1633214711326778</v>
       </c>
       <c r="CD4" s="2" t="n">
-        <v>0.1592265123217423</v>
+        <v>0.1589241528599579</v>
       </c>
       <c r="CE4" s="2" t="n">
-        <v>0.1513955024575319</v>
+        <v>0.1515771066342916</v>
       </c>
       <c r="CF4" s="2" t="n">
-        <v>0.1514344187656693</v>
+        <v>0.1517339283803754</v>
       </c>
       <c r="CG4" s="2" t="n">
-        <v>0.1548916358030307</v>
+        <v>0.1553315478837955</v>
       </c>
       <c r="CH4" s="2" t="n">
-        <v>0.2223731066742649</v>
+        <v>0.219234978006195</v>
       </c>
       <c r="CI4" s="2" t="n">
-        <v>0.2236589587425816</v>
+        <v>0.2202745809352028</v>
       </c>
       <c r="CJ4" s="2" t="n">
-        <v>0.2194610077506175</v>
+        <v>0.2167820695406069</v>
       </c>
       <c r="CK4" s="2" t="n">
-        <v>0.213549364798435</v>
+        <v>0.2114398223093832</v>
       </c>
       <c r="CL4" s="2" t="n">
-        <v>0.2095100481317977</v>
+        <v>0.2078399520622234</v>
       </c>
       <c r="CM4" s="2" t="n">
-        <v>0.2012638056978872</v>
+        <v>0.2001766430542161</v>
       </c>
       <c r="CN4" s="2" t="n">
-        <v>0.2009782727838456</v>
+        <v>0.1999173659861981</v>
       </c>
       <c r="CO4" s="2" t="n">
-        <v>0.193620119469018</v>
+        <v>0.1927842090295267</v>
       </c>
       <c r="CP4" s="2" t="n">
-        <v>0.1914113401656645</v>
+        <v>0.1907148151879804</v>
       </c>
       <c r="CQ4" s="2" t="n">
-        <v>0.1912371130357698</v>
+        <v>0.1905619525979475</v>
       </c>
       <c r="CR4" s="2" t="n">
-        <v>0.1756335241415827</v>
+        <v>0.1755507034876673</v>
       </c>
       <c r="CS4" s="2" t="n">
-        <v>0.1723524013969157</v>
+        <v>0.172745527556822</v>
       </c>
       <c r="CT4" s="2" t="n">
-        <v>0.1718375811576204</v>
+        <v>0.1723568642734842</v>
       </c>
       <c r="CU4" s="2" t="n">
-        <v>0.1789225375232927</v>
+        <v>0.1795231362757913</v>
       </c>
       <c r="CV4" s="2" t="n">
-        <v>0.2627716841810157</v>
+        <v>0.2602460081391742</v>
       </c>
       <c r="CW4" s="2" t="n">
-        <v>0.251732165129776</v>
+        <v>0.249556193264122</v>
       </c>
       <c r="CX4" s="2" t="n">
-        <v>0.2486097640344593</v>
+        <v>0.2465794770965072</v>
       </c>
       <c r="CY4" s="2" t="n">
-        <v>0.2464580581730547</v>
+        <v>0.2450877958184424</v>
       </c>
       <c r="CZ4" s="2" t="n">
-        <v>0.2357338501296284</v>
+        <v>0.2345710007629635</v>
       </c>
       <c r="DA4" s="2" t="n">
-        <v>0.2311929564502484</v>
+        <v>0.2303194913592583</v>
       </c>
       <c r="DB4" s="2" t="n">
-        <v>0.230405134553429</v>
+        <v>0.2296834824926819</v>
       </c>
       <c r="DC4" s="2" t="n">
-        <v>0.2238239826432569</v>
+        <v>0.2232423046401841</v>
       </c>
       <c r="DD4" s="2" t="n">
-        <v>0.221927875786649</v>
+        <v>0.2216334549184907</v>
       </c>
       <c r="DE4" s="2" t="n">
-        <v>0.2152790525769245</v>
+        <v>0.2151992903863441</v>
       </c>
       <c r="DF4" s="2" t="n">
-        <v>0.2074571542808289</v>
+        <v>0.2077378437289471</v>
       </c>
       <c r="DG4" s="2" t="n">
-        <v>0.2040216519604745</v>
+        <v>0.204490006632668</v>
       </c>
       <c r="DH4" s="2" t="n">
-        <v>0.2018607118636994</v>
+        <v>0.2024970361501603</v>
       </c>
       <c r="DI4" s="2" t="n">
-        <v>0.2045327814035469</v>
+        <v>0.2055518792681748</v>
       </c>
       <c r="DJ4" s="2" t="n">
-        <v>0.2830895745789456</v>
+        <v>0.2812338882719922</v>
       </c>
       <c r="DK4" s="2" t="n">
-        <v>0.2770791278331312</v>
+        <v>0.2758851164131196</v>
       </c>
       <c r="DL4" s="2" t="n">
-        <v>0.2669923787529769</v>
+        <v>0.2658583258803191</v>
       </c>
       <c r="DM4" s="2" t="n">
-        <v>0.2644269791563473</v>
+        <v>0.2634605866988621</v>
       </c>
       <c r="DN4" s="2" t="n">
-        <v>0.2559989811970684</v>
+        <v>0.2554088393344376</v>
       </c>
       <c r="DO4" s="2" t="n">
-        <v>0.2548929647198498</v>
+        <v>0.2542583913198292</v>
       </c>
       <c r="DP4" s="2" t="n">
-        <v>0.2466364040619061</v>
+        <v>0.246445907617204</v>
       </c>
       <c r="DQ4" s="2" t="n">
-        <v>0.2395611031865414</v>
+        <v>0.2394593878602322</v>
       </c>
       <c r="DR4" s="2" t="n">
-        <v>0.2366930774376839</v>
+        <v>0.2368724240885228</v>
       </c>
       <c r="DS4" s="2" t="n">
-        <v>0.2323908522030973</v>
+        <v>0.2326873853108549</v>
       </c>
       <c r="DT4" s="2" t="n">
-        <v>0.2265083314815356</v>
+        <v>0.227044534865935</v>
       </c>
       <c r="DU4" s="2" t="n">
-        <v>0.2233038706298819</v>
+        <v>0.223906596523141</v>
       </c>
       <c r="DV4" s="2" t="n">
-        <v>0.2262496713503021</v>
+        <v>0.2271778088017124</v>
       </c>
       <c r="DW4" s="2" t="n">
-        <v>0.2281719267758586</v>
+        <v>0.2294033475610473</v>
       </c>
       <c r="DX4" s="2" t="n">
-        <v>0.2974530853471884</v>
+        <v>0.2963162087044844</v>
       </c>
       <c r="DY4" s="2" t="n">
-        <v>0.2855566338092306</v>
+        <v>0.2846946835905531</v>
       </c>
       <c r="DZ4" s="2" t="n">
-        <v>0.2834702021348963</v>
+        <v>0.2829605451691637</v>
       </c>
       <c r="EA4" s="2" t="n">
-        <v>0.2729944446284414</v>
+        <v>0.2723721386093736</v>
       </c>
       <c r="EB4" s="2" t="n">
-        <v>0.2700533213238718</v>
+        <v>0.2698692621808054</v>
       </c>
       <c r="EC4" s="2" t="n">
-        <v>0.2631357636476966</v>
+        <v>0.2630446132446739</v>
       </c>
       <c r="ED4" s="2" t="n">
-        <v>0.2587819864373592</v>
+        <v>0.2589357477944282</v>
       </c>
       <c r="EE4" s="2" t="n">
-        <v>0.2559622945283424</v>
+        <v>0.2563189053927433</v>
       </c>
       <c r="EF4" s="2" t="n">
-        <v>0.2529638623875231</v>
+        <v>0.2531438497882933</v>
       </c>
       <c r="EG4" s="2" t="n">
-        <v>0.2500809442836476</v>
+        <v>0.2504227918225956</v>
       </c>
       <c r="EH4" s="2" t="n">
-        <v>0.2368374451327144</v>
+        <v>0.2377606912779628</v>
       </c>
       <c r="EI4" s="2" t="n">
-        <v>0.2389674722103995</v>
+        <v>0.2400820418147963</v>
       </c>
       <c r="EJ4" s="2" t="n">
-        <v>0.2390220403463788</v>
+        <v>0.2403808548839039</v>
       </c>
       <c r="EK4" s="2" t="n">
-        <v>0.2413649509913743</v>
+        <v>0.2427215713329137</v>
       </c>
       <c r="EL4" s="2" t="n">
-        <v>0.3032865860249836</v>
+        <v>0.3030463644053776</v>
       </c>
       <c r="EM4" s="2" t="n">
-        <v>0.2971829725996277</v>
+        <v>0.2974978266850731</v>
       </c>
       <c r="EN4" s="2" t="n">
-        <v>0.2910130949586285</v>
+        <v>0.2914153145521535</v>
       </c>
       <c r="EO4" s="2" t="n">
-        <v>0.2823259211475632</v>
+        <v>0.2828013426954529</v>
       </c>
       <c r="EP4" s="2" t="n">
-        <v>0.2848335916414553</v>
+        <v>0.2852506080880457</v>
       </c>
       <c r="EQ4" s="2" t="n">
-        <v>0.272370724797201</v>
+        <v>0.2730474014281749</v>
       </c>
       <c r="ER4" s="2" t="n">
-        <v>0.2725858583946231</v>
+        <v>0.2732074901361468</v>
       </c>
       <c r="ES4" s="2" t="n">
-        <v>0.2648707711225387</v>
+        <v>0.2660451763397094</v>
       </c>
       <c r="ET4" s="2" t="n">
-        <v>0.2668991225111</v>
+        <v>0.2677903572368138</v>
       </c>
       <c r="EU4" s="2" t="n">
-        <v>0.2654204900868127</v>
+        <v>0.2664583112604806</v>
       </c>
       <c r="EV4" s="2" t="n">
-        <v>0.2615172774021953</v>
+        <v>0.2627913266842693</v>
       </c>
       <c r="EW4" s="2" t="n">
-        <v>0.259996172364123</v>
+        <v>0.261284176583655</v>
       </c>
       <c r="EX4" s="2" t="n">
-        <v>0.2592943006692043</v>
+        <v>0.2608272948799244</v>
       </c>
       <c r="EY4" s="2" t="n">
-        <v>0.272201837997985</v>
+        <v>0.2740272823982955</v>
       </c>
       <c r="EZ4" s="2" t="n">
-        <v>0.2990633640309601</v>
+        <v>0.2999356482049256</v>
       </c>
       <c r="FA4" s="2" t="n">
-        <v>0.2992624940832617</v>
+        <v>0.3002730535825254</v>
       </c>
       <c r="FB4" s="2" t="n">
-        <v>0.2874849681250449</v>
+        <v>0.2884441931239958</v>
       </c>
       <c r="FC4" s="2" t="n">
-        <v>0.289572342256323</v>
+        <v>0.2906476696527158</v>
       </c>
       <c r="FD4" s="2" t="n">
-        <v>0.2793430181277108</v>
+        <v>0.2804729284775567</v>
       </c>
       <c r="FE4" s="2" t="n">
-        <v>0.2809534496367786</v>
+        <v>0.2822056389153812</v>
       </c>
       <c r="FF4" s="2" t="n">
-        <v>0.2803668060229901</v>
+        <v>0.2816282638238553</v>
       </c>
       <c r="FG4" s="2" t="n">
-        <v>0.277096629231305</v>
+        <v>0.2784352154425095</v>
       </c>
       <c r="FH4" s="2" t="n">
-        <v>0.2723679320365889</v>
+        <v>0.2737010793239577</v>
       </c>
       <c r="FI4" s="2" t="n">
-        <v>0.2710425974618008</v>
+        <v>0.2723191948424389</v>
       </c>
       <c r="FJ4" s="2" t="n">
-        <v>0.2734059583644494</v>
+        <v>0.2748507749538049</v>
       </c>
       <c r="FK4" s="2" t="n">
-        <v>0.2742971105394396</v>
+        <v>0.2759867383060488</v>
       </c>
       <c r="FL4" s="2" t="n">
-        <v>0.2841924964540348</v>
+        <v>0.2860195799820766</v>
       </c>
       <c r="FM4" s="2" t="n">
-        <v>0.2949420139737131</v>
+        <v>0.2970536724276545</v>
       </c>
       <c r="FN4" s="2" t="n">
-        <v>0.3023898125197296</v>
+        <v>0.303891782512844</v>
       </c>
       <c r="FO4" s="2" t="n">
-        <v>0.3020518215091094</v>
+        <v>0.303515488067375</v>
       </c>
       <c r="FP4" s="2" t="n">
-        <v>0.293622826446825</v>
+        <v>0.2950859267609653</v>
       </c>
       <c r="FQ4" s="2" t="n">
-        <v>0.2917229412994232</v>
+        <v>0.2933382718763199</v>
       </c>
       <c r="FR4" s="2" t="n">
-        <v>0.2975323776850581</v>
+        <v>0.2990738059530139</v>
       </c>
       <c r="FS4" s="2" t="n">
-        <v>0.2954064657719226</v>
+        <v>0.2969961216480823</v>
       </c>
       <c r="FT4" s="2" t="n">
-        <v>0.2960053270967867</v>
+        <v>0.2976426592381861</v>
       </c>
       <c r="FU4" s="2" t="n">
-        <v>0.2942711566040751</v>
+        <v>0.2960048992583987</v>
       </c>
       <c r="FV4" s="2" t="n">
-        <v>0.2964009004014155</v>
+        <v>0.2982519151943347</v>
       </c>
       <c r="FW4" s="2" t="n">
-        <v>0.2970014313344114</v>
+        <v>0.2988845581297033</v>
       </c>
       <c r="FX4" s="2" t="n">
-        <v>0.2954789290485018</v>
+        <v>0.2977016160544985</v>
       </c>
       <c r="FY4" s="2" t="n">
-        <v>0.3058867464718714</v>
+        <v>0.3082372481880084</v>
       </c>
       <c r="FZ4" s="2" t="n">
-        <v>0.3109451284186611</v>
+        <v>0.3134150554911861</v>
       </c>
       <c r="GA4" s="2" t="n">
-        <v>0.3259159345484623</v>
+        <v>0.3284168783880124</v>
       </c>
       <c r="GB4" s="2" t="n">
-        <v>0.3232906393224539</v>
+        <v>0.325125702422315</v>
       </c>
       <c r="GC4" s="2" t="n">
-        <v>0.3244577242275014</v>
+        <v>0.3264963744421735</v>
       </c>
       <c r="GD4" s="2" t="n">
-        <v>0.3265265639190996</v>
+        <v>0.3286097015505159</v>
       </c>
       <c r="GE4" s="2" t="n">
-        <v>0.3267237522333781</v>
+        <v>0.3288518839210192</v>
       </c>
       <c r="GF4" s="2" t="n">
-        <v>0.3245194112242734</v>
+        <v>0.3266682927788769</v>
       </c>
       <c r="GG4" s="2" t="n">
-        <v>0.3225036525460563</v>
+        <v>0.3246846982570968</v>
       </c>
       <c r="GH4" s="2" t="n">
-        <v>0.3189389013711919</v>
+        <v>0.3211583622757901</v>
       </c>
       <c r="GI4" s="2" t="n">
-        <v>0.3193189155487088</v>
+        <v>0.3220514979390172</v>
       </c>
       <c r="GJ4" s="2" t="n">
-        <v>0.3198983858134861</v>
+        <v>0.3223655636217709</v>
       </c>
       <c r="GK4" s="2" t="n">
-        <v>0.324040913764142</v>
+        <v>0.326677495423459</v>
       </c>
       <c r="GL4" s="2" t="n">
-        <v>0.3297948710674808</v>
+        <v>0.3326763607615993</v>
       </c>
       <c r="GM4" s="2" t="n">
-        <v>0.335412721038766</v>
+        <v>0.3384616103777361</v>
       </c>
       <c r="GN4" s="2" t="n">
-        <v>0.3508941681671052</v>
+        <v>0.3540218697476296</v>
       </c>
       <c r="GO4" s="2" t="n">
-        <v>0.3601672092257197</v>
+        <v>0.3634939009128267</v>
       </c>
       <c r="GP4" s="2" t="n">
-        <v>0.352994728544894</v>
+        <v>0.3556836281811626</v>
       </c>
       <c r="GQ4" s="2" t="n">
-        <v>0.3487749796825085</v>
+        <v>0.3514200997071896</v>
       </c>
       <c r="GR4" s="2" t="n">
-        <v>0.3481590359708516</v>
+        <v>0.3504801600476949</v>
       </c>
       <c r="GS4" s="2" t="n">
-        <v>0.3463946600541053</v>
+        <v>0.3490489591940818</v>
       </c>
       <c r="GT4" s="2" t="n">
-        <v>0.3484312106702905</v>
+        <v>0.3510318432782274</v>
       </c>
       <c r="GU4" s="2" t="n">
-        <v>0.3427690237565244</v>
+        <v>0.3454945131941045</v>
       </c>
       <c r="GV4" s="2" t="n">
-        <v>0.3486308026389003</v>
+        <v>0.3514703455642582</v>
       </c>
       <c r="GW4" s="2" t="n">
-        <v>0.3436196579952673</v>
+        <v>0.3464314996619658</v>
       </c>
       <c r="GX4" s="2" t="n">
-        <v>0.3452376159921292</v>
+        <v>0.3483453425660732</v>
       </c>
       <c r="GY4" s="2" t="n">
-        <v>0.3461044124051811</v>
+        <v>0.3494208520933868</v>
       </c>
       <c r="GZ4" s="2" t="n">
-        <v>0.3584210579063948</v>
+        <v>0.3618067879941519</v>
       </c>
       <c r="HA4" s="2" t="n">
-        <v>0.3706782167144266</v>
+        <v>0.3739312221594301</v>
       </c>
       <c r="HB4" s="2" t="n">
-        <v>0.3846852635094284</v>
+        <v>0.3879942079135536</v>
       </c>
       <c r="HC4" s="2" t="n">
-        <v>0.3746689546974368</v>
+        <v>0.3775525529058643</v>
       </c>
       <c r="HD4" s="2" t="n">
-        <v>0.3704231429350535</v>
+        <v>0.3745797249925296</v>
       </c>
       <c r="HE4" s="2" t="n">
-        <v>0.3642517630285451</v>
+        <v>0.3680064011639783</v>
       </c>
       <c r="HF4" s="2" t="n">
-        <v>0.3661939244141561</v>
+        <v>0.3701223696937543</v>
       </c>
       <c r="HG4" s="2" t="n">
-        <v>0.3736394133477739</v>
+        <v>0.3776642318873933</v>
       </c>
       <c r="HH4" s="2" t="n">
-        <v>0.3733263371453815</v>
+        <v>0.3772266788349682</v>
       </c>
       <c r="HI4" s="2" t="n">
-        <v>0.3722075440427537</v>
+        <v>0.3762009658357377</v>
       </c>
       <c r="HJ4" s="2" t="n">
-        <v>0.3755844707548776</v>
+        <v>0.3792417596042313</v>
       </c>
       <c r="HK4" s="2" t="n">
-        <v>0.3695375771288706</v>
+        <v>0.3735057265524698</v>
       </c>
       <c r="HL4" s="2" t="n">
-        <v>0.3721071744459541</v>
+        <v>0.3759024331468017</v>
       </c>
       <c r="HM4" s="2" t="n">
-        <v>0.3698326564441826</v>
+        <v>0.3735702625523712</v>
       </c>
       <c r="HN4" s="2" t="n">
-        <v>0.3918735313650622</v>
+        <v>0.395578712546493</v>
       </c>
       <c r="HO4" s="2" t="n">
-        <v>0.4060177162498385</v>
+        <v>0.4099102124780565</v>
       </c>
       <c r="HP4" s="2" t="n">
-        <v>0.3782264375145689</v>
+        <v>0.3812445485050932</v>
       </c>
       <c r="HQ4" s="2" t="n">
-        <v>0.3615241243597562</v>
+        <v>0.3642640381213719</v>
       </c>
       <c r="HR4" s="3" t="n">
         <v>55514</v>
@@ -3555,676 +3555,676 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.02918500620868477</v>
+        <v>0.02905753329392943</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.03806103436407338</v>
+        <v>0.0377252339026023</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.04014434790143438</v>
+        <v>0.03978886673131653</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.04164978029545744</v>
+        <v>0.04125561477955778</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.0419340212467792</v>
+        <v>0.04146968802546286</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04103504644579856</v>
+        <v>0.04059534111864535</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.04034000561957822</v>
+        <v>0.03994827085559831</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.04000229234013929</v>
+        <v>0.03963247811559811</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.04019793081113983</v>
+        <v>0.03984551462361503</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03939409422254612</v>
+        <v>0.03911041616028597</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.03814224962887557</v>
+        <v>0.03793523338434489</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.03667017903727578</v>
+        <v>0.03666301530403183</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.03656675475292655</v>
+        <v>0.03658079444073888</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.03710270765039616</v>
+        <v>0.03720695338014059</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.05668346282729922</v>
+        <v>0.05648813002446709</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.06843880048906589</v>
+        <v>0.06783827996766353</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.07153284964517669</v>
+        <v>0.07072862279967383</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.07202696670600774</v>
+        <v>0.07121715006241204</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.07325577195439271</v>
+        <v>0.07245165873024396</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.07032834557519517</v>
+        <v>0.06962774885521493</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.07116098571345714</v>
+        <v>0.07046334873661902</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.07045088853857789</v>
+        <v>0.06989011127672468</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.0700372106140707</v>
+        <v>0.06948586578725319</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.06941728134465089</v>
+        <v>0.06891349543642869</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.06585892550022693</v>
+        <v>0.06550852655739875</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.06301114552970616</v>
+        <v>0.06300147560741393</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>0.06295059537428921</v>
+        <v>0.06293552378106421</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.06416676334285627</v>
+        <v>0.06429634849721085</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>0.09008956963591548</v>
+        <v>0.08954880649619075</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>0.1028337293200008</v>
+        <v>0.1017208491347543</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.1032453318723098</v>
+        <v>0.101837369579877</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>0.1044906292549647</v>
+        <v>0.103146361976055</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.1046991657803363</v>
+        <v>0.1034126870671815</v>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>0.1037512114548998</v>
+        <v>0.1026115222180204</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>0.1001748207038431</v>
+        <v>0.09920763662216947</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>0.09881707005972229</v>
+        <v>0.09806442172104679</v>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>0.09933842002491039</v>
+        <v>0.09851979120711368</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>0.09588967943799465</v>
+        <v>0.09524635719370811</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.09062828592385953</v>
+        <v>0.09030583038356012</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>0.08835464930768538</v>
+        <v>0.08831043756242324</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>0.09084998445392314</v>
+        <v>0.09084412084699336</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.09134552258754666</v>
+        <v>0.0914666634401172</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.1206822480680899</v>
+        <v>0.1198434505286174</v>
       </c>
       <c r="AS5" s="2" t="n">
-        <v>0.1295125648270128</v>
+        <v>0.1274712677935837</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>0.1299130770346392</v>
+        <v>0.1278822555175294</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>0.1302742492968801</v>
+        <v>0.1284042280728582</v>
       </c>
       <c r="AV5" s="2" t="n">
-        <v>0.1291668977064327</v>
+        <v>0.12761801885788</v>
       </c>
       <c r="AW5" s="2" t="n">
-        <v>0.1236884023474931</v>
+        <v>0.1223552252578019</v>
       </c>
       <c r="AX5" s="2" t="n">
-        <v>0.1241158222311405</v>
+        <v>0.1229877689385084</v>
       </c>
       <c r="AY5" s="2" t="n">
-        <v>0.1228008533228656</v>
+        <v>0.1218511762429496</v>
       </c>
       <c r="AZ5" s="2" t="n">
-        <v>0.1215229747987212</v>
+        <v>0.1205895977265061</v>
       </c>
       <c r="BA5" s="2" t="n">
-        <v>0.1171213233289786</v>
+        <v>0.1163975143251486</v>
       </c>
       <c r="BB5" s="2" t="n">
-        <v>0.11134912243384</v>
+        <v>0.1109211722602235</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>0.109492978143952</v>
+        <v>0.1094001234206177</v>
       </c>
       <c r="BD5" s="2" t="n">
-        <v>0.1081785008018836</v>
+        <v>0.1082391429400071</v>
       </c>
       <c r="BE5" s="2" t="n">
-        <v>0.1111605791635679</v>
+        <v>0.1113568982370065</v>
       </c>
       <c r="BF5" s="2" t="n">
-        <v>0.150573591955467</v>
+        <v>0.1487643860955675</v>
       </c>
       <c r="BG5" s="2" t="n">
-        <v>0.1541596606473553</v>
+        <v>0.1516950756411182</v>
       </c>
       <c r="BH5" s="2" t="n">
-        <v>0.1530401733966047</v>
+        <v>0.1507080448122198</v>
       </c>
       <c r="BI5" s="2" t="n">
-        <v>0.1492911463863563</v>
+        <v>0.1469787767417144</v>
       </c>
       <c r="BJ5" s="2" t="n">
-        <v>0.1495895098021539</v>
+        <v>0.14780334113746</v>
       </c>
       <c r="BK5" s="2" t="n">
-        <v>0.1422388457959693</v>
+        <v>0.1407855839735072</v>
       </c>
       <c r="BL5" s="2" t="n">
-        <v>0.1410190725692073</v>
+        <v>0.1397637242444316</v>
       </c>
       <c r="BM5" s="2" t="n">
-        <v>0.1381757952051193</v>
+        <v>0.1372210852580101</v>
       </c>
       <c r="BN5" s="2" t="n">
-        <v>0.1363208268641962</v>
+        <v>0.1353200499772562</v>
       </c>
       <c r="BO5" s="2" t="n">
-        <v>0.1371390938714008</v>
+        <v>0.1363129362419109</v>
       </c>
       <c r="BP5" s="2" t="n">
-        <v>0.1276045307496645</v>
+        <v>0.1272344846258023</v>
       </c>
       <c r="BQ5" s="2" t="n">
-        <v>0.126612001829341</v>
+        <v>0.1266282757600098</v>
       </c>
       <c r="BR5" s="2" t="n">
-        <v>0.1260027670171435</v>
+        <v>0.1261134919580396</v>
       </c>
       <c r="BS5" s="2" t="n">
-        <v>0.1256052385887771</v>
+        <v>0.1258943695447117</v>
       </c>
       <c r="BT5" s="2" t="n">
-        <v>0.1906735906324964</v>
+        <v>0.1877394961140733</v>
       </c>
       <c r="BU5" s="2" t="n">
-        <v>0.1888679191883235</v>
+        <v>0.1854863316233783</v>
       </c>
       <c r="BV5" s="2" t="n">
-        <v>0.1848012089743658</v>
+        <v>0.1819584175958677</v>
       </c>
       <c r="BW5" s="2" t="n">
-        <v>0.1836053156799252</v>
+        <v>0.1809105263596947</v>
       </c>
       <c r="BX5" s="2" t="n">
-        <v>0.1799838817953704</v>
+        <v>0.1780409193873047</v>
       </c>
       <c r="BY5" s="2" t="n">
-        <v>0.1755424509717121</v>
+        <v>0.1740515562666549</v>
       </c>
       <c r="BZ5" s="2" t="n">
-        <v>0.1707873315716341</v>
+        <v>0.1695045576596811</v>
       </c>
       <c r="CA5" s="2" t="n">
-        <v>0.167249017141767</v>
+        <v>0.1661712347790675</v>
       </c>
       <c r="CB5" s="2" t="n">
-        <v>0.1645486595533305</v>
+        <v>0.1637288535437995</v>
       </c>
       <c r="CC5" s="2" t="n">
-        <v>0.1595806129244924</v>
+        <v>0.1587705709008337</v>
       </c>
       <c r="CD5" s="2" t="n">
-        <v>0.154793545155766</v>
+        <v>0.1544404174377942</v>
       </c>
       <c r="CE5" s="2" t="n">
-        <v>0.1471791169115109</v>
+        <v>0.1472925296493573</v>
       </c>
       <c r="CF5" s="2" t="n">
-        <v>0.1472126860868415</v>
+        <v>0.1474559102904281</v>
       </c>
       <c r="CG5" s="2" t="n">
-        <v>0.1504686107995493</v>
+        <v>0.1508481620016081</v>
       </c>
       <c r="CH5" s="2" t="n">
-        <v>0.218192631777874</v>
+        <v>0.2150123439994965</v>
       </c>
       <c r="CI5" s="2" t="n">
-        <v>0.2177191258371891</v>
+        <v>0.214242655128342</v>
       </c>
       <c r="CJ5" s="2" t="n">
-        <v>0.2134849131830254</v>
+        <v>0.2107205317147293</v>
       </c>
       <c r="CK5" s="2" t="n">
-        <v>0.2075634612842481</v>
+        <v>0.2053705766006391</v>
       </c>
       <c r="CL5" s="2" t="n">
-        <v>0.2034394749618517</v>
+        <v>0.2016698018825994</v>
       </c>
       <c r="CM5" s="2" t="n">
-        <v>0.1954450088978214</v>
+        <v>0.194256540709774</v>
       </c>
       <c r="CN5" s="2" t="n">
-        <v>0.1952499826287364</v>
+        <v>0.1941142161225414</v>
       </c>
       <c r="CO5" s="2" t="n">
-        <v>0.1879933731643182</v>
+        <v>0.1870673144248945</v>
       </c>
       <c r="CP5" s="2" t="n">
-        <v>0.1858565181100113</v>
+        <v>0.1850820377075417</v>
       </c>
       <c r="CQ5" s="2" t="n">
-        <v>0.1858117892942001</v>
+        <v>0.1850761301419308</v>
       </c>
       <c r="CR5" s="2" t="n">
-        <v>0.1709716157734069</v>
+        <v>0.1708059148609313</v>
       </c>
       <c r="CS5" s="2" t="n">
-        <v>0.1677144433122025</v>
+        <v>0.1680505576293812</v>
       </c>
       <c r="CT5" s="2" t="n">
-        <v>0.167359994655565</v>
+        <v>0.1678262259122884</v>
       </c>
       <c r="CU5" s="2" t="n">
-        <v>0.1740561317951679</v>
+        <v>0.1745932255239487</v>
       </c>
       <c r="CV5" s="2" t="n">
-        <v>0.2554401271344611</v>
+        <v>0.2528009265960642</v>
       </c>
       <c r="CW5" s="2" t="n">
-        <v>0.2437814082374064</v>
+        <v>0.2414922397007434</v>
       </c>
       <c r="CX5" s="2" t="n">
-        <v>0.2413644315498585</v>
+        <v>0.2392515064972157</v>
       </c>
       <c r="CY5" s="2" t="n">
-        <v>0.2391983666077644</v>
+        <v>0.2377287023321182</v>
       </c>
       <c r="CZ5" s="2" t="n">
-        <v>0.2285517445925703</v>
+        <v>0.2273146166626444</v>
       </c>
       <c r="DA5" s="2" t="n">
-        <v>0.2241873020432346</v>
+        <v>0.2232220197222584</v>
       </c>
       <c r="DB5" s="2" t="n">
-        <v>0.2237129980709291</v>
+        <v>0.2228961573924757</v>
       </c>
       <c r="DC5" s="2" t="n">
-        <v>0.217578359004872</v>
+        <v>0.2169098370343616</v>
       </c>
       <c r="DD5" s="2" t="n">
-        <v>0.2162544998832456</v>
+        <v>0.2158954564042799</v>
       </c>
       <c r="DE5" s="2" t="n">
-        <v>0.2098109906544013</v>
+        <v>0.2096596656371875</v>
       </c>
       <c r="DF5" s="2" t="n">
-        <v>0.2023479482358224</v>
+        <v>0.2025527497952706</v>
       </c>
       <c r="DG5" s="2" t="n">
-        <v>0.1988789434894754</v>
+        <v>0.1992726247176363</v>
       </c>
       <c r="DH5" s="2" t="n">
-        <v>0.1970156251755939</v>
+        <v>0.1975815377501236</v>
       </c>
       <c r="DI5" s="2" t="n">
-        <v>0.1995631987871986</v>
+        <v>0.2005132968249183</v>
       </c>
       <c r="DJ5" s="2" t="n">
-        <v>0.2741586359163021</v>
+        <v>0.2721929939408993</v>
       </c>
       <c r="DK5" s="2" t="n">
-        <v>0.2687844636465541</v>
+        <v>0.2674736271227828</v>
       </c>
       <c r="DL5" s="2" t="n">
-        <v>0.2589691944420943</v>
+        <v>0.2577209465206274</v>
       </c>
       <c r="DM5" s="2" t="n">
-        <v>0.2565899437517218</v>
+        <v>0.2555244809240393</v>
       </c>
       <c r="DN5" s="2" t="n">
-        <v>0.2484246052332354</v>
+        <v>0.2477104596324397</v>
       </c>
       <c r="DO5" s="2" t="n">
-        <v>0.2477359296728167</v>
+        <v>0.2470028037179502</v>
       </c>
       <c r="DP5" s="2" t="n">
-        <v>0.2402978650250836</v>
+        <v>0.2400059550025864</v>
       </c>
       <c r="DQ5" s="2" t="n">
-        <v>0.2335396930988516</v>
+        <v>0.2333417870517458</v>
       </c>
       <c r="DR5" s="2" t="n">
-        <v>0.2311153099176975</v>
+        <v>0.2312239878115746</v>
       </c>
       <c r="DS5" s="2" t="n">
-        <v>0.227234352015225</v>
+        <v>0.2274583984243551</v>
       </c>
       <c r="DT5" s="2" t="n">
-        <v>0.2214849746020199</v>
+        <v>0.2219574308188321</v>
       </c>
       <c r="DU5" s="2" t="n">
-        <v>0.2185980365130854</v>
+        <v>0.2191453487131548</v>
       </c>
       <c r="DV5" s="2" t="n">
-        <v>0.2213878110223504</v>
+        <v>0.2222470604055616</v>
       </c>
       <c r="DW5" s="2" t="n">
-        <v>0.2232353582061151</v>
+        <v>0.2243955886937002</v>
       </c>
       <c r="DX5" s="2" t="n">
-        <v>0.2887729693477155</v>
+        <v>0.2875429902498723</v>
       </c>
       <c r="DY5" s="2" t="n">
-        <v>0.2772721495203782</v>
+        <v>0.2763110916786004</v>
       </c>
       <c r="DZ5" s="2" t="n">
-        <v>0.2753093327437638</v>
+        <v>0.2747015590821503</v>
       </c>
       <c r="EA5" s="2" t="n">
-        <v>0.2655833497151999</v>
+        <v>0.2648604720339446</v>
       </c>
       <c r="EB5" s="2" t="n">
-        <v>0.2633504955946153</v>
+        <v>0.2630613236604875</v>
       </c>
       <c r="EC5" s="2" t="n">
-        <v>0.2566793747048076</v>
+        <v>0.2564922123949226</v>
       </c>
       <c r="ED5" s="2" t="n">
-        <v>0.2528651574857377</v>
+        <v>0.2529320674247884</v>
       </c>
       <c r="EE5" s="2" t="n">
-        <v>0.2504136572936525</v>
+        <v>0.2506869371393671</v>
       </c>
       <c r="EF5" s="2" t="n">
-        <v>0.2475518223071844</v>
+        <v>0.2476634320045263</v>
       </c>
       <c r="EG5" s="2" t="n">
-        <v>0.2448492194300042</v>
+        <v>0.2451367038076268</v>
       </c>
       <c r="EH5" s="2" t="n">
-        <v>0.2318649517854362</v>
+        <v>0.2327173280080467</v>
       </c>
       <c r="EI5" s="2" t="n">
-        <v>0.2344373932984389</v>
+        <v>0.235483916750244</v>
       </c>
       <c r="EJ5" s="2" t="n">
-        <v>0.2346666502938471</v>
+        <v>0.2359620976433954</v>
       </c>
       <c r="EK5" s="2" t="n">
-        <v>0.2367007914031151</v>
+        <v>0.2380007426286342</v>
       </c>
       <c r="EL5" s="2" t="n">
-        <v>0.2952869563434929</v>
+        <v>0.2949261992309899</v>
       </c>
       <c r="EM5" s="2" t="n">
-        <v>0.2900470781727004</v>
+        <v>0.2902778450055289</v>
       </c>
       <c r="EN5" s="2" t="n">
-        <v>0.2845597035940579</v>
+        <v>0.2848845489080838</v>
       </c>
       <c r="EO5" s="2" t="n">
-        <v>0.2763850919914386</v>
+        <v>0.276773736627116</v>
       </c>
       <c r="EP5" s="2" t="n">
-        <v>0.2790949011613677</v>
+        <v>0.2794354746510337</v>
       </c>
       <c r="EQ5" s="2" t="n">
-        <v>0.2670915965295448</v>
+        <v>0.26769427399403</v>
       </c>
       <c r="ER5" s="2" t="n">
-        <v>0.2673631572446798</v>
+        <v>0.2679091208896612</v>
       </c>
       <c r="ES5" s="2" t="n">
-        <v>0.2600275784331839</v>
+        <v>0.2611338778931181</v>
       </c>
       <c r="ET5" s="2" t="n">
-        <v>0.2623453998059324</v>
+        <v>0.2631731704861215</v>
       </c>
       <c r="EU5" s="2" t="n">
-        <v>0.2608984953982417</v>
+        <v>0.2618864796382968</v>
       </c>
       <c r="EV5" s="2" t="n">
-        <v>0.2569910774390616</v>
+        <v>0.2582037786405005</v>
       </c>
       <c r="EW5" s="2" t="n">
-        <v>0.2559003591043845</v>
+        <v>0.2571342348558798</v>
       </c>
       <c r="EX5" s="2" t="n">
-        <v>0.2552333031151012</v>
+        <v>0.2567098964307025</v>
       </c>
       <c r="EY5" s="2" t="n">
-        <v>0.2678170503851423</v>
+        <v>0.2695745082375059</v>
       </c>
       <c r="EZ5" s="2" t="n">
-        <v>0.2942343967550791</v>
+        <v>0.2950435596102274</v>
       </c>
       <c r="FA5" s="2" t="n">
-        <v>0.2946275778391291</v>
+        <v>0.2955770649292399</v>
       </c>
       <c r="FB5" s="2" t="n">
-        <v>0.2832985391542618</v>
+        <v>0.2841987481043045</v>
       </c>
       <c r="FC5" s="2" t="n">
-        <v>0.2854632941915548</v>
+        <v>0.2864950356914556</v>
       </c>
       <c r="FD5" s="2" t="n">
-        <v>0.2754301024156436</v>
+        <v>0.2765038279372081</v>
       </c>
       <c r="FE5" s="2" t="n">
-        <v>0.2769219091693698</v>
+        <v>0.2781315183798609</v>
       </c>
       <c r="FF5" s="2" t="n">
-        <v>0.2764851201234452</v>
+        <v>0.27769177890402</v>
       </c>
       <c r="FG5" s="2" t="n">
-        <v>0.2731571211661999</v>
+        <v>0.2744446634497349</v>
       </c>
       <c r="FH5" s="2" t="n">
-        <v>0.2685046841429267</v>
+        <v>0.2697901775167976</v>
       </c>
       <c r="FI5" s="2" t="n">
-        <v>0.267197687714997</v>
+        <v>0.2684216094908149</v>
       </c>
       <c r="FJ5" s="2" t="n">
-        <v>0.2693599824612673</v>
+        <v>0.2707488749926623</v>
       </c>
       <c r="FK5" s="2" t="n">
-        <v>0.2704524382095567</v>
+        <v>0.2720818578343621</v>
       </c>
       <c r="FL5" s="2" t="n">
-        <v>0.280316806141749</v>
+        <v>0.2820964220208079</v>
       </c>
       <c r="FM5" s="2" t="n">
-        <v>0.2908591653212089</v>
+        <v>0.2929221267803688</v>
       </c>
       <c r="FN5" s="2" t="n">
-        <v>0.298066688203449</v>
+        <v>0.2995022735234449</v>
       </c>
       <c r="FO5" s="2" t="n">
-        <v>0.2978555500320459</v>
+        <v>0.2992708250693346</v>
       </c>
       <c r="FP5" s="2" t="n">
-        <v>0.2895051159623938</v>
+        <v>0.2909028299812155</v>
       </c>
       <c r="FQ5" s="2" t="n">
-        <v>0.2875421339838846</v>
+        <v>0.2890987688868387</v>
       </c>
       <c r="FR5" s="2" t="n">
-        <v>0.2932627889354639</v>
+        <v>0.2947429659803323</v>
       </c>
       <c r="FS5" s="2" t="n">
-        <v>0.2909366294395933</v>
+        <v>0.2924721046936521</v>
       </c>
       <c r="FT5" s="2" t="n">
-        <v>0.2913881481219944</v>
+        <v>0.2929661885430034</v>
       </c>
       <c r="FU5" s="2" t="n">
-        <v>0.2895435265794428</v>
+        <v>0.2912149600282343</v>
       </c>
       <c r="FV5" s="2" t="n">
-        <v>0.2914510448254289</v>
+        <v>0.2932457257784548</v>
       </c>
       <c r="FW5" s="2" t="n">
-        <v>0.2919635990872778</v>
+        <v>0.2937888944759764</v>
       </c>
       <c r="FX5" s="2" t="n">
-        <v>0.2904371293682457</v>
+        <v>0.2925982671279312</v>
       </c>
       <c r="FY5" s="2" t="n">
-        <v>0.3007865573483584</v>
+        <v>0.3030829902011035</v>
       </c>
       <c r="FZ5" s="2" t="n">
-        <v>0.3057243094552099</v>
+        <v>0.3081293643224775</v>
       </c>
       <c r="GA5" s="2" t="n">
-        <v>0.320666060801532</v>
+        <v>0.3230964550934097</v>
       </c>
       <c r="GB5" s="2" t="n">
-        <v>0.3169960489516674</v>
+        <v>0.3187693616395413</v>
       </c>
       <c r="GC5" s="2" t="n">
-        <v>0.317920842615556</v>
+        <v>0.319864170102071</v>
       </c>
       <c r="GD5" s="2" t="n">
-        <v>0.3196793968736452</v>
+        <v>0.3216617356001657</v>
       </c>
       <c r="GE5" s="2" t="n">
-        <v>0.3197789142352725</v>
+        <v>0.3217921803218509</v>
       </c>
       <c r="GF5" s="2" t="n">
-        <v>0.3175800619926452</v>
+        <v>0.3196298061218261</v>
       </c>
       <c r="GG5" s="2" t="n">
-        <v>0.3156846395098653</v>
+        <v>0.3177706456148114</v>
       </c>
       <c r="GH5" s="2" t="n">
-        <v>0.3118655500658385</v>
+        <v>0.3139974144943588</v>
       </c>
       <c r="GI5" s="2" t="n">
-        <v>0.3119909791324014</v>
+        <v>0.3146476997110719</v>
       </c>
       <c r="GJ5" s="2" t="n">
-        <v>0.3128764958980542</v>
+        <v>0.3152509661319715</v>
       </c>
       <c r="GK5" s="2" t="n">
-        <v>0.3168458601657196</v>
+        <v>0.3194015881243988</v>
       </c>
       <c r="GL5" s="2" t="n">
-        <v>0.3227299934890357</v>
+        <v>0.3255125767257301</v>
       </c>
       <c r="GM5" s="2" t="n">
-        <v>0.3286132096444736</v>
+        <v>0.331574793080009</v>
       </c>
       <c r="GN5" s="2" t="n">
-        <v>0.3441493489765652</v>
+        <v>0.3471806698464878</v>
       </c>
       <c r="GO5" s="2" t="n">
-        <v>0.352997307532294</v>
+        <v>0.3562304273776843</v>
       </c>
       <c r="GP5" s="2" t="n">
-        <v>0.3459539544558627</v>
+        <v>0.3485461753583057</v>
       </c>
       <c r="GQ5" s="2" t="n">
-        <v>0.3421110848252223</v>
+        <v>0.344673384195988</v>
       </c>
       <c r="GR5" s="2" t="n">
-        <v>0.3412663239265173</v>
+        <v>0.3434991884256094</v>
       </c>
       <c r="GS5" s="2" t="n">
-        <v>0.3395627537206174</v>
+        <v>0.3421336436108113</v>
       </c>
       <c r="GT5" s="2" t="n">
-        <v>0.3413887245889669</v>
+        <v>0.3438858239289289</v>
       </c>
       <c r="GU5" s="2" t="n">
-        <v>0.3356708292138598</v>
+        <v>0.3382945362699054</v>
       </c>
       <c r="GV5" s="2" t="n">
-        <v>0.3413139748956537</v>
+        <v>0.3440527189161157</v>
       </c>
       <c r="GW5" s="2" t="n">
-        <v>0.3363673052832671</v>
+        <v>0.3390950224444457</v>
       </c>
       <c r="GX5" s="2" t="n">
-        <v>0.3378168051124882</v>
+        <v>0.3408329342485737</v>
       </c>
       <c r="GY5" s="2" t="n">
-        <v>0.3384239147588348</v>
+        <v>0.3416440631434059</v>
       </c>
       <c r="GZ5" s="2" t="n">
-        <v>0.3512394959689901</v>
+        <v>0.3545342172147558</v>
       </c>
       <c r="HA5" s="2" t="n">
-        <v>0.3635707956091419</v>
+        <v>0.3667304750815883</v>
       </c>
       <c r="HB5" s="2" t="n">
-        <v>0.3772629126366663</v>
+        <v>0.3804734795745898</v>
       </c>
       <c r="HC5" s="2" t="n">
-        <v>0.3685748493541943</v>
+        <v>0.3713811030854451</v>
       </c>
       <c r="HD5" s="2" t="n">
-        <v>0.3619621219748773</v>
+        <v>0.3660214814061441</v>
       </c>
       <c r="HE5" s="2" t="n">
-        <v>0.3564995701052289</v>
+        <v>0.3601523215509992</v>
       </c>
       <c r="HF5" s="2" t="n">
-        <v>0.3582061029890317</v>
+        <v>0.3620350159624356</v>
       </c>
       <c r="HG5" s="2" t="n">
-        <v>0.365254020956993</v>
+        <v>0.3691728475370406</v>
       </c>
       <c r="HH5" s="2" t="n">
-        <v>0.3646857384971522</v>
+        <v>0.3684818093112849</v>
       </c>
       <c r="HI5" s="2" t="n">
-        <v>0.3634033316827028</v>
+        <v>0.3672790343022554</v>
       </c>
       <c r="HJ5" s="2" t="n">
-        <v>0.3665206695506737</v>
+        <v>0.3700763473818466</v>
       </c>
       <c r="HK5" s="2" t="n">
-        <v>0.3603809700758736</v>
+        <v>0.3642349170000831</v>
       </c>
       <c r="HL5" s="2" t="n">
-        <v>0.362631892081603</v>
+        <v>0.366315332468852</v>
       </c>
       <c r="HM5" s="2" t="n">
-        <v>0.3601150962409393</v>
+        <v>0.3636989223656074</v>
       </c>
       <c r="HN5" s="2" t="n">
-        <v>0.3826582076854654</v>
+        <v>0.3862567561573931</v>
       </c>
       <c r="HO5" s="2" t="n">
-        <v>0.3966491027173855</v>
+        <v>0.4003799138960697</v>
       </c>
       <c r="HP5" s="2" t="n">
-        <v>0.3718157352715245</v>
+        <v>0.3747801350265256</v>
       </c>
       <c r="HQ5" s="2" t="n">
-        <v>0.3566136440328385</v>
+        <v>0.3592902725628639</v>
       </c>
       <c r="HR5" s="3" t="n">
         <v>55516</v>
@@ -4237,676 +4237,676 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.02695118908203359</v>
+        <v>0.02682867778829451</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.03628996895416723</v>
+        <v>0.03595574987842785</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.0385784514682936</v>
+        <v>0.03822182570273154</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0402982468170651</v>
+        <v>0.03990245241798244</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.04092653251419698</v>
+        <v>0.04045961859802638</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.04012307581483073</v>
+        <v>0.03967557624905057</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.03956206530890323</v>
+        <v>0.03916037656924583</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.03926860482996383</v>
+        <v>0.03888548945641199</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03947422571986278</v>
+        <v>0.03911090560763439</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.03867895489516517</v>
+        <v>0.03837803432675859</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.03756169295709</v>
+        <v>0.03733924469749794</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.03582534330748614</v>
+        <v>0.03580097152703103</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.03568416495553128</v>
+        <v>0.03568319265476338</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.03607481235313366</v>
+        <v>0.03616036271351526</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.05301386324278722</v>
+        <v>0.05282398799024234</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.06603032469268383</v>
+        <v>0.0654377315890366</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.06957607446999836</v>
+        <v>0.06877087718637276</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.07063597996631218</v>
+        <v>0.06982209716835572</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.07203134909215506</v>
+        <v>0.0712136944377714</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.06905932569729664</v>
+        <v>0.0683450590245662</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.07027369708757357</v>
+        <v>0.0695545335207458</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.06943463821943749</v>
+        <v>0.06885374438997258</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.06931204756066112</v>
+        <v>0.06872889247998504</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.06877807259005804</v>
+        <v>0.06825277685565252</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.06532829838297192</v>
+        <v>0.06495292230001513</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.06185456272033953</v>
+        <v>0.06181848980305694</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.06180187123867847</v>
+        <v>0.06175784482660868</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.06277713670007649</v>
+        <v>0.062872552560491</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.08656181246206279</v>
+        <v>0.08602852970525737</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.1008905012012238</v>
+        <v>0.0997871577591414</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.101977668027993</v>
+        <v>0.1005669136304815</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>0.1039337296503223</v>
+        <v>0.1025769267695582</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.1040912141966688</v>
+        <v>0.102790182636963</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>0.1031472472686155</v>
+        <v>0.1019839750815018</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.09973848330697527</v>
+        <v>0.09874081144949903</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>0.09813964855424519</v>
+        <v>0.09735673409453983</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.09905093044962959</v>
+        <v>0.09819985249068813</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>0.09544435614625633</v>
+        <v>0.09476691396812618</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.08983854941858758</v>
+        <v>0.08947601161732187</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>0.08716745189435512</v>
+        <v>0.0870840743095401</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>0.08957915908763546</v>
+        <v>0.0895300243712439</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.08995916004533558</v>
+        <v>0.09004274065847187</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.1175130459111022</v>
+        <v>0.1166863462518739</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>0.1292356262845273</v>
+        <v>0.1271964899194713</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>0.1302471302493249</v>
+        <v>0.1282019160731469</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>0.1310495063157381</v>
+        <v>0.1291592530401053</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>0.1286798759148461</v>
+        <v>0.1270948896900755</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>0.1236990740124722</v>
+        <v>0.1223322631393214</v>
       </c>
       <c r="AX6" s="2" t="n">
-        <v>0.1239228598039566</v>
+        <v>0.1227496615808426</v>
       </c>
       <c r="AY6" s="2" t="n">
-        <v>0.1223324799526539</v>
+        <v>0.1213443560142126</v>
       </c>
       <c r="AZ6" s="2" t="n">
-        <v>0.1214645790865322</v>
+        <v>0.1204869250764748</v>
       </c>
       <c r="BA6" s="2" t="n">
-        <v>0.1166619227060987</v>
+        <v>0.1158954684415771</v>
       </c>
       <c r="BB6" s="2" t="n">
-        <v>0.1108044524636182</v>
+        <v>0.1103364088531646</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>0.1083083958957371</v>
+        <v>0.1081771576438126</v>
       </c>
       <c r="BD6" s="2" t="n">
-        <v>0.1066235830968349</v>
+        <v>0.1066458454316585</v>
       </c>
       <c r="BE6" s="2" t="n">
-        <v>0.109551447103049</v>
+        <v>0.1097027553564565</v>
       </c>
       <c r="BF6" s="2" t="n">
-        <v>0.1500277903551909</v>
+        <v>0.1482284006352278</v>
       </c>
       <c r="BG6" s="2" t="n">
-        <v>0.1546946200891296</v>
+        <v>0.1522191721363822</v>
       </c>
       <c r="BH6" s="2" t="n">
-        <v>0.1539539387138943</v>
+        <v>0.1516065215381245</v>
       </c>
       <c r="BI6" s="2" t="n">
-        <v>0.1511371911130235</v>
+        <v>0.1488021568022058</v>
       </c>
       <c r="BJ6" s="2" t="n">
-        <v>0.1498326760355057</v>
+        <v>0.1480117131594242</v>
       </c>
       <c r="BK6" s="2" t="n">
-        <v>0.1424188577883871</v>
+        <v>0.1409229264908464</v>
       </c>
       <c r="BL6" s="2" t="n">
-        <v>0.1413942153911854</v>
+        <v>0.1400948788385655</v>
       </c>
       <c r="BM6" s="2" t="n">
-        <v>0.1378712734355413</v>
+        <v>0.1368756448997938</v>
       </c>
       <c r="BN6" s="2" t="n">
-        <v>0.1364725765877045</v>
+        <v>0.1354182002239502</v>
       </c>
       <c r="BO6" s="2" t="n">
-        <v>0.1373324285901047</v>
+        <v>0.1364639926410176</v>
       </c>
       <c r="BP6" s="2" t="n">
-        <v>0.1270935143322258</v>
+        <v>0.1266812811583786</v>
       </c>
       <c r="BQ6" s="2" t="n">
-        <v>0.1251952930433375</v>
+        <v>0.1251557304603679</v>
       </c>
       <c r="BR6" s="2" t="n">
-        <v>0.1242411671189961</v>
+        <v>0.1242953458784518</v>
       </c>
       <c r="BS6" s="2" t="n">
-        <v>0.1235317330461726</v>
+        <v>0.1237687453281865</v>
       </c>
       <c r="BT6" s="2" t="n">
-        <v>0.1908946628877519</v>
+        <v>0.1879317085453866</v>
       </c>
       <c r="BU6" s="2" t="n">
-        <v>0.1906422451001205</v>
+        <v>0.1872213668983974</v>
       </c>
       <c r="BV6" s="2" t="n">
-        <v>0.1861476415771155</v>
+        <v>0.1832514071839957</v>
       </c>
       <c r="BW6" s="2" t="n">
-        <v>0.1862619014161726</v>
+        <v>0.183511329599013</v>
       </c>
       <c r="BX6" s="2" t="n">
-        <v>0.1808266605488821</v>
+        <v>0.1788351687840983</v>
       </c>
       <c r="BY6" s="2" t="n">
-        <v>0.1755365938135845</v>
+        <v>0.1739826485702259</v>
       </c>
       <c r="BZ6" s="2" t="n">
-        <v>0.1714042790500225</v>
+        <v>0.1700576499370636</v>
       </c>
       <c r="CA6" s="2" t="n">
-        <v>0.1672984109947734</v>
+        <v>0.1661731833348327</v>
       </c>
       <c r="CB6" s="2" t="n">
-        <v>0.1644797172214165</v>
+        <v>0.1635981831516399</v>
       </c>
       <c r="CC6" s="2" t="n">
-        <v>0.1594725717588192</v>
+        <v>0.1586083118601567</v>
       </c>
       <c r="CD6" s="2" t="n">
-        <v>0.1540981251507251</v>
+        <v>0.1536933351068943</v>
       </c>
       <c r="CE6" s="2" t="n">
-        <v>0.1453188025429276</v>
+        <v>0.1453722716345814</v>
       </c>
       <c r="CF6" s="2" t="n">
-        <v>0.1450752379782088</v>
+        <v>0.1452651309258826</v>
       </c>
       <c r="CG6" s="2" t="n">
-        <v>0.1478727048246386</v>
+        <v>0.1481965256838324</v>
       </c>
       <c r="CH6" s="2" t="n">
-        <v>0.2197470215001663</v>
+        <v>0.2165194113591274</v>
       </c>
       <c r="CI6" s="2" t="n">
-        <v>0.2205175858858564</v>
+        <v>0.2169540737691858</v>
       </c>
       <c r="CJ6" s="2" t="n">
-        <v>0.2149510252058727</v>
+        <v>0.2121139856755954</v>
       </c>
       <c r="CK6" s="2" t="n">
-        <v>0.2090901013150059</v>
+        <v>0.206827371163591</v>
       </c>
       <c r="CL6" s="2" t="n">
-        <v>0.2042207662188192</v>
+        <v>0.202368689718165</v>
       </c>
       <c r="CM6" s="2" t="n">
-        <v>0.1953925357033022</v>
+        <v>0.1941137366760977</v>
       </c>
       <c r="CN6" s="2" t="n">
-        <v>0.195151690106776</v>
+        <v>0.1939552199951675</v>
       </c>
       <c r="CO6" s="2" t="n">
-        <v>0.1877702164833265</v>
+        <v>0.1867653678540903</v>
       </c>
       <c r="CP6" s="2" t="n">
-        <v>0.1859162477084082</v>
+        <v>0.1850667697616499</v>
       </c>
       <c r="CQ6" s="2" t="n">
-        <v>0.1860882048742253</v>
+        <v>0.1852888060049492</v>
       </c>
       <c r="CR6" s="2" t="n">
-        <v>0.1695520238010895</v>
+        <v>0.1693136014966976</v>
       </c>
       <c r="CS6" s="2" t="n">
-        <v>0.165237411964732</v>
+        <v>0.1655152590163525</v>
       </c>
       <c r="CT6" s="2" t="n">
-        <v>0.1643884966670979</v>
+        <v>0.1648036206662167</v>
       </c>
       <c r="CU6" s="2" t="n">
-        <v>0.1708579823432708</v>
+        <v>0.1713398262916351</v>
       </c>
       <c r="CV6" s="2" t="n">
-        <v>0.2576046482581382</v>
+        <v>0.2548613556582218</v>
       </c>
       <c r="CW6" s="2" t="n">
-        <v>0.2455300285097781</v>
+        <v>0.2431298276957694</v>
       </c>
       <c r="CX6" s="2" t="n">
-        <v>0.2423138464944803</v>
+        <v>0.2401183429317915</v>
       </c>
       <c r="CY6" s="2" t="n">
-        <v>0.2387616543963041</v>
+        <v>0.2372092029943552</v>
       </c>
       <c r="CZ6" s="2" t="n">
-        <v>0.2285405431492676</v>
+        <v>0.2272231091363777</v>
       </c>
       <c r="DA6" s="2" t="n">
-        <v>0.2240578895346566</v>
+        <v>0.2230029059485836</v>
       </c>
       <c r="DB6" s="2" t="n">
-        <v>0.223370297591223</v>
+        <v>0.2224682110948699</v>
       </c>
       <c r="DC6" s="2" t="n">
-        <v>0.2174455978705613</v>
+        <v>0.2166954100861279</v>
       </c>
       <c r="DD6" s="2" t="n">
-        <v>0.2146949668910043</v>
+        <v>0.2142748621787565</v>
       </c>
       <c r="DE6" s="2" t="n">
-        <v>0.2082128786712028</v>
+        <v>0.2079872676401474</v>
       </c>
       <c r="DF6" s="2" t="n">
-        <v>0.1999742747411664</v>
+        <v>0.2001144574150976</v>
       </c>
       <c r="DG6" s="2" t="n">
-        <v>0.1963313983143788</v>
+        <v>0.1966591270030957</v>
       </c>
       <c r="DH6" s="2" t="n">
-        <v>0.1938515998796169</v>
+        <v>0.1943498649076167</v>
       </c>
       <c r="DI6" s="2" t="n">
-        <v>0.1953822771622363</v>
+        <v>0.1962662140442553</v>
       </c>
       <c r="DJ6" s="2" t="n">
-        <v>0.2738006280516548</v>
+        <v>0.2717359306072159</v>
       </c>
       <c r="DK6" s="2" t="n">
-        <v>0.2674150199691839</v>
+        <v>0.2660099447767324</v>
       </c>
       <c r="DL6" s="2" t="n">
-        <v>0.2589208068184408</v>
+        <v>0.2575702363483461</v>
       </c>
       <c r="DM6" s="2" t="n">
-        <v>0.2562381661731442</v>
+        <v>0.2550772129792412</v>
       </c>
       <c r="DN6" s="2" t="n">
-        <v>0.2474928149339352</v>
+        <v>0.2466653050240669</v>
       </c>
       <c r="DO6" s="2" t="n">
-        <v>0.2473461783380837</v>
+        <v>0.2465221366734833</v>
       </c>
       <c r="DP6" s="2" t="n">
-        <v>0.2388395378592015</v>
+        <v>0.2384618642034531</v>
       </c>
       <c r="DQ6" s="2" t="n">
-        <v>0.2317827154816717</v>
+        <v>0.2314997014524073</v>
       </c>
       <c r="DR6" s="2" t="n">
-        <v>0.2285356833555515</v>
+        <v>0.2285833856978233</v>
       </c>
       <c r="DS6" s="2" t="n">
-        <v>0.2240578091349134</v>
+        <v>0.2242160035874375</v>
       </c>
       <c r="DT6" s="2" t="n">
-        <v>0.2183523535214893</v>
+        <v>0.2187709234141341</v>
       </c>
       <c r="DU6" s="2" t="n">
-        <v>0.2154588881135709</v>
+        <v>0.2159532676637895</v>
       </c>
       <c r="DV6" s="2" t="n">
-        <v>0.2172448942440838</v>
+        <v>0.2180378744381756</v>
       </c>
       <c r="DW6" s="2" t="n">
-        <v>0.2184194322769092</v>
+        <v>0.2195078205410884</v>
       </c>
       <c r="DX6" s="2" t="n">
-        <v>0.2875802341206432</v>
+        <v>0.2862542095883251</v>
       </c>
       <c r="DY6" s="2" t="n">
-        <v>0.2763643655802601</v>
+        <v>0.2753115985419148</v>
       </c>
       <c r="DZ6" s="2" t="n">
-        <v>0.2737251678089384</v>
+        <v>0.2730146357397321</v>
       </c>
       <c r="EA6" s="2" t="n">
-        <v>0.2647301408418105</v>
+        <v>0.2639272066720412</v>
       </c>
       <c r="EB6" s="2" t="n">
-        <v>0.2612917853657649</v>
+        <v>0.260912070250933</v>
       </c>
       <c r="EC6" s="2" t="n">
-        <v>0.2545322407867033</v>
+        <v>0.2542637553896028</v>
       </c>
       <c r="ED6" s="2" t="n">
-        <v>0.2501002811761573</v>
+        <v>0.2500845865281299</v>
       </c>
       <c r="EE6" s="2" t="n">
-        <v>0.2469684921138756</v>
+        <v>0.2471688046985142</v>
       </c>
       <c r="EF6" s="2" t="n">
-        <v>0.2447880600915488</v>
+        <v>0.2448345889673766</v>
       </c>
       <c r="EG6" s="2" t="n">
-        <v>0.2419031916259961</v>
+        <v>0.2421379221677022</v>
       </c>
       <c r="EH6" s="2" t="n">
-        <v>0.2274886241793544</v>
+        <v>0.228275349611035</v>
       </c>
       <c r="EI6" s="2" t="n">
-        <v>0.2297706949897057</v>
+        <v>0.2307575616426712</v>
       </c>
       <c r="EJ6" s="2" t="n">
-        <v>0.2292482597954859</v>
+        <v>0.2304867772586932</v>
       </c>
       <c r="EK6" s="2" t="n">
-        <v>0.2312735810262986</v>
+        <v>0.2325199439508744</v>
       </c>
       <c r="EL6" s="2" t="n">
-        <v>0.2932313012461727</v>
+        <v>0.2927724348883694</v>
       </c>
       <c r="EM6" s="2" t="n">
-        <v>0.2865434415939191</v>
+        <v>0.2866957836153844</v>
       </c>
       <c r="EN6" s="2" t="n">
-        <v>0.2807156899641662</v>
+        <v>0.280964159376493</v>
       </c>
       <c r="EO6" s="2" t="n">
-        <v>0.2724840405541951</v>
+        <v>0.2727974417764241</v>
       </c>
       <c r="EP6" s="2" t="n">
-        <v>0.2753875469943798</v>
+        <v>0.2756539276024616</v>
       </c>
       <c r="EQ6" s="2" t="n">
-        <v>0.263151928906613</v>
+        <v>0.263687715058499</v>
       </c>
       <c r="ER6" s="2" t="n">
-        <v>0.2629148566215921</v>
+        <v>0.2633937948435236</v>
       </c>
       <c r="ES6" s="2" t="n">
-        <v>0.2545673547199008</v>
+        <v>0.2556119633724925</v>
       </c>
       <c r="ET6" s="2" t="n">
-        <v>0.2575928274992331</v>
+        <v>0.2583638620081767</v>
       </c>
       <c r="EU6" s="2" t="n">
-        <v>0.2558656095102923</v>
+        <v>0.2568071282044547</v>
       </c>
       <c r="EV6" s="2" t="n">
-        <v>0.2515012119376669</v>
+        <v>0.2526583020055304</v>
       </c>
       <c r="EW6" s="2" t="n">
-        <v>0.250128047154023</v>
+        <v>0.2513143770254391</v>
       </c>
       <c r="EX6" s="2" t="n">
-        <v>0.2489305011883121</v>
+        <v>0.2503527611449103</v>
       </c>
       <c r="EY6" s="2" t="n">
-        <v>0.2603837327744108</v>
+        <v>0.2620825620080572</v>
       </c>
       <c r="EZ6" s="2" t="n">
-        <v>0.2896501952937916</v>
+        <v>0.2904071966341809</v>
       </c>
       <c r="FA6" s="2" t="n">
-        <v>0.2894765786336366</v>
+        <v>0.2903681151078645</v>
       </c>
       <c r="FB6" s="2" t="n">
-        <v>0.2782395230838289</v>
+        <v>0.2790868254610529</v>
       </c>
       <c r="FC6" s="2" t="n">
-        <v>0.279895990435908</v>
+        <v>0.2808842428968646</v>
       </c>
       <c r="FD6" s="2" t="n">
-        <v>0.2697519624763357</v>
+        <v>0.2707780638867247</v>
       </c>
       <c r="FE6" s="2" t="n">
-        <v>0.2709197849609489</v>
+        <v>0.2720823959090347</v>
       </c>
       <c r="FF6" s="2" t="n">
-        <v>0.2705017996466764</v>
+        <v>0.2716554549968847</v>
       </c>
       <c r="FG6" s="2" t="n">
-        <v>0.2670366985881111</v>
+        <v>0.2682728244149467</v>
       </c>
       <c r="FH6" s="2" t="n">
-        <v>0.2625435892880189</v>
+        <v>0.2637828592598664</v>
       </c>
       <c r="FI6" s="2" t="n">
-        <v>0.2612861858890141</v>
+        <v>0.2624608816788281</v>
       </c>
       <c r="FJ6" s="2" t="n">
-        <v>0.2628715431475937</v>
+        <v>0.2642141005182564</v>
       </c>
       <c r="FK6" s="2" t="n">
-        <v>0.2634959545495645</v>
+        <v>0.2650714245202676</v>
       </c>
       <c r="FL6" s="2" t="n">
-        <v>0.2723973975345595</v>
+        <v>0.2741354764267905</v>
       </c>
       <c r="FM6" s="2" t="n">
-        <v>0.282404445156088</v>
+        <v>0.2844160646643544</v>
       </c>
       <c r="FN6" s="2" t="n">
-        <v>0.2907405144832032</v>
+        <v>0.2921122632286446</v>
       </c>
       <c r="FO6" s="2" t="n">
-        <v>0.2905810724567883</v>
+        <v>0.2919441859793179</v>
       </c>
       <c r="FP6" s="2" t="n">
-        <v>0.2824474799999854</v>
+        <v>0.2837903130421302</v>
       </c>
       <c r="FQ6" s="2" t="n">
-        <v>0.2802323968147087</v>
+        <v>0.2817352161740112</v>
       </c>
       <c r="FR6" s="2" t="n">
-        <v>0.2861400768904982</v>
+        <v>0.2875615359096823</v>
       </c>
       <c r="FS6" s="2" t="n">
-        <v>0.2834845055752457</v>
+        <v>0.2849687804394425</v>
       </c>
       <c r="FT6" s="2" t="n">
-        <v>0.2840214475877945</v>
+        <v>0.2855413213260833</v>
       </c>
       <c r="FU6" s="2" t="n">
-        <v>0.2820631827345318</v>
+        <v>0.2836742664804883</v>
       </c>
       <c r="FV6" s="2" t="n">
-        <v>0.2836189346500048</v>
+        <v>0.2853565367050776</v>
       </c>
       <c r="FW6" s="2" t="n">
-        <v>0.2840470671725478</v>
+        <v>0.2858148962331023</v>
       </c>
       <c r="FX6" s="2" t="n">
-        <v>0.2818750968000489</v>
+        <v>0.2839753409645158</v>
       </c>
       <c r="FY6" s="2" t="n">
-        <v>0.2914428786862128</v>
+        <v>0.2936801837313406</v>
       </c>
       <c r="FZ6" s="2" t="n">
-        <v>0.2959102503615119</v>
+        <v>0.2982491142707565</v>
       </c>
       <c r="GA6" s="2" t="n">
-        <v>0.3105179436207666</v>
+        <v>0.3128864682913675</v>
       </c>
       <c r="GB6" s="2" t="n">
-        <v>0.3087534446700633</v>
+        <v>0.3104669366463245</v>
       </c>
       <c r="GC6" s="2" t="n">
-        <v>0.3095116536327118</v>
+        <v>0.3113678316779846</v>
       </c>
       <c r="GD6" s="2" t="n">
-        <v>0.3110626379363061</v>
+        <v>0.3129591906778336</v>
       </c>
       <c r="GE6" s="2" t="n">
-        <v>0.3110851042204607</v>
+        <v>0.312999165826391</v>
       </c>
       <c r="GF6" s="2" t="n">
-        <v>0.3088602824018413</v>
+        <v>0.3108160821602756</v>
       </c>
       <c r="GG6" s="2" t="n">
-        <v>0.3069612035326412</v>
+        <v>0.3089667955212048</v>
       </c>
       <c r="GH6" s="2" t="n">
-        <v>0.3032403613878842</v>
+        <v>0.3052840779973622</v>
       </c>
       <c r="GI6" s="2" t="n">
-        <v>0.3023801173861537</v>
+        <v>0.3049582566912684</v>
       </c>
       <c r="GJ6" s="2" t="n">
-        <v>0.3034414652472545</v>
+        <v>0.305731550205331</v>
       </c>
       <c r="GK6" s="2" t="n">
-        <v>0.3068966476677898</v>
+        <v>0.3093740625738147</v>
       </c>
       <c r="GL6" s="2" t="n">
-        <v>0.3117817963115579</v>
+        <v>0.3144716645233042</v>
       </c>
       <c r="GM6" s="2" t="n">
-        <v>0.3166150337986535</v>
+        <v>0.3194968662194795</v>
       </c>
       <c r="GN6" s="2" t="n">
-        <v>0.3316736873641332</v>
+        <v>0.3346247952833493</v>
       </c>
       <c r="GO6" s="2" t="n">
-        <v>0.3403903142958888</v>
+        <v>0.3435337366014728</v>
       </c>
       <c r="GP6" s="2" t="n">
-        <v>0.3356531263192433</v>
+        <v>0.338146939953162</v>
       </c>
       <c r="GQ6" s="2" t="n">
-        <v>0.3313018235948335</v>
+        <v>0.3337821889307748</v>
       </c>
       <c r="GR6" s="2" t="n">
-        <v>0.3316136483802023</v>
+        <v>0.3337712024106207</v>
       </c>
       <c r="GS6" s="2" t="n">
-        <v>0.3293838788468937</v>
+        <v>0.3318723653156857</v>
       </c>
       <c r="GT6" s="2" t="n">
-        <v>0.3307863054829951</v>
+        <v>0.3331908388096209</v>
       </c>
       <c r="GU6" s="2" t="n">
-        <v>0.3247612183574105</v>
+        <v>0.3272852887991333</v>
       </c>
       <c r="GV6" s="2" t="n">
-        <v>0.3300113157613164</v>
+        <v>0.3326671869737988</v>
       </c>
       <c r="GW6" s="2" t="n">
-        <v>0.3244963583831211</v>
+        <v>0.3271530193571468</v>
       </c>
       <c r="GX6" s="2" t="n">
-        <v>0.3255421904885228</v>
+        <v>0.32846997063989</v>
       </c>
       <c r="GY6" s="2" t="n">
-        <v>0.32577921756568</v>
+        <v>0.328916537845755</v>
       </c>
       <c r="GZ6" s="2" t="n">
-        <v>0.3375596325045536</v>
+        <v>0.3407626669054935</v>
       </c>
       <c r="HA6" s="2" t="n">
-        <v>0.3507710787351114</v>
+        <v>0.3538386392290575</v>
       </c>
       <c r="HB6" s="2" t="n">
-        <v>0.3629385438884106</v>
+        <v>0.3660621774519291</v>
       </c>
       <c r="HC6" s="2" t="n">
-        <v>0.3565391508454407</v>
+        <v>0.3592764643544282</v>
       </c>
       <c r="HD6" s="2" t="n">
-        <v>0.3442774092782729</v>
+        <v>0.3482405444611304</v>
       </c>
       <c r="HE6" s="2" t="n">
-        <v>0.3388940911017965</v>
+        <v>0.3424590300046514</v>
       </c>
       <c r="HF6" s="2" t="n">
-        <v>0.3411250189117638</v>
+        <v>0.3448579237035958</v>
       </c>
       <c r="HG6" s="2" t="n">
-        <v>0.3482215881334066</v>
+        <v>0.3520451813922644</v>
       </c>
       <c r="HH6" s="2" t="n">
-        <v>0.3475192634825289</v>
+        <v>0.351220317042309</v>
       </c>
       <c r="HI6" s="2" t="n">
-        <v>0.3461056314847495</v>
+        <v>0.3498804979465033</v>
       </c>
       <c r="HJ6" s="2" t="n">
-        <v>0.3493911940290598</v>
+        <v>0.3528566304280428</v>
       </c>
       <c r="HK6" s="2" t="n">
-        <v>0.3432693378019131</v>
+        <v>0.3470183656501568</v>
       </c>
       <c r="HL6" s="2" t="n">
-        <v>0.3458872558966084</v>
+        <v>0.3494629236355229</v>
       </c>
       <c r="HM6" s="2" t="n">
-        <v>0.3438912963648958</v>
+        <v>0.3473519196888132</v>
       </c>
       <c r="HN6" s="2" t="n">
-        <v>0.3657519000276082</v>
+        <v>0.3692457231386654</v>
       </c>
       <c r="HO6" s="2" t="n">
-        <v>0.3790279658223829</v>
+        <v>0.3826136396910391</v>
       </c>
       <c r="HP6" s="2" t="n">
-        <v>0.3573437024068727</v>
+        <v>0.3602521632027521</v>
       </c>
       <c r="HQ6" s="2" t="n">
-        <v>0.3444596542116353</v>
+        <v>0.34707810860836</v>
       </c>
       <c r="HR6" s="3" t="n">
         <v>55517</v>
@@ -4919,676 +4919,676 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.0278243437428271</v>
+        <v>0.02772115832383386</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.03668829255389302</v>
+        <v>0.0363731786294493</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03895005056216976</v>
+        <v>0.03860914831563494</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.04072632970930028</v>
+        <v>0.04034430770845103</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.04131745516635058</v>
+        <v>0.04086234948910353</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.04062490050596125</v>
+        <v>0.04018154066902525</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.04020619107354359</v>
+        <v>0.0398036287533112</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.04000583128971801</v>
+        <v>0.03961798572880969</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.04030241703499671</v>
+        <v>0.03993604777265902</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.03959603512630577</v>
+        <v>0.03928267860756035</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.03856582103148626</v>
+        <v>0.03832968512401508</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03697249895084558</v>
+        <v>0.03693047022569833</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.03690204830660458</v>
+        <v>0.03688601279451485</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.0374262405126773</v>
+        <v>0.03748949780459034</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.05419416637318145</v>
+        <v>0.05403572512017499</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.06637226326503746</v>
+        <v>0.06581550559141629</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.06997149003244815</v>
+        <v>0.06919326385058341</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.07110756211129729</v>
+        <v>0.07031269505766932</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.07270325302736208</v>
+        <v>0.07189270250157759</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.07000216718273983</v>
+        <v>0.06929301719623432</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.07127747122463685</v>
+        <v>0.07054986428734761</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.07074433789031914</v>
+        <v>0.07015373967962674</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.07067779134159688</v>
+        <v>0.07006843629425172</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.07020945143547438</v>
+        <v>0.06966910180297278</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.06690451144403239</v>
+        <v>0.06650520037090799</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.06376872872108658</v>
+        <v>0.06370348771208961</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0.06383271091171513</v>
+        <v>0.06375512149670134</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0.06493488118260815</v>
+        <v>0.0649904736897321</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>0.08695876507098477</v>
+        <v>0.08646512871618073</v>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>0.1006770921644512</v>
+        <v>0.09961959214478162</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.1020372390662112</v>
+        <v>0.1006602805022874</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>0.1042282576709967</v>
+        <v>0.1028888612091522</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.104861451351282</v>
+        <v>0.1035732571419448</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>0.1042088398737114</v>
+        <v>0.1030416170162361</v>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>0.1010317637257395</v>
+        <v>0.1000162942938623</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>0.09979622415632354</v>
+        <v>0.09899274795681583</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>0.1007354267818308</v>
+        <v>0.09985999473756317</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>0.09730849565156756</v>
+        <v>0.09660257921704112</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.09186202696527056</v>
+        <v>0.09145660921002439</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>0.0896208661446839</v>
+        <v>0.08949315946796232</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>0.09226290513846409</v>
+        <v>0.09216209878298771</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>0.09277402976486118</v>
+        <v>0.09281010733875664</v>
       </c>
       <c r="AR7" s="2" t="n">
-        <v>0.1172416525407848</v>
+        <v>0.1164635045900164</v>
       </c>
       <c r="AS7" s="2" t="n">
-        <v>0.1284248094314941</v>
+        <v>0.1264354299063095</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>0.1298661683193056</v>
+        <v>0.1278469790211527</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>0.1310363503712361</v>
+        <v>0.1291587351429408</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>0.129921757049194</v>
+        <v>0.1283281858929307</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>0.1249330097916581</v>
+        <v>0.1235507743540265</v>
       </c>
       <c r="AX7" s="2" t="n">
-        <v>0.1255800598604645</v>
+        <v>0.1243740809453692</v>
       </c>
       <c r="AY7" s="2" t="n">
-        <v>0.1243573803602377</v>
+        <v>0.1233390890209594</v>
       </c>
       <c r="AZ7" s="2" t="n">
-        <v>0.1235086276117692</v>
+        <v>0.1224924820397029</v>
       </c>
       <c r="BA7" s="2" t="n">
-        <v>0.1188772827722499</v>
+        <v>0.1180720296092698</v>
       </c>
       <c r="BB7" s="2" t="n">
-        <v>0.1131756306425362</v>
+        <v>0.11266499206281</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>0.1112253669192165</v>
+        <v>0.1110491420616477</v>
       </c>
       <c r="BD7" s="2" t="n">
-        <v>0.1097477489150057</v>
+        <v>0.1097250637597332</v>
       </c>
       <c r="BE7" s="2" t="n">
-        <v>0.1128828824067204</v>
+        <v>0.1129769348108857</v>
       </c>
       <c r="BF7" s="2" t="n">
-        <v>0.1484240073571139</v>
+        <v>0.1466814208636218</v>
       </c>
       <c r="BG7" s="2" t="n">
-        <v>0.1541086238158458</v>
+        <v>0.1516711775494331</v>
       </c>
       <c r="BH7" s="2" t="n">
-        <v>0.1540051074769258</v>
+        <v>0.1516828881647347</v>
       </c>
       <c r="BI7" s="2" t="n">
-        <v>0.1515594819126068</v>
+        <v>0.1492318795559346</v>
       </c>
       <c r="BJ7" s="2" t="n">
-        <v>0.1514243947648537</v>
+        <v>0.1495904343509209</v>
       </c>
       <c r="BK7" s="2" t="n">
-        <v>0.144209205629153</v>
+        <v>0.142686422439141</v>
       </c>
       <c r="BL7" s="2" t="n">
-        <v>0.1432910430180446</v>
+        <v>0.1419567818688766</v>
       </c>
       <c r="BM7" s="2" t="n">
-        <v>0.1402836996955153</v>
+        <v>0.1392546217781779</v>
       </c>
       <c r="BN7" s="2" t="n">
-        <v>0.1388678086266918</v>
+        <v>0.137765495227377</v>
       </c>
       <c r="BO7" s="2" t="n">
-        <v>0.1398120352850925</v>
+        <v>0.1389018239305984</v>
       </c>
       <c r="BP7" s="2" t="n">
-        <v>0.1298522373016324</v>
+        <v>0.1293909942086186</v>
       </c>
       <c r="BQ7" s="2" t="n">
-        <v>0.1285359513110093</v>
+        <v>0.1284301828688554</v>
       </c>
       <c r="BR7" s="2" t="n">
-        <v>0.1277904251141659</v>
+        <v>0.1277740021718851</v>
       </c>
       <c r="BS7" s="2" t="n">
-        <v>0.1272306766807847</v>
+        <v>0.1274017885774189</v>
       </c>
       <c r="BT7" s="2" t="n">
-        <v>0.1903656777314363</v>
+        <v>0.1874300521187006</v>
       </c>
       <c r="BU7" s="2" t="n">
-        <v>0.1911590523177121</v>
+        <v>0.1877497523182366</v>
       </c>
       <c r="BV7" s="2" t="n">
-        <v>0.1876762680520571</v>
+        <v>0.1847637019862688</v>
       </c>
       <c r="BW7" s="2" t="n">
-        <v>0.1878306315607796</v>
+        <v>0.1850513973600635</v>
       </c>
       <c r="BX7" s="2" t="n">
-        <v>0.1831313504279618</v>
+        <v>0.1811131483317379</v>
       </c>
       <c r="BY7" s="2" t="n">
-        <v>0.1784311858412108</v>
+        <v>0.1768301044997058</v>
       </c>
       <c r="BZ7" s="2" t="n">
-        <v>0.1742197837810712</v>
+        <v>0.1728110503535467</v>
       </c>
       <c r="CA7" s="2" t="n">
-        <v>0.1704784683232605</v>
+        <v>0.1693102545385659</v>
       </c>
       <c r="CB7" s="2" t="n">
-        <v>0.1676532760345835</v>
+        <v>0.1667079128408332</v>
       </c>
       <c r="CC7" s="2" t="n">
-        <v>0.1625596275331933</v>
+        <v>0.1616401737334687</v>
       </c>
       <c r="CD7" s="2" t="n">
-        <v>0.1575366721523926</v>
+        <v>0.1570700758172199</v>
       </c>
       <c r="CE7" s="2" t="n">
-        <v>0.1492020632503844</v>
+        <v>0.1491832579849577</v>
       </c>
       <c r="CF7" s="2" t="n">
-        <v>0.1491016455396537</v>
+        <v>0.1492263310059432</v>
       </c>
       <c r="CG7" s="2" t="n">
-        <v>0.1522922638770766</v>
+        <v>0.1525472339209742</v>
       </c>
       <c r="CH7" s="2" t="n">
-        <v>0.22105386784896</v>
+        <v>0.2178208374105368</v>
       </c>
       <c r="CI7" s="2" t="n">
-        <v>0.2226280213147707</v>
+        <v>0.2190130852908201</v>
       </c>
       <c r="CJ7" s="2" t="n">
-        <v>0.2178464186984433</v>
+        <v>0.2149691348570718</v>
       </c>
       <c r="CK7" s="2" t="n">
-        <v>0.2121414031497208</v>
+        <v>0.2098254348746506</v>
       </c>
       <c r="CL7" s="2" t="n">
-        <v>0.207778705502475</v>
+        <v>0.2058534941026814</v>
       </c>
       <c r="CM7" s="2" t="n">
-        <v>0.1992444984661713</v>
+        <v>0.1978715464519634</v>
       </c>
       <c r="CN7" s="2" t="n">
-        <v>0.1990113764390017</v>
+        <v>0.1977529286726976</v>
       </c>
       <c r="CO7" s="2" t="n">
-        <v>0.1917003296165246</v>
+        <v>0.1906102686970013</v>
       </c>
       <c r="CP7" s="2" t="n">
-        <v>0.1897175300355103</v>
+        <v>0.1887862149114755</v>
       </c>
       <c r="CQ7" s="2" t="n">
-        <v>0.1897506739288928</v>
+        <v>0.1888798314422728</v>
       </c>
       <c r="CR7" s="2" t="n">
-        <v>0.1735265320805869</v>
+        <v>0.1732039256660304</v>
       </c>
       <c r="CS7" s="2" t="n">
-        <v>0.1697484238875848</v>
+        <v>0.1699527188075525</v>
       </c>
       <c r="CT7" s="2" t="n">
-        <v>0.1689976874159878</v>
+        <v>0.1693456444310253</v>
       </c>
       <c r="CU7" s="2" t="n">
-        <v>0.1758827197198232</v>
+        <v>0.1762952620927652</v>
       </c>
       <c r="CV7" s="2" t="n">
-        <v>0.2612329259389899</v>
+        <v>0.2584040075415633</v>
       </c>
       <c r="CW7" s="2" t="n">
-        <v>0.2498329741327023</v>
+        <v>0.2473275897471165</v>
       </c>
       <c r="CX7" s="2" t="n">
-        <v>0.2465931579944362</v>
+        <v>0.2443263188478222</v>
       </c>
       <c r="CY7" s="2" t="n">
-        <v>0.2437603287497559</v>
+        <v>0.2421299256483116</v>
       </c>
       <c r="CZ7" s="2" t="n">
-        <v>0.2334282977364993</v>
+        <v>0.2320248467706179</v>
       </c>
       <c r="DA7" s="2" t="n">
-        <v>0.2289556169984616</v>
+        <v>0.2278063984689988</v>
       </c>
       <c r="DB7" s="2" t="n">
-        <v>0.2281630991459348</v>
+        <v>0.2271649262369135</v>
       </c>
       <c r="DC7" s="2" t="n">
-        <v>0.2219048177484147</v>
+        <v>0.2210578282955758</v>
       </c>
       <c r="DD7" s="2" t="n">
-        <v>0.2193683702871674</v>
+        <v>0.2188819703087681</v>
       </c>
       <c r="DE7" s="2" t="n">
-        <v>0.212813708038372</v>
+        <v>0.2124972669792594</v>
       </c>
       <c r="DF7" s="2" t="n">
-        <v>0.2047657077863929</v>
+        <v>0.2048271191969631</v>
       </c>
       <c r="DG7" s="2" t="n">
-        <v>0.2012744933035698</v>
+        <v>0.2015167079534855</v>
       </c>
       <c r="DH7" s="2" t="n">
-        <v>0.1988600630755125</v>
+        <v>0.1992747400397955</v>
       </c>
       <c r="DI7" s="2" t="n">
-        <v>0.2009533607120196</v>
+        <v>0.2017500624711196</v>
       </c>
       <c r="DJ7" s="2" t="n">
-        <v>0.2798295939742969</v>
+        <v>0.2776702667056964</v>
       </c>
       <c r="DK7" s="2" t="n">
-        <v>0.2735774631488176</v>
+        <v>0.272076752303824</v>
       </c>
       <c r="DL7" s="2" t="n">
-        <v>0.2644085825755179</v>
+        <v>0.2629501686765731</v>
       </c>
       <c r="DM7" s="2" t="n">
-        <v>0.2617877099481686</v>
+        <v>0.2605263937083347</v>
       </c>
       <c r="DN7" s="2" t="n">
-        <v>0.2531984727346947</v>
+        <v>0.2522408458852818</v>
       </c>
       <c r="DO7" s="2" t="n">
-        <v>0.2525985624138802</v>
+        <v>0.2516725521032304</v>
       </c>
       <c r="DP7" s="2" t="n">
-        <v>0.2439970845577961</v>
+        <v>0.2435232574341541</v>
       </c>
       <c r="DQ7" s="2" t="n">
-        <v>0.2368600178137404</v>
+        <v>0.2364771883562189</v>
       </c>
       <c r="DR7" s="2" t="n">
-        <v>0.2336716485833896</v>
+        <v>0.2336442043697608</v>
       </c>
       <c r="DS7" s="2" t="n">
-        <v>0.2291542155354847</v>
+        <v>0.2292355274468292</v>
       </c>
       <c r="DT7" s="2" t="n">
-        <v>0.2234196964770535</v>
+        <v>0.2237690765529851</v>
       </c>
       <c r="DU7" s="2" t="n">
-        <v>0.2203765584865895</v>
+        <v>0.2208026832679597</v>
       </c>
       <c r="DV7" s="2" t="n">
-        <v>0.2227015648682726</v>
+        <v>0.2234092582662714</v>
       </c>
       <c r="DW7" s="2" t="n">
-        <v>0.2242563099989196</v>
+        <v>0.2252497741410038</v>
       </c>
       <c r="DX7" s="2" t="n">
-        <v>0.294003204922017</v>
+        <v>0.2925784527462091</v>
       </c>
       <c r="DY7" s="2" t="n">
-        <v>0.282480209169544</v>
+        <v>0.2813251680113447</v>
       </c>
       <c r="DZ7" s="2" t="n">
-        <v>0.2801071311933669</v>
+        <v>0.2792803253633651</v>
       </c>
       <c r="EA7" s="2" t="n">
-        <v>0.2703207613152349</v>
+        <v>0.2694294707101667</v>
       </c>
       <c r="EB7" s="2" t="n">
-        <v>0.2669428617410278</v>
+        <v>0.2664579332522964</v>
       </c>
       <c r="EC7" s="2" t="n">
-        <v>0.2600826232747214</v>
+        <v>0.2597191765026228</v>
       </c>
       <c r="ED7" s="2" t="n">
-        <v>0.2555358607421773</v>
+        <v>0.2554177839408773</v>
       </c>
       <c r="EE7" s="2" t="n">
-        <v>0.2524753459332953</v>
+        <v>0.252589086496688</v>
       </c>
       <c r="EF7" s="2" t="n">
-        <v>0.2499157186037131</v>
+        <v>0.2498869481867381</v>
       </c>
       <c r="EG7" s="2" t="n">
-        <v>0.2469962357405696</v>
+        <v>0.2471662021104369</v>
       </c>
       <c r="EH7" s="2" t="n">
-        <v>0.2330785098882508</v>
+        <v>0.2337839643867802</v>
       </c>
       <c r="EI7" s="2" t="n">
-        <v>0.2351654057894629</v>
+        <v>0.2360730764959734</v>
       </c>
       <c r="EJ7" s="2" t="n">
-        <v>0.2348837110460573</v>
+        <v>0.2360494549632841</v>
       </c>
       <c r="EK7" s="2" t="n">
-        <v>0.2371555231324452</v>
+        <v>0.2383303306809681</v>
       </c>
       <c r="EL7" s="2" t="n">
-        <v>0.2998255888254788</v>
+        <v>0.2992533544333127</v>
       </c>
       <c r="EM7" s="2" t="n">
-        <v>0.2932166954823353</v>
+        <v>0.29327516763886</v>
       </c>
       <c r="EN7" s="2" t="n">
-        <v>0.2870487204156098</v>
+        <v>0.2872063597998795</v>
       </c>
       <c r="EO7" s="2" t="n">
-        <v>0.2785040865582304</v>
+        <v>0.2787320668739157</v>
       </c>
       <c r="EP7" s="2" t="n">
-        <v>0.2811731104944595</v>
+        <v>0.2813507770393738</v>
       </c>
       <c r="EQ7" s="2" t="n">
-        <v>0.2687254433890692</v>
+        <v>0.269178811218392</v>
       </c>
       <c r="ER7" s="2" t="n">
-        <v>0.2686006390403017</v>
+        <v>0.2690024414013132</v>
       </c>
       <c r="ES7" s="2" t="n">
-        <v>0.2604592680291357</v>
+        <v>0.2614275454835119</v>
       </c>
       <c r="ET7" s="2" t="n">
-        <v>0.2629568253385797</v>
+        <v>0.2636604283678308</v>
       </c>
       <c r="EU7" s="2" t="n">
-        <v>0.2613794338379179</v>
+        <v>0.2622634936545168</v>
       </c>
       <c r="EV7" s="2" t="n">
-        <v>0.2572678780700066</v>
+        <v>0.2583545974041321</v>
       </c>
       <c r="EW7" s="2" t="n">
-        <v>0.2557049353718698</v>
+        <v>0.2568327930867612</v>
       </c>
       <c r="EX7" s="2" t="n">
-        <v>0.2547349641710303</v>
+        <v>0.2560885782032988</v>
       </c>
       <c r="EY7" s="2" t="n">
-        <v>0.2668716498363675</v>
+        <v>0.2684958540547551</v>
       </c>
       <c r="EZ7" s="2" t="n">
-        <v>0.2951828386688398</v>
+        <v>0.2958738502168821</v>
       </c>
       <c r="FA7" s="2" t="n">
-        <v>0.295091526488191</v>
+        <v>0.295913116911775</v>
       </c>
       <c r="FB7" s="2" t="n">
-        <v>0.2834758479940269</v>
+        <v>0.2842592467414711</v>
       </c>
       <c r="FC7" s="2" t="n">
-        <v>0.2853076534189527</v>
+        <v>0.2862444298185651</v>
       </c>
       <c r="FD7" s="2" t="n">
-        <v>0.275079236923926</v>
+        <v>0.2760513141744066</v>
       </c>
       <c r="FE7" s="2" t="n">
-        <v>0.27649197475724</v>
+        <v>0.2775983189206578</v>
       </c>
       <c r="FF7" s="2" t="n">
-        <v>0.275940086888933</v>
+        <v>0.2770320216294763</v>
       </c>
       <c r="FG7" s="2" t="n">
-        <v>0.2725922725970585</v>
+        <v>0.27376581354688</v>
       </c>
       <c r="FH7" s="2" t="n">
-        <v>0.267971391961471</v>
+        <v>0.26915289013137</v>
       </c>
       <c r="FI7" s="2" t="n">
-        <v>0.2666800535508869</v>
+        <v>0.2677966646143673</v>
       </c>
       <c r="FJ7" s="2" t="n">
-        <v>0.2687028256099233</v>
+        <v>0.2699874994199285</v>
       </c>
       <c r="FK7" s="2" t="n">
-        <v>0.2694057470198048</v>
+        <v>0.2709114125008953</v>
       </c>
       <c r="FL7" s="2" t="n">
-        <v>0.2787412360654158</v>
+        <v>0.2804273397074026</v>
       </c>
       <c r="FM7" s="2" t="n">
-        <v>0.2891380939034187</v>
+        <v>0.291081860974189</v>
       </c>
       <c r="FN7" s="2" t="n">
-        <v>0.2970476630376936</v>
+        <v>0.2983441534685255</v>
       </c>
       <c r="FO7" s="2" t="n">
-        <v>0.2967888076198197</v>
+        <v>0.2980909753930664</v>
       </c>
       <c r="FP7" s="2" t="n">
-        <v>0.2885153028840444</v>
+        <v>0.2897926453227422</v>
       </c>
       <c r="FQ7" s="2" t="n">
-        <v>0.2864796671339639</v>
+        <v>0.2879174503752359</v>
       </c>
       <c r="FR7" s="2" t="n">
-        <v>0.2923562394518562</v>
+        <v>0.2937070818681426</v>
       </c>
       <c r="FS7" s="2" t="n">
-        <v>0.2900235156785016</v>
+        <v>0.2914462189446454</v>
       </c>
       <c r="FT7" s="2" t="n">
-        <v>0.2906351597692624</v>
+        <v>0.2920818166520253</v>
       </c>
       <c r="FU7" s="2" t="n">
-        <v>0.2888155405424664</v>
+        <v>0.2903504644535611</v>
       </c>
       <c r="FV7" s="2" t="n">
-        <v>0.290717824144999</v>
+        <v>0.2923847797948517</v>
       </c>
       <c r="FW7" s="2" t="n">
-        <v>0.2912524066328208</v>
+        <v>0.2929441131114165</v>
       </c>
       <c r="FX7" s="2" t="n">
-        <v>0.2894137038108242</v>
+        <v>0.2914318574782742</v>
       </c>
       <c r="FY7" s="2" t="n">
-        <v>0.2993784627257579</v>
+        <v>0.301536225372433</v>
       </c>
       <c r="FZ7" s="2" t="n">
-        <v>0.3041068910027815</v>
+        <v>0.3063595963980032</v>
       </c>
       <c r="GA7" s="2" t="n">
-        <v>0.3188624787643614</v>
+        <v>0.3211488384321394</v>
       </c>
       <c r="GB7" s="2" t="n">
-        <v>0.3170131708072084</v>
+        <v>0.3186459655450242</v>
       </c>
       <c r="GC7" s="2" t="n">
-        <v>0.3180596190777351</v>
+        <v>0.3198026228037407</v>
       </c>
       <c r="GD7" s="2" t="n">
-        <v>0.3199259878667924</v>
+        <v>0.3217129872712228</v>
       </c>
       <c r="GE7" s="2" t="n">
-        <v>0.3200644191271394</v>
+        <v>0.3218543093568414</v>
       </c>
       <c r="GF7" s="2" t="n">
-        <v>0.3178727121364034</v>
+        <v>0.3197093547593511</v>
       </c>
       <c r="GG7" s="2" t="n">
-        <v>0.3158823929333789</v>
+        <v>0.3177773214483364</v>
       </c>
       <c r="GH7" s="2" t="n">
-        <v>0.3123614712949808</v>
+        <v>0.3142897039052065</v>
       </c>
       <c r="GI7" s="2" t="n">
-        <v>0.3121945828328919</v>
+        <v>0.3146527677903962</v>
       </c>
       <c r="GJ7" s="2" t="n">
-        <v>0.3128738415445068</v>
+        <v>0.3150467288697937</v>
       </c>
       <c r="GK7" s="2" t="n">
-        <v>0.3167011959687113</v>
+        <v>0.3190709946885943</v>
       </c>
       <c r="GL7" s="2" t="n">
-        <v>0.3219290525194954</v>
+        <v>0.32449745391577</v>
       </c>
       <c r="GM7" s="2" t="n">
-        <v>0.3269789012637622</v>
+        <v>0.3297557699051387</v>
       </c>
       <c r="GN7" s="2" t="n">
-        <v>0.3421808399704576</v>
+        <v>0.3450267754939676</v>
       </c>
       <c r="GO7" s="2" t="n">
-        <v>0.3512611861289424</v>
+        <v>0.3542850713194293</v>
       </c>
       <c r="GP7" s="2" t="n">
-        <v>0.3454057407090666</v>
+        <v>0.347768580586672</v>
       </c>
       <c r="GQ7" s="2" t="n">
-        <v>0.3409897755537593</v>
+        <v>0.3433642010841929</v>
       </c>
       <c r="GR7" s="2" t="n">
-        <v>0.3410097349752174</v>
+        <v>0.3430680845249877</v>
       </c>
       <c r="GS7" s="2" t="n">
-        <v>0.3389683239904815</v>
+        <v>0.3413450293985778</v>
       </c>
       <c r="GT7" s="2" t="n">
-        <v>0.340703779144487</v>
+        <v>0.3429899525477501</v>
       </c>
       <c r="GU7" s="2" t="n">
-        <v>0.3348514891685087</v>
+        <v>0.3372446380079824</v>
       </c>
       <c r="GV7" s="2" t="n">
-        <v>0.3404442788105583</v>
+        <v>0.3429910288196182</v>
       </c>
       <c r="GW7" s="2" t="n">
-        <v>0.3351155935136903</v>
+        <v>0.337676894506656</v>
       </c>
       <c r="GX7" s="2" t="n">
-        <v>0.3364614273735863</v>
+        <v>0.3392715777584893</v>
       </c>
       <c r="GY7" s="2" t="n">
-        <v>0.3370747497139321</v>
+        <v>0.3400940900502549</v>
       </c>
       <c r="GZ7" s="2" t="n">
-        <v>0.3488652984720115</v>
+        <v>0.3519473726969604</v>
       </c>
       <c r="HA7" s="2" t="n">
-        <v>0.3616599003516046</v>
+        <v>0.3646068806491701</v>
       </c>
       <c r="HB7" s="2" t="n">
-        <v>0.3746808184668627</v>
+        <v>0.3776962099954692</v>
       </c>
       <c r="HC7" s="2" t="n">
-        <v>0.3663209038719709</v>
+        <v>0.3689671638354833</v>
       </c>
       <c r="HD7" s="2" t="n">
-        <v>0.3582449826815298</v>
+        <v>0.3620851683833769</v>
       </c>
       <c r="HE7" s="2" t="n">
-        <v>0.3522436585444852</v>
+        <v>0.3557041403073713</v>
       </c>
       <c r="HF7" s="2" t="n">
-        <v>0.3544325613251032</v>
+        <v>0.3580398120751681</v>
       </c>
       <c r="HG7" s="2" t="n">
-        <v>0.3618296260103839</v>
+        <v>0.3655234078035015</v>
       </c>
       <c r="HH7" s="2" t="n">
-        <v>0.361374807126874</v>
+        <v>0.3649551761821451</v>
       </c>
       <c r="HI7" s="2" t="n">
-        <v>0.3601213716877551</v>
+        <v>0.3637713813198657</v>
       </c>
       <c r="HJ7" s="2" t="n">
-        <v>0.3635199127472747</v>
+        <v>0.3668802959598411</v>
       </c>
       <c r="HK7" s="2" t="n">
-        <v>0.3574831254257582</v>
+        <v>0.3611005015148543</v>
       </c>
       <c r="HL7" s="2" t="n">
-        <v>0.3601492838787964</v>
+        <v>0.3635912136959961</v>
       </c>
       <c r="HM7" s="2" t="n">
-        <v>0.3581095426984946</v>
+        <v>0.3614147394605796</v>
       </c>
       <c r="HN7" s="2" t="n">
-        <v>0.3798674758511063</v>
+        <v>0.3832277026014801</v>
       </c>
       <c r="HO7" s="2" t="n">
-        <v>0.3936095289586018</v>
+        <v>0.3970232732294033</v>
       </c>
       <c r="HP7" s="2" t="n">
-        <v>0.3683234185410131</v>
+        <v>0.3711673424077619</v>
       </c>
       <c r="HQ7" s="2" t="n">
-        <v>0.3533648210832124</v>
+        <v>0.3559099766680246</v>
       </c>
       <c r="HR7" s="3" t="n">
         <v>55519</v>
@@ -5673,7 +5673,7 @@
         <v>0.0707983495227468</v>
       </c>
       <c r="Z8" s="7" t="n">
-        <v>0.06776289641857147</v>
+        <v>0.06796811521053314</v>
       </c>
       <c r="AA8" s="6" t="n">
         <v>0.06325361731976981</v>
@@ -5712,7 +5712,7 @@
         <v>0.102714844045793</v>
       </c>
       <c r="AM8" s="7" t="n">
-        <v>0.09959778934717178</v>
+        <v>0.09900931268930435</v>
       </c>
       <c r="AN8" s="6" t="n">
         <v>0.09259502537764119</v>
@@ -5871,7 +5871,7 @@
         <v>0.204818851764059</v>
       </c>
       <c r="CN8" s="7" t="n">
-        <v>0.2053440064191818</v>
+        <v>0.2052146941423416</v>
       </c>
       <c r="CO8" s="6" t="n">
         <v>0.196500406731799</v>
@@ -6129,7 +6129,7 @@
         <v>0.277654055693251</v>
       </c>
       <c r="FV8" s="7" t="n">
-        <v>0.2791333496570587</v>
+        <v>0.2790730893611908</v>
       </c>
       <c r="FW8" s="6" t="n">
         <v>0.279414809816803</v>
@@ -6295,7 +6295,7 @@
         <v>0.0381157332974437</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.0413268469274044</v>
+        <v>0.03983543068170547</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>0.0395341519679435</v>
@@ -6418,7 +6418,7 @@
         <v>0.131315746744894</v>
       </c>
       <c r="AU9" s="7" t="n">
-        <v>0.1363729536533356</v>
+        <v>0.1340141743421555</v>
       </c>
       <c r="AV9" s="6" t="n">
         <v>0.132513088922263</v>
@@ -6499,7 +6499,7 @@
         <v>0.199955283513327</v>
       </c>
       <c r="BV9" s="7" t="n">
-        <v>0.1966657787561417</v>
+        <v>0.1944539099931717</v>
       </c>
       <c r="BW9" s="6" t="n">
         <v>0.200606296983058</v>
@@ -6640,7 +6640,7 @@
         <v>0.251323415697041</v>
       </c>
       <c r="DQ9" s="7" t="n">
-        <v>0.2402604669332504</v>
+        <v>0.243425041437149</v>
       </c>
       <c r="DR9" s="6" t="n">
         <v>0.23764445461862</v>
@@ -6694,7 +6694,7 @@
         <v>0.232519744722409</v>
       </c>
       <c r="EI9" s="7" t="n">
-        <v>0.2326757311820984</v>
+        <v>0.2338796854019165</v>
       </c>
       <c r="EJ9" s="6" t="n">
         <v>0.231332738185024</v>
@@ -6853,7 +6853,7 @@
         <v>0.304890545827317</v>
       </c>
       <c r="GJ9" s="7" t="n">
-        <v>0.305094450712204</v>
+        <v>0.3060636520385742</v>
       </c>
       <c r="GK9" s="6" t="n">
         <v>0.308508043694741</v>

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -1509,676 +1509,676 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.03199679721235036</v>
+        <v>0.03202020833356976</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.04053134040746519</v>
+        <v>0.04043800232771465</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.04265038969501743</v>
+        <v>0.04266802615061292</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.04422283736683141</v>
+        <v>0.04442547732658397</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.04453795708964913</v>
+        <v>0.04491252478461116</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.04357367614921131</v>
+        <v>0.04414302064742841</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.04295486885590625</v>
+        <v>0.04366780560000014</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.04265720008694518</v>
+        <v>0.0434752524160682</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.04283502366326388</v>
+        <v>0.04370901681415375</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.04198828436810705</v>
+        <v>0.04284890931476089</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.04069910039100472</v>
+        <v>0.04162936125788514</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.03875228960395846</v>
+        <v>0.0395235634628037</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.03859512909246023</v>
+        <v>0.03942557173711594</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.03902558151770179</v>
+        <v>0.03984495073694531</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.0600859761786902</v>
+        <v>0.05961743244801403</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.07228123687028877</v>
+        <v>0.07196118227958671</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.07579686614995332</v>
+        <v>0.07609059970205159</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.07635531106451082</v>
+        <v>0.07707532958546209</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.07773379948032409</v>
+        <v>0.07867990214419872</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.07424316015589597</v>
+        <v>0.07536977548647286</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.07549595007234115</v>
+        <v>0.07683683851295013</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.07448804653544953</v>
+        <v>0.0759247513051801</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.07450037661209502</v>
+        <v>0.0760604574085752</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.0737495963989124</v>
+        <v>0.07533349204494807</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.07001900937349534</v>
+        <v>0.0716584444412682</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.06634786270291416</v>
+        <v>0.06770845699787943</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0.06638268000709563</v>
+        <v>0.0678337187625721</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0.06731349185293745</v>
+        <v>0.06869541622882913</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.0942665824815843</v>
+        <v>0.09326618557425474</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>0.10835715935688</v>
+        <v>0.1082138865546463</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>0.1094308991258452</v>
+        <v>0.1103392180328677</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.1107695609703629</v>
+        <v>0.112143913693723</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.1109083137807119</v>
+        <v>0.1126192371693122</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>0.1098612292187316</v>
+        <v>0.1116937572585446</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>0.1061737753226148</v>
+        <v>0.1081311899943935</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>0.1043714251893537</v>
+        <v>0.1063306484895723</v>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>0.1054490065950185</v>
+        <v>0.1076941589641601</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>0.1015638996974554</v>
+        <v>0.1036993869707909</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.09540986223907874</v>
+        <v>0.09723855695517467</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>0.09267983966532763</v>
+        <v>0.09457107828024443</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>0.09537130267986174</v>
+        <v>0.09731577569314356</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.09564884631561488</v>
+        <v>0.09771725601183623</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.1258376697771628</v>
+        <v>0.1245008214138825</v>
       </c>
       <c r="AS2" s="2" t="n">
-        <v>0.1378674332074378</v>
+        <v>0.1388971667758677</v>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>0.1385757258355903</v>
+        <v>0.1401547571838187</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>0.1383995784726253</v>
+        <v>0.1404334714915862</v>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>0.1369828107980583</v>
+        <v>0.1395015186843965</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>0.1311140987001803</v>
+        <v>0.1335548846893456</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>0.1314190984100373</v>
+        <v>0.134020191091326</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>0.1295355817339776</v>
+        <v>0.1320206968150494</v>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>0.1287857434078625</v>
+        <v>0.1315216990485362</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>0.123493463536691</v>
+        <v>0.1259577952231878</v>
       </c>
       <c r="BB2" s="2" t="n">
-        <v>0.1169335248358378</v>
+        <v>0.119240781519545</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>0.1145135947801047</v>
+        <v>0.1169452016539746</v>
       </c>
       <c r="BD2" s="2" t="n">
-        <v>0.1129332704641884</v>
+        <v>0.1152050512083833</v>
       </c>
       <c r="BE2" s="2" t="n">
-        <v>0.1159715429340147</v>
+        <v>0.1183595378343605</v>
       </c>
       <c r="BF2" s="2" t="n">
-        <v>0.1585804350778947</v>
+        <v>0.1582912966713796</v>
       </c>
       <c r="BG2" s="2" t="n">
-        <v>0.163795371299079</v>
+        <v>0.1658270626714736</v>
       </c>
       <c r="BH2" s="2" t="n">
-        <v>0.1627649764641955</v>
+        <v>0.1652577432915404</v>
       </c>
       <c r="BI2" s="2" t="n">
-        <v>0.1596361298662923</v>
+        <v>0.1628383447033666</v>
       </c>
       <c r="BJ2" s="2" t="n">
-        <v>0.1587384758234879</v>
+        <v>0.1620087442637345</v>
       </c>
       <c r="BK2" s="2" t="n">
-        <v>0.1507291563198711</v>
+        <v>0.1538437709555771</v>
       </c>
       <c r="BL2" s="2" t="n">
-        <v>0.149280852720206</v>
+        <v>0.1523612282127788</v>
       </c>
       <c r="BM2" s="2" t="n">
-        <v>0.1456825939413003</v>
+        <v>0.1487408747371129</v>
       </c>
       <c r="BN2" s="2" t="n">
-        <v>0.1443339860351504</v>
+        <v>0.1475729098828257</v>
       </c>
       <c r="BO2" s="2" t="n">
-        <v>0.1448879284952469</v>
+        <v>0.1480703881178685</v>
       </c>
       <c r="BP2" s="2" t="n">
-        <v>0.1338458990135015</v>
+        <v>0.1364783083476843</v>
       </c>
       <c r="BQ2" s="2" t="n">
-        <v>0.1319252393337821</v>
+        <v>0.1345443288925027</v>
       </c>
       <c r="BR2" s="2" t="n">
-        <v>0.1310918785537921</v>
+        <v>0.1335949811990701</v>
       </c>
       <c r="BS2" s="2" t="n">
-        <v>0.1303161674949395</v>
+        <v>0.1328095322313773</v>
       </c>
       <c r="BT2" s="2" t="n">
-        <v>0.2028970732857863</v>
+        <v>0.2050785287787597</v>
       </c>
       <c r="BU2" s="2" t="n">
-        <v>0.2019616015449929</v>
+        <v>0.2062278002695012</v>
       </c>
       <c r="BV2" s="2" t="n">
-        <v>0.198254332027557</v>
+        <v>0.2027010173417354</v>
       </c>
       <c r="BW2" s="2" t="n">
-        <v>0.1977345085653233</v>
+        <v>0.2029143645378518</v>
       </c>
       <c r="BX2" s="2" t="n">
-        <v>0.1911913464906102</v>
+        <v>0.195309394145239</v>
       </c>
       <c r="BY2" s="2" t="n">
-        <v>0.1858509082756082</v>
+        <v>0.1898494039139788</v>
       </c>
       <c r="BZ2" s="2" t="n">
-        <v>0.1813966568339907</v>
+        <v>0.1854987602461421</v>
       </c>
       <c r="CA2" s="2" t="n">
-        <v>0.1767876138154679</v>
+        <v>0.1808862117294484</v>
       </c>
       <c r="CB2" s="2" t="n">
-        <v>0.173641384628212</v>
+        <v>0.1774429725972767</v>
       </c>
       <c r="CC2" s="2" t="n">
-        <v>0.1679787922488898</v>
+        <v>0.1714360032068938</v>
       </c>
       <c r="CD2" s="2" t="n">
-        <v>0.1619490247409222</v>
+        <v>0.1651419114510891</v>
       </c>
       <c r="CE2" s="2" t="n">
-        <v>0.152765762249505</v>
+        <v>0.1555227825441713</v>
       </c>
       <c r="CF2" s="2" t="n">
-        <v>0.1525899584409843</v>
+        <v>0.1554454232570777</v>
       </c>
       <c r="CG2" s="2" t="n">
-        <v>0.1554149044605344</v>
+        <v>0.1582701904626935</v>
       </c>
       <c r="CH2" s="2" t="n">
-        <v>0.2326558072024756</v>
+        <v>0.2373699646347933</v>
       </c>
       <c r="CI2" s="2" t="n">
-        <v>0.2345709893384642</v>
+        <v>0.2407310399690337</v>
       </c>
       <c r="CJ2" s="2" t="n">
-        <v>0.2284798836931279</v>
+        <v>0.2344034864231637</v>
       </c>
       <c r="CK2" s="2" t="n">
-        <v>0.2215519480137394</v>
+        <v>0.2268753021685646</v>
       </c>
       <c r="CL2" s="2" t="n">
-        <v>0.2166462691469874</v>
+        <v>0.2218862475796427</v>
       </c>
       <c r="CM2" s="2" t="n">
-        <v>0.2071172909154483</v>
+        <v>0.2118472957326957</v>
       </c>
       <c r="CN2" s="2" t="n">
-        <v>0.2061585624632331</v>
+        <v>0.2108533483859988</v>
       </c>
       <c r="CO2" s="2" t="n">
-        <v>0.1982477472054485</v>
+        <v>0.2024902121054653</v>
       </c>
       <c r="CP2" s="2" t="n">
-        <v>0.1961096761077089</v>
+        <v>0.2004968946128531</v>
       </c>
       <c r="CQ2" s="2" t="n">
-        <v>0.1956262749868508</v>
+        <v>0.1997502272266027</v>
       </c>
       <c r="CR2" s="2" t="n">
-        <v>0.1777091797248957</v>
+        <v>0.1809491094009516</v>
       </c>
       <c r="CS2" s="2" t="n">
-        <v>0.1731421332168618</v>
+        <v>0.1761344577479402</v>
       </c>
       <c r="CT2" s="2" t="n">
-        <v>0.1721148124728365</v>
+        <v>0.174930487463252</v>
       </c>
       <c r="CU2" s="2" t="n">
-        <v>0.1790682442664351</v>
+        <v>0.1822373748003688</v>
       </c>
       <c r="CV2" s="2" t="n">
-        <v>0.2726582718658723</v>
+        <v>0.2792199944722928</v>
       </c>
       <c r="CW2" s="2" t="n">
-        <v>0.2617652918562935</v>
+        <v>0.2683258000180768</v>
       </c>
       <c r="CX2" s="2" t="n">
-        <v>0.2563819516514159</v>
+        <v>0.2627846937690593</v>
       </c>
       <c r="CY2" s="2" t="n">
-        <v>0.2528110526945433</v>
+        <v>0.2588628463890394</v>
       </c>
       <c r="CZ2" s="2" t="n">
-        <v>0.2417179599331573</v>
+        <v>0.2474686346875385</v>
       </c>
       <c r="DA2" s="2" t="n">
-        <v>0.236762971619653</v>
+        <v>0.2423232840397828</v>
       </c>
       <c r="DB2" s="2" t="n">
-        <v>0.2354665999063317</v>
+        <v>0.2403789986618821</v>
       </c>
       <c r="DC2" s="2" t="n">
-        <v>0.2283757736743119</v>
+        <v>0.2330442329705384</v>
       </c>
       <c r="DD2" s="2" t="n">
-        <v>0.2249702652758945</v>
+        <v>0.2290199538535465</v>
       </c>
       <c r="DE2" s="2" t="n">
-        <v>0.2178792298178166</v>
+        <v>0.2216553181747883</v>
       </c>
       <c r="DF2" s="2" t="n">
-        <v>0.2085600905482605</v>
+        <v>0.2119216360514</v>
       </c>
       <c r="DG2" s="2" t="n">
-        <v>0.2048139577442284</v>
+        <v>0.2081609932416554</v>
       </c>
       <c r="DH2" s="2" t="n">
-        <v>0.2018504212410842</v>
+        <v>0.2049000742645655</v>
       </c>
       <c r="DI2" s="2" t="n">
-        <v>0.2036743351157925</v>
+        <v>0.2066341900166295</v>
       </c>
       <c r="DJ2" s="2" t="n">
-        <v>0.2910593861421552</v>
+        <v>0.2982729712208715</v>
       </c>
       <c r="DK2" s="2" t="n">
-        <v>0.2834065916103801</v>
+        <v>0.2900009850127181</v>
       </c>
       <c r="DL2" s="2" t="n">
-        <v>0.2738382702552207</v>
+        <v>0.2803292272471317</v>
       </c>
       <c r="DM2" s="2" t="n">
-        <v>0.2705209010457476</v>
+        <v>0.2766841107224901</v>
       </c>
       <c r="DN2" s="2" t="n">
-        <v>0.2610748751564624</v>
+        <v>0.2666507406635882</v>
       </c>
       <c r="DO2" s="2" t="n">
-        <v>0.2595181199689796</v>
+        <v>0.2650522994776656</v>
       </c>
       <c r="DP2" s="2" t="n">
-        <v>0.2500389771510682</v>
+        <v>0.2544532598902306</v>
       </c>
       <c r="DQ2" s="2" t="n">
-        <v>0.242362247445329</v>
+        <v>0.2465056009969552</v>
       </c>
       <c r="DR2" s="2" t="n">
-        <v>0.2384614898779182</v>
+        <v>0.24234829013727</v>
       </c>
       <c r="DS2" s="2" t="n">
-        <v>0.2333005858817032</v>
+        <v>0.2368238872148922</v>
       </c>
       <c r="DT2" s="2" t="n">
-        <v>0.2269154814244581</v>
+        <v>0.2302118343473745</v>
       </c>
       <c r="DU2" s="2" t="n">
-        <v>0.2227316879835113</v>
+        <v>0.2257852488365157</v>
       </c>
       <c r="DV2" s="2" t="n">
-        <v>0.22518553294322</v>
+        <v>0.2280020684756945</v>
       </c>
       <c r="DW2" s="2" t="n">
-        <v>0.2265275576831135</v>
+        <v>0.229465601009253</v>
       </c>
       <c r="DX2" s="2" t="n">
-        <v>0.3037059318219613</v>
+        <v>0.3103415530120324</v>
       </c>
       <c r="DY2" s="2" t="n">
-        <v>0.2915273671369424</v>
+        <v>0.2977044125418534</v>
       </c>
       <c r="DZ2" s="2" t="n">
-        <v>0.2886402718158145</v>
+        <v>0.2945593110652347</v>
       </c>
       <c r="EA2" s="2" t="n">
-        <v>0.2776642418613678</v>
+        <v>0.2831329009642845</v>
       </c>
       <c r="EB2" s="2" t="n">
-        <v>0.2733038503349819</v>
+        <v>0.2780445169330635</v>
       </c>
       <c r="EC2" s="2" t="n">
-        <v>0.2658669779372098</v>
+        <v>0.2704373130869748</v>
       </c>
       <c r="ED2" s="2" t="n">
-        <v>0.2607353477520796</v>
+        <v>0.264777053032622</v>
       </c>
       <c r="EE2" s="2" t="n">
-        <v>0.2569183470705533</v>
+        <v>0.2607080550888562</v>
       </c>
       <c r="EF2" s="2" t="n">
-        <v>0.2540058396508554</v>
+        <v>0.2577049337079386</v>
       </c>
       <c r="EG2" s="2" t="n">
-        <v>0.2508513258253514</v>
+        <v>0.2542995625590264</v>
       </c>
       <c r="EH2" s="2" t="n">
-        <v>0.2361497202137611</v>
+        <v>0.2391393141070507</v>
       </c>
       <c r="EI2" s="2" t="n">
-        <v>0.2377404236728622</v>
+        <v>0.2402992622489406</v>
       </c>
       <c r="EJ2" s="2" t="n">
-        <v>0.2365834525826724</v>
+        <v>0.2390055283013137</v>
       </c>
       <c r="EK2" s="2" t="n">
-        <v>0.2389715656115778</v>
+        <v>0.2415759905650385</v>
       </c>
       <c r="EL2" s="2" t="n">
-        <v>0.307133403864763</v>
+        <v>0.3127977822693803</v>
       </c>
       <c r="EM2" s="2" t="n">
-        <v>0.2990689451255857</v>
+        <v>0.3040332893290578</v>
       </c>
       <c r="EN2" s="2" t="n">
-        <v>0.2921707583553806</v>
+        <v>0.2965816063768879</v>
       </c>
       <c r="EO2" s="2" t="n">
-        <v>0.2828447249992933</v>
+        <v>0.2867906120880689</v>
       </c>
       <c r="EP2" s="2" t="n">
-        <v>0.2852953704397844</v>
+        <v>0.2892123194735216</v>
       </c>
       <c r="EQ2" s="2" t="n">
-        <v>0.2724064551448885</v>
+        <v>0.2757285349226061</v>
       </c>
       <c r="ER2" s="2" t="n">
-        <v>0.2727721903790541</v>
+        <v>0.2761130605210371</v>
       </c>
       <c r="ES2" s="2" t="n">
-        <v>0.2638802994930796</v>
+        <v>0.2666588556909613</v>
       </c>
       <c r="ET2" s="2" t="n">
-        <v>0.2661409094223919</v>
+        <v>0.2689295760581436</v>
       </c>
       <c r="EU2" s="2" t="n">
-        <v>0.2639278601287403</v>
+        <v>0.2666246648310222</v>
       </c>
       <c r="EV2" s="2" t="n">
-        <v>0.2592851561608392</v>
+        <v>0.2618120801749307</v>
       </c>
       <c r="EW2" s="2" t="n">
-        <v>0.2570490216315529</v>
+        <v>0.2593172838390609</v>
       </c>
       <c r="EX2" s="2" t="n">
-        <v>0.2556176849808897</v>
+        <v>0.2577908815052714</v>
       </c>
       <c r="EY2" s="2" t="n">
-        <v>0.2684189302947192</v>
+        <v>0.2706555051829486</v>
       </c>
       <c r="EZ2" s="2" t="n">
-        <v>0.2980383282687089</v>
+        <v>0.3010101115490815</v>
       </c>
       <c r="FA2" s="2" t="n">
-        <v>0.297953541024723</v>
+        <v>0.3007406542144203</v>
       </c>
       <c r="FB2" s="2" t="n">
-        <v>0.2860148449726985</v>
+        <v>0.2885476623960421</v>
       </c>
       <c r="FC2" s="2" t="n">
-        <v>0.2875067214987435</v>
+        <v>0.2899639006278671</v>
       </c>
       <c r="FD2" s="2" t="n">
-        <v>0.2770657373485639</v>
+        <v>0.2793552411613539</v>
       </c>
       <c r="FE2" s="2" t="n">
-        <v>0.278248549290096</v>
+        <v>0.28050777394334</v>
       </c>
       <c r="FF2" s="2" t="n">
-        <v>0.2778056597761299</v>
+        <v>0.279973145430484</v>
       </c>
       <c r="FG2" s="2" t="n">
-        <v>0.2743484901669388</v>
+        <v>0.2764969470384483</v>
       </c>
       <c r="FH2" s="2" t="n">
-        <v>0.2697605549859765</v>
+        <v>0.2718184202480081</v>
       </c>
       <c r="FI2" s="2" t="n">
-        <v>0.2684342854394446</v>
+        <v>0.2706016071810255</v>
       </c>
       <c r="FJ2" s="2" t="n">
-        <v>0.2700656719444282</v>
+        <v>0.272302015864659</v>
       </c>
       <c r="FK2" s="2" t="n">
-        <v>0.2701108124879981</v>
+        <v>0.2720578876165534</v>
       </c>
       <c r="FL2" s="2" t="n">
-        <v>0.279062820800466</v>
+        <v>0.2808214036904997</v>
       </c>
       <c r="FM2" s="2" t="n">
-        <v>0.289507651440261</v>
+        <v>0.2913180829206687</v>
       </c>
       <c r="FN2" s="2" t="n">
-        <v>0.2993684328977979</v>
+        <v>0.3015836842243588</v>
       </c>
       <c r="FO2" s="2" t="n">
-        <v>0.2987075644145912</v>
+        <v>0.300941747666449</v>
       </c>
       <c r="FP2" s="2" t="n">
-        <v>0.2903371596555052</v>
+        <v>0.2924362415293989</v>
       </c>
       <c r="FQ2" s="2" t="n">
-        <v>0.2880232732334984</v>
+        <v>0.29013006645831</v>
       </c>
       <c r="FR2" s="2" t="n">
-        <v>0.2943991400997871</v>
+        <v>0.2966451846759551</v>
       </c>
       <c r="FS2" s="2" t="n">
-        <v>0.2916134147680282</v>
+        <v>0.2941077573931693</v>
       </c>
       <c r="FT2" s="2" t="n">
-        <v>0.2924656776305541</v>
+        <v>0.2949138862606391</v>
       </c>
       <c r="FU2" s="2" t="n">
-        <v>0.2907120154496159</v>
+        <v>0.2930896521802868</v>
       </c>
       <c r="FV2" s="2" t="n">
-        <v>0.2923911867472699</v>
+        <v>0.294837361368852</v>
       </c>
       <c r="FW2" s="2" t="n">
-        <v>0.2929473645870794</v>
+        <v>0.2955710492913831</v>
       </c>
       <c r="FX2" s="2" t="n">
-        <v>0.2904204898768871</v>
+        <v>0.2928468012505977</v>
       </c>
       <c r="FY2" s="2" t="n">
-        <v>0.2997431986204789</v>
+        <v>0.3022810824386285</v>
       </c>
       <c r="FZ2" s="2" t="n">
-        <v>0.3048064342601922</v>
+        <v>0.3071558556421426</v>
       </c>
       <c r="GA2" s="2" t="n">
-        <v>0.3198519581276059</v>
+        <v>0.3223954447823644</v>
       </c>
       <c r="GB2" s="2" t="n">
-        <v>0.3199206903278554</v>
+        <v>0.3234621077477658</v>
       </c>
       <c r="GC2" s="2" t="n">
-        <v>0.3210411038149929</v>
+        <v>0.3247657831658459</v>
       </c>
       <c r="GD2" s="2" t="n">
-        <v>0.3232739862792653</v>
+        <v>0.3269912299506825</v>
       </c>
       <c r="GE2" s="2" t="n">
-        <v>0.3234617652924993</v>
+        <v>0.3273483457597234</v>
       </c>
       <c r="GF2" s="2" t="n">
-        <v>0.3208973570768664</v>
+        <v>0.3248665272300074</v>
       </c>
       <c r="GG2" s="2" t="n">
-        <v>0.3187453620206149</v>
+        <v>0.3225237228046687</v>
       </c>
       <c r="GH2" s="2" t="n">
-        <v>0.3149477221012649</v>
+        <v>0.3188903681874808</v>
       </c>
       <c r="GI2" s="2" t="n">
-        <v>0.3138966120148088</v>
+        <v>0.3177545449996377</v>
       </c>
       <c r="GJ2" s="2" t="n">
-        <v>0.3153083452709063</v>
+        <v>0.3188685232527598</v>
       </c>
       <c r="GK2" s="2" t="n">
-        <v>0.3189419535753148</v>
+        <v>0.3228446421977895</v>
       </c>
       <c r="GL2" s="2" t="n">
-        <v>0.3235170207581931</v>
+        <v>0.3271425626836234</v>
       </c>
       <c r="GM2" s="2" t="n">
-        <v>0.3281024104377023</v>
+        <v>0.3314688509722939</v>
       </c>
       <c r="GN2" s="2" t="n">
-        <v>0.3432415275392958</v>
+        <v>0.3464334903774687</v>
       </c>
       <c r="GO2" s="2" t="n">
-        <v>0.3531394789729405</v>
+        <v>0.3563650960836697</v>
       </c>
       <c r="GP2" s="2" t="n">
-        <v>0.3478785271510793</v>
+        <v>0.3515997345313741</v>
       </c>
       <c r="GQ2" s="2" t="n">
-        <v>0.3427011341844254</v>
+        <v>0.3460974813495331</v>
       </c>
       <c r="GR2" s="2" t="n">
-        <v>0.3428398899270828</v>
+        <v>0.3466946862174804</v>
       </c>
       <c r="GS2" s="2" t="n">
-        <v>0.3408567943395481</v>
+        <v>0.3442706950725421</v>
       </c>
       <c r="GT2" s="2" t="n">
-        <v>0.3426868541219573</v>
+        <v>0.3464627562144141</v>
       </c>
       <c r="GU2" s="2" t="n">
-        <v>0.336742839329201</v>
+        <v>0.3404361889886439</v>
       </c>
       <c r="GV2" s="2" t="n">
-        <v>0.3424141738087506</v>
+        <v>0.3462017137080998</v>
       </c>
       <c r="GW2" s="2" t="n">
-        <v>0.3368172787651424</v>
+        <v>0.3405924507007008</v>
       </c>
       <c r="GX2" s="2" t="n">
-        <v>0.3384387814499383</v>
+        <v>0.3422356420256143</v>
       </c>
       <c r="GY2" s="2" t="n">
-        <v>0.3391167522361842</v>
+        <v>0.3428422213485804</v>
       </c>
       <c r="GZ2" s="2" t="n">
-        <v>0.3505569451893402</v>
+        <v>0.3538482242668701</v>
       </c>
       <c r="HA2" s="2" t="n">
-        <v>0.3633005379001412</v>
+        <v>0.3666541261832032</v>
       </c>
       <c r="HB2" s="2" t="n">
-        <v>0.3761819032105005</v>
+        <v>0.3799481418999232</v>
       </c>
       <c r="HC2" s="2" t="n">
-        <v>0.3673004158049784</v>
+        <v>0.3698693461924754</v>
       </c>
       <c r="HD2" s="2" t="n">
-        <v>0.3598024156363583</v>
+        <v>0.364063052502451</v>
       </c>
       <c r="HE2" s="2" t="n">
-        <v>0.3535362041076392</v>
+        <v>0.3571252381881446</v>
       </c>
       <c r="HF2" s="2" t="n">
-        <v>0.3562420365930886</v>
+        <v>0.3597086948872895</v>
       </c>
       <c r="HG2" s="2" t="n">
-        <v>0.3638368006492321</v>
+        <v>0.3677590768480961</v>
       </c>
       <c r="HH2" s="2" t="n">
-        <v>0.3633983680011476</v>
+        <v>0.3675282173754418</v>
       </c>
       <c r="HI2" s="2" t="n">
-        <v>0.3623787527086561</v>
+        <v>0.3665095036032026</v>
       </c>
       <c r="HJ2" s="2" t="n">
-        <v>0.3656615505341159</v>
+        <v>0.370308336091386</v>
       </c>
       <c r="HK2" s="2" t="n">
-        <v>0.3600596357109312</v>
+        <v>0.3645249400260214</v>
       </c>
       <c r="HL2" s="2" t="n">
-        <v>0.3630113521952946</v>
+        <v>0.3677304679889996</v>
       </c>
       <c r="HM2" s="2" t="n">
-        <v>0.3614902964108357</v>
+        <v>0.3663827946656117</v>
       </c>
       <c r="HN2" s="2" t="n">
-        <v>0.382178326604493</v>
+        <v>0.3868151730872467</v>
       </c>
       <c r="HO2" s="2" t="n">
-        <v>0.395227534869986</v>
+        <v>0.3999272344506554</v>
       </c>
       <c r="HP2" s="2" t="n">
-        <v>0.3697016403174691</v>
+        <v>0.3727281779146485</v>
       </c>
       <c r="HQ2" s="2" t="n">
-        <v>0.3541566264011627</v>
+        <v>0.3560318108775383</v>
       </c>
       <c r="HR2" s="3" t="n">
         <v>55511</v>
@@ -2191,676 +2191,676 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.02838799634529712</v>
+        <v>0.02843674828811051</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.03792388290194198</v>
+        <v>0.03788638506112024</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.04022006958147284</v>
+        <v>0.04029648925533291</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.04183899155387345</v>
+        <v>0.04209526451805297</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.04226155528550224</v>
+        <v>0.0426847193924077</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.04138671121112462</v>
+        <v>0.04199077727756854</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.0407692825054915</v>
+        <v>0.04150161404220176</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.04048257082576622</v>
+        <v>0.04130948934579958</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.04067552771360909</v>
+        <v>0.0415499231958512</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.03990652822867559</v>
+        <v>0.04076629170194791</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.03873312613907671</v>
+        <v>0.0396432238722167</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.03709049748615836</v>
+        <v>0.03783264795677279</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.03696047131335977</v>
+        <v>0.03775547992801908</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.03744560473241761</v>
+        <v>0.03822128467836335</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.05558588789286947</v>
+        <v>0.05519537781807517</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.06855545040563232</v>
+        <v>0.06835273500875122</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.07195026666839949</v>
+        <v>0.07234334626217714</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.07267617358916102</v>
+        <v>0.07346345595174132</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.07405093869943781</v>
+        <v>0.07506364210326834</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.07094957092099777</v>
+        <v>0.07211234578185668</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.07204718822090286</v>
+        <v>0.07340834224073547</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.07125415582048748</v>
+        <v>0.07268889736223076</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.07110952298142845</v>
+        <v>0.07266522656180793</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.07051563299234385</v>
+        <v>0.07208054362769599</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.06699755370636615</v>
+        <v>0.06859076444079312</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.06380254821404584</v>
+        <v>0.06510351085588105</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.06378398184205225</v>
+        <v>0.06517228670890263</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.06488348616775948</v>
+        <v>0.06619588079419809</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.08983945374104191</v>
+        <v>0.08898666587385345</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>0.1037370394167307</v>
+        <v>0.1037653460350636</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>0.1044766052885218</v>
+        <v>0.1055133237762614</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0.1060054356677105</v>
+        <v>0.1074837016386558</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>0.1061382850016743</v>
+        <v>0.1079191879685313</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>0.1052256047474397</v>
+        <v>0.1071085769431842</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>0.1017368117982911</v>
+        <v>0.1037123984361457</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>0.1002362524274371</v>
+        <v>0.1021863320026181</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>0.101047969633903</v>
+        <v>0.1032682184373993</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>0.09751723876226648</v>
+        <v>0.09962283616889223</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.09195290065138306</v>
+        <v>0.09373904510168996</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>0.08951855549984937</v>
+        <v>0.0913289534526444</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>0.09208027923545399</v>
+        <v>0.0939397597505764</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.09249745925294563</v>
+        <v>0.09444794861005947</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.1212286035782091</v>
+        <v>0.120115803486704</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>0.1316230187653774</v>
+        <v>0.132857809075641</v>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>0.1322642421797413</v>
+        <v>0.1340194909349579</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>0.1325986005698237</v>
+        <v>0.1347519673739467</v>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>0.1311121821423941</v>
+        <v>0.1336850278099947</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>0.1257170007181676</v>
+        <v>0.1281830069226535</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>0.1261616741120641</v>
+        <v>0.1287620105594223</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>0.1246268301566813</v>
+        <v>0.127104042034385</v>
       </c>
       <c r="AZ3" s="2" t="n">
-        <v>0.1236788115228916</v>
+        <v>0.1263828991677071</v>
       </c>
       <c r="BA3" s="2" t="n">
-        <v>0.1189433255453215</v>
+        <v>0.1213642203469382</v>
       </c>
       <c r="BB3" s="2" t="n">
-        <v>0.1130133775520261</v>
+        <v>0.115258097787493</v>
       </c>
       <c r="BC3" s="2" t="n">
-        <v>0.1109115405781936</v>
+        <v>0.1132246943964433</v>
       </c>
       <c r="BD3" s="2" t="n">
-        <v>0.109434225381599</v>
+        <v>0.1115865863573413</v>
       </c>
       <c r="BE3" s="2" t="n">
-        <v>0.1124702390766032</v>
+        <v>0.1147163190430291</v>
       </c>
       <c r="BF3" s="2" t="n">
-        <v>0.1528462592850969</v>
+        <v>0.152831831235771</v>
       </c>
       <c r="BG3" s="2" t="n">
-        <v>0.156842218717246</v>
+        <v>0.1590628717147397</v>
       </c>
       <c r="BH3" s="2" t="n">
-        <v>0.1557986060833528</v>
+        <v>0.1584400902247026</v>
       </c>
       <c r="BI3" s="2" t="n">
-        <v>0.1524698567227703</v>
+        <v>0.1557629798189979</v>
       </c>
       <c r="BJ3" s="2" t="n">
-        <v>0.1521261848148142</v>
+        <v>0.1554112128552233</v>
       </c>
       <c r="BK3" s="2" t="n">
-        <v>0.1446704486715206</v>
+        <v>0.1477838563131699</v>
       </c>
       <c r="BL3" s="2" t="n">
-        <v>0.1435122030737225</v>
+        <v>0.1465655962886635</v>
       </c>
       <c r="BM3" s="2" t="n">
-        <v>0.1403488634516454</v>
+        <v>0.1433509407927251</v>
       </c>
       <c r="BN3" s="2" t="n">
-        <v>0.138785972317342</v>
+        <v>0.1419671765171329</v>
       </c>
       <c r="BO3" s="2" t="n">
-        <v>0.139616557672466</v>
+        <v>0.1427213114647519</v>
       </c>
       <c r="BP3" s="2" t="n">
-        <v>0.1295445420774233</v>
+        <v>0.1320819043549311</v>
       </c>
       <c r="BQ3" s="2" t="n">
-        <v>0.1281423380078396</v>
+        <v>0.1306269166471085</v>
       </c>
       <c r="BR3" s="2" t="n">
-        <v>0.1273514255323591</v>
+        <v>0.1297241709568681</v>
       </c>
       <c r="BS3" s="2" t="n">
-        <v>0.1267704809426787</v>
+        <v>0.1291117178618434</v>
       </c>
       <c r="BT3" s="2" t="n">
-        <v>0.1941433198325971</v>
+        <v>0.196593886571441</v>
       </c>
       <c r="BU3" s="2" t="n">
-        <v>0.1928331347056201</v>
+        <v>0.1972555497535041</v>
       </c>
       <c r="BV3" s="2" t="n">
-        <v>0.1887301611768952</v>
+        <v>0.1932626660036793</v>
       </c>
       <c r="BW3" s="2" t="n">
-        <v>0.1881214362091595</v>
+        <v>0.1933096368319565</v>
       </c>
       <c r="BX3" s="2" t="n">
-        <v>0.1833790490080107</v>
+        <v>0.1874951855887164</v>
       </c>
       <c r="BY3" s="2" t="n">
-        <v>0.1785947756135622</v>
+        <v>0.1825523042345205</v>
       </c>
       <c r="BZ3" s="2" t="n">
-        <v>0.1741592120797979</v>
+        <v>0.178176237312113</v>
       </c>
       <c r="CA3" s="2" t="n">
-        <v>0.1701886710315441</v>
+        <v>0.1741810795455669</v>
       </c>
       <c r="CB3" s="2" t="n">
-        <v>0.1674690012136326</v>
+        <v>0.1711643848815785</v>
       </c>
       <c r="CC3" s="2" t="n">
-        <v>0.1622019764847179</v>
+        <v>0.1655807328290363</v>
       </c>
       <c r="CD3" s="2" t="n">
-        <v>0.1570309325765962</v>
+        <v>0.1600973717581625</v>
       </c>
       <c r="CE3" s="2" t="n">
-        <v>0.1486771248705909</v>
+        <v>0.1512930460699126</v>
       </c>
       <c r="CF3" s="2" t="n">
-        <v>0.148556990205829</v>
+        <v>0.151243896811788</v>
       </c>
       <c r="CG3" s="2" t="n">
-        <v>0.1515856394845125</v>
+        <v>0.1542582260745641</v>
       </c>
       <c r="CH3" s="2" t="n">
-        <v>0.2225091518313154</v>
+        <v>0.2273280569762453</v>
       </c>
       <c r="CI3" s="2" t="n">
-        <v>0.2229374152015944</v>
+        <v>0.2291480217468043</v>
       </c>
       <c r="CJ3" s="2" t="n">
-        <v>0.2179215237430582</v>
+        <v>0.2238185390762339</v>
       </c>
       <c r="CK3" s="2" t="n">
-        <v>0.2119495402801185</v>
+        <v>0.2172468844580799</v>
       </c>
       <c r="CL3" s="2" t="n">
-        <v>0.2075403903397307</v>
+        <v>0.2127091337712989</v>
       </c>
       <c r="CM3" s="2" t="n">
-        <v>0.1991050313613769</v>
+        <v>0.2037252704999801</v>
       </c>
       <c r="CN3" s="2" t="n">
-        <v>0.1986464971484413</v>
+        <v>0.2032182032050362</v>
       </c>
       <c r="CO3" s="2" t="n">
-        <v>0.1912150544097638</v>
+        <v>0.1953535464575505</v>
       </c>
       <c r="CP3" s="2" t="n">
-        <v>0.1891963279975404</v>
+        <v>0.193440875334834</v>
       </c>
       <c r="CQ3" s="2" t="n">
-        <v>0.1890564443704782</v>
+        <v>0.1930488454339205</v>
       </c>
       <c r="CR3" s="2" t="n">
-        <v>0.1729517119481816</v>
+        <v>0.1760502109780564</v>
       </c>
       <c r="CS3" s="2" t="n">
-        <v>0.169044233194722</v>
+        <v>0.1718516827441586</v>
       </c>
       <c r="CT3" s="2" t="n">
-        <v>0.1683011100468459</v>
+        <v>0.1709357769069495</v>
       </c>
       <c r="CU3" s="2" t="n">
-        <v>0.1750250817802188</v>
+        <v>0.1779759177532432</v>
       </c>
       <c r="CV3" s="2" t="n">
-        <v>0.2608284489509282</v>
+        <v>0.2673290991481957</v>
       </c>
       <c r="CW3" s="2" t="n">
-        <v>0.2494599535617406</v>
+        <v>0.2559580258581216</v>
       </c>
       <c r="CX3" s="2" t="n">
-        <v>0.2459698071499722</v>
+        <v>0.2522601237316983</v>
       </c>
       <c r="CY3" s="2" t="n">
-        <v>0.2432776923438609</v>
+        <v>0.2491715523561538</v>
       </c>
       <c r="CZ3" s="2" t="n">
-        <v>0.2326384457786442</v>
+        <v>0.2382151271243454</v>
       </c>
       <c r="DA3" s="2" t="n">
-        <v>0.2281810795836515</v>
+        <v>0.233548209624774</v>
       </c>
       <c r="DB3" s="2" t="n">
-        <v>0.2274170647020495</v>
+        <v>0.2321709747071422</v>
       </c>
       <c r="DC3" s="2" t="n">
-        <v>0.2210712316498992</v>
+        <v>0.2255812692508933</v>
       </c>
       <c r="DD3" s="2" t="n">
-        <v>0.2187106417999723</v>
+        <v>0.2225892017171839</v>
       </c>
       <c r="DE3" s="2" t="n">
-        <v>0.2121884013931025</v>
+        <v>0.2157832022229899</v>
       </c>
       <c r="DF3" s="2" t="n">
-        <v>0.2040046499181665</v>
+        <v>0.2071899184096731</v>
       </c>
       <c r="DG3" s="2" t="n">
-        <v>0.2003654110784951</v>
+        <v>0.2035073544438306</v>
       </c>
       <c r="DH3" s="2" t="n">
-        <v>0.1979657873414563</v>
+        <v>0.2008102774523304</v>
       </c>
       <c r="DI3" s="2" t="n">
-        <v>0.2000398840680069</v>
+        <v>0.2027595210745281</v>
       </c>
       <c r="DJ3" s="2" t="n">
-        <v>0.2790540835018896</v>
+        <v>0.2860976724084162</v>
       </c>
       <c r="DK3" s="2" t="n">
-        <v>0.2729736750941847</v>
+        <v>0.2793693801384542</v>
       </c>
       <c r="DL3" s="2" t="n">
-        <v>0.2635861154596566</v>
+        <v>0.2698711607556104</v>
       </c>
       <c r="DM3" s="2" t="n">
-        <v>0.260942693937004</v>
+        <v>0.2668962964298133</v>
       </c>
       <c r="DN3" s="2" t="n">
-        <v>0.2523648955277578</v>
+        <v>0.2577479549101964</v>
       </c>
       <c r="DO3" s="2" t="n">
-        <v>0.2514353799575023</v>
+        <v>0.2567466939740829</v>
       </c>
       <c r="DP3" s="2" t="n">
-        <v>0.2431964166392969</v>
+        <v>0.2474404424359487</v>
       </c>
       <c r="DQ3" s="2" t="n">
-        <v>0.2360670573749061</v>
+        <v>0.2400432832278724</v>
       </c>
       <c r="DR3" s="2" t="n">
-        <v>0.2330062833190449</v>
+        <v>0.2366903085768708</v>
       </c>
       <c r="DS3" s="2" t="n">
-        <v>0.2284927757366554</v>
+        <v>0.2318172695024864</v>
       </c>
       <c r="DT3" s="2" t="n">
-        <v>0.2226352199427696</v>
+        <v>0.2257213510088535</v>
       </c>
       <c r="DU3" s="2" t="n">
-        <v>0.2193200407936619</v>
+        <v>0.2221569722905205</v>
       </c>
       <c r="DV3" s="2" t="n">
-        <v>0.221746290938136</v>
+        <v>0.2243407581906289</v>
       </c>
       <c r="DW3" s="2" t="n">
-        <v>0.2232423665953275</v>
+        <v>0.2259176540208455</v>
       </c>
       <c r="DX3" s="2" t="n">
-        <v>0.2930082139279788</v>
+        <v>0.2994268220570033</v>
       </c>
       <c r="DY3" s="2" t="n">
-        <v>0.2815832146211895</v>
+        <v>0.2875483282610211</v>
       </c>
       <c r="DZ3" s="2" t="n">
-        <v>0.2793017680717378</v>
+        <v>0.2849787305069833</v>
       </c>
       <c r="EA3" s="2" t="n">
-        <v>0.2692407649364147</v>
+        <v>0.2744970824923191</v>
       </c>
       <c r="EB3" s="2" t="n">
-        <v>0.2660904247432101</v>
+        <v>0.2706220764785159</v>
       </c>
       <c r="EC3" s="2" t="n">
-        <v>0.2592112311578935</v>
+        <v>0.2635658161200231</v>
       </c>
       <c r="ED3" s="2" t="n">
-        <v>0.2548273519120231</v>
+        <v>0.2586624600431934</v>
       </c>
       <c r="EE3" s="2" t="n">
-        <v>0.2517493141375493</v>
+        <v>0.2553203625164936</v>
       </c>
       <c r="EF3" s="2" t="n">
-        <v>0.2490517683905138</v>
+        <v>0.2525440119784845</v>
       </c>
       <c r="EG3" s="2" t="n">
-        <v>0.2461535832715074</v>
+        <v>0.2493977635037939</v>
       </c>
       <c r="EH3" s="2" t="n">
-        <v>0.2322366630347933</v>
+        <v>0.2349998971136774</v>
       </c>
       <c r="EI3" s="2" t="n">
-        <v>0.2344186217453101</v>
+        <v>0.2367550604905704</v>
       </c>
       <c r="EJ3" s="2" t="n">
-        <v>0.2339973773662964</v>
+        <v>0.2361783187692086</v>
       </c>
       <c r="EK3" s="2" t="n">
-        <v>0.236183557726472</v>
+        <v>0.2385334671214515</v>
       </c>
       <c r="EL3" s="2" t="n">
-        <v>0.2986423626300413</v>
+        <v>0.3040600299593527</v>
       </c>
       <c r="EM3" s="2" t="n">
-        <v>0.2922151532013216</v>
+        <v>0.2968940284092226</v>
       </c>
       <c r="EN3" s="2" t="n">
-        <v>0.2861992134849926</v>
+        <v>0.290356510798206</v>
       </c>
       <c r="EO3" s="2" t="n">
-        <v>0.2776295571622502</v>
+        <v>0.281340229421581</v>
       </c>
       <c r="EP3" s="2" t="n">
-        <v>0.2802546624316697</v>
+        <v>0.2839315686597352</v>
       </c>
       <c r="EQ3" s="2" t="n">
-        <v>0.2679879909727644</v>
+        <v>0.2710905915472578</v>
       </c>
       <c r="ER3" s="2" t="n">
-        <v>0.2679775954015485</v>
+        <v>0.2711107508070699</v>
       </c>
       <c r="ES3" s="2" t="n">
-        <v>0.2599540112578825</v>
+        <v>0.2624993493819193</v>
       </c>
       <c r="ET3" s="2" t="n">
-        <v>0.2624168664181009</v>
+        <v>0.2649944469296708</v>
       </c>
       <c r="EU3" s="2" t="n">
-        <v>0.2606256091228372</v>
+        <v>0.263097693138445</v>
       </c>
       <c r="EV3" s="2" t="n">
-        <v>0.2564607039383143</v>
+        <v>0.2587477639606684</v>
       </c>
       <c r="EW3" s="2" t="n">
-        <v>0.2548708779582971</v>
+        <v>0.2569100459883207</v>
       </c>
       <c r="EX3" s="2" t="n">
-        <v>0.2538136478674315</v>
+        <v>0.2557309840035342</v>
       </c>
       <c r="EY3" s="2" t="n">
-        <v>0.2660423317479555</v>
+        <v>0.2680065730142061</v>
       </c>
       <c r="EZ3" s="2" t="n">
-        <v>0.2943967401313369</v>
+        <v>0.2971386208462303</v>
       </c>
       <c r="FA3" s="2" t="n">
-        <v>0.294446366924759</v>
+        <v>0.2970097987837754</v>
       </c>
       <c r="FB3" s="2" t="n">
-        <v>0.2829685143043261</v>
+        <v>0.2852961576391917</v>
       </c>
       <c r="FC3" s="2" t="n">
-        <v>0.284768247024496</v>
+        <v>0.2870017895264224</v>
       </c>
       <c r="FD3" s="2" t="n">
-        <v>0.2745511149563178</v>
+        <v>0.2766343047417983</v>
       </c>
       <c r="FE3" s="2" t="n">
-        <v>0.2758641603590878</v>
+        <v>0.2778909939529332</v>
       </c>
       <c r="FF3" s="2" t="n">
-        <v>0.2754645268434304</v>
+        <v>0.2774204830640573</v>
       </c>
       <c r="FG3" s="2" t="n">
-        <v>0.2720551335156428</v>
+        <v>0.2739873521864878</v>
       </c>
       <c r="FH3" s="2" t="n">
-        <v>0.2674777667269776</v>
+        <v>0.2693251530871461</v>
       </c>
       <c r="FI3" s="2" t="n">
-        <v>0.2661270844717588</v>
+        <v>0.2680717158098783</v>
       </c>
       <c r="FJ3" s="2" t="n">
-        <v>0.2679216534391383</v>
+        <v>0.2699147582546214</v>
       </c>
       <c r="FK3" s="2" t="n">
-        <v>0.2685752322746303</v>
+        <v>0.2702702244592693</v>
       </c>
       <c r="FL3" s="2" t="n">
-        <v>0.2778134953735235</v>
+        <v>0.2793087151406172</v>
       </c>
       <c r="FM3" s="2" t="n">
-        <v>0.2882794494967513</v>
+        <v>0.289796238694673</v>
       </c>
       <c r="FN3" s="2" t="n">
-        <v>0.2966029805644831</v>
+        <v>0.2985914511188349</v>
       </c>
       <c r="FO3" s="2" t="n">
-        <v>0.2962160988654108</v>
+        <v>0.2982144786919566</v>
       </c>
       <c r="FP3" s="2" t="n">
-        <v>0.2879286595422499</v>
+        <v>0.2898037024575941</v>
       </c>
       <c r="FQ3" s="2" t="n">
-        <v>0.2858861190003162</v>
+        <v>0.2877466481846577</v>
       </c>
       <c r="FR3" s="2" t="n">
-        <v>0.291804483438781</v>
+        <v>0.2938130109560997</v>
       </c>
       <c r="FS3" s="2" t="n">
-        <v>0.2892331938436397</v>
+        <v>0.2914568196227916</v>
       </c>
       <c r="FT3" s="2" t="n">
-        <v>0.2898438341520416</v>
+        <v>0.2920194111369239</v>
       </c>
       <c r="FU3" s="2" t="n">
-        <v>0.288030112972964</v>
+        <v>0.2901447367579829</v>
       </c>
       <c r="FV3" s="2" t="n">
-        <v>0.2897738604947618</v>
+        <v>0.291938052992492</v>
       </c>
       <c r="FW3" s="2" t="n">
-        <v>0.2902652864956148</v>
+        <v>0.2925790941023119</v>
       </c>
       <c r="FX3" s="2" t="n">
-        <v>0.2882955402650007</v>
+        <v>0.290397661975778</v>
       </c>
       <c r="FY3" s="2" t="n">
-        <v>0.2979757970673439</v>
+        <v>0.3001534155113098</v>
       </c>
       <c r="FZ3" s="2" t="n">
-        <v>0.302841664856541</v>
+        <v>0.3048427045403598</v>
       </c>
       <c r="GA3" s="2" t="n">
-        <v>0.3176363612644903</v>
+        <v>0.3198208714955084</v>
       </c>
       <c r="GB3" s="2" t="n">
-        <v>0.3159097968310103</v>
+        <v>0.3191108121246085</v>
       </c>
       <c r="GC3" s="2" t="n">
-        <v>0.3170001408773636</v>
+        <v>0.3203674084264015</v>
       </c>
       <c r="GD3" s="2" t="n">
-        <v>0.3187781192244749</v>
+        <v>0.3221430100383024</v>
       </c>
       <c r="GE3" s="2" t="n">
-        <v>0.3189131915707379</v>
+        <v>0.3224291950602323</v>
       </c>
       <c r="GF3" s="2" t="n">
-        <v>0.3165974990698076</v>
+        <v>0.3201824725838877</v>
       </c>
       <c r="GG3" s="2" t="n">
-        <v>0.3146633162101719</v>
+        <v>0.3180552228292439</v>
       </c>
       <c r="GH3" s="2" t="n">
-        <v>0.3108529229633772</v>
+        <v>0.3143861745469534</v>
       </c>
       <c r="GI3" s="2" t="n">
-        <v>0.3104387858192372</v>
+        <v>0.3138250970522809</v>
       </c>
       <c r="GJ3" s="2" t="n">
-        <v>0.3114280819459437</v>
+        <v>0.3145993619723796</v>
       </c>
       <c r="GK3" s="2" t="n">
-        <v>0.3151287330093213</v>
+        <v>0.3185770330729313</v>
       </c>
       <c r="GL3" s="2" t="n">
-        <v>0.3202056730844503</v>
+        <v>0.3233827124096876</v>
       </c>
       <c r="GM3" s="2" t="n">
-        <v>0.325164752020808</v>
+        <v>0.3280822727226932</v>
       </c>
       <c r="GN3" s="2" t="n">
-        <v>0.3405657797338525</v>
+        <v>0.3433052092077294</v>
       </c>
       <c r="GO3" s="2" t="n">
-        <v>0.3498553820714532</v>
+        <v>0.3526272960767328</v>
       </c>
       <c r="GP3" s="2" t="n">
-        <v>0.344178266741438</v>
+        <v>0.3474614321366978</v>
       </c>
       <c r="GQ3" s="2" t="n">
-        <v>0.3395714773931774</v>
+        <v>0.3425511880913051</v>
       </c>
       <c r="GR3" s="2" t="n">
-        <v>0.339434801329663</v>
+        <v>0.34287182866483</v>
       </c>
       <c r="GS3" s="2" t="n">
-        <v>0.3376050400133911</v>
+        <v>0.3406118037696663</v>
       </c>
       <c r="GT3" s="2" t="n">
-        <v>0.3391622304855721</v>
+        <v>0.3425139859258073</v>
       </c>
       <c r="GU3" s="2" t="n">
-        <v>0.3332908649786558</v>
+        <v>0.3365509782775488</v>
       </c>
       <c r="GV3" s="2" t="n">
-        <v>0.3388688202914374</v>
+        <v>0.3422090124305861</v>
       </c>
       <c r="GW3" s="2" t="n">
-        <v>0.3333794821927001</v>
+        <v>0.3367031414935042</v>
       </c>
       <c r="GX3" s="2" t="n">
-        <v>0.3349001276095637</v>
+        <v>0.3382203372915514</v>
       </c>
       <c r="GY3" s="2" t="n">
-        <v>0.3354882399048837</v>
+        <v>0.3387338394727739</v>
       </c>
       <c r="GZ3" s="2" t="n">
-        <v>0.347466371577796</v>
+        <v>0.3502878840981093</v>
       </c>
       <c r="HA3" s="2" t="n">
-        <v>0.3602134404222525</v>
+        <v>0.3630918381254232</v>
       </c>
       <c r="HB3" s="2" t="n">
-        <v>0.3732090583207497</v>
+        <v>0.3764559989931473</v>
       </c>
       <c r="HC3" s="2" t="n">
-        <v>0.3650377696955998</v>
+        <v>0.3672233602608044</v>
       </c>
       <c r="HD3" s="2" t="n">
-        <v>0.3566774009250885</v>
+        <v>0.360311183192659</v>
       </c>
       <c r="HE3" s="2" t="n">
-        <v>0.3506927117792953</v>
+        <v>0.3537278771488059</v>
       </c>
       <c r="HF3" s="2" t="n">
-        <v>0.3530344160418419</v>
+        <v>0.3559449555497078</v>
       </c>
       <c r="HG3" s="2" t="n">
-        <v>0.3604425286313661</v>
+        <v>0.3637920116445192</v>
       </c>
       <c r="HH3" s="2" t="n">
-        <v>0.3598116854618804</v>
+        <v>0.3633526483963744</v>
       </c>
       <c r="HI3" s="2" t="n">
-        <v>0.3586749319912998</v>
+        <v>0.3622556437732784</v>
       </c>
       <c r="HJ3" s="2" t="n">
-        <v>0.3617717906904969</v>
+        <v>0.365838779516295</v>
       </c>
       <c r="HK3" s="2" t="n">
-        <v>0.3559455327905243</v>
+        <v>0.3598151259339875</v>
       </c>
       <c r="HL3" s="2" t="n">
-        <v>0.358524806524342</v>
+        <v>0.362662128830975</v>
       </c>
       <c r="HM3" s="2" t="n">
-        <v>0.356502994499418</v>
+        <v>0.3608401413776605</v>
       </c>
       <c r="HN3" s="2" t="n">
-        <v>0.3785696239653219</v>
+        <v>0.3826140747848142</v>
       </c>
       <c r="HO3" s="2" t="n">
-        <v>0.3923139026257488</v>
+        <v>0.396427450129697</v>
       </c>
       <c r="HP3" s="2" t="n">
-        <v>0.367423394551692</v>
+        <v>0.3699945899156904</v>
       </c>
       <c r="HQ3" s="2" t="n">
-        <v>0.3525903415682343</v>
+        <v>0.354118463099244</v>
       </c>
       <c r="HR3" s="3" t="n">
         <v>55513</v>
@@ -2873,676 +2873,676 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.02926647725018748</v>
+        <v>0.02929720810118207</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.03761772450710657</v>
+        <v>0.03757861175294044</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03980352497294967</v>
+        <v>0.03988570860222403</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.04148331654415405</v>
+        <v>0.04174044073716676</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.04183653083146882</v>
+        <v>0.04225604415388179</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.04113907878863596</v>
+        <v>0.04173196339624904</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.04072059720176147</v>
+        <v>0.0414311367215483</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.04053575147517154</v>
+        <v>0.04133255009181926</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.04085053410514909</v>
+        <v>0.04168943781539518</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.04021125867739219</v>
+        <v>0.04103741537555951</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.03916767267464133</v>
+        <v>0.04003263292788001</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.03786184090194007</v>
+        <v>0.03855720638301869</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.03782899420886286</v>
+        <v>0.03857314050375469</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.03852517865891567</v>
+        <v>0.03924606982911935</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.0563817452139545</v>
+        <v>0.05599523144432788</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.06753347956993401</v>
+        <v>0.0673562190816623</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07086780831960697</v>
+        <v>0.07126776479927559</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.07174287265151821</v>
+        <v>0.07251354394465767</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.07332634300677005</v>
+        <v>0.07432192125109854</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.07073087719340659</v>
+        <v>0.07186268557865955</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.07184853744600726</v>
+        <v>0.07316662338469936</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.0715233775713783</v>
+        <v>0.07290342812624986</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.07135375287104551</v>
+        <v>0.0728549480037779</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.07086519302767982</v>
+        <v>0.07236396299642792</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.06761043857025166</v>
+        <v>0.06912425312387009</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.06508274595464121</v>
+        <v>0.06629963438237559</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>0.06515904025898075</v>
+        <v>0.06646642436996794</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>0.06651857910925978</v>
+        <v>0.06774376655245655</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.08864126421172418</v>
+        <v>0.08782786011357106</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>0.1012439421598664</v>
+        <v>0.1013151101057282</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.1022213842285723</v>
+        <v>0.103260064081654</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>0.1041434194530388</v>
+        <v>0.1056143652285476</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1049336735115476</v>
+        <v>0.1066818684295841</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>0.1044572561535227</v>
+        <v>0.1063008855584251</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>0.1013530533927824</v>
+        <v>0.1032674446869041</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>0.1004477930872413</v>
+        <v>0.1023210478632423</v>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>0.1011573688079998</v>
+        <v>0.1032909897108958</v>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>0.09795473841827057</v>
+        <v>0.09997376566629551</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.09288766766517356</v>
+        <v>0.09459430883257583</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>0.09111069439577721</v>
+        <v>0.09281747898685597</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>0.09388780738851489</v>
+        <v>0.09563760790666999</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.09455749220563707</v>
+        <v>0.09637387856258688</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.1184829589559568</v>
+        <v>0.1174531005903018</v>
       </c>
       <c r="AS4" s="2" t="n">
-        <v>0.1275733609614344</v>
+        <v>0.1288487066445322</v>
       </c>
       <c r="AT4" s="2" t="n">
-        <v>0.1288300939485096</v>
+        <v>0.1306059957131409</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>0.1298898100578472</v>
+        <v>0.1320324927293941</v>
       </c>
       <c r="AV4" s="2" t="n">
-        <v>0.1299696988981493</v>
+        <v>0.1324811778586634</v>
       </c>
       <c r="AW4" s="2" t="n">
-        <v>0.124828786163178</v>
+        <v>0.1272244998650222</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>0.125827656534079</v>
+        <v>0.1283444235441717</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>0.1248988206274191</v>
+        <v>0.1272932286150137</v>
       </c>
       <c r="AZ4" s="2" t="n">
-        <v>0.1238779262319958</v>
+        <v>0.1264806505904353</v>
       </c>
       <c r="BA4" s="2" t="n">
-        <v>0.1195951692747326</v>
+        <v>0.1219134137021751</v>
       </c>
       <c r="BB4" s="2" t="n">
-        <v>0.1140924376117962</v>
+        <v>0.1162319910394925</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>0.1128087582863981</v>
+        <v>0.1149801685340817</v>
       </c>
       <c r="BD4" s="2" t="n">
-        <v>0.1116824368468084</v>
+        <v>0.1136903571418084</v>
       </c>
       <c r="BE4" s="2" t="n">
-        <v>0.1149870347471272</v>
+        <v>0.1170757360996042</v>
       </c>
       <c r="BF4" s="2" t="n">
-        <v>0.1476165439286384</v>
+        <v>0.1477037939527187</v>
       </c>
       <c r="BG4" s="2" t="n">
-        <v>0.1526472920740768</v>
+        <v>0.1548789197767898</v>
       </c>
       <c r="BH4" s="2" t="n">
-        <v>0.1525733053158972</v>
+        <v>0.1552088140916083</v>
       </c>
       <c r="BI4" s="2" t="n">
-        <v>0.1497426001993724</v>
+        <v>0.1529860390988895</v>
       </c>
       <c r="BJ4" s="2" t="n">
-        <v>0.1510530765302635</v>
+        <v>0.1542330737359977</v>
       </c>
       <c r="BK4" s="2" t="n">
-        <v>0.1441186749659459</v>
+        <v>0.1471352660380284</v>
       </c>
       <c r="BL4" s="2" t="n">
-        <v>0.1432324055791272</v>
+        <v>0.1461722519457711</v>
       </c>
       <c r="BM4" s="2" t="n">
-        <v>0.1408728336985967</v>
+        <v>0.143748079806175</v>
       </c>
       <c r="BN4" s="2" t="n">
-        <v>0.1391877078638139</v>
+        <v>0.1422484697029653</v>
       </c>
       <c r="BO4" s="2" t="n">
-        <v>0.1402265988717575</v>
+        <v>0.1431913450787564</v>
       </c>
       <c r="BP4" s="2" t="n">
-        <v>0.1309221195238796</v>
+        <v>0.1333226220864025</v>
       </c>
       <c r="BQ4" s="2" t="n">
-        <v>0.1304517000380539</v>
+        <v>0.1327819231364512</v>
       </c>
       <c r="BR4" s="2" t="n">
-        <v>0.1299943718884208</v>
+        <v>0.1322197932574966</v>
       </c>
       <c r="BS4" s="2" t="n">
-        <v>0.129758597102356</v>
+        <v>0.1319391436244965</v>
       </c>
       <c r="BT4" s="2" t="n">
-        <v>0.1889731046018866</v>
+        <v>0.1914650965688494</v>
       </c>
       <c r="BU4" s="2" t="n">
-        <v>0.1888197358262171</v>
+        <v>0.1932016308915247</v>
       </c>
       <c r="BV4" s="2" t="n">
-        <v>0.186222022483949</v>
+        <v>0.1906593163412851</v>
       </c>
       <c r="BW4" s="2" t="n">
-        <v>0.1858041395010409</v>
+        <v>0.1908555362882075</v>
       </c>
       <c r="BX4" s="2" t="n">
-        <v>0.182618680769226</v>
+        <v>0.1866070361674041</v>
       </c>
       <c r="BY4" s="2" t="n">
-        <v>0.1787872132049392</v>
+        <v>0.182594567923386</v>
       </c>
       <c r="BZ4" s="2" t="n">
-        <v>0.1743874032837927</v>
+        <v>0.1782350917203009</v>
       </c>
       <c r="CA4" s="2" t="n">
-        <v>0.1710546291311873</v>
+        <v>0.1748627214571131</v>
       </c>
       <c r="CB4" s="2" t="n">
-        <v>0.1684960874205817</v>
+        <v>0.1720240416413535</v>
       </c>
       <c r="CC4" s="2" t="n">
-        <v>0.1633214711326778</v>
+        <v>0.1665638855773628</v>
       </c>
       <c r="CD4" s="2" t="n">
-        <v>0.1589241528599579</v>
+        <v>0.1618239933340866</v>
       </c>
       <c r="CE4" s="2" t="n">
-        <v>0.1515771066342916</v>
+        <v>0.1540325833057489</v>
       </c>
       <c r="CF4" s="2" t="n">
-        <v>0.1517339283803754</v>
+        <v>0.1542340116778664</v>
       </c>
       <c r="CG4" s="2" t="n">
-        <v>0.1553315478837955</v>
+        <v>0.1578113246238697</v>
       </c>
       <c r="CH4" s="2" t="n">
-        <v>0.219234978006195</v>
+        <v>0.2239547159233798</v>
       </c>
       <c r="CI4" s="2" t="n">
-        <v>0.2202745809352028</v>
+        <v>0.2263344622349369</v>
       </c>
       <c r="CJ4" s="2" t="n">
-        <v>0.2167820695406069</v>
+        <v>0.2224984231954684</v>
       </c>
       <c r="CK4" s="2" t="n">
-        <v>0.2114398223093832</v>
+        <v>0.2165747214785898</v>
       </c>
       <c r="CL4" s="2" t="n">
-        <v>0.2078399520622234</v>
+        <v>0.2128283579157333</v>
       </c>
       <c r="CM4" s="2" t="n">
-        <v>0.2001766430542161</v>
+        <v>0.2046019004985978</v>
       </c>
       <c r="CN4" s="2" t="n">
-        <v>0.1999173659861981</v>
+        <v>0.2042960125983655</v>
       </c>
       <c r="CO4" s="2" t="n">
-        <v>0.1927842090295267</v>
+        <v>0.196747191475482</v>
       </c>
       <c r="CP4" s="2" t="n">
-        <v>0.1907148151879804</v>
+        <v>0.1947569488769071</v>
       </c>
       <c r="CQ4" s="2" t="n">
-        <v>0.1905619525979475</v>
+        <v>0.1943601319263891</v>
       </c>
       <c r="CR4" s="2" t="n">
-        <v>0.1755507034876673</v>
+        <v>0.1784805847027628</v>
       </c>
       <c r="CS4" s="2" t="n">
-        <v>0.172745527556822</v>
+        <v>0.1753508242282126</v>
       </c>
       <c r="CT4" s="2" t="n">
-        <v>0.1723568642734842</v>
+        <v>0.1747973801791029</v>
       </c>
       <c r="CU4" s="2" t="n">
-        <v>0.1795231362757913</v>
+        <v>0.1822479402599565</v>
       </c>
       <c r="CV4" s="2" t="n">
-        <v>0.2602460081391742</v>
+        <v>0.2665253015869071</v>
       </c>
       <c r="CW4" s="2" t="n">
-        <v>0.249556193264122</v>
+        <v>0.2558346187192154</v>
       </c>
       <c r="CX4" s="2" t="n">
-        <v>0.2465794770965072</v>
+        <v>0.2526324666091891</v>
       </c>
       <c r="CY4" s="2" t="n">
-        <v>0.2450877958184424</v>
+        <v>0.2507217795795145</v>
       </c>
       <c r="CZ4" s="2" t="n">
-        <v>0.2345710007629635</v>
+        <v>0.2398779263875725</v>
       </c>
       <c r="DA4" s="2" t="n">
-        <v>0.2303194913592583</v>
+        <v>0.2354146714833028</v>
       </c>
       <c r="DB4" s="2" t="n">
-        <v>0.2296834824926819</v>
+        <v>0.2342076799221004</v>
       </c>
       <c r="DC4" s="2" t="n">
-        <v>0.2232423046401841</v>
+        <v>0.2275356793574197</v>
       </c>
       <c r="DD4" s="2" t="n">
-        <v>0.2216334549184907</v>
+        <v>0.2252877560850251</v>
       </c>
       <c r="DE4" s="2" t="n">
-        <v>0.2151992903863441</v>
+        <v>0.2185669043873798</v>
       </c>
       <c r="DF4" s="2" t="n">
-        <v>0.2077378437289471</v>
+        <v>0.2107252397009606</v>
       </c>
       <c r="DG4" s="2" t="n">
-        <v>0.204490006632668</v>
+        <v>0.2074196457038942</v>
       </c>
       <c r="DH4" s="2" t="n">
-        <v>0.2024970361501603</v>
+        <v>0.2051301421136288</v>
       </c>
       <c r="DI4" s="2" t="n">
-        <v>0.2055518792681748</v>
+        <v>0.2080396840088421</v>
       </c>
       <c r="DJ4" s="2" t="n">
-        <v>0.2812338882719922</v>
+        <v>0.2879725509917188</v>
       </c>
       <c r="DK4" s="2" t="n">
-        <v>0.2758851164131196</v>
+        <v>0.2819843069760831</v>
       </c>
       <c r="DL4" s="2" t="n">
-        <v>0.2658583258803191</v>
+        <v>0.2718400356884303</v>
       </c>
       <c r="DM4" s="2" t="n">
-        <v>0.2634605866988621</v>
+        <v>0.2691157077570877</v>
       </c>
       <c r="DN4" s="2" t="n">
-        <v>0.2554088393344376</v>
+        <v>0.260526699025819</v>
       </c>
       <c r="DO4" s="2" t="n">
-        <v>0.2542583913198292</v>
+        <v>0.259289507626611</v>
       </c>
       <c r="DP4" s="2" t="n">
-        <v>0.246445907617204</v>
+        <v>0.2504649892097638</v>
       </c>
       <c r="DQ4" s="2" t="n">
-        <v>0.2394593878602322</v>
+        <v>0.2432234621559914</v>
       </c>
       <c r="DR4" s="2" t="n">
-        <v>0.2368724240885228</v>
+        <v>0.2403179525361508</v>
       </c>
       <c r="DS4" s="2" t="n">
-        <v>0.2326873853108549</v>
+        <v>0.235794612695899</v>
       </c>
       <c r="DT4" s="2" t="n">
-        <v>0.227044534865935</v>
+        <v>0.229912587437947</v>
       </c>
       <c r="DU4" s="2" t="n">
-        <v>0.223906596523141</v>
+        <v>0.2265284148570052</v>
       </c>
       <c r="DV4" s="2" t="n">
-        <v>0.2271778088017124</v>
+        <v>0.2295520033641475</v>
       </c>
       <c r="DW4" s="2" t="n">
-        <v>0.2294033475610473</v>
+        <v>0.231829759517596</v>
       </c>
       <c r="DX4" s="2" t="n">
-        <v>0.2963162087044844</v>
+        <v>0.3024064175925383</v>
       </c>
       <c r="DY4" s="2" t="n">
-        <v>0.2846946835905531</v>
+        <v>0.2903517008215406</v>
       </c>
       <c r="DZ4" s="2" t="n">
-        <v>0.2829605451691637</v>
+        <v>0.2883108070958147</v>
       </c>
       <c r="EA4" s="2" t="n">
-        <v>0.2723721386093736</v>
+        <v>0.2773563795883298</v>
       </c>
       <c r="EB4" s="2" t="n">
-        <v>0.2698692621808054</v>
+        <v>0.2741460146527293</v>
       </c>
       <c r="EC4" s="2" t="n">
-        <v>0.2630446132446739</v>
+        <v>0.2671463925565692</v>
       </c>
       <c r="ED4" s="2" t="n">
-        <v>0.2589357477944282</v>
+        <v>0.2625292708497432</v>
       </c>
       <c r="EE4" s="2" t="n">
-        <v>0.2563189053927433</v>
+        <v>0.2596497731302749</v>
       </c>
       <c r="EF4" s="2" t="n">
-        <v>0.2531438497882933</v>
+        <v>0.2563976002913565</v>
       </c>
       <c r="EG4" s="2" t="n">
-        <v>0.2504227918225956</v>
+        <v>0.253440079523964</v>
       </c>
       <c r="EH4" s="2" t="n">
-        <v>0.2377606912779628</v>
+        <v>0.2402955836880027</v>
       </c>
       <c r="EI4" s="2" t="n">
-        <v>0.2400820418147963</v>
+        <v>0.242200357362501</v>
       </c>
       <c r="EJ4" s="2" t="n">
-        <v>0.2403808548839039</v>
+        <v>0.2423377796800084</v>
       </c>
       <c r="EK4" s="2" t="n">
-        <v>0.2427215713329137</v>
+        <v>0.2448366421527684</v>
       </c>
       <c r="EL4" s="2" t="n">
-        <v>0.3030463644053776</v>
+        <v>0.3081668504264194</v>
       </c>
       <c r="EM4" s="2" t="n">
-        <v>0.2974978266850731</v>
+        <v>0.3018615423337243</v>
       </c>
       <c r="EN4" s="2" t="n">
-        <v>0.2914153145521535</v>
+        <v>0.2952875526517285</v>
       </c>
       <c r="EO4" s="2" t="n">
-        <v>0.2828013426954529</v>
+        <v>0.2862532786423943</v>
       </c>
       <c r="EP4" s="2" t="n">
-        <v>0.2852506080880457</v>
+        <v>0.288669903041392</v>
       </c>
       <c r="EQ4" s="2" t="n">
-        <v>0.2730474014281749</v>
+        <v>0.2759193767308711</v>
       </c>
       <c r="ER4" s="2" t="n">
-        <v>0.2732074901361468</v>
+        <v>0.2761125311155322</v>
       </c>
       <c r="ES4" s="2" t="n">
-        <v>0.2660451763397094</v>
+        <v>0.2683548078959819</v>
       </c>
       <c r="ET4" s="2" t="n">
-        <v>0.2677903572368138</v>
+        <v>0.2701512376117222</v>
       </c>
       <c r="EU4" s="2" t="n">
-        <v>0.2664583112604806</v>
+        <v>0.2687095004625508</v>
       </c>
       <c r="EV4" s="2" t="n">
-        <v>0.2627913266842693</v>
+        <v>0.2648464166050285</v>
       </c>
       <c r="EW4" s="2" t="n">
-        <v>0.261284176583655</v>
+        <v>0.2631060968593432</v>
       </c>
       <c r="EX4" s="2" t="n">
-        <v>0.2608272948799244</v>
+        <v>0.2625143261191956</v>
       </c>
       <c r="EY4" s="2" t="n">
-        <v>0.2740272823982955</v>
+        <v>0.2757496256643058</v>
       </c>
       <c r="EZ4" s="2" t="n">
-        <v>0.2999356482049256</v>
+        <v>0.3024460319300919</v>
       </c>
       <c r="FA4" s="2" t="n">
-        <v>0.3002730535825254</v>
+        <v>0.302605964477873</v>
       </c>
       <c r="FB4" s="2" t="n">
-        <v>0.2884441931239958</v>
+        <v>0.2905638907544013</v>
       </c>
       <c r="FC4" s="2" t="n">
-        <v>0.2906476696527158</v>
+        <v>0.2926564281380331</v>
       </c>
       <c r="FD4" s="2" t="n">
-        <v>0.2804729284775567</v>
+        <v>0.2823522703779053</v>
       </c>
       <c r="FE4" s="2" t="n">
-        <v>0.2822056389153812</v>
+        <v>0.2840025028885219</v>
       </c>
       <c r="FF4" s="2" t="n">
-        <v>0.2816282638238553</v>
+        <v>0.2833816089557294</v>
       </c>
       <c r="FG4" s="2" t="n">
-        <v>0.2784352154425095</v>
+        <v>0.2801589743188332</v>
       </c>
       <c r="FH4" s="2" t="n">
-        <v>0.2737010793239577</v>
+        <v>0.2753439248949988</v>
       </c>
       <c r="FI4" s="2" t="n">
-        <v>0.2723191948424389</v>
+        <v>0.2740529598485043</v>
       </c>
       <c r="FJ4" s="2" t="n">
-        <v>0.2748507749538049</v>
+        <v>0.276621420333825</v>
       </c>
       <c r="FK4" s="2" t="n">
-        <v>0.2759867383060488</v>
+        <v>0.2774635700402292</v>
       </c>
       <c r="FL4" s="2" t="n">
-        <v>0.2860195799820766</v>
+        <v>0.2872843011372432</v>
       </c>
       <c r="FM4" s="2" t="n">
-        <v>0.2970536724276545</v>
+        <v>0.2983150706238749</v>
       </c>
       <c r="FN4" s="2" t="n">
-        <v>0.303891782512844</v>
+        <v>0.305657070925415</v>
       </c>
       <c r="FO4" s="2" t="n">
-        <v>0.303515488067375</v>
+        <v>0.3052800016195639</v>
       </c>
       <c r="FP4" s="2" t="n">
-        <v>0.2950859267609653</v>
+        <v>0.2967474211352406</v>
       </c>
       <c r="FQ4" s="2" t="n">
-        <v>0.2933382718763199</v>
+        <v>0.2949635713300552</v>
       </c>
       <c r="FR4" s="2" t="n">
-        <v>0.2990738059530139</v>
+        <v>0.3008554036865115</v>
       </c>
       <c r="FS4" s="2" t="n">
-        <v>0.2969961216480823</v>
+        <v>0.2989669492275805</v>
       </c>
       <c r="FT4" s="2" t="n">
-        <v>0.2976426592381861</v>
+        <v>0.2995590305241015</v>
       </c>
       <c r="FU4" s="2" t="n">
-        <v>0.2960048992583987</v>
+        <v>0.2978696156690356</v>
       </c>
       <c r="FV4" s="2" t="n">
-        <v>0.2982519151943347</v>
+        <v>0.3001487585085055</v>
       </c>
       <c r="FW4" s="2" t="n">
-        <v>0.2988845581297033</v>
+        <v>0.3009115779880636</v>
       </c>
       <c r="FX4" s="2" t="n">
-        <v>0.2977016160544985</v>
+        <v>0.2995130012092226</v>
       </c>
       <c r="FY4" s="2" t="n">
-        <v>0.3082372481880084</v>
+        <v>0.3101024712381258</v>
       </c>
       <c r="FZ4" s="2" t="n">
-        <v>0.3134150554911861</v>
+        <v>0.3151123573558101</v>
       </c>
       <c r="GA4" s="2" t="n">
-        <v>0.3284168783880124</v>
+        <v>0.3302868698097119</v>
       </c>
       <c r="GB4" s="2" t="n">
-        <v>0.325125702422315</v>
+        <v>0.327996776204759</v>
       </c>
       <c r="GC4" s="2" t="n">
-        <v>0.3264963744421735</v>
+        <v>0.3295293493409887</v>
       </c>
       <c r="GD4" s="2" t="n">
-        <v>0.3286097015505159</v>
+        <v>0.3316380943422639</v>
       </c>
       <c r="GE4" s="2" t="n">
-        <v>0.3288518839210192</v>
+        <v>0.3320177175730387</v>
       </c>
       <c r="GF4" s="2" t="n">
-        <v>0.3266682927788769</v>
+        <v>0.3298935895146405</v>
       </c>
       <c r="GG4" s="2" t="n">
-        <v>0.3246846982570968</v>
+        <v>0.3277251609894118</v>
       </c>
       <c r="GH4" s="2" t="n">
-        <v>0.3211583622757901</v>
+        <v>0.3243157842223157</v>
       </c>
       <c r="GI4" s="2" t="n">
-        <v>0.3220514979390172</v>
+        <v>0.3250255238441495</v>
       </c>
       <c r="GJ4" s="2" t="n">
-        <v>0.3223655636217709</v>
+        <v>0.3251759300735111</v>
       </c>
       <c r="GK4" s="2" t="n">
-        <v>0.326677495423459</v>
+        <v>0.3297081680928697</v>
       </c>
       <c r="GL4" s="2" t="n">
-        <v>0.3326763607615993</v>
+        <v>0.3354653962010906</v>
       </c>
       <c r="GM4" s="2" t="n">
-        <v>0.3384616103777361</v>
+        <v>0.3409952250132037</v>
       </c>
       <c r="GN4" s="2" t="n">
-        <v>0.3540218697476296</v>
+        <v>0.3563694284844308</v>
       </c>
       <c r="GO4" s="2" t="n">
-        <v>0.3634939009128267</v>
+        <v>0.3658602798162157</v>
       </c>
       <c r="GP4" s="2" t="n">
-        <v>0.3556836281811626</v>
+        <v>0.3585713316594989</v>
       </c>
       <c r="GQ4" s="2" t="n">
-        <v>0.3514200997071896</v>
+        <v>0.3540243681984577</v>
       </c>
       <c r="GR4" s="2" t="n">
-        <v>0.3504801600476949</v>
+        <v>0.3535384073158948</v>
       </c>
       <c r="GS4" s="2" t="n">
-        <v>0.3490489591940818</v>
+        <v>0.3516815398916183</v>
       </c>
       <c r="GT4" s="2" t="n">
-        <v>0.3510318432782274</v>
+        <v>0.3540041331980806</v>
       </c>
       <c r="GU4" s="2" t="n">
-        <v>0.3454945131941045</v>
+        <v>0.3483680158658231</v>
       </c>
       <c r="GV4" s="2" t="n">
-        <v>0.3514703455642582</v>
+        <v>0.3544067311362148</v>
       </c>
       <c r="GW4" s="2" t="n">
-        <v>0.3464314996619658</v>
+        <v>0.3493473663349585</v>
       </c>
       <c r="GX4" s="2" t="n">
-        <v>0.3483453425660732</v>
+        <v>0.3512412193313244</v>
       </c>
       <c r="GY4" s="2" t="n">
-        <v>0.3494208520933868</v>
+        <v>0.3522395855471374</v>
       </c>
       <c r="GZ4" s="2" t="n">
-        <v>0.3618067879941519</v>
+        <v>0.3642095555331762</v>
       </c>
       <c r="HA4" s="2" t="n">
-        <v>0.3739312221594301</v>
+        <v>0.3763908078260866</v>
       </c>
       <c r="HB4" s="2" t="n">
-        <v>0.3879942079135536</v>
+        <v>0.390780911321318</v>
       </c>
       <c r="HC4" s="2" t="n">
-        <v>0.3775525529058643</v>
+        <v>0.379399618891067</v>
       </c>
       <c r="HD4" s="2" t="n">
-        <v>0.3745797249925296</v>
+        <v>0.3776610541594188</v>
       </c>
       <c r="HE4" s="2" t="n">
-        <v>0.3680064011639783</v>
+        <v>0.3705567647046277</v>
       </c>
       <c r="HF4" s="2" t="n">
-        <v>0.3701223696937543</v>
+        <v>0.3725429441204053</v>
       </c>
       <c r="HG4" s="2" t="n">
-        <v>0.3776642318873933</v>
+        <v>0.3805152859597734</v>
       </c>
       <c r="HH4" s="2" t="n">
-        <v>0.3772266788349682</v>
+        <v>0.3802356777654224</v>
       </c>
       <c r="HI4" s="2" t="n">
-        <v>0.3762009658357377</v>
+        <v>0.3792926960131402</v>
       </c>
       <c r="HJ4" s="2" t="n">
-        <v>0.3792417596042313</v>
+        <v>0.3827773059666314</v>
       </c>
       <c r="HK4" s="2" t="n">
-        <v>0.3735057265524698</v>
+        <v>0.3768340871696306</v>
       </c>
       <c r="HL4" s="2" t="n">
-        <v>0.3759024331468017</v>
+        <v>0.3795046175020607</v>
       </c>
       <c r="HM4" s="2" t="n">
-        <v>0.3735702625523712</v>
+        <v>0.3774024016271736</v>
       </c>
       <c r="HN4" s="2" t="n">
-        <v>0.395578712546493</v>
+        <v>0.3990823182698741</v>
       </c>
       <c r="HO4" s="2" t="n">
-        <v>0.4099102124780565</v>
+        <v>0.4134915650099665</v>
       </c>
       <c r="HP4" s="2" t="n">
-        <v>0.3812445485050932</v>
+        <v>0.3833962985332265</v>
       </c>
       <c r="HQ4" s="2" t="n">
-        <v>0.3642640381213719</v>
+        <v>0.3654924376961285</v>
       </c>
       <c r="HR4" s="3" t="n">
         <v>55514</v>
@@ -3555,676 +3555,676 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.02905753329392943</v>
+        <v>0.02905983738597902</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.0377252339026023</v>
+        <v>0.0376776526322652</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.03978886673131653</v>
+        <v>0.03986144563087889</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.04125561477955778</v>
+        <v>0.04149582429197033</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.04146968802546286</v>
+        <v>0.04186693528776192</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04059534111864535</v>
+        <v>0.04115755261726348</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.03994827085559831</v>
+        <v>0.0406156771016644</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.03963247811559811</v>
+        <v>0.04037767587367668</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03984551462361503</v>
+        <v>0.04062339155951429</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03911041616028597</v>
+        <v>0.03988109304136088</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.03793523338434489</v>
+        <v>0.03873213537779839</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.03666301530403183</v>
+        <v>0.03729250461411761</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.03658079444073888</v>
+        <v>0.0372516009455249</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.03720695338014059</v>
+        <v>0.03785125910106592</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.05648813002446709</v>
+        <v>0.05609440781811295</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.06783827996766353</v>
+        <v>0.06766585490619922</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.07072862279967383</v>
+        <v>0.07111214143590049</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.07121715006241204</v>
+        <v>0.07194426712402703</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.07245165873024396</v>
+        <v>0.07339886035475664</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.06962774885521493</v>
+        <v>0.07069309806154332</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.07046334873661902</v>
+        <v>0.0717022722564688</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.06989011127672468</v>
+        <v>0.07117681350729738</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.06948586578725319</v>
+        <v>0.07089433471916656</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.06891349543642869</v>
+        <v>0.07030267295253148</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.06550852655739875</v>
+        <v>0.066899507114006</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.06300147560741393</v>
+        <v>0.0640994527688214</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>0.06293552378106421</v>
+        <v>0.06412070812571352</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.06429634849721085</v>
+        <v>0.0654002479388703</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>0.08954880649619075</v>
+        <v>0.08877101058535548</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>0.1017208491347543</v>
+        <v>0.1018055566482059</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.101837369579877</v>
+        <v>0.1028443565257446</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>0.103146361976055</v>
+        <v>0.1045612141928948</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.1034126870671815</v>
+        <v>0.105075868997962</v>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>0.1026115222180204</v>
+        <v>0.1043603597486333</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>0.09920763662216947</v>
+        <v>0.1010096936499862</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>0.09806442172104679</v>
+        <v>0.09981292770082317</v>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>0.09851979120711368</v>
+        <v>0.100506907618442</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>0.09524635719370811</v>
+        <v>0.09712423878025978</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.09030583038356012</v>
+        <v>0.09188368454005426</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>0.08831043756242324</v>
+        <v>0.08986467896636058</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>0.09084412084699336</v>
+        <v>0.09243420326889221</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.0914666634401172</v>
+        <v>0.09309695292020734</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.1198434505286174</v>
+        <v>0.1188900462957578</v>
       </c>
       <c r="AS5" s="2" t="n">
-        <v>0.1274712677935837</v>
+        <v>0.1287414483616827</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>0.1278822555175294</v>
+        <v>0.1296204443058241</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>0.1284042280728582</v>
+        <v>0.1304789167458776</v>
       </c>
       <c r="AV5" s="2" t="n">
-        <v>0.12761801885788</v>
+        <v>0.1300036277097896</v>
       </c>
       <c r="AW5" s="2" t="n">
-        <v>0.1223552252578019</v>
+        <v>0.1246178287493466</v>
       </c>
       <c r="AX5" s="2" t="n">
-        <v>0.1229877689385084</v>
+        <v>0.1253556025677589</v>
       </c>
       <c r="AY5" s="2" t="n">
-        <v>0.1218511762429496</v>
+        <v>0.1240893660445233</v>
       </c>
       <c r="AZ5" s="2" t="n">
-        <v>0.1205895977265061</v>
+        <v>0.1230215473270835</v>
       </c>
       <c r="BA5" s="2" t="n">
-        <v>0.1163975143251486</v>
+        <v>0.1185534031508036</v>
       </c>
       <c r="BB5" s="2" t="n">
-        <v>0.1109211722602235</v>
+        <v>0.1128962466706621</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>0.1094001234206177</v>
+        <v>0.1113695689174153</v>
       </c>
       <c r="BD5" s="2" t="n">
-        <v>0.1082391429400071</v>
+        <v>0.1100462514614686</v>
       </c>
       <c r="BE5" s="2" t="n">
-        <v>0.1113568982370065</v>
+        <v>0.1132271895445751</v>
       </c>
       <c r="BF5" s="2" t="n">
-        <v>0.1487643860955675</v>
+        <v>0.1489176110108335</v>
       </c>
       <c r="BG5" s="2" t="n">
-        <v>0.1516950756411182</v>
+        <v>0.1538756519655811</v>
       </c>
       <c r="BH5" s="2" t="n">
-        <v>0.1507080448122198</v>
+        <v>0.1532586765737707</v>
       </c>
       <c r="BI5" s="2" t="n">
-        <v>0.1469787767417144</v>
+        <v>0.1500856055206966</v>
       </c>
       <c r="BJ5" s="2" t="n">
-        <v>0.14780334113746</v>
+        <v>0.1508037309220345</v>
       </c>
       <c r="BK5" s="2" t="n">
-        <v>0.1407855839735072</v>
+        <v>0.1436289937501948</v>
       </c>
       <c r="BL5" s="2" t="n">
-        <v>0.1397637242444316</v>
+        <v>0.1425128245719234</v>
       </c>
       <c r="BM5" s="2" t="n">
-        <v>0.1372210852580101</v>
+        <v>0.1398962050454647</v>
       </c>
       <c r="BN5" s="2" t="n">
-        <v>0.1353200499772562</v>
+        <v>0.1381744232832922</v>
       </c>
       <c r="BO5" s="2" t="n">
-        <v>0.1363129362419109</v>
+        <v>0.1390614628746967</v>
       </c>
       <c r="BP5" s="2" t="n">
-        <v>0.1272344846258023</v>
+        <v>0.1294318284818985</v>
       </c>
       <c r="BQ5" s="2" t="n">
-        <v>0.1266282757600098</v>
+        <v>0.1287472301950007</v>
       </c>
       <c r="BR5" s="2" t="n">
-        <v>0.1261134919580396</v>
+        <v>0.1281301480587895</v>
       </c>
       <c r="BS5" s="2" t="n">
-        <v>0.1258943695447117</v>
+        <v>0.1278508175036579</v>
       </c>
       <c r="BT5" s="2" t="n">
-        <v>0.1877394961140733</v>
+        <v>0.1901958333275895</v>
       </c>
       <c r="BU5" s="2" t="n">
-        <v>0.1854863316233783</v>
+        <v>0.1897150390263228</v>
       </c>
       <c r="BV5" s="2" t="n">
-        <v>0.1819584175958677</v>
+        <v>0.1861857280149504</v>
       </c>
       <c r="BW5" s="2" t="n">
-        <v>0.1809105263596947</v>
+        <v>0.1856964105314191</v>
       </c>
       <c r="BX5" s="2" t="n">
-        <v>0.1780409193873047</v>
+        <v>0.1817978262245296</v>
       </c>
       <c r="BY5" s="2" t="n">
-        <v>0.1740515562666549</v>
+        <v>0.1776097933722629</v>
       </c>
       <c r="BZ5" s="2" t="n">
-        <v>0.1695045576596811</v>
+        <v>0.1730833024883822</v>
       </c>
       <c r="CA5" s="2" t="n">
-        <v>0.1661712347790675</v>
+        <v>0.1696920140907245</v>
       </c>
       <c r="CB5" s="2" t="n">
-        <v>0.1637288535437995</v>
+        <v>0.1669952663085871</v>
       </c>
       <c r="CC5" s="2" t="n">
-        <v>0.1587705709008337</v>
+        <v>0.1617836005953908</v>
       </c>
       <c r="CD5" s="2" t="n">
-        <v>0.1544404174377942</v>
+        <v>0.1570932450881029</v>
       </c>
       <c r="CE5" s="2" t="n">
-        <v>0.1472925296493573</v>
+        <v>0.1495199514993233</v>
       </c>
       <c r="CF5" s="2" t="n">
-        <v>0.1474559102904281</v>
+        <v>0.149700218881317</v>
       </c>
       <c r="CG5" s="2" t="n">
-        <v>0.1508481620016081</v>
+        <v>0.1530624820055944</v>
       </c>
       <c r="CH5" s="2" t="n">
-        <v>0.2150123439994965</v>
+        <v>0.2195136420694504</v>
       </c>
       <c r="CI5" s="2" t="n">
-        <v>0.214242655128342</v>
+        <v>0.2200149849952281</v>
       </c>
       <c r="CJ5" s="2" t="n">
-        <v>0.2107205317147293</v>
+        <v>0.2161186487205544</v>
       </c>
       <c r="CK5" s="2" t="n">
-        <v>0.2053705766006391</v>
+        <v>0.2102122916980665</v>
       </c>
       <c r="CL5" s="2" t="n">
-        <v>0.2016698018825994</v>
+        <v>0.2063402169562326</v>
       </c>
       <c r="CM5" s="2" t="n">
-        <v>0.194256540709774</v>
+        <v>0.1983756351709766</v>
       </c>
       <c r="CN5" s="2" t="n">
-        <v>0.1941142161225414</v>
+        <v>0.1981696118449306</v>
       </c>
       <c r="CO5" s="2" t="n">
-        <v>0.1870673144248945</v>
+        <v>0.1907486574737055</v>
       </c>
       <c r="CP5" s="2" t="n">
-        <v>0.1850820377075417</v>
+        <v>0.1888190365934117</v>
       </c>
       <c r="CQ5" s="2" t="n">
-        <v>0.1850761301419308</v>
+        <v>0.1885769195458462</v>
       </c>
       <c r="CR5" s="2" t="n">
-        <v>0.1708059148609313</v>
+        <v>0.1734887087464007</v>
       </c>
       <c r="CS5" s="2" t="n">
-        <v>0.1680505576293812</v>
+        <v>0.1703804175119744</v>
       </c>
       <c r="CT5" s="2" t="n">
-        <v>0.1678262259122884</v>
+        <v>0.1699969674703634</v>
       </c>
       <c r="CU5" s="2" t="n">
-        <v>0.1745932255239487</v>
+        <v>0.1770215895326138</v>
       </c>
       <c r="CV5" s="2" t="n">
-        <v>0.2528009265960642</v>
+        <v>0.2587203011216113</v>
       </c>
       <c r="CW5" s="2" t="n">
-        <v>0.2414922397007434</v>
+        <v>0.2473763208260028</v>
       </c>
       <c r="CX5" s="2" t="n">
-        <v>0.2392515064972157</v>
+        <v>0.2448957161801571</v>
       </c>
       <c r="CY5" s="2" t="n">
-        <v>0.2377287023321182</v>
+        <v>0.2429562494710475</v>
       </c>
       <c r="CZ5" s="2" t="n">
-        <v>0.2273146166626444</v>
+        <v>0.2322081058446397</v>
       </c>
       <c r="DA5" s="2" t="n">
-        <v>0.2232220197222584</v>
+        <v>0.2279128568373077</v>
       </c>
       <c r="DB5" s="2" t="n">
-        <v>0.2228961573924757</v>
+        <v>0.2270720662560201</v>
       </c>
       <c r="DC5" s="2" t="n">
-        <v>0.2169098370343616</v>
+        <v>0.2208662555188109</v>
       </c>
       <c r="DD5" s="2" t="n">
-        <v>0.2158954564042799</v>
+        <v>0.219224670112919</v>
       </c>
       <c r="DE5" s="2" t="n">
-        <v>0.2096596656371875</v>
+        <v>0.212715711258821</v>
       </c>
       <c r="DF5" s="2" t="n">
-        <v>0.2025527497952706</v>
+        <v>0.2052525496309525</v>
       </c>
       <c r="DG5" s="2" t="n">
-        <v>0.1992726247176363</v>
+        <v>0.2019050154253675</v>
       </c>
       <c r="DH5" s="2" t="n">
-        <v>0.1975815377501236</v>
+        <v>0.1999298303691135</v>
       </c>
       <c r="DI5" s="2" t="n">
-        <v>0.2005132968249183</v>
+        <v>0.2026954154195648</v>
       </c>
       <c r="DJ5" s="2" t="n">
-        <v>0.2721929939408993</v>
+        <v>0.2784447388668751</v>
       </c>
       <c r="DK5" s="2" t="n">
-        <v>0.2674736271227828</v>
+        <v>0.2731037812854282</v>
       </c>
       <c r="DL5" s="2" t="n">
-        <v>0.2577209465206274</v>
+        <v>0.2632529281080374</v>
       </c>
       <c r="DM5" s="2" t="n">
-        <v>0.2555244809240393</v>
+        <v>0.2607317960113577</v>
       </c>
       <c r="DN5" s="2" t="n">
-        <v>0.2477104596324397</v>
+        <v>0.2524324811525774</v>
       </c>
       <c r="DO5" s="2" t="n">
-        <v>0.2470028037179502</v>
+        <v>0.2516299048412832</v>
       </c>
       <c r="DP5" s="2" t="n">
-        <v>0.2400059550025864</v>
+        <v>0.2436887620904847</v>
       </c>
       <c r="DQ5" s="2" t="n">
-        <v>0.2333417870517458</v>
+        <v>0.2367870510037627</v>
       </c>
       <c r="DR5" s="2" t="n">
-        <v>0.2312239878115746</v>
+        <v>0.234332992160091</v>
       </c>
       <c r="DS5" s="2" t="n">
-        <v>0.2274583984243551</v>
+        <v>0.2302587140428701</v>
       </c>
       <c r="DT5" s="2" t="n">
-        <v>0.2219574308188321</v>
+        <v>0.2245196370573403</v>
       </c>
       <c r="DU5" s="2" t="n">
-        <v>0.2191453487131548</v>
+        <v>0.2214731000814391</v>
       </c>
       <c r="DV5" s="2" t="n">
-        <v>0.2222470604055616</v>
+        <v>0.2243379540913793</v>
       </c>
       <c r="DW5" s="2" t="n">
-        <v>0.2243955886937002</v>
+        <v>0.2265093444860796</v>
       </c>
       <c r="DX5" s="2" t="n">
-        <v>0.2875429902498723</v>
+        <v>0.293142980736971</v>
       </c>
       <c r="DY5" s="2" t="n">
-        <v>0.2763110916786004</v>
+        <v>0.2814958985619355</v>
       </c>
       <c r="DZ5" s="2" t="n">
-        <v>0.2747015590821503</v>
+        <v>0.2795846621547936</v>
       </c>
       <c r="EA5" s="2" t="n">
-        <v>0.2648604720339446</v>
+        <v>0.2694408133134513</v>
       </c>
       <c r="EB5" s="2" t="n">
-        <v>0.2630613236604875</v>
+        <v>0.2669750465928262</v>
       </c>
       <c r="EC5" s="2" t="n">
-        <v>0.2564922123949226</v>
+        <v>0.2602211758296188</v>
       </c>
       <c r="ED5" s="2" t="n">
-        <v>0.2529320674247884</v>
+        <v>0.256191115290656</v>
       </c>
       <c r="EE5" s="2" t="n">
-        <v>0.2506869371393671</v>
+        <v>0.2536858107307901</v>
       </c>
       <c r="EF5" s="2" t="n">
-        <v>0.2476634320045263</v>
+        <v>0.2505962822759897</v>
       </c>
       <c r="EG5" s="2" t="n">
-        <v>0.2451367038076268</v>
+        <v>0.2478344621842252</v>
       </c>
       <c r="EH5" s="2" t="n">
-        <v>0.2327173280080467</v>
+        <v>0.2349495182295948</v>
       </c>
       <c r="EI5" s="2" t="n">
-        <v>0.235483916750244</v>
+        <v>0.2373261435833491</v>
       </c>
       <c r="EJ5" s="2" t="n">
-        <v>0.2359620976433954</v>
+        <v>0.237640996573945</v>
       </c>
       <c r="EK5" s="2" t="n">
-        <v>0.2380007426286342</v>
+        <v>0.2398094232226017</v>
       </c>
       <c r="EL5" s="2" t="n">
-        <v>0.2949261992309899</v>
+        <v>0.2995991139744134</v>
       </c>
       <c r="EM5" s="2" t="n">
-        <v>0.2902778450055289</v>
+        <v>0.2941995549602676</v>
       </c>
       <c r="EN5" s="2" t="n">
-        <v>0.2848845489080838</v>
+        <v>0.2883578829224995</v>
       </c>
       <c r="EO5" s="2" t="n">
-        <v>0.276773736627116</v>
+        <v>0.2798714421701572</v>
       </c>
       <c r="EP5" s="2" t="n">
-        <v>0.2794354746510337</v>
+        <v>0.2825013885666678</v>
       </c>
       <c r="EQ5" s="2" t="n">
-        <v>0.26769427399403</v>
+        <v>0.2702440563893929</v>
       </c>
       <c r="ER5" s="2" t="n">
-        <v>0.2679091208896612</v>
+        <v>0.2705022731146787</v>
       </c>
       <c r="ES5" s="2" t="n">
-        <v>0.2611338778931181</v>
+        <v>0.2631390973526518</v>
       </c>
       <c r="ET5" s="2" t="n">
-        <v>0.2631731704861215</v>
+        <v>0.2652464137465051</v>
       </c>
       <c r="EU5" s="2" t="n">
-        <v>0.2618864796382968</v>
+        <v>0.2638408935887401</v>
       </c>
       <c r="EV5" s="2" t="n">
-        <v>0.2582037786405005</v>
+        <v>0.2599702144424834</v>
       </c>
       <c r="EW5" s="2" t="n">
-        <v>0.2571342348558798</v>
+        <v>0.2586873605353728</v>
       </c>
       <c r="EX5" s="2" t="n">
-        <v>0.2567098964307025</v>
+        <v>0.2581283379647449</v>
       </c>
       <c r="EY5" s="2" t="n">
-        <v>0.2695745082375059</v>
+        <v>0.2710028217908392</v>
       </c>
       <c r="EZ5" s="2" t="n">
-        <v>0.2950435596102274</v>
+        <v>0.2972491624349154</v>
       </c>
       <c r="FA5" s="2" t="n">
-        <v>0.2955770649292399</v>
+        <v>0.2976127796151568</v>
       </c>
       <c r="FB5" s="2" t="n">
-        <v>0.2841987481043045</v>
+        <v>0.286048943333358</v>
       </c>
       <c r="FC5" s="2" t="n">
-        <v>0.2864950356914556</v>
+        <v>0.2882193682624853</v>
       </c>
       <c r="FD5" s="2" t="n">
-        <v>0.2765038279372081</v>
+        <v>0.278123479850851</v>
       </c>
       <c r="FE5" s="2" t="n">
-        <v>0.2781315183798609</v>
+        <v>0.2796492314497767</v>
       </c>
       <c r="FF5" s="2" t="n">
-        <v>0.27769177890402</v>
+        <v>0.2791854713020913</v>
       </c>
       <c r="FG5" s="2" t="n">
-        <v>0.2744446634497349</v>
+        <v>0.2759051337089246</v>
       </c>
       <c r="FH5" s="2" t="n">
-        <v>0.2697901775167976</v>
+        <v>0.2711733107493911</v>
       </c>
       <c r="FI5" s="2" t="n">
-        <v>0.2684216094908149</v>
+        <v>0.2698916388449104</v>
       </c>
       <c r="FJ5" s="2" t="n">
-        <v>0.2707488749926623</v>
+        <v>0.2722412486379679</v>
       </c>
       <c r="FK5" s="2" t="n">
-        <v>0.2720818578343621</v>
+        <v>0.2732990293841592</v>
       </c>
       <c r="FL5" s="2" t="n">
-        <v>0.2820964220208079</v>
+        <v>0.2830863210600764</v>
       </c>
       <c r="FM5" s="2" t="n">
-        <v>0.2929221267803688</v>
+        <v>0.2938852856858749</v>
       </c>
       <c r="FN5" s="2" t="n">
-        <v>0.2995022735234449</v>
+        <v>0.3009909218784521</v>
       </c>
       <c r="FO5" s="2" t="n">
-        <v>0.2992708250693346</v>
+        <v>0.3007473811320329</v>
       </c>
       <c r="FP5" s="2" t="n">
-        <v>0.2909028299812155</v>
+        <v>0.2922970198754148</v>
       </c>
       <c r="FQ5" s="2" t="n">
-        <v>0.2890987688868387</v>
+        <v>0.2904447237222536</v>
       </c>
       <c r="FR5" s="2" t="n">
-        <v>0.2947429659803323</v>
+        <v>0.2962389159043245</v>
       </c>
       <c r="FS5" s="2" t="n">
-        <v>0.2924721046936521</v>
+        <v>0.2941278025162229</v>
       </c>
       <c r="FT5" s="2" t="n">
-        <v>0.2929661885430034</v>
+        <v>0.2945741579462703</v>
       </c>
       <c r="FU5" s="2" t="n">
-        <v>0.2912149600282343</v>
+        <v>0.2927701942220362</v>
       </c>
       <c r="FV5" s="2" t="n">
-        <v>0.2932457257784548</v>
+        <v>0.2948098559654894</v>
       </c>
       <c r="FW5" s="2" t="n">
-        <v>0.2937888944759764</v>
+        <v>0.2954703191533484</v>
       </c>
       <c r="FX5" s="2" t="n">
-        <v>0.2925982671279312</v>
+        <v>0.29406309597677</v>
       </c>
       <c r="FY5" s="2" t="n">
-        <v>0.3030829902011035</v>
+        <v>0.3045769508200762</v>
       </c>
       <c r="FZ5" s="2" t="n">
-        <v>0.3081293643224775</v>
+        <v>0.3094642997491895</v>
       </c>
       <c r="GA5" s="2" t="n">
-        <v>0.3230964550934097</v>
+        <v>0.3245919654331467</v>
       </c>
       <c r="GB5" s="2" t="n">
-        <v>0.3187693616395413</v>
+        <v>0.3212138002758442</v>
       </c>
       <c r="GC5" s="2" t="n">
-        <v>0.319864170102071</v>
+        <v>0.3224699361600392</v>
       </c>
       <c r="GD5" s="2" t="n">
-        <v>0.3216617356001657</v>
+        <v>0.3242591868101877</v>
       </c>
       <c r="GE5" s="2" t="n">
-        <v>0.3217921803218509</v>
+        <v>0.3245149726492549</v>
       </c>
       <c r="GF5" s="2" t="n">
-        <v>0.3196298061218261</v>
+        <v>0.3223957373108863</v>
       </c>
       <c r="GG5" s="2" t="n">
-        <v>0.3177706456148114</v>
+        <v>0.3203613093459096</v>
       </c>
       <c r="GH5" s="2" t="n">
-        <v>0.3139974144943588</v>
+        <v>0.3166917977579467</v>
       </c>
       <c r="GI5" s="2" t="n">
-        <v>0.3146476997110719</v>
+        <v>0.3171168072197313</v>
       </c>
       <c r="GJ5" s="2" t="n">
-        <v>0.3152509661319715</v>
+        <v>0.3176082106235486</v>
       </c>
       <c r="GK5" s="2" t="n">
-        <v>0.3194015881243988</v>
+        <v>0.3219288176122947</v>
       </c>
       <c r="GL5" s="2" t="n">
-        <v>0.3255125767257301</v>
+        <v>0.3278251326348869</v>
       </c>
       <c r="GM5" s="2" t="n">
-        <v>0.331574793080009</v>
+        <v>0.3336334481035839</v>
       </c>
       <c r="GN5" s="2" t="n">
-        <v>0.3471806698464878</v>
+        <v>0.3490652271532543</v>
       </c>
       <c r="GO5" s="2" t="n">
-        <v>0.3562304273776843</v>
+        <v>0.3581067145399882</v>
       </c>
       <c r="GP5" s="2" t="n">
-        <v>0.3485461753583057</v>
+        <v>0.3509582486724956</v>
       </c>
       <c r="GQ5" s="2" t="n">
-        <v>0.344673384195988</v>
+        <v>0.3468238154713558</v>
       </c>
       <c r="GR5" s="2" t="n">
-        <v>0.3434991884256094</v>
+        <v>0.3460909473920554</v>
       </c>
       <c r="GS5" s="2" t="n">
-        <v>0.3421336436108113</v>
+        <v>0.3443130352929593</v>
       </c>
       <c r="GT5" s="2" t="n">
-        <v>0.3438858239289289</v>
+        <v>0.3463846369024282</v>
       </c>
       <c r="GU5" s="2" t="n">
-        <v>0.3382945362699054</v>
+        <v>0.3406979222071193</v>
       </c>
       <c r="GV5" s="2" t="n">
-        <v>0.3440527189161157</v>
+        <v>0.3464951533462381</v>
       </c>
       <c r="GW5" s="2" t="n">
-        <v>0.3390950224444457</v>
+        <v>0.341506589119155</v>
       </c>
       <c r="GX5" s="2" t="n">
-        <v>0.3408329342485737</v>
+        <v>0.3432199289084744</v>
       </c>
       <c r="GY5" s="2" t="n">
-        <v>0.3416440631434059</v>
+        <v>0.3439431707545852</v>
       </c>
       <c r="GZ5" s="2" t="n">
-        <v>0.3545342172147558</v>
+        <v>0.3564347113134191</v>
       </c>
       <c r="HA5" s="2" t="n">
-        <v>0.3667304750815883</v>
+        <v>0.3686910134092822</v>
       </c>
       <c r="HB5" s="2" t="n">
-        <v>0.3804734795745898</v>
+        <v>0.3827240466531802</v>
       </c>
       <c r="HC5" s="2" t="n">
-        <v>0.3713811030854451</v>
+        <v>0.3728154963125455</v>
       </c>
       <c r="HD5" s="2" t="n">
-        <v>0.3660214814061441</v>
+        <v>0.3684580000752725</v>
       </c>
       <c r="HE5" s="2" t="n">
-        <v>0.3601523215509992</v>
+        <v>0.3621338556148153</v>
       </c>
       <c r="HF5" s="2" t="n">
-        <v>0.3620350159624356</v>
+        <v>0.3638800404885548</v>
       </c>
       <c r="HG5" s="2" t="n">
-        <v>0.3691728475370406</v>
+        <v>0.3714225056447982</v>
       </c>
       <c r="HH5" s="2" t="n">
-        <v>0.3684818093112849</v>
+        <v>0.3708661590150737</v>
       </c>
       <c r="HI5" s="2" t="n">
-        <v>0.3672790343022554</v>
+        <v>0.3697674015617578</v>
       </c>
       <c r="HJ5" s="2" t="n">
-        <v>0.3700763473818466</v>
+        <v>0.3729710693071053</v>
       </c>
       <c r="HK5" s="2" t="n">
-        <v>0.3642349170000831</v>
+        <v>0.3669160605819504</v>
       </c>
       <c r="HL5" s="2" t="n">
-        <v>0.366315332468852</v>
+        <v>0.3692677516902532</v>
       </c>
       <c r="HM5" s="2" t="n">
-        <v>0.3636989223656074</v>
+        <v>0.3668963539299385</v>
       </c>
       <c r="HN5" s="2" t="n">
-        <v>0.3862567561573931</v>
+        <v>0.3891188072867342</v>
       </c>
       <c r="HO5" s="2" t="n">
-        <v>0.4003799138960697</v>
+        <v>0.4033383978900768</v>
       </c>
       <c r="HP5" s="2" t="n">
-        <v>0.3747801350265256</v>
+        <v>0.3764388875871411</v>
       </c>
       <c r="HQ5" s="2" t="n">
-        <v>0.3592902725628639</v>
+        <v>0.3601555308393265</v>
       </c>
       <c r="HR5" s="3" t="n">
         <v>55516</v>
@@ -4237,676 +4237,676 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.02682867778829451</v>
+        <v>0.02682408403969522</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.03595574987842785</v>
+        <v>0.03592871824069963</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.03822182570273154</v>
+        <v>0.03830726802969449</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.03990245241798244</v>
+        <v>0.04014786802358709</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.04045961859802638</v>
+        <v>0.04085784281770621</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.03967557624905057</v>
+        <v>0.04022736345409102</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.03916037656924583</v>
+        <v>0.03980298448911763</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.03888548945641199</v>
+        <v>0.03959846531605402</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03911090560763439</v>
+        <v>0.03984614007680973</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.03837803432675859</v>
+        <v>0.03910719843539259</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.03733924469749794</v>
+        <v>0.03808020586918459</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.03580097152703103</v>
+        <v>0.0363751160617977</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.03568319265476338</v>
+        <v>0.03629076980731361</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.03616036271351526</v>
+        <v>0.03673783952045391</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.05282398799024234</v>
+        <v>0.05245728810839067</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.0654377315890366</v>
+        <v>0.06531076438243927</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.06877087718637276</v>
+        <v>0.0691794837901144</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.06982209716835572</v>
+        <v>0.07054538276889874</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.0712136944377714</v>
+        <v>0.07214898630919989</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.0683450590245662</v>
+        <v>0.06937541471647599</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.0695545335207458</v>
+        <v>0.07074540638368086</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.06885374438997258</v>
+        <v>0.0700705061578368</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.06872889247998504</v>
+        <v>0.07006641512080936</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.06825277685565252</v>
+        <v>0.06955596908373136</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.06495292230001513</v>
+        <v>0.06624077378264491</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.06181848980305694</v>
+        <v>0.06281587667582535</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.06175784482660868</v>
+        <v>0.06283110096159555</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.062872552560491</v>
+        <v>0.06386971964113179</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.08602852970525737</v>
+        <v>0.08534154705867286</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.0997871577591414</v>
+        <v>0.09994391611225553</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.1005669136304815</v>
+        <v>0.1015945051569899</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>0.1025769267695582</v>
+        <v>0.1039817858951724</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.102790182636963</v>
+        <v>0.1044114736783372</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>0.1019839750815018</v>
+        <v>0.1036739101845606</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.09874081144949903</v>
+        <v>0.1004665745320033</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>0.09735673409453983</v>
+        <v>0.09901140373698826</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.09819985249068813</v>
+        <v>0.1000719021352776</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>0.09476691396812618</v>
+        <v>0.09652965055684269</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.08947601161732187</v>
+        <v>0.09094236783518304</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>0.0870840743095401</v>
+        <v>0.08850056751675636</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>0.0895300243712439</v>
+        <v>0.09097520603904861</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.09004274065847187</v>
+        <v>0.09150472338552265</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.1166863462518739</v>
+        <v>0.1158674082349824</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>0.1271964899194713</v>
+        <v>0.1285246993345495</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>0.1282019160731469</v>
+        <v>0.1299688398881589</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>0.1291592530401053</v>
+        <v>0.1312182768674197</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>0.1270948896900755</v>
+        <v>0.1294030553446156</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>0.1223322631393214</v>
+        <v>0.1245032989953299</v>
       </c>
       <c r="AX6" s="2" t="n">
-        <v>0.1227496615808426</v>
+        <v>0.1250066044937788</v>
       </c>
       <c r="AY6" s="2" t="n">
-        <v>0.1213443560142126</v>
+        <v>0.1234610994894114</v>
       </c>
       <c r="AZ6" s="2" t="n">
-        <v>0.1204869250764748</v>
+        <v>0.1227830710818669</v>
       </c>
       <c r="BA6" s="2" t="n">
-        <v>0.1158954684415771</v>
+        <v>0.1179158330688192</v>
       </c>
       <c r="BB6" s="2" t="n">
-        <v>0.1103364088531646</v>
+        <v>0.112167193457118</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>0.1081771576438126</v>
+        <v>0.1099613649431642</v>
       </c>
       <c r="BD6" s="2" t="n">
-        <v>0.1066458454316585</v>
+        <v>0.1082714317327468</v>
       </c>
       <c r="BE6" s="2" t="n">
-        <v>0.1097027553564565</v>
+        <v>0.1113741366511838</v>
       </c>
       <c r="BF6" s="2" t="n">
-        <v>0.1482284006352278</v>
+        <v>0.1485196065778586</v>
       </c>
       <c r="BG6" s="2" t="n">
-        <v>0.1522191721363822</v>
+        <v>0.1544254604144851</v>
       </c>
       <c r="BH6" s="2" t="n">
-        <v>0.1516065215381245</v>
+        <v>0.1541283344539265</v>
       </c>
       <c r="BI6" s="2" t="n">
-        <v>0.1488021568022058</v>
+        <v>0.151824548151283</v>
       </c>
       <c r="BJ6" s="2" t="n">
-        <v>0.1480117131594242</v>
+        <v>0.1508856665912689</v>
       </c>
       <c r="BK6" s="2" t="n">
-        <v>0.1409229264908464</v>
+        <v>0.1436330267542036</v>
       </c>
       <c r="BL6" s="2" t="n">
-        <v>0.1400948788385655</v>
+        <v>0.1426974076192642</v>
       </c>
       <c r="BM6" s="2" t="n">
-        <v>0.1368756448997938</v>
+        <v>0.1393824262692415</v>
       </c>
       <c r="BN6" s="2" t="n">
-        <v>0.1354182002239502</v>
+        <v>0.1380949330621041</v>
       </c>
       <c r="BO6" s="2" t="n">
-        <v>0.1364639926410176</v>
+        <v>0.1390259716368176</v>
       </c>
       <c r="BP6" s="2" t="n">
-        <v>0.1266812811583786</v>
+        <v>0.1287016215712337</v>
       </c>
       <c r="BQ6" s="2" t="n">
-        <v>0.1251557304603679</v>
+        <v>0.1270785502237899</v>
       </c>
       <c r="BR6" s="2" t="n">
-        <v>0.1242953458784518</v>
+        <v>0.126118365114778</v>
       </c>
       <c r="BS6" s="2" t="n">
-        <v>0.1237687453281865</v>
+        <v>0.125512896443604</v>
       </c>
       <c r="BT6" s="2" t="n">
-        <v>0.1879317085453866</v>
+        <v>0.190447359831035</v>
       </c>
       <c r="BU6" s="2" t="n">
-        <v>0.1872213668983974</v>
+        <v>0.1913674101096191</v>
       </c>
       <c r="BV6" s="2" t="n">
-        <v>0.1832514071839957</v>
+        <v>0.1873471925038008</v>
       </c>
       <c r="BW6" s="2" t="n">
-        <v>0.183511329599013</v>
+        <v>0.1880898045080801</v>
       </c>
       <c r="BX6" s="2" t="n">
-        <v>0.1788351687840983</v>
+        <v>0.1824111084692046</v>
       </c>
       <c r="BY6" s="2" t="n">
-        <v>0.1739826485702259</v>
+        <v>0.1773445479759438</v>
       </c>
       <c r="BZ6" s="2" t="n">
-        <v>0.1700576499370636</v>
+        <v>0.1734131679205002</v>
       </c>
       <c r="CA6" s="2" t="n">
-        <v>0.1661731833348327</v>
+        <v>0.169448715610271</v>
       </c>
       <c r="CB6" s="2" t="n">
-        <v>0.1635981831516399</v>
+        <v>0.1666337098743095</v>
       </c>
       <c r="CC6" s="2" t="n">
-        <v>0.1586083118601567</v>
+        <v>0.1614118610306507</v>
       </c>
       <c r="CD6" s="2" t="n">
-        <v>0.1536933351068943</v>
+        <v>0.1561286207049339</v>
       </c>
       <c r="CE6" s="2" t="n">
-        <v>0.1453722716345814</v>
+        <v>0.1473872886076001</v>
       </c>
       <c r="CF6" s="2" t="n">
-        <v>0.1452651309258826</v>
+        <v>0.1472724887020476</v>
       </c>
       <c r="CG6" s="2" t="n">
-        <v>0.1481965256838324</v>
+        <v>0.1501614971069815</v>
       </c>
       <c r="CH6" s="2" t="n">
-        <v>0.2165194113591274</v>
+        <v>0.220888413194712</v>
       </c>
       <c r="CI6" s="2" t="n">
-        <v>0.2169540737691858</v>
+        <v>0.2225164052966573</v>
       </c>
       <c r="CJ6" s="2" t="n">
-        <v>0.2121139856755954</v>
+        <v>0.2172494883418304</v>
       </c>
       <c r="CK6" s="2" t="n">
-        <v>0.206827371163591</v>
+        <v>0.2114245842828594</v>
       </c>
       <c r="CL6" s="2" t="n">
-        <v>0.202368689718165</v>
+        <v>0.2067619543694635</v>
       </c>
       <c r="CM6" s="2" t="n">
-        <v>0.1941137366760977</v>
+        <v>0.1979648486543902</v>
       </c>
       <c r="CN6" s="2" t="n">
-        <v>0.1939552199951675</v>
+        <v>0.1977154870442417</v>
       </c>
       <c r="CO6" s="2" t="n">
-        <v>0.1867653678540903</v>
+        <v>0.1901962559108454</v>
       </c>
       <c r="CP6" s="2" t="n">
-        <v>0.1850667697616499</v>
+        <v>0.188532444579212</v>
       </c>
       <c r="CQ6" s="2" t="n">
-        <v>0.1852888060049492</v>
+        <v>0.1885309410528618</v>
       </c>
       <c r="CR6" s="2" t="n">
-        <v>0.1693136014966976</v>
+        <v>0.1717658110885631</v>
       </c>
       <c r="CS6" s="2" t="n">
-        <v>0.1655152590163525</v>
+        <v>0.1675940566845711</v>
       </c>
       <c r="CT6" s="2" t="n">
-        <v>0.1648036206662167</v>
+        <v>0.1667248311042298</v>
       </c>
       <c r="CU6" s="2" t="n">
-        <v>0.1713398262916351</v>
+        <v>0.17348535508497</v>
       </c>
       <c r="CV6" s="2" t="n">
-        <v>0.2548613556582218</v>
+        <v>0.2604869314390903</v>
       </c>
       <c r="CW6" s="2" t="n">
-        <v>0.2431298276957694</v>
+        <v>0.2486935375806514</v>
       </c>
       <c r="CX6" s="2" t="n">
-        <v>0.2401183429317915</v>
+        <v>0.2454172144787752</v>
       </c>
       <c r="CY6" s="2" t="n">
-        <v>0.2372092029943552</v>
+        <v>0.2420695817961779</v>
       </c>
       <c r="CZ6" s="2" t="n">
-        <v>0.2272231091363777</v>
+        <v>0.2317613732619633</v>
       </c>
       <c r="DA6" s="2" t="n">
-        <v>0.2230029059485836</v>
+        <v>0.227335895402853</v>
       </c>
       <c r="DB6" s="2" t="n">
-        <v>0.2224682110948699</v>
+        <v>0.2263299215240615</v>
       </c>
       <c r="DC6" s="2" t="n">
-        <v>0.2166954100861279</v>
+        <v>0.2203479156627385</v>
       </c>
       <c r="DD6" s="2" t="n">
-        <v>0.2142748621787565</v>
+        <v>0.2173116070713537</v>
       </c>
       <c r="DE6" s="2" t="n">
-        <v>0.2079872676401474</v>
+        <v>0.2107682378261425</v>
       </c>
       <c r="DF6" s="2" t="n">
-        <v>0.2001144574150976</v>
+        <v>0.2025424451694425</v>
       </c>
       <c r="DG6" s="2" t="n">
-        <v>0.1966591270030957</v>
+        <v>0.1990080752731782</v>
       </c>
       <c r="DH6" s="2" t="n">
-        <v>0.1943498649076167</v>
+        <v>0.1964327119663898</v>
       </c>
       <c r="DI6" s="2" t="n">
-        <v>0.1962662140442553</v>
+        <v>0.1981591495289031</v>
       </c>
       <c r="DJ6" s="2" t="n">
-        <v>0.2717359306072159</v>
+        <v>0.2775597365354462</v>
       </c>
       <c r="DK6" s="2" t="n">
-        <v>0.2660099447767324</v>
+        <v>0.2712099880973882</v>
       </c>
       <c r="DL6" s="2" t="n">
-        <v>0.2575702363483461</v>
+        <v>0.2627000951997789</v>
       </c>
       <c r="DM6" s="2" t="n">
-        <v>0.2550772129792412</v>
+        <v>0.2598870433170041</v>
       </c>
       <c r="DN6" s="2" t="n">
-        <v>0.2466653050240669</v>
+        <v>0.2510296763238106</v>
       </c>
       <c r="DO6" s="2" t="n">
-        <v>0.2465221366734833</v>
+        <v>0.2507795250864358</v>
       </c>
       <c r="DP6" s="2" t="n">
-        <v>0.2384618642034531</v>
+        <v>0.2418337771894932</v>
       </c>
       <c r="DQ6" s="2" t="n">
-        <v>0.2314997014524073</v>
+        <v>0.234652444434318</v>
       </c>
       <c r="DR6" s="2" t="n">
-        <v>0.2285833856978233</v>
+        <v>0.2313797227062996</v>
       </c>
       <c r="DS6" s="2" t="n">
-        <v>0.2242160035874375</v>
+        <v>0.2267303063179978</v>
       </c>
       <c r="DT6" s="2" t="n">
-        <v>0.2187709234141341</v>
+        <v>0.2210415474556915</v>
       </c>
       <c r="DU6" s="2" t="n">
-        <v>0.2159532676637895</v>
+        <v>0.2180029484630354</v>
       </c>
       <c r="DV6" s="2" t="n">
-        <v>0.2180378744381756</v>
+        <v>0.2198641197759003</v>
       </c>
       <c r="DW6" s="2" t="n">
-        <v>0.2195078205410884</v>
+        <v>0.2213271331135677</v>
       </c>
       <c r="DX6" s="2" t="n">
-        <v>0.2862542095883251</v>
+        <v>0.2914300683243633</v>
       </c>
       <c r="DY6" s="2" t="n">
-        <v>0.2753115985419148</v>
+        <v>0.280073629679858</v>
       </c>
       <c r="DZ6" s="2" t="n">
-        <v>0.2730146357397321</v>
+        <v>0.2774911829809431</v>
       </c>
       <c r="EA6" s="2" t="n">
-        <v>0.2639272066720412</v>
+        <v>0.2681307273872778</v>
       </c>
       <c r="EB6" s="2" t="n">
-        <v>0.260912070250933</v>
+        <v>0.2644886953894542</v>
       </c>
       <c r="EC6" s="2" t="n">
-        <v>0.2542637553896028</v>
+        <v>0.2576413494433481</v>
       </c>
       <c r="ED6" s="2" t="n">
-        <v>0.2500845865281299</v>
+        <v>0.2530406937869266</v>
       </c>
       <c r="EE6" s="2" t="n">
-        <v>0.2471688046985142</v>
+        <v>0.2498559385471814</v>
       </c>
       <c r="EF6" s="2" t="n">
-        <v>0.2448345889673766</v>
+        <v>0.2474733610973891</v>
       </c>
       <c r="EG6" s="2" t="n">
-        <v>0.2421379221677022</v>
+        <v>0.2445435581802564</v>
       </c>
       <c r="EH6" s="2" t="n">
-        <v>0.228275349611035</v>
+        <v>0.2302234901726157</v>
       </c>
       <c r="EI6" s="2" t="n">
-        <v>0.2307575616426712</v>
+        <v>0.2323358628340012</v>
       </c>
       <c r="EJ6" s="2" t="n">
-        <v>0.2304867772586932</v>
+        <v>0.2318969262965311</v>
       </c>
       <c r="EK6" s="2" t="n">
-        <v>0.2325199439508744</v>
+        <v>0.234035008339388</v>
       </c>
       <c r="EL6" s="2" t="n">
-        <v>0.2927724348883694</v>
+        <v>0.2970185952763623</v>
       </c>
       <c r="EM6" s="2" t="n">
-        <v>0.2866957836153844</v>
+        <v>0.2902067281606534</v>
       </c>
       <c r="EN6" s="2" t="n">
-        <v>0.280964159376493</v>
+        <v>0.2840737858484893</v>
       </c>
       <c r="EO6" s="2" t="n">
-        <v>0.2727974417764241</v>
+        <v>0.2755628141719395</v>
       </c>
       <c r="EP6" s="2" t="n">
-        <v>0.2756539276024616</v>
+        <v>0.2783943852564609</v>
       </c>
       <c r="EQ6" s="2" t="n">
-        <v>0.263687715058499</v>
+        <v>0.2659363747884566</v>
       </c>
       <c r="ER6" s="2" t="n">
-        <v>0.2633937948435236</v>
+        <v>0.2656966128438402</v>
       </c>
       <c r="ES6" s="2" t="n">
-        <v>0.2556119633724925</v>
+        <v>0.2573332561066387</v>
       </c>
       <c r="ET6" s="2" t="n">
-        <v>0.2583638620081767</v>
+        <v>0.26016650018128</v>
       </c>
       <c r="EU6" s="2" t="n">
-        <v>0.2568071282044547</v>
+        <v>0.2584831661120551</v>
       </c>
       <c r="EV6" s="2" t="n">
-        <v>0.2526583020055304</v>
+        <v>0.2541498262846479</v>
       </c>
       <c r="EW6" s="2" t="n">
-        <v>0.2513143770254391</v>
+        <v>0.2526091649986046</v>
       </c>
       <c r="EX6" s="2" t="n">
-        <v>0.2503527611449103</v>
+        <v>0.2515133641615253</v>
       </c>
       <c r="EY6" s="2" t="n">
-        <v>0.2620825620080572</v>
+        <v>0.2632223145748717</v>
       </c>
       <c r="EZ6" s="2" t="n">
-        <v>0.2904071966341809</v>
+        <v>0.2923207739523724</v>
       </c>
       <c r="FA6" s="2" t="n">
-        <v>0.2903681151078645</v>
+        <v>0.2921289853261415</v>
       </c>
       <c r="FB6" s="2" t="n">
-        <v>0.2790868254610529</v>
+        <v>0.2806837605544558</v>
       </c>
       <c r="FC6" s="2" t="n">
-        <v>0.2808842428968646</v>
+        <v>0.2823462405250766</v>
       </c>
       <c r="FD6" s="2" t="n">
-        <v>0.2707780638867247</v>
+        <v>0.272150423579775</v>
       </c>
       <c r="FE6" s="2" t="n">
-        <v>0.2720823959090347</v>
+        <v>0.2733453959800834</v>
       </c>
       <c r="FF6" s="2" t="n">
-        <v>0.2716554549968847</v>
+        <v>0.2729065564907202</v>
       </c>
       <c r="FG6" s="2" t="n">
-        <v>0.2682728244149467</v>
+        <v>0.2694901524269363</v>
       </c>
       <c r="FH6" s="2" t="n">
-        <v>0.2637828592598664</v>
+        <v>0.2649246905386674</v>
       </c>
       <c r="FI6" s="2" t="n">
-        <v>0.2624608816788281</v>
+        <v>0.2636810930655087</v>
       </c>
       <c r="FJ6" s="2" t="n">
-        <v>0.2642141005182564</v>
+        <v>0.2654349824571907</v>
       </c>
       <c r="FK6" s="2" t="n">
-        <v>0.2650714245202676</v>
+        <v>0.2660345089199678</v>
       </c>
       <c r="FL6" s="2" t="n">
-        <v>0.2741354764267905</v>
+        <v>0.2748576686546309</v>
       </c>
       <c r="FM6" s="2" t="n">
-        <v>0.2844160646643544</v>
+        <v>0.2850966155972386</v>
       </c>
       <c r="FN6" s="2" t="n">
-        <v>0.2921122632286446</v>
+        <v>0.2933463550469773</v>
       </c>
       <c r="FO6" s="2" t="n">
-        <v>0.2919441859793179</v>
+        <v>0.2931596662473195</v>
       </c>
       <c r="FP6" s="2" t="n">
-        <v>0.2837903130421302</v>
+        <v>0.2849283817777297</v>
       </c>
       <c r="FQ6" s="2" t="n">
-        <v>0.2817352161740112</v>
+        <v>0.2828177110289383</v>
       </c>
       <c r="FR6" s="2" t="n">
-        <v>0.2875615359096823</v>
+        <v>0.2887917534261046</v>
       </c>
       <c r="FS6" s="2" t="n">
-        <v>0.2849687804394425</v>
+        <v>0.2863254492097558</v>
       </c>
       <c r="FT6" s="2" t="n">
-        <v>0.2855413213260833</v>
+        <v>0.2868621528037254</v>
       </c>
       <c r="FU6" s="2" t="n">
-        <v>0.2836742664804883</v>
+        <v>0.2849397326937146</v>
       </c>
       <c r="FV6" s="2" t="n">
-        <v>0.2853565367050776</v>
+        <v>0.2866105066724429</v>
       </c>
       <c r="FW6" s="2" t="n">
-        <v>0.2858148962331023</v>
+        <v>0.2871693074774947</v>
       </c>
       <c r="FX6" s="2" t="n">
-        <v>0.2839753409645158</v>
+        <v>0.2851104667207795</v>
       </c>
       <c r="FY6" s="2" t="n">
-        <v>0.2936801837313406</v>
+        <v>0.29482112094047</v>
       </c>
       <c r="FZ6" s="2" t="n">
-        <v>0.2982491142707565</v>
+        <v>0.2992382682519653</v>
       </c>
       <c r="GA6" s="2" t="n">
-        <v>0.3128864682913675</v>
+        <v>0.3140144042373552</v>
       </c>
       <c r="GB6" s="2" t="n">
-        <v>0.3104669366463245</v>
+        <v>0.3125113312586368</v>
       </c>
       <c r="GC6" s="2" t="n">
-        <v>0.3113678316779846</v>
+        <v>0.3135663713522667</v>
       </c>
       <c r="GD6" s="2" t="n">
-        <v>0.3129591906778336</v>
+        <v>0.3151409739963532</v>
       </c>
       <c r="GE6" s="2" t="n">
-        <v>0.312999165826391</v>
+        <v>0.3152929760747659</v>
       </c>
       <c r="GF6" s="2" t="n">
-        <v>0.3108160821602756</v>
+        <v>0.313144947390359</v>
       </c>
       <c r="GG6" s="2" t="n">
-        <v>0.3089667955212048</v>
+        <v>0.3111174652151516</v>
       </c>
       <c r="GH6" s="2" t="n">
-        <v>0.3052840779973622</v>
+        <v>0.3075394730521794</v>
       </c>
       <c r="GI6" s="2" t="n">
-        <v>0.3049582566912684</v>
+        <v>0.3069416310484919</v>
       </c>
       <c r="GJ6" s="2" t="n">
-        <v>0.305731550205331</v>
+        <v>0.307653121996503</v>
       </c>
       <c r="GK6" s="2" t="n">
-        <v>0.3093740625738147</v>
+        <v>0.3114187179564479</v>
       </c>
       <c r="GL6" s="2" t="n">
-        <v>0.3144716645233042</v>
+        <v>0.3163210997931368</v>
       </c>
       <c r="GM6" s="2" t="n">
-        <v>0.3194968662194795</v>
+        <v>0.3210885337524003</v>
       </c>
       <c r="GN6" s="2" t="n">
-        <v>0.3346247952833493</v>
+        <v>0.3360502478137334</v>
       </c>
       <c r="GO6" s="2" t="n">
-        <v>0.3435337366014728</v>
+        <v>0.3449434907585391</v>
       </c>
       <c r="GP6" s="2" t="n">
-        <v>0.338146939953162</v>
+        <v>0.3401090429027813</v>
       </c>
       <c r="GQ6" s="2" t="n">
-        <v>0.3337821889307748</v>
+        <v>0.3354995179560434</v>
       </c>
       <c r="GR6" s="2" t="n">
-        <v>0.3337712024106207</v>
+        <v>0.3359053988708677</v>
       </c>
       <c r="GS6" s="2" t="n">
-        <v>0.3318723653156857</v>
+        <v>0.3336224321920971</v>
       </c>
       <c r="GT6" s="2" t="n">
-        <v>0.3331908388096209</v>
+        <v>0.3352295039254542</v>
       </c>
       <c r="GU6" s="2" t="n">
-        <v>0.3272852887991333</v>
+        <v>0.329237698543396</v>
       </c>
       <c r="GV6" s="2" t="n">
-        <v>0.3326671869737988</v>
+        <v>0.3346231431944257</v>
       </c>
       <c r="GW6" s="2" t="n">
-        <v>0.3271530193571468</v>
+        <v>0.3290716407184024</v>
       </c>
       <c r="GX6" s="2" t="n">
-        <v>0.32846997063989</v>
+        <v>0.3303698388897832</v>
       </c>
       <c r="GY6" s="2" t="n">
-        <v>0.328916537845755</v>
+        <v>0.3307112635022644</v>
       </c>
       <c r="GZ6" s="2" t="n">
-        <v>0.3407626669054935</v>
+        <v>0.3421861226802776</v>
       </c>
       <c r="HA6" s="2" t="n">
-        <v>0.3538386392290575</v>
+        <v>0.3553201499278528</v>
       </c>
       <c r="HB6" s="2" t="n">
-        <v>0.3660621774519291</v>
+        <v>0.3677889314616528</v>
       </c>
       <c r="HC6" s="2" t="n">
-        <v>0.3592764643544282</v>
+        <v>0.3603105974907006</v>
       </c>
       <c r="HD6" s="2" t="n">
-        <v>0.3482405444611304</v>
+        <v>0.3500582849611037</v>
       </c>
       <c r="HE6" s="2" t="n">
-        <v>0.3424590300046514</v>
+        <v>0.3438815097533773</v>
       </c>
       <c r="HF6" s="2" t="n">
-        <v>0.3448579237035958</v>
+        <v>0.3461522311143128</v>
       </c>
       <c r="HG6" s="2" t="n">
-        <v>0.3520451813922644</v>
+        <v>0.3537094622836828</v>
       </c>
       <c r="HH6" s="2" t="n">
-        <v>0.351220317042309</v>
+        <v>0.3530011995200693</v>
       </c>
       <c r="HI6" s="2" t="n">
-        <v>0.3498804979465033</v>
+        <v>0.3517818935654189</v>
       </c>
       <c r="HJ6" s="2" t="n">
-        <v>0.3528566304280428</v>
+        <v>0.3551365080907015</v>
       </c>
       <c r="HK6" s="2" t="n">
-        <v>0.3470183656501568</v>
+        <v>0.349081580429057</v>
       </c>
       <c r="HL6" s="2" t="n">
-        <v>0.3494629236355229</v>
+        <v>0.351799023379366</v>
       </c>
       <c r="HM6" s="2" t="n">
-        <v>0.3473519196888132</v>
+        <v>0.3499252533694429</v>
       </c>
       <c r="HN6" s="2" t="n">
-        <v>0.3692457231386654</v>
+        <v>0.3715008797749035</v>
       </c>
       <c r="HO6" s="2" t="n">
-        <v>0.3826136396910391</v>
+        <v>0.3849716068889341</v>
       </c>
       <c r="HP6" s="2" t="n">
-        <v>0.3602521632027521</v>
+        <v>0.3614475790572061</v>
       </c>
       <c r="HQ6" s="2" t="n">
-        <v>0.34707810860836</v>
+        <v>0.3475945158001134</v>
       </c>
       <c r="HR6" s="3" t="n">
         <v>55517</v>
@@ -4919,676 +4919,676 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.02772115832383386</v>
+        <v>0.02765591964314333</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.0363731786294493</v>
+        <v>0.03630399533199399</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03860914831563494</v>
+        <v>0.03864667223348877</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.04034430770845103</v>
+        <v>0.04053421183199572</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.04086234948910353</v>
+        <v>0.04120216115690348</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.04018154066902525</v>
+        <v>0.04067021959376461</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0398036287533112</v>
+        <v>0.04037412157226281</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.03961798572880969</v>
+        <v>0.04025325296414838</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.03993604777265902</v>
+        <v>0.04058604387451525</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.03928267860756035</v>
+        <v>0.03993175549403544</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.03832968512401508</v>
+        <v>0.03898483702764438</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03693047022569833</v>
+        <v>0.03742587423074899</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.03688601279451485</v>
+        <v>0.03740769313468571</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.03748949780459034</v>
+        <v>0.03798338375384437</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.05403572512017499</v>
+        <v>0.05360385314719687</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.06581550559141629</v>
+        <v>0.06563167927899353</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.06919326385058341</v>
+        <v>0.06952332270838199</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.07031269505766932</v>
+        <v>0.07094044000057284</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.07189270250157759</v>
+        <v>0.07272440150038645</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.06929301719623432</v>
+        <v>0.07020873452978954</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.07054986428734761</v>
+        <v>0.07162104357299309</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.07015373967962674</v>
+        <v>0.07123777680473736</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.07006843629425172</v>
+        <v>0.07127665597146157</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.06966910180297278</v>
+        <v>0.07082956139591121</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.06650520037090799</v>
+        <v>0.06764968871301433</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.06370348771208961</v>
+        <v>0.06456750081026991</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0.06375512149670134</v>
+        <v>0.0646876994941474</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0.0649904736897321</v>
+        <v>0.06585384324401333</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>0.08646512871618073</v>
+        <v>0.08574939055378239</v>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>0.09961959214478162</v>
+        <v>0.0997115676996055</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.1006602805022874</v>
+        <v>0.1015723023478665</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>0.1028888612091522</v>
+        <v>0.104162659034131</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.1035732571419448</v>
+        <v>0.105037804731366</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>0.1030416170162361</v>
+        <v>0.1045710554373663</v>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>0.1000162942938623</v>
+        <v>0.1015794112019358</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>0.09899274795681583</v>
+        <v>0.1004769259634648</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>0.09985999473756317</v>
+        <v>0.1015452154857493</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>0.09660257921704112</v>
+        <v>0.09818305970319567</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.09145660921002439</v>
+        <v>0.09276548995638899</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>0.08949315946796232</v>
+        <v>0.09073641177513891</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>0.09216209878298771</v>
+        <v>0.0934281200644685</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>0.09281010733875664</v>
+        <v>0.094078382420868</v>
       </c>
       <c r="AR7" s="2" t="n">
-        <v>0.1164635045900164</v>
+        <v>0.1156339699848709</v>
       </c>
       <c r="AS7" s="2" t="n">
-        <v>0.1264354299063095</v>
+        <v>0.1276493082994827</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>0.1278469790211527</v>
+        <v>0.1294798370889036</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>0.1291587351429408</v>
+        <v>0.1310657168346589</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>0.1283281858929307</v>
+        <v>0.1304311606951863</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>0.1235507743540265</v>
+        <v>0.1255266087236859</v>
       </c>
       <c r="AX7" s="2" t="n">
-        <v>0.1243740809453692</v>
+        <v>0.1264275913430419</v>
       </c>
       <c r="AY7" s="2" t="n">
-        <v>0.1233390890209594</v>
+        <v>0.1252480767815033</v>
       </c>
       <c r="AZ7" s="2" t="n">
-        <v>0.1224924820397029</v>
+        <v>0.1245722482833991</v>
       </c>
       <c r="BA7" s="2" t="n">
-        <v>0.1180720296092698</v>
+        <v>0.119885512102432</v>
       </c>
       <c r="BB7" s="2" t="n">
-        <v>0.11266499206281</v>
+        <v>0.11429833814359</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>0.1110491420616477</v>
+        <v>0.1126136615415185</v>
       </c>
       <c r="BD7" s="2" t="n">
-        <v>0.1097250637597332</v>
+        <v>0.1111325659788141</v>
       </c>
       <c r="BE7" s="2" t="n">
-        <v>0.1129769348108857</v>
+        <v>0.1144224759692042</v>
       </c>
       <c r="BF7" s="2" t="n">
-        <v>0.1466814208636218</v>
+        <v>0.1469355266401702</v>
       </c>
       <c r="BG7" s="2" t="n">
-        <v>0.1516711775494331</v>
+        <v>0.1537187610102409</v>
       </c>
       <c r="BH7" s="2" t="n">
-        <v>0.1516828881647347</v>
+        <v>0.1540097566392182</v>
       </c>
       <c r="BI7" s="2" t="n">
-        <v>0.1492318795559346</v>
+        <v>0.1520245955822407</v>
       </c>
       <c r="BJ7" s="2" t="n">
-        <v>0.1495904343509209</v>
+        <v>0.1522118615293038</v>
       </c>
       <c r="BK7" s="2" t="n">
-        <v>0.142686422439141</v>
+        <v>0.1451553921120594</v>
       </c>
       <c r="BL7" s="2" t="n">
-        <v>0.1419567818688766</v>
+        <v>0.1443213204788581</v>
       </c>
       <c r="BM7" s="2" t="n">
-        <v>0.1392546217781779</v>
+        <v>0.1415094356877085</v>
       </c>
       <c r="BN7" s="2" t="n">
-        <v>0.137765495227377</v>
+        <v>0.140188379334013</v>
       </c>
       <c r="BO7" s="2" t="n">
-        <v>0.1389018239305984</v>
+        <v>0.1412079537139904</v>
       </c>
       <c r="BP7" s="2" t="n">
-        <v>0.1293909942086186</v>
+        <v>0.1311841254408803</v>
       </c>
       <c r="BQ7" s="2" t="n">
-        <v>0.1284301828688554</v>
+        <v>0.1301231671220235</v>
       </c>
       <c r="BR7" s="2" t="n">
-        <v>0.1277740021718851</v>
+        <v>0.129371561251413</v>
       </c>
       <c r="BS7" s="2" t="n">
-        <v>0.1274017885774189</v>
+        <v>0.1289102498888784</v>
       </c>
       <c r="BT7" s="2" t="n">
-        <v>0.1874300521187006</v>
+        <v>0.1897651981882273</v>
       </c>
       <c r="BU7" s="2" t="n">
-        <v>0.1877497523182366</v>
+        <v>0.1915985806935761</v>
       </c>
       <c r="BV7" s="2" t="n">
-        <v>0.1847637019862688</v>
+        <v>0.1885327011158026</v>
       </c>
       <c r="BW7" s="2" t="n">
-        <v>0.1850513973600635</v>
+        <v>0.189267297214962</v>
       </c>
       <c r="BX7" s="2" t="n">
-        <v>0.1811131483317379</v>
+        <v>0.1843672601879601</v>
       </c>
       <c r="BY7" s="2" t="n">
-        <v>0.1768301044997058</v>
+        <v>0.1798702915605387</v>
       </c>
       <c r="BZ7" s="2" t="n">
-        <v>0.1728110503535467</v>
+        <v>0.1758497286718088</v>
       </c>
       <c r="CA7" s="2" t="n">
-        <v>0.1693102545385659</v>
+        <v>0.1722469418590367</v>
       </c>
       <c r="CB7" s="2" t="n">
-        <v>0.1667079128408332</v>
+        <v>0.1694371983492274</v>
       </c>
       <c r="CC7" s="2" t="n">
-        <v>0.1616401737334687</v>
+        <v>0.1641586227121312</v>
       </c>
       <c r="CD7" s="2" t="n">
-        <v>0.1570700758172199</v>
+        <v>0.1592345439864323</v>
       </c>
       <c r="CE7" s="2" t="n">
-        <v>0.1491832579849577</v>
+        <v>0.1509472984252787</v>
       </c>
       <c r="CF7" s="2" t="n">
-        <v>0.1492263310059432</v>
+        <v>0.1509642459854011</v>
       </c>
       <c r="CG7" s="2" t="n">
-        <v>0.1525472339209742</v>
+        <v>0.1542336095091529</v>
       </c>
       <c r="CH7" s="2" t="n">
-        <v>0.2178208374105368</v>
+        <v>0.2218413420639906</v>
       </c>
       <c r="CI7" s="2" t="n">
-        <v>0.2190130852908201</v>
+        <v>0.2241571822017736</v>
       </c>
       <c r="CJ7" s="2" t="n">
-        <v>0.2149691348570718</v>
+        <v>0.2196636674600972</v>
       </c>
       <c r="CK7" s="2" t="n">
-        <v>0.2098254348746506</v>
+        <v>0.2140240419319836</v>
       </c>
       <c r="CL7" s="2" t="n">
-        <v>0.2058534941026814</v>
+        <v>0.2098403519341595</v>
       </c>
       <c r="CM7" s="2" t="n">
-        <v>0.1978715464519634</v>
+        <v>0.2013537094043865</v>
       </c>
       <c r="CN7" s="2" t="n">
-        <v>0.1977529286726976</v>
+        <v>0.2011276877805258</v>
       </c>
       <c r="CO7" s="2" t="n">
-        <v>0.1906102686970013</v>
+        <v>0.1937010377495068</v>
       </c>
       <c r="CP7" s="2" t="n">
-        <v>0.1887862149114755</v>
+        <v>0.1919061120088246</v>
       </c>
       <c r="CQ7" s="2" t="n">
-        <v>0.1888798314422728</v>
+        <v>0.1917910899311663</v>
       </c>
       <c r="CR7" s="2" t="n">
-        <v>0.1732039256660304</v>
+        <v>0.1753791412977538</v>
       </c>
       <c r="CS7" s="2" t="n">
-        <v>0.1699527188075525</v>
+        <v>0.1717449857724649</v>
       </c>
       <c r="CT7" s="2" t="n">
-        <v>0.1693456444310253</v>
+        <v>0.1709864224659508</v>
       </c>
       <c r="CU7" s="2" t="n">
-        <v>0.1762952620927652</v>
+        <v>0.1781269016508421</v>
       </c>
       <c r="CV7" s="2" t="n">
-        <v>0.2584040075415633</v>
+        <v>0.2635569482916854</v>
       </c>
       <c r="CW7" s="2" t="n">
-        <v>0.2473275897471165</v>
+        <v>0.252396882828877</v>
       </c>
       <c r="CX7" s="2" t="n">
-        <v>0.2443263188478222</v>
+        <v>0.2491357505795231</v>
       </c>
       <c r="CY7" s="2" t="n">
-        <v>0.2421299256483116</v>
+        <v>0.2464986406365433</v>
       </c>
       <c r="CZ7" s="2" t="n">
-        <v>0.2320248467706179</v>
+        <v>0.2360995804749465</v>
       </c>
       <c r="DA7" s="2" t="n">
-        <v>0.2278063984689988</v>
+        <v>0.2316864820299424</v>
       </c>
       <c r="DB7" s="2" t="n">
-        <v>0.2271649262369135</v>
+        <v>0.2306221222937563</v>
       </c>
       <c r="DC7" s="2" t="n">
-        <v>0.2210578282955758</v>
+        <v>0.2243352977219693</v>
       </c>
       <c r="DD7" s="2" t="n">
-        <v>0.2188819703087681</v>
+        <v>0.2215524334833496</v>
       </c>
       <c r="DE7" s="2" t="n">
-        <v>0.2124972669792594</v>
+        <v>0.214947155715269</v>
       </c>
       <c r="DF7" s="2" t="n">
-        <v>0.2048271191969631</v>
+        <v>0.2069388819590328</v>
       </c>
       <c r="DG7" s="2" t="n">
-        <v>0.2015167079534855</v>
+        <v>0.2035542778339711</v>
       </c>
       <c r="DH7" s="2" t="n">
-        <v>0.1992747400397955</v>
+        <v>0.2010623913700281</v>
       </c>
       <c r="DI7" s="2" t="n">
-        <v>0.2017500624711196</v>
+        <v>0.2033335567171256</v>
       </c>
       <c r="DJ7" s="2" t="n">
-        <v>0.2776702667056964</v>
+        <v>0.2829026157438205</v>
       </c>
       <c r="DK7" s="2" t="n">
-        <v>0.272076752303824</v>
+        <v>0.2767157147514673</v>
       </c>
       <c r="DL7" s="2" t="n">
-        <v>0.2629501686765731</v>
+        <v>0.2675611541940749</v>
       </c>
       <c r="DM7" s="2" t="n">
-        <v>0.2605263937083347</v>
+        <v>0.264828239735709</v>
       </c>
       <c r="DN7" s="2" t="n">
-        <v>0.2522408458852818</v>
+        <v>0.2561575676763108</v>
       </c>
       <c r="DO7" s="2" t="n">
-        <v>0.2516725521032304</v>
+        <v>0.2554830584172696</v>
       </c>
       <c r="DP7" s="2" t="n">
-        <v>0.2435232574341541</v>
+        <v>0.246507900416637</v>
       </c>
       <c r="DQ7" s="2" t="n">
-        <v>0.2364771883562189</v>
+        <v>0.2392709809914213</v>
       </c>
       <c r="DR7" s="2" t="n">
-        <v>0.2336442043697608</v>
+        <v>0.2360737083172572</v>
       </c>
       <c r="DS7" s="2" t="n">
-        <v>0.2292355274468292</v>
+        <v>0.2314149228542675</v>
       </c>
       <c r="DT7" s="2" t="n">
-        <v>0.2237690765529851</v>
+        <v>0.2257108692198972</v>
       </c>
       <c r="DU7" s="2" t="n">
-        <v>0.2208026832679597</v>
+        <v>0.2225511668959942</v>
       </c>
       <c r="DV7" s="2" t="n">
-        <v>0.2234092582662714</v>
+        <v>0.2249460858007086</v>
       </c>
       <c r="DW7" s="2" t="n">
-        <v>0.2252497741410038</v>
+        <v>0.2267632999846241</v>
       </c>
       <c r="DX7" s="2" t="n">
-        <v>0.2925784527462091</v>
+        <v>0.2971946462195482</v>
       </c>
       <c r="DY7" s="2" t="n">
-        <v>0.2813251680113447</v>
+        <v>0.2855508542038572</v>
       </c>
       <c r="DZ7" s="2" t="n">
-        <v>0.2792803253633651</v>
+        <v>0.2832417022092018</v>
       </c>
       <c r="EA7" s="2" t="n">
-        <v>0.2694294707101667</v>
+        <v>0.273164588324436</v>
       </c>
       <c r="EB7" s="2" t="n">
-        <v>0.2664579332522964</v>
+        <v>0.2696235731892204</v>
       </c>
       <c r="EC7" s="2" t="n">
-        <v>0.2597191765026228</v>
+        <v>0.2626858263329642</v>
       </c>
       <c r="ED7" s="2" t="n">
-        <v>0.2554177839408773</v>
+        <v>0.2580158051203149</v>
       </c>
       <c r="EE7" s="2" t="n">
-        <v>0.252589086496688</v>
+        <v>0.2549140960513125</v>
       </c>
       <c r="EF7" s="2" t="n">
-        <v>0.2498869481867381</v>
+        <v>0.2521792422419615</v>
       </c>
       <c r="EG7" s="2" t="n">
-        <v>0.2471662021104369</v>
+        <v>0.2492306760374579</v>
       </c>
       <c r="EH7" s="2" t="n">
-        <v>0.2337839643867802</v>
+        <v>0.2354171093018841</v>
       </c>
       <c r="EI7" s="2" t="n">
-        <v>0.2360730764959734</v>
+        <v>0.2373660763297957</v>
       </c>
       <c r="EJ7" s="2" t="n">
-        <v>0.2360494549632841</v>
+        <v>0.2371763925314719</v>
       </c>
       <c r="EK7" s="2" t="n">
-        <v>0.2383303306809681</v>
+        <v>0.2395394220761078</v>
       </c>
       <c r="EL7" s="2" t="n">
-        <v>0.2992533544333127</v>
+        <v>0.3029939705760625</v>
       </c>
       <c r="EM7" s="2" t="n">
-        <v>0.29327516763886</v>
+        <v>0.2963130971737721</v>
       </c>
       <c r="EN7" s="2" t="n">
-        <v>0.2872063597998795</v>
+        <v>0.289891601201075</v>
       </c>
       <c r="EO7" s="2" t="n">
-        <v>0.2787320668739157</v>
+        <v>0.281107274715312</v>
       </c>
       <c r="EP7" s="2" t="n">
-        <v>0.2813507770393738</v>
+        <v>0.2837205385063538</v>
       </c>
       <c r="EQ7" s="2" t="n">
-        <v>0.269178811218392</v>
+        <v>0.271085042264115</v>
       </c>
       <c r="ER7" s="2" t="n">
-        <v>0.2690024414013132</v>
+        <v>0.2709637843917116</v>
       </c>
       <c r="ES7" s="2" t="n">
-        <v>0.2614275454835119</v>
+        <v>0.2628274574236097</v>
       </c>
       <c r="ET7" s="2" t="n">
-        <v>0.2636604283678308</v>
+        <v>0.265154768966414</v>
       </c>
       <c r="EU7" s="2" t="n">
-        <v>0.2622634936545168</v>
+        <v>0.263628961560515</v>
       </c>
       <c r="EV7" s="2" t="n">
-        <v>0.2583545974041321</v>
+        <v>0.2595482549215653</v>
       </c>
       <c r="EW7" s="2" t="n">
-        <v>0.2568327930867612</v>
+        <v>0.2578483556508958</v>
       </c>
       <c r="EX7" s="2" t="n">
-        <v>0.2560885782032988</v>
+        <v>0.2569818320363543</v>
       </c>
       <c r="EY7" s="2" t="n">
-        <v>0.2684958540547551</v>
+        <v>0.2693366744268597</v>
       </c>
       <c r="EZ7" s="2" t="n">
-        <v>0.2958738502168821</v>
+        <v>0.2974626045727895</v>
       </c>
       <c r="FA7" s="2" t="n">
-        <v>0.295913116911775</v>
+        <v>0.2973613160647215</v>
       </c>
       <c r="FB7" s="2" t="n">
-        <v>0.2842592467414711</v>
+        <v>0.2855701763974998</v>
       </c>
       <c r="FC7" s="2" t="n">
-        <v>0.2862444298185651</v>
+        <v>0.2874105201877897</v>
       </c>
       <c r="FD7" s="2" t="n">
-        <v>0.2760513141744066</v>
+        <v>0.2771436065428187</v>
       </c>
       <c r="FE7" s="2" t="n">
-        <v>0.2775983189206578</v>
+        <v>0.2785781075220563</v>
       </c>
       <c r="FF7" s="2" t="n">
-        <v>0.2770320216294763</v>
+        <v>0.2780118474837778</v>
       </c>
       <c r="FG7" s="2" t="n">
-        <v>0.27376581354688</v>
+        <v>0.2747130133087475</v>
       </c>
       <c r="FH7" s="2" t="n">
-        <v>0.26915289013137</v>
+        <v>0.270027141258613</v>
       </c>
       <c r="FI7" s="2" t="n">
-        <v>0.2677966646143673</v>
+        <v>0.2687441027948139</v>
       </c>
       <c r="FJ7" s="2" t="n">
-        <v>0.2699874994199285</v>
+        <v>0.2709195148985395</v>
       </c>
       <c r="FK7" s="2" t="n">
-        <v>0.2709114125008953</v>
+        <v>0.2716159319515599</v>
       </c>
       <c r="FL7" s="2" t="n">
-        <v>0.2804273397074026</v>
+        <v>0.2808702767238898</v>
       </c>
       <c r="FM7" s="2" t="n">
-        <v>0.291081860974189</v>
+        <v>0.29147716642892</v>
       </c>
       <c r="FN7" s="2" t="n">
-        <v>0.2983441534685255</v>
+        <v>0.2992868232773901</v>
       </c>
       <c r="FO7" s="2" t="n">
-        <v>0.2980909753930664</v>
+        <v>0.2990115691316224</v>
       </c>
       <c r="FP7" s="2" t="n">
-        <v>0.2897926453227422</v>
+        <v>0.2906464669579885</v>
       </c>
       <c r="FQ7" s="2" t="n">
-        <v>0.2879174503752359</v>
+        <v>0.2887097972699769</v>
       </c>
       <c r="FR7" s="2" t="n">
-        <v>0.2937070818681426</v>
+        <v>0.2946408407826133</v>
       </c>
       <c r="FS7" s="2" t="n">
-        <v>0.2914462189446454</v>
+        <v>0.2924802850256925</v>
       </c>
       <c r="FT7" s="2" t="n">
-        <v>0.2920818166520253</v>
+        <v>0.2930892767097607</v>
       </c>
       <c r="FU7" s="2" t="n">
-        <v>0.2903504644535611</v>
+        <v>0.291299765279157</v>
       </c>
       <c r="FV7" s="2" t="n">
-        <v>0.2923847797948517</v>
+        <v>0.2933012608129181</v>
       </c>
       <c r="FW7" s="2" t="n">
-        <v>0.2929441131114165</v>
+        <v>0.2939539275526206</v>
       </c>
       <c r="FX7" s="2" t="n">
-        <v>0.2914318574782742</v>
+        <v>0.2922273336168659</v>
       </c>
       <c r="FY7" s="2" t="n">
-        <v>0.301536225372433</v>
+        <v>0.3023260018168681</v>
       </c>
       <c r="FZ7" s="2" t="n">
-        <v>0.3063595963980032</v>
+        <v>0.3069986624981237</v>
       </c>
       <c r="GA7" s="2" t="n">
-        <v>0.3211488384321394</v>
+        <v>0.3219064879730406</v>
       </c>
       <c r="GB7" s="2" t="n">
-        <v>0.3186459655450242</v>
+        <v>0.3202549109743493</v>
       </c>
       <c r="GC7" s="2" t="n">
-        <v>0.3198026228037407</v>
+        <v>0.3215657654490997</v>
       </c>
       <c r="GD7" s="2" t="n">
-        <v>0.3217129872712228</v>
+        <v>0.3234433250102136</v>
       </c>
       <c r="GE7" s="2" t="n">
-        <v>0.3218543093568414</v>
+        <v>0.3236916821366876</v>
       </c>
       <c r="GF7" s="2" t="n">
-        <v>0.3197093547593511</v>
+        <v>0.3215792120705999</v>
       </c>
       <c r="GG7" s="2" t="n">
-        <v>0.3177773214483364</v>
+        <v>0.3194730288887127</v>
       </c>
       <c r="GH7" s="2" t="n">
-        <v>0.3142897039052065</v>
+        <v>0.3160861580964144</v>
       </c>
       <c r="GI7" s="2" t="n">
-        <v>0.3146527677903962</v>
+        <v>0.3161598116288972</v>
       </c>
       <c r="GJ7" s="2" t="n">
-        <v>0.3150467288697937</v>
+        <v>0.3165161472762802</v>
       </c>
       <c r="GK7" s="2" t="n">
-        <v>0.3190709946885943</v>
+        <v>0.3206233231559634</v>
       </c>
       <c r="GL7" s="2" t="n">
-        <v>0.32449745391577</v>
+        <v>0.3258791417357277</v>
       </c>
       <c r="GM7" s="2" t="n">
-        <v>0.3297557699051387</v>
+        <v>0.3308792206016071</v>
       </c>
       <c r="GN7" s="2" t="n">
-        <v>0.3450267754939676</v>
+        <v>0.3459864698794962</v>
       </c>
       <c r="GO7" s="2" t="n">
-        <v>0.3542850713194293</v>
+        <v>0.3552130038798732</v>
       </c>
       <c r="GP7" s="2" t="n">
-        <v>0.347768580586672</v>
+        <v>0.3492684420654776</v>
       </c>
       <c r="GQ7" s="2" t="n">
-        <v>0.3433642010841929</v>
+        <v>0.3446340780411326</v>
       </c>
       <c r="GR7" s="2" t="n">
-        <v>0.3430680845249877</v>
+        <v>0.3447301376928077</v>
       </c>
       <c r="GS7" s="2" t="n">
-        <v>0.3413450293985778</v>
+        <v>0.3426454760877067</v>
       </c>
       <c r="GT7" s="2" t="n">
-        <v>0.3429899525477501</v>
+        <v>0.3445533972813698</v>
       </c>
       <c r="GU7" s="2" t="n">
-        <v>0.3372446380079824</v>
+        <v>0.3387369073451597</v>
       </c>
       <c r="GV7" s="2" t="n">
-        <v>0.3429910288196182</v>
+        <v>0.3444448084574318</v>
       </c>
       <c r="GW7" s="2" t="n">
-        <v>0.337676894506656</v>
+        <v>0.3390850244371522</v>
       </c>
       <c r="GX7" s="2" t="n">
-        <v>0.3392715777584893</v>
+        <v>0.3406684275099617</v>
       </c>
       <c r="GY7" s="2" t="n">
-        <v>0.3400940900502549</v>
+        <v>0.3413695474920617</v>
       </c>
       <c r="GZ7" s="2" t="n">
-        <v>0.3519473726969604</v>
+        <v>0.3528789411407356</v>
       </c>
       <c r="HA7" s="2" t="n">
-        <v>0.3646068806491701</v>
+        <v>0.3656036565743295</v>
       </c>
       <c r="HB7" s="2" t="n">
-        <v>0.3776962099954692</v>
+        <v>0.3788841305658427</v>
       </c>
       <c r="HC7" s="2" t="n">
-        <v>0.3689671638354833</v>
+        <v>0.3695872235045011</v>
       </c>
       <c r="HD7" s="2" t="n">
-        <v>0.3620851683833769</v>
+        <v>0.3632726642706564</v>
       </c>
       <c r="HE7" s="2" t="n">
-        <v>0.3557041403073713</v>
+        <v>0.3565444614905759</v>
       </c>
       <c r="HF7" s="2" t="n">
-        <v>0.3580398120751681</v>
+        <v>0.3587657295933069</v>
       </c>
       <c r="HG7" s="2" t="n">
-        <v>0.3655234078035015</v>
+        <v>0.3665879095062869</v>
       </c>
       <c r="HH7" s="2" t="n">
-        <v>0.3649551761821451</v>
+        <v>0.3661057544425669</v>
       </c>
       <c r="HI7" s="2" t="n">
-        <v>0.3637713813198657</v>
+        <v>0.3650495880259128</v>
       </c>
       <c r="HJ7" s="2" t="n">
-        <v>0.3668802959598411</v>
+        <v>0.3684964461006034</v>
       </c>
       <c r="HK7" s="2" t="n">
-        <v>0.3611005015148543</v>
+        <v>0.3625065974368475</v>
       </c>
       <c r="HL7" s="2" t="n">
-        <v>0.3635912136959961</v>
+        <v>0.3652647035050324</v>
       </c>
       <c r="HM7" s="2" t="n">
-        <v>0.3614147394605796</v>
+        <v>0.3633247405000846</v>
       </c>
       <c r="HN7" s="2" t="n">
-        <v>0.3832277026014801</v>
+        <v>0.3848335560398575</v>
       </c>
       <c r="HO7" s="2" t="n">
-        <v>0.3970232732294033</v>
+        <v>0.3987442157862614</v>
       </c>
       <c r="HP7" s="2" t="n">
-        <v>0.3711673424077619</v>
+        <v>0.3718612298799147</v>
       </c>
       <c r="HQ7" s="2" t="n">
-        <v>0.3559099766680246</v>
+        <v>0.3560643675991541</v>
       </c>
       <c r="HR7" s="3" t="n">
         <v>55519</v>
@@ -5673,7 +5673,7 @@
         <v>0.0707983495227468</v>
       </c>
       <c r="Z8" s="7" t="n">
-        <v>0.06796811521053314</v>
+        <v>0.06606723368167877</v>
       </c>
       <c r="AA8" s="6" t="n">
         <v>0.06325361731976981</v>
@@ -5712,7 +5712,7 @@
         <v>0.102714844045793</v>
       </c>
       <c r="AM8" s="7" t="n">
-        <v>0.09900931268930435</v>
+        <v>0.09674420952796936</v>
       </c>
       <c r="AN8" s="6" t="n">
         <v>0.09259502537764119</v>
@@ -5871,7 +5871,7 @@
         <v>0.204818851764059</v>
       </c>
       <c r="CN8" s="7" t="n">
-        <v>0.2052146941423416</v>
+        <v>0.197417363524437</v>
       </c>
       <c r="CO8" s="6" t="n">
         <v>0.196500406731799</v>
@@ -6129,7 +6129,7 @@
         <v>0.277654055693251</v>
       </c>
       <c r="FV8" s="7" t="n">
-        <v>0.2790730893611908</v>
+        <v>0.2831661403179169</v>
       </c>
       <c r="FW8" s="6" t="n">
         <v>0.279414809816803</v>
@@ -6295,7 +6295,7 @@
         <v>0.0381157332974437</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.03983543068170547</v>
+        <v>0.04116935655474663</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>0.0395341519679435</v>
@@ -6418,7 +6418,7 @@
         <v>0.131315746744894</v>
       </c>
       <c r="AU9" s="7" t="n">
-        <v>0.1340141743421555</v>
+        <v>0.1342417746782303</v>
       </c>
       <c r="AV9" s="6" t="n">
         <v>0.132513088922263</v>
@@ -6499,7 +6499,7 @@
         <v>0.199955283513327</v>
       </c>
       <c r="BV9" s="7" t="n">
-        <v>0.1944539099931717</v>
+        <v>0.198971688747406</v>
       </c>
       <c r="BW9" s="6" t="n">
         <v>0.200606296983058</v>
@@ -6640,7 +6640,7 @@
         <v>0.251323415697041</v>
       </c>
       <c r="DQ9" s="7" t="n">
-        <v>0.243425041437149</v>
+        <v>0.2427415102720261</v>
       </c>
       <c r="DR9" s="6" t="n">
         <v>0.23764445461862</v>
@@ -6694,7 +6694,7 @@
         <v>0.232519744722409</v>
       </c>
       <c r="EI9" s="7" t="n">
-        <v>0.2338796854019165</v>
+        <v>0.2365200370550156</v>
       </c>
       <c r="EJ9" s="6" t="n">
         <v>0.231332738185024</v>
@@ -6853,7 +6853,7 @@
         <v>0.304890545827317</v>
       </c>
       <c r="GJ9" s="7" t="n">
-        <v>0.3060636520385742</v>
+        <v>0.3046151995658875</v>
       </c>
       <c r="GK9" s="6" t="n">
         <v>0.308508043694741</v>
